--- a/upload files/Preferences v6.xlsx
+++ b/upload files/Preferences v6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a8cad284f0e3288/Desktop/GitHub Repo/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E846D7B7-4F52-EA4C-98E1-C56242AA7549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{E846D7B7-4F52-EA4C-98E1-C56242AA7549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9C3D05C-D114-4373-8F81-F9CC74EC0F96}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30120" yWindow="525" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -600,7 +600,7 @@
   <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -610,7 +610,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -623,7 +623,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -636,7 +636,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -648,7 +648,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -657,7 +657,7 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -666,7 +666,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -678,7 +678,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -690,28 +690,28 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="1" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -720,7 +720,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -731,40 +731,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1078,6 +1044,40 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF6F8F9"/>
@@ -1121,18 +1121,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}" name="Table2" displayName="Table2" ref="A1:U79" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}" name="Table2" displayName="Table2" ref="A1:U79" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
   <autoFilter ref="A1:U79" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U79">
     <sortCondition ref="D1:D79"/>
   </sortState>
   <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{BB8E1DF3-CFA5-4F4C-9341-683B2C7FBF55}" name="STAFF NAME" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{DC3F26C1-C7E8-BF46-A039-72B08D99BCA8}" name="ROLE" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{EF43028D-AE4E-434A-B652-8A0CDCEE720A}" name="No Matrix" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{4AEC7AC0-93A2-5043-AADB-962C27827986}" name="Seniority" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{4F928FE3-37CC-8D4A-B5A7-68E54BB080BE}" name="Reduced Rest OK" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{9B205F7E-D438-4E43-BF45-7B6996C87B80}" name="D7B" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{BB8E1DF3-CFA5-4F4C-9341-683B2C7FBF55}" name="STAFF NAME" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{DC3F26C1-C7E8-BF46-A039-72B08D99BCA8}" name="ROLE" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{EF43028D-AE4E-434A-B652-8A0CDCEE720A}" name="No Matrix" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{4AEC7AC0-93A2-5043-AADB-962C27827986}" name="Seniority" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{4F928FE3-37CC-8D4A-B5A7-68E54BB080BE}" name="Reduced Rest OK" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{9B205F7E-D438-4E43-BF45-7B6996C87B80}" name="D7B" dataDxfId="3"/>
     <tableColumn id="7" xr3:uid="{6FBAC0EB-B977-8D43-8FA4-B2A0FBD880DB}" name="GR"/>
     <tableColumn id="8" xr3:uid="{9A17850C-E6C1-B042-A5E8-EC7DE6104419}" name="D11B"/>
     <tableColumn id="9" xr3:uid="{9034B9B8-E76D-5847-BFED-8C23DB865066}" name="FW"/>
@@ -1142,12 +1142,12 @@
     <tableColumn id="13" xr3:uid="{71923762-727D-B14B-87C8-72188F6EA491}" name="PG"/>
     <tableColumn id="14" xr3:uid="{8BC734F3-1D59-AD43-8CE1-CA4E535CE633}" name="D11M"/>
     <tableColumn id="15" xr3:uid="{D9F28E89-F340-4B4B-B432-43AF835746B9}" name="MG"/>
-    <tableColumn id="16" xr3:uid="{A660998B-FE07-BF4A-B784-90FC1426BF26}" name="N7B" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{A660998B-FE07-BF4A-B784-90FC1426BF26}" name="N7B" dataDxfId="2"/>
     <tableColumn id="17" xr3:uid="{C228DA61-8989-7846-A7D5-6A77004F8103}" name="NG"/>
     <tableColumn id="18" xr3:uid="{97C3F635-2908-824A-AA6F-EE11ED8DE3FE}" name="N9L"/>
     <tableColumn id="19" xr3:uid="{E4EE6987-8112-BE4D-B329-53CB0C70AB46}" name="N7P"/>
-    <tableColumn id="20" xr3:uid="{51AFC6C1-38A4-954C-83CA-412B18BD76F0}" name="NP" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{27EDDB97-5263-BC41-AC06-CAA6A57A4DA2}" name="N to D Flex" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{51AFC6C1-38A4-954C-83CA-412B18BD76F0}" name="NP" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{27EDDB97-5263-BC41-AC06-CAA6A57A4DA2}" name="N to D Flex" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Sheet1-style" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1352,33 +1352,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U997"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.6640625" customWidth="1"/>
-    <col min="5" max="5" width="19.6640625" customWidth="1"/>
-    <col min="6" max="6" width="9.1640625" customWidth="1"/>
-    <col min="7" max="7" width="8.1640625" customWidth="1"/>
-    <col min="8" max="8" width="10.1640625" customWidth="1"/>
-    <col min="9" max="9" width="8.33203125" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" customWidth="1"/>
+    <col min="9" max="9" width="8.28515625" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
-    <col min="12" max="12" width="9.1640625" customWidth="1"/>
-    <col min="13" max="13" width="8.1640625" customWidth="1"/>
-    <col min="14" max="14" width="10.1640625" customWidth="1"/>
-    <col min="15" max="15" width="8.5" customWidth="1"/>
-    <col min="16" max="16" width="9.1640625" customWidth="1"/>
-    <col min="17" max="17" width="8.1640625" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" customWidth="1"/>
+    <col min="14" max="14" width="10.140625" customWidth="1"/>
+    <col min="15" max="15" width="8.42578125" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" customWidth="1"/>
+    <col min="17" max="17" width="8.140625" customWidth="1"/>
     <col min="18" max="18" width="9" customWidth="1"/>
-    <col min="19" max="19" width="9.1640625" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" customWidth="1"/>
     <col min="20" max="20" width="8" customWidth="1"/>
-    <col min="21" max="21" width="12.83203125" customWidth="1"/>
-    <col min="22" max="26" width="8.83203125" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" customWidth="1"/>
+    <col min="22" max="26" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
@@ -1443,7 +1443,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>20</v>
       </c>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="U2" s="10"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="36" t="s">
         <v>22</v>
       </c>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="U3" s="15"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="37" t="s">
         <v>23</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="36" t="s">
         <v>24</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="37" t="s">
         <v>26</v>
       </c>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="U6" s="10"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
         <v>27</v>
       </c>
@@ -1827,7 +1827,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="36" t="s">
         <v>28</v>
       </c>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="U8" s="15"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="36" t="s">
         <v>29</v>
       </c>
@@ -1955,7 +1955,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="36" t="s">
         <v>30</v>
       </c>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="U10" s="15"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
         <v>31</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="36" t="s">
         <v>32</v>
       </c>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="U12" s="15"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
         <v>33</v>
       </c>
@@ -2211,7 +2211,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="36" t="s">
         <v>34</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
         <v>35</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
         <v>36</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="37" t="s">
         <v>38</v>
       </c>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="U17" s="10"/>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="37" t="s">
         <v>39</v>
       </c>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="U18" s="10"/>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="37" t="s">
         <v>40</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="37" t="s">
         <v>42</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="37" t="s">
         <v>41</v>
       </c>
@@ -2727,7 +2727,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="36" t="s">
         <v>43</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
         <v>44</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="37" t="s">
         <v>45</v>
       </c>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="U24" s="10"/>
     </row>
-    <row r="25" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="36" t="s">
         <v>46</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="36" t="s">
         <v>47</v>
       </c>
@@ -3050,7 +3050,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="39" t="s">
         <v>48</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
         <v>49</v>
       </c>
@@ -3180,7 +3180,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="36" t="s">
         <v>50</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="36" t="s">
         <v>51</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="37" t="s">
         <v>52</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="37" t="s">
         <v>54</v>
       </c>
@@ -3440,7 +3440,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="37" t="s">
         <v>53</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
         <v>56</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="37" t="s">
         <v>55</v>
       </c>
@@ -3635,7 +3635,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="37" t="s">
         <v>57</v>
       </c>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="U36" s="10"/>
     </row>
-    <row r="37" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="37" t="s">
         <v>61</v>
       </c>
@@ -3763,7 +3763,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="38" t="s">
         <v>59</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="37" t="s">
         <v>60</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="36" t="s">
         <v>58</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="36" t="s">
         <v>74</v>
       </c>
@@ -4021,7 +4021,7 @@
       </c>
       <c r="U41" s="15"/>
     </row>
-    <row r="42" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="37" t="s">
         <v>63</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="36" t="s">
         <v>64</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="36" t="s">
         <v>62</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="36" t="s">
         <v>65</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="36" t="s">
         <v>66</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="36" t="s">
         <v>67</v>
       </c>
@@ -4411,7 +4411,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="36" t="s">
         <v>68</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="36" t="s">
         <v>70</v>
       </c>
@@ -4541,7 +4541,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="37" t="s">
         <v>71</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="37" t="s">
         <v>69</v>
       </c>
@@ -4671,7 +4671,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="37" t="s">
         <v>73</v>
       </c>
@@ -4736,7 +4736,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="37" t="s">
         <v>72</v>
       </c>
@@ -4801,7 +4801,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="36" t="s">
         <v>75</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="36" t="s">
         <v>76</v>
       </c>
@@ -4931,7 +4931,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="37" t="s">
         <v>103</v>
       </c>
@@ -4996,7 +4996,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="36" t="s">
         <v>78</v>
       </c>
@@ -5061,7 +5061,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="58" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="36" t="s">
         <v>77</v>
       </c>
@@ -5126,7 +5126,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="36" t="s">
         <v>79</v>
       </c>
@@ -5134,7 +5134,7 @@
         <v>21</v>
       </c>
       <c r="C59" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" s="12">
         <v>61</v>
@@ -5191,7 +5191,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="37" t="s">
         <v>80</v>
       </c>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="U60" s="10"/>
     </row>
-    <row r="61" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="36" t="s">
         <v>83</v>
       </c>
@@ -5319,7 +5319,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="37" t="s">
         <v>81</v>
       </c>
@@ -5384,7 +5384,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="37" t="s">
         <v>84</v>
       </c>
@@ -5449,7 +5449,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="64" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="37" t="s">
         <v>82</v>
       </c>
@@ -5514,7 +5514,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="37" t="s">
         <v>85</v>
       </c>
@@ -5579,7 +5579,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="36" t="s">
         <v>86</v>
       </c>
@@ -5644,7 +5644,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="36" t="s">
         <v>87</v>
       </c>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="U67" s="15"/>
     </row>
-    <row r="68" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="36" t="s">
         <v>89</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="69" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="37" t="s">
         <v>88</v>
       </c>
@@ -5837,7 +5837,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="37" t="s">
         <v>90</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="37" t="s">
         <v>91</v>
       </c>
@@ -5967,7 +5967,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="36" t="s">
         <v>92</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="37" t="s">
         <v>94</v>
       </c>
@@ -6097,7 +6097,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="36" t="s">
         <v>93</v>
       </c>
@@ -6162,7 +6162,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="36" t="s">
         <v>95</v>
       </c>
@@ -6227,7 +6227,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="37" t="s">
         <v>97</v>
       </c>
@@ -6292,7 +6292,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="37" t="s">
         <v>96</v>
       </c>
@@ -6357,7 +6357,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="37" t="s">
         <v>104</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="79" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="40" t="s">
         <v>98</v>
       </c>
@@ -6487,2758 +6487,2758 @@
         <v>100</v>
       </c>
     </row>
-    <row r="80" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D80" s="1"/>
     </row>
-    <row r="81" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="1"/>
     </row>
-    <row r="82" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D82" s="1"/>
     </row>
-    <row r="83" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D83" s="1"/>
     </row>
-    <row r="84" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D84" s="1"/>
     </row>
-    <row r="85" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D85" s="1"/>
     </row>
-    <row r="86" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D86" s="1"/>
     </row>
-    <row r="87" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D87" s="1"/>
     </row>
-    <row r="88" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D88" s="1"/>
     </row>
-    <row r="89" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D89" s="1"/>
     </row>
-    <row r="90" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D90" s="1"/>
     </row>
-    <row r="91" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D91" s="1"/>
     </row>
-    <row r="92" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D92" s="1"/>
     </row>
-    <row r="93" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D93" s="1"/>
     </row>
-    <row r="94" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D94" s="1"/>
     </row>
-    <row r="95" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D95" s="1"/>
     </row>
-    <row r="96" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D96" s="1"/>
     </row>
-    <row r="97" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D97" s="1"/>
     </row>
-    <row r="98" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D98" s="1"/>
     </row>
-    <row r="99" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D99" s="1"/>
     </row>
-    <row r="100" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D100" s="1"/>
     </row>
-    <row r="101" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D101" s="1"/>
     </row>
-    <row r="102" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D102" s="1"/>
     </row>
-    <row r="103" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D103" s="1"/>
     </row>
-    <row r="104" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D104" s="1"/>
     </row>
-    <row r="105" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D105" s="1"/>
     </row>
-    <row r="106" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D106" s="1"/>
     </row>
-    <row r="107" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D107" s="1"/>
     </row>
-    <row r="108" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D108" s="1"/>
     </row>
-    <row r="109" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D109" s="1"/>
     </row>
-    <row r="110" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D110" s="1"/>
     </row>
-    <row r="111" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D111" s="1"/>
     </row>
-    <row r="112" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D112" s="1"/>
     </row>
-    <row r="113" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D113" s="1"/>
     </row>
-    <row r="114" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D114" s="1"/>
     </row>
-    <row r="115" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D115" s="1"/>
     </row>
-    <row r="116" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D116" s="1"/>
     </row>
-    <row r="117" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D117" s="1"/>
     </row>
-    <row r="118" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D118" s="1"/>
     </row>
-    <row r="119" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D119" s="1"/>
     </row>
-    <row r="120" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D120" s="1"/>
     </row>
-    <row r="121" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D121" s="1"/>
     </row>
-    <row r="122" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D122" s="1"/>
     </row>
-    <row r="123" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D123" s="1"/>
     </row>
-    <row r="124" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D124" s="1"/>
     </row>
-    <row r="125" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D125" s="1"/>
     </row>
-    <row r="126" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D126" s="1"/>
     </row>
-    <row r="127" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D127" s="1"/>
     </row>
-    <row r="128" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D128" s="1"/>
     </row>
-    <row r="129" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D129" s="1"/>
     </row>
-    <row r="130" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D130" s="1"/>
     </row>
-    <row r="131" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D131" s="1"/>
     </row>
-    <row r="132" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D132" s="1"/>
     </row>
-    <row r="133" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D133" s="1"/>
     </row>
-    <row r="134" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D134" s="1"/>
     </row>
-    <row r="135" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D135" s="1"/>
     </row>
-    <row r="136" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D136" s="1"/>
     </row>
-    <row r="137" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D137" s="1"/>
     </row>
-    <row r="138" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D138" s="1"/>
     </row>
-    <row r="139" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D139" s="1"/>
     </row>
-    <row r="140" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D140" s="1"/>
     </row>
-    <row r="141" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D141" s="1"/>
     </row>
-    <row r="142" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D142" s="1"/>
     </row>
-    <row r="143" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D143" s="1"/>
     </row>
-    <row r="144" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D144" s="1"/>
     </row>
-    <row r="145" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D145" s="1"/>
     </row>
-    <row r="146" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D146" s="1"/>
     </row>
-    <row r="147" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D147" s="1"/>
     </row>
-    <row r="148" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D148" s="1"/>
     </row>
-    <row r="149" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D149" s="1"/>
     </row>
-    <row r="150" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D150" s="1"/>
     </row>
-    <row r="151" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D151" s="1"/>
     </row>
-    <row r="152" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D152" s="1"/>
     </row>
-    <row r="153" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D153" s="1"/>
     </row>
-    <row r="154" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D154" s="1"/>
     </row>
-    <row r="155" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D155" s="1"/>
     </row>
-    <row r="156" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D156" s="1"/>
     </row>
-    <row r="157" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D157" s="1"/>
     </row>
-    <row r="158" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D158" s="1"/>
     </row>
-    <row r="159" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D159" s="1"/>
     </row>
-    <row r="160" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D160" s="1"/>
     </row>
-    <row r="161" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="1"/>
     </row>
-    <row r="162" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="1"/>
     </row>
-    <row r="163" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="1"/>
     </row>
-    <row r="164" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="1"/>
     </row>
-    <row r="165" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D165" s="1"/>
     </row>
-    <row r="166" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D166" s="1"/>
     </row>
-    <row r="167" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="1"/>
     </row>
-    <row r="168" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="1"/>
     </row>
-    <row r="169" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="1"/>
     </row>
-    <row r="170" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1"/>
     </row>
-    <row r="171" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D171" s="1"/>
     </row>
-    <row r="172" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D172" s="1"/>
     </row>
-    <row r="173" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="1"/>
     </row>
-    <row r="174" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="1"/>
     </row>
-    <row r="175" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1"/>
     </row>
-    <row r="176" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D176" s="1"/>
     </row>
-    <row r="177" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D177" s="1"/>
     </row>
-    <row r="178" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="1"/>
     </row>
-    <row r="179" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="1"/>
     </row>
-    <row r="180" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="1"/>
     </row>
-    <row r="181" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="1"/>
     </row>
-    <row r="182" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="1"/>
     </row>
-    <row r="183" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="1"/>
     </row>
-    <row r="184" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="1"/>
     </row>
-    <row r="185" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="1"/>
     </row>
-    <row r="186" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="1"/>
     </row>
-    <row r="187" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="1"/>
     </row>
-    <row r="188" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="1"/>
     </row>
-    <row r="189" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="1"/>
     </row>
-    <row r="190" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="1"/>
     </row>
-    <row r="191" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="1"/>
     </row>
-    <row r="192" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="1"/>
     </row>
-    <row r="193" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="1"/>
     </row>
-    <row r="194" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="1"/>
     </row>
-    <row r="195" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="1"/>
     </row>
-    <row r="196" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="1"/>
     </row>
-    <row r="197" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D197" s="1"/>
     </row>
-    <row r="198" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D198" s="1"/>
     </row>
-    <row r="199" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D199" s="1"/>
     </row>
-    <row r="200" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D200" s="1"/>
     </row>
-    <row r="201" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D201" s="1"/>
     </row>
-    <row r="202" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D202" s="1"/>
     </row>
-    <row r="203" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D203" s="1"/>
     </row>
-    <row r="204" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D204" s="1"/>
     </row>
-    <row r="205" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D205" s="1"/>
     </row>
-    <row r="206" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D206" s="1"/>
     </row>
-    <row r="207" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D207" s="1"/>
     </row>
-    <row r="208" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D208" s="1"/>
     </row>
-    <row r="209" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D209" s="1"/>
     </row>
-    <row r="210" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D210" s="1"/>
     </row>
-    <row r="211" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D211" s="1"/>
     </row>
-    <row r="212" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D212" s="1"/>
     </row>
-    <row r="213" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D213" s="1"/>
     </row>
-    <row r="214" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D214" s="1"/>
     </row>
-    <row r="215" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D215" s="1"/>
     </row>
-    <row r="216" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D216" s="1"/>
     </row>
-    <row r="217" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D217" s="1"/>
     </row>
-    <row r="218" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D218" s="1"/>
     </row>
-    <row r="219" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D219" s="1"/>
     </row>
-    <row r="220" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D220" s="1"/>
     </row>
-    <row r="221" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D221" s="1"/>
     </row>
-    <row r="222" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D222" s="1"/>
     </row>
-    <row r="223" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D223" s="1"/>
     </row>
-    <row r="224" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D224" s="1"/>
     </row>
-    <row r="225" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D225" s="1"/>
     </row>
-    <row r="226" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D226" s="1"/>
     </row>
-    <row r="227" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D227" s="1"/>
     </row>
-    <row r="228" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D228" s="1"/>
     </row>
-    <row r="229" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D229" s="1"/>
     </row>
-    <row r="230" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D230" s="1"/>
     </row>
-    <row r="231" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D231" s="1"/>
     </row>
-    <row r="232" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D232" s="1"/>
     </row>
-    <row r="233" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D233" s="1"/>
     </row>
-    <row r="234" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D234" s="1"/>
     </row>
-    <row r="235" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D235" s="1"/>
     </row>
-    <row r="236" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D236" s="1"/>
     </row>
-    <row r="237" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D237" s="1"/>
     </row>
-    <row r="238" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D238" s="1"/>
     </row>
-    <row r="239" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D239" s="1"/>
     </row>
-    <row r="240" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D240" s="1"/>
     </row>
-    <row r="241" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D241" s="1"/>
     </row>
-    <row r="242" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D242" s="1"/>
     </row>
-    <row r="243" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D243" s="1"/>
     </row>
-    <row r="244" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D244" s="1"/>
     </row>
-    <row r="245" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D245" s="1"/>
     </row>
-    <row r="246" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D246" s="1"/>
     </row>
-    <row r="247" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D247" s="1"/>
     </row>
-    <row r="248" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D248" s="1"/>
     </row>
-    <row r="249" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D249" s="1"/>
     </row>
-    <row r="250" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D250" s="1"/>
     </row>
-    <row r="251" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D251" s="1"/>
     </row>
-    <row r="252" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D252" s="1"/>
     </row>
-    <row r="253" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D253" s="1"/>
     </row>
-    <row r="254" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D254" s="1"/>
     </row>
-    <row r="255" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D255" s="1"/>
     </row>
-    <row r="256" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D256" s="1"/>
     </row>
-    <row r="257" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D257" s="1"/>
     </row>
-    <row r="258" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D258" s="1"/>
     </row>
-    <row r="259" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D259" s="1"/>
     </row>
-    <row r="260" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D260" s="1"/>
     </row>
-    <row r="261" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D261" s="1"/>
     </row>
-    <row r="262" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D262" s="1"/>
     </row>
-    <row r="263" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D263" s="1"/>
     </row>
-    <row r="264" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D264" s="1"/>
     </row>
-    <row r="265" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D265" s="1"/>
     </row>
-    <row r="266" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D266" s="1"/>
     </row>
-    <row r="267" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D267" s="1"/>
     </row>
-    <row r="268" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D268" s="1"/>
     </row>
-    <row r="269" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D269" s="1"/>
     </row>
-    <row r="270" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D270" s="1"/>
     </row>
-    <row r="271" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D271" s="1"/>
     </row>
-    <row r="272" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D272" s="1"/>
     </row>
-    <row r="273" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D273" s="1"/>
     </row>
-    <row r="274" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D274" s="1"/>
     </row>
-    <row r="275" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D275" s="1"/>
     </row>
-    <row r="276" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D276" s="1"/>
     </row>
-    <row r="277" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D277" s="1"/>
     </row>
-    <row r="278" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D278" s="1"/>
     </row>
-    <row r="279" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D279" s="1"/>
     </row>
-    <row r="280" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D280" s="1"/>
     </row>
-    <row r="281" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D281" s="1"/>
     </row>
-    <row r="282" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D282" s="1"/>
     </row>
-    <row r="283" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D283" s="1"/>
     </row>
-    <row r="284" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D284" s="1"/>
     </row>
-    <row r="285" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D285" s="1"/>
     </row>
-    <row r="286" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D286" s="1"/>
     </row>
-    <row r="287" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D287" s="1"/>
     </row>
-    <row r="288" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D288" s="1"/>
     </row>
-    <row r="289" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D289" s="1"/>
     </row>
-    <row r="290" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D290" s="1"/>
     </row>
-    <row r="291" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D291" s="1"/>
     </row>
-    <row r="292" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D292" s="1"/>
     </row>
-    <row r="293" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D293" s="1"/>
     </row>
-    <row r="294" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D294" s="1"/>
     </row>
-    <row r="295" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D295" s="1"/>
     </row>
-    <row r="296" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D296" s="1"/>
     </row>
-    <row r="297" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D297" s="1"/>
     </row>
-    <row r="298" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D298" s="1"/>
     </row>
-    <row r="299" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D299" s="1"/>
     </row>
-    <row r="300" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D300" s="1"/>
     </row>
-    <row r="301" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D301" s="1"/>
     </row>
-    <row r="302" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D302" s="1"/>
     </row>
-    <row r="303" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D303" s="1"/>
     </row>
-    <row r="304" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D304" s="1"/>
     </row>
-    <row r="305" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D305" s="1"/>
     </row>
-    <row r="306" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D306" s="1"/>
     </row>
-    <row r="307" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D307" s="1"/>
     </row>
-    <row r="308" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D308" s="1"/>
     </row>
-    <row r="309" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D309" s="1"/>
     </row>
-    <row r="310" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D310" s="1"/>
     </row>
-    <row r="311" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D311" s="1"/>
     </row>
-    <row r="312" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D312" s="1"/>
     </row>
-    <row r="313" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D313" s="1"/>
     </row>
-    <row r="314" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D314" s="1"/>
     </row>
-    <row r="315" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D315" s="1"/>
     </row>
-    <row r="316" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D316" s="1"/>
     </row>
-    <row r="317" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D317" s="1"/>
     </row>
-    <row r="318" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D318" s="1"/>
     </row>
-    <row r="319" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D319" s="1"/>
     </row>
-    <row r="320" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D320" s="1"/>
     </row>
-    <row r="321" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D321" s="1"/>
     </row>
-    <row r="322" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D322" s="1"/>
     </row>
-    <row r="323" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D323" s="1"/>
     </row>
-    <row r="324" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D324" s="1"/>
     </row>
-    <row r="325" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D325" s="1"/>
     </row>
-    <row r="326" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D326" s="1"/>
     </row>
-    <row r="327" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D327" s="1"/>
     </row>
-    <row r="328" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D328" s="1"/>
     </row>
-    <row r="329" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D329" s="1"/>
     </row>
-    <row r="330" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D330" s="1"/>
     </row>
-    <row r="331" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D331" s="1"/>
     </row>
-    <row r="332" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D332" s="1"/>
     </row>
-    <row r="333" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D333" s="1"/>
     </row>
-    <row r="334" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D334" s="1"/>
     </row>
-    <row r="335" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D335" s="1"/>
     </row>
-    <row r="336" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D336" s="1"/>
     </row>
-    <row r="337" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D337" s="1"/>
     </row>
-    <row r="338" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D338" s="1"/>
     </row>
-    <row r="339" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D339" s="1"/>
     </row>
-    <row r="340" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D340" s="1"/>
     </row>
-    <row r="341" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D341" s="1"/>
     </row>
-    <row r="342" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D342" s="1"/>
     </row>
-    <row r="343" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D343" s="1"/>
     </row>
-    <row r="344" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D344" s="1"/>
     </row>
-    <row r="345" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D345" s="1"/>
     </row>
-    <row r="346" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D346" s="1"/>
     </row>
-    <row r="347" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D347" s="1"/>
     </row>
-    <row r="348" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D348" s="1"/>
     </row>
-    <row r="349" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D349" s="1"/>
     </row>
-    <row r="350" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D350" s="1"/>
     </row>
-    <row r="351" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D351" s="1"/>
     </row>
-    <row r="352" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D352" s="1"/>
     </row>
-    <row r="353" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D353" s="1"/>
     </row>
-    <row r="354" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D354" s="1"/>
     </row>
-    <row r="355" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D355" s="1"/>
     </row>
-    <row r="356" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D356" s="1"/>
     </row>
-    <row r="357" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D357" s="1"/>
     </row>
-    <row r="358" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D358" s="1"/>
     </row>
-    <row r="359" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D359" s="1"/>
     </row>
-    <row r="360" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D360" s="1"/>
     </row>
-    <row r="361" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D361" s="1"/>
     </row>
-    <row r="362" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D362" s="1"/>
     </row>
-    <row r="363" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D363" s="1"/>
     </row>
-    <row r="364" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D364" s="1"/>
     </row>
-    <row r="365" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D365" s="1"/>
     </row>
-    <row r="366" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D366" s="1"/>
     </row>
-    <row r="367" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D367" s="1"/>
     </row>
-    <row r="368" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D368" s="1"/>
     </row>
-    <row r="369" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D369" s="1"/>
     </row>
-    <row r="370" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D370" s="1"/>
     </row>
-    <row r="371" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D371" s="1"/>
     </row>
-    <row r="372" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D372" s="1"/>
     </row>
-    <row r="373" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D373" s="1"/>
     </row>
-    <row r="374" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="374" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D374" s="1"/>
     </row>
-    <row r="375" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D375" s="1"/>
     </row>
-    <row r="376" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="376" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D376" s="1"/>
     </row>
-    <row r="377" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D377" s="1"/>
     </row>
-    <row r="378" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D378" s="1"/>
     </row>
-    <row r="379" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D379" s="1"/>
     </row>
-    <row r="380" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D380" s="1"/>
     </row>
-    <row r="381" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="381" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D381" s="1"/>
     </row>
-    <row r="382" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D382" s="1"/>
     </row>
-    <row r="383" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="383" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D383" s="1"/>
     </row>
-    <row r="384" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D384" s="1"/>
     </row>
-    <row r="385" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D385" s="1"/>
     </row>
-    <row r="386" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D386" s="1"/>
     </row>
-    <row r="387" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D387" s="1"/>
     </row>
-    <row r="388" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D388" s="1"/>
     </row>
-    <row r="389" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D389" s="1"/>
     </row>
-    <row r="390" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D390" s="1"/>
     </row>
-    <row r="391" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D391" s="1"/>
     </row>
-    <row r="392" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D392" s="1"/>
     </row>
-    <row r="393" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D393" s="1"/>
     </row>
-    <row r="394" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D394" s="1"/>
     </row>
-    <row r="395" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D395" s="1"/>
     </row>
-    <row r="396" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D396" s="1"/>
     </row>
-    <row r="397" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D397" s="1"/>
     </row>
-    <row r="398" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D398" s="1"/>
     </row>
-    <row r="399" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D399" s="1"/>
     </row>
-    <row r="400" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D400" s="1"/>
     </row>
-    <row r="401" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D401" s="1"/>
     </row>
-    <row r="402" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D402" s="1"/>
     </row>
-    <row r="403" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D403" s="1"/>
     </row>
-    <row r="404" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D404" s="1"/>
     </row>
-    <row r="405" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D405" s="1"/>
     </row>
-    <row r="406" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D406" s="1"/>
     </row>
-    <row r="407" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D407" s="1"/>
     </row>
-    <row r="408" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D408" s="1"/>
     </row>
-    <row r="409" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D409" s="1"/>
     </row>
-    <row r="410" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D410" s="1"/>
     </row>
-    <row r="411" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D411" s="1"/>
     </row>
-    <row r="412" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D412" s="1"/>
     </row>
-    <row r="413" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D413" s="1"/>
     </row>
-    <row r="414" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D414" s="1"/>
     </row>
-    <row r="415" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D415" s="1"/>
     </row>
-    <row r="416" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D416" s="1"/>
     </row>
-    <row r="417" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D417" s="1"/>
     </row>
-    <row r="418" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D418" s="1"/>
     </row>
-    <row r="419" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D419" s="1"/>
     </row>
-    <row r="420" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D420" s="1"/>
     </row>
-    <row r="421" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D421" s="1"/>
     </row>
-    <row r="422" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D422" s="1"/>
     </row>
-    <row r="423" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D423" s="1"/>
     </row>
-    <row r="424" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D424" s="1"/>
     </row>
-    <row r="425" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D425" s="1"/>
     </row>
-    <row r="426" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D426" s="1"/>
     </row>
-    <row r="427" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D427" s="1"/>
     </row>
-    <row r="428" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D428" s="1"/>
     </row>
-    <row r="429" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D429" s="1"/>
     </row>
-    <row r="430" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D430" s="1"/>
     </row>
-    <row r="431" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D431" s="1"/>
     </row>
-    <row r="432" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D432" s="1"/>
     </row>
-    <row r="433" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D433" s="1"/>
     </row>
-    <row r="434" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D434" s="1"/>
     </row>
-    <row r="435" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D435" s="1"/>
     </row>
-    <row r="436" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D436" s="1"/>
     </row>
-    <row r="437" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D437" s="1"/>
     </row>
-    <row r="438" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D438" s="1"/>
     </row>
-    <row r="439" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D439" s="1"/>
     </row>
-    <row r="440" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D440" s="1"/>
     </row>
-    <row r="441" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D441" s="1"/>
     </row>
-    <row r="442" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D442" s="1"/>
     </row>
-    <row r="443" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D443" s="1"/>
     </row>
-    <row r="444" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D444" s="1"/>
     </row>
-    <row r="445" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D445" s="1"/>
     </row>
-    <row r="446" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D446" s="1"/>
     </row>
-    <row r="447" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D447" s="1"/>
     </row>
-    <row r="448" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D448" s="1"/>
     </row>
-    <row r="449" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D449" s="1"/>
     </row>
-    <row r="450" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="450" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D450" s="1"/>
     </row>
-    <row r="451" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D451" s="1"/>
     </row>
-    <row r="452" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D452" s="1"/>
     </row>
-    <row r="453" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D453" s="1"/>
     </row>
-    <row r="454" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D454" s="1"/>
     </row>
-    <row r="455" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D455" s="1"/>
     </row>
-    <row r="456" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D456" s="1"/>
     </row>
-    <row r="457" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D457" s="1"/>
     </row>
-    <row r="458" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D458" s="1"/>
     </row>
-    <row r="459" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D459" s="1"/>
     </row>
-    <row r="460" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D460" s="1"/>
     </row>
-    <row r="461" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D461" s="1"/>
     </row>
-    <row r="462" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D462" s="1"/>
     </row>
-    <row r="463" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D463" s="1"/>
     </row>
-    <row r="464" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D464" s="1"/>
     </row>
-    <row r="465" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D465" s="1"/>
     </row>
-    <row r="466" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D466" s="1"/>
     </row>
-    <row r="467" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D467" s="1"/>
     </row>
-    <row r="468" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D468" s="1"/>
     </row>
-    <row r="469" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D469" s="1"/>
     </row>
-    <row r="470" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D470" s="1"/>
     </row>
-    <row r="471" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D471" s="1"/>
     </row>
-    <row r="472" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D472" s="1"/>
     </row>
-    <row r="473" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D473" s="1"/>
     </row>
-    <row r="474" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D474" s="1"/>
     </row>
-    <row r="475" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D475" s="1"/>
     </row>
-    <row r="476" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D476" s="1"/>
     </row>
-    <row r="477" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D477" s="1"/>
     </row>
-    <row r="478" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D478" s="1"/>
     </row>
-    <row r="479" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D479" s="1"/>
     </row>
-    <row r="480" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D480" s="1"/>
     </row>
-    <row r="481" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D481" s="1"/>
     </row>
-    <row r="482" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D482" s="1"/>
     </row>
-    <row r="483" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D483" s="1"/>
     </row>
-    <row r="484" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D484" s="1"/>
     </row>
-    <row r="485" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D485" s="1"/>
     </row>
-    <row r="486" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D486" s="1"/>
     </row>
-    <row r="487" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D487" s="1"/>
     </row>
-    <row r="488" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D488" s="1"/>
     </row>
-    <row r="489" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D489" s="1"/>
     </row>
-    <row r="490" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D490" s="1"/>
     </row>
-    <row r="491" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D491" s="1"/>
     </row>
-    <row r="492" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D492" s="1"/>
     </row>
-    <row r="493" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D493" s="1"/>
     </row>
-    <row r="494" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D494" s="1"/>
     </row>
-    <row r="495" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D495" s="1"/>
     </row>
-    <row r="496" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D496" s="1"/>
     </row>
-    <row r="497" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D497" s="1"/>
     </row>
-    <row r="498" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D498" s="1"/>
     </row>
-    <row r="499" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D499" s="1"/>
     </row>
-    <row r="500" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D500" s="1"/>
     </row>
-    <row r="501" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D501" s="1"/>
     </row>
-    <row r="502" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D502" s="1"/>
     </row>
-    <row r="503" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D503" s="1"/>
     </row>
-    <row r="504" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D504" s="1"/>
     </row>
-    <row r="505" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D505" s="1"/>
     </row>
-    <row r="506" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D506" s="1"/>
     </row>
-    <row r="507" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D507" s="1"/>
     </row>
-    <row r="508" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D508" s="1"/>
     </row>
-    <row r="509" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D509" s="1"/>
     </row>
-    <row r="510" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D510" s="1"/>
     </row>
-    <row r="511" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D511" s="1"/>
     </row>
-    <row r="512" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="512" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D512" s="1"/>
     </row>
-    <row r="513" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D513" s="1"/>
     </row>
-    <row r="514" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="514" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D514" s="1"/>
     </row>
-    <row r="515" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D515" s="1"/>
     </row>
-    <row r="516" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D516" s="1"/>
     </row>
-    <row r="517" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D517" s="1"/>
     </row>
-    <row r="518" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D518" s="1"/>
     </row>
-    <row r="519" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D519" s="1"/>
     </row>
-    <row r="520" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D520" s="1"/>
     </row>
-    <row r="521" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D521" s="1"/>
     </row>
-    <row r="522" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D522" s="1"/>
     </row>
-    <row r="523" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D523" s="1"/>
     </row>
-    <row r="524" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D524" s="1"/>
     </row>
-    <row r="525" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D525" s="1"/>
     </row>
-    <row r="526" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D526" s="1"/>
     </row>
-    <row r="527" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D527" s="1"/>
     </row>
-    <row r="528" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D528" s="1"/>
     </row>
-    <row r="529" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D529" s="1"/>
     </row>
-    <row r="530" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D530" s="1"/>
     </row>
-    <row r="531" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D531" s="1"/>
     </row>
-    <row r="532" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D532" s="1"/>
     </row>
-    <row r="533" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D533" s="1"/>
     </row>
-    <row r="534" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D534" s="1"/>
     </row>
-    <row r="535" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D535" s="1"/>
     </row>
-    <row r="536" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D536" s="1"/>
     </row>
-    <row r="537" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="537" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D537" s="1"/>
     </row>
-    <row r="538" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D538" s="1"/>
     </row>
-    <row r="539" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="539" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D539" s="1"/>
     </row>
-    <row r="540" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D540" s="1"/>
     </row>
-    <row r="541" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D541" s="1"/>
     </row>
-    <row r="542" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D542" s="1"/>
     </row>
-    <row r="543" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D543" s="1"/>
     </row>
-    <row r="544" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D544" s="1"/>
     </row>
-    <row r="545" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D545" s="1"/>
     </row>
-    <row r="546" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D546" s="1"/>
     </row>
-    <row r="547" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D547" s="1"/>
     </row>
-    <row r="548" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D548" s="1"/>
     </row>
-    <row r="549" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D549" s="1"/>
     </row>
-    <row r="550" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D550" s="1"/>
     </row>
-    <row r="551" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D551" s="1"/>
     </row>
-    <row r="552" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D552" s="1"/>
     </row>
-    <row r="553" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D553" s="1"/>
     </row>
-    <row r="554" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D554" s="1"/>
     </row>
-    <row r="555" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D555" s="1"/>
     </row>
-    <row r="556" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="556" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D556" s="1"/>
     </row>
-    <row r="557" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D557" s="1"/>
     </row>
-    <row r="558" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D558" s="1"/>
     </row>
-    <row r="559" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="559" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D559" s="1"/>
     </row>
-    <row r="560" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="560" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D560" s="1"/>
     </row>
-    <row r="561" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D561" s="1"/>
     </row>
-    <row r="562" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D562" s="1"/>
     </row>
-    <row r="563" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D563" s="1"/>
     </row>
-    <row r="564" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="564" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D564" s="1"/>
     </row>
-    <row r="565" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D565" s="1"/>
     </row>
-    <row r="566" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="566" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D566" s="1"/>
     </row>
-    <row r="567" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D567" s="1"/>
     </row>
-    <row r="568" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D568" s="1"/>
     </row>
-    <row r="569" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D569" s="1"/>
     </row>
-    <row r="570" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D570" s="1"/>
     </row>
-    <row r="571" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="571" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D571" s="1"/>
     </row>
-    <row r="572" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D572" s="1"/>
     </row>
-    <row r="573" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D573" s="1"/>
     </row>
-    <row r="574" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D574" s="1"/>
     </row>
-    <row r="575" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D575" s="1"/>
     </row>
-    <row r="576" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="576" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D576" s="1"/>
     </row>
-    <row r="577" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D577" s="1"/>
     </row>
-    <row r="578" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D578" s="1"/>
     </row>
-    <row r="579" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="579" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D579" s="1"/>
     </row>
-    <row r="580" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="580" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D580" s="1"/>
     </row>
-    <row r="581" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="581" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D581" s="1"/>
     </row>
-    <row r="582" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="582" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D582" s="1"/>
     </row>
-    <row r="583" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D583" s="1"/>
     </row>
-    <row r="584" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D584" s="1"/>
     </row>
-    <row r="585" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D585" s="1"/>
     </row>
-    <row r="586" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D586" s="1"/>
     </row>
-    <row r="587" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D587" s="1"/>
     </row>
-    <row r="588" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D588" s="1"/>
     </row>
-    <row r="589" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D589" s="1"/>
     </row>
-    <row r="590" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D590" s="1"/>
     </row>
-    <row r="591" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="591" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D591" s="1"/>
     </row>
-    <row r="592" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D592" s="1"/>
     </row>
-    <row r="593" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="593" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D593" s="1"/>
     </row>
-    <row r="594" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D594" s="1"/>
     </row>
-    <row r="595" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D595" s="1"/>
     </row>
-    <row r="596" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D596" s="1"/>
     </row>
-    <row r="597" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D597" s="1"/>
     </row>
-    <row r="598" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D598" s="1"/>
     </row>
-    <row r="599" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D599" s="1"/>
     </row>
-    <row r="600" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D600" s="1"/>
     </row>
-    <row r="601" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D601" s="1"/>
     </row>
-    <row r="602" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D602" s="1"/>
     </row>
-    <row r="603" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="603" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D603" s="1"/>
     </row>
-    <row r="604" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D604" s="1"/>
     </row>
-    <row r="605" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="605" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D605" s="1"/>
     </row>
-    <row r="606" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D606" s="1"/>
     </row>
-    <row r="607" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D607" s="1"/>
     </row>
-    <row r="608" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D608" s="1"/>
     </row>
-    <row r="609" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D609" s="1"/>
     </row>
-    <row r="610" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D610" s="1"/>
     </row>
-    <row r="611" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D611" s="1"/>
     </row>
-    <row r="612" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D612" s="1"/>
     </row>
-    <row r="613" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D613" s="1"/>
     </row>
-    <row r="614" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D614" s="1"/>
     </row>
-    <row r="615" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D615" s="1"/>
     </row>
-    <row r="616" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D616" s="1"/>
     </row>
-    <row r="617" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D617" s="1"/>
     </row>
-    <row r="618" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D618" s="1"/>
     </row>
-    <row r="619" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D619" s="1"/>
     </row>
-    <row r="620" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D620" s="1"/>
     </row>
-    <row r="621" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D621" s="1"/>
     </row>
-    <row r="622" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D622" s="1"/>
     </row>
-    <row r="623" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D623" s="1"/>
     </row>
-    <row r="624" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="624" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D624" s="1"/>
     </row>
-    <row r="625" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D625" s="1"/>
     </row>
-    <row r="626" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D626" s="1"/>
     </row>
-    <row r="627" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D627" s="1"/>
     </row>
-    <row r="628" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D628" s="1"/>
     </row>
-    <row r="629" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D629" s="1"/>
     </row>
-    <row r="630" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D630" s="1"/>
     </row>
-    <row r="631" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D631" s="1"/>
     </row>
-    <row r="632" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D632" s="1"/>
     </row>
-    <row r="633" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D633" s="1"/>
     </row>
-    <row r="634" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D634" s="1"/>
     </row>
-    <row r="635" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D635" s="1"/>
     </row>
-    <row r="636" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D636" s="1"/>
     </row>
-    <row r="637" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D637" s="1"/>
     </row>
-    <row r="638" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D638" s="1"/>
     </row>
-    <row r="639" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D639" s="1"/>
     </row>
-    <row r="640" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D640" s="1"/>
     </row>
-    <row r="641" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D641" s="1"/>
     </row>
-    <row r="642" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D642" s="1"/>
     </row>
-    <row r="643" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D643" s="1"/>
     </row>
-    <row r="644" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D644" s="1"/>
     </row>
-    <row r="645" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D645" s="1"/>
     </row>
-    <row r="646" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D646" s="1"/>
     </row>
-    <row r="647" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D647" s="1"/>
     </row>
-    <row r="648" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D648" s="1"/>
     </row>
-    <row r="649" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D649" s="1"/>
     </row>
-    <row r="650" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D650" s="1"/>
     </row>
-    <row r="651" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D651" s="1"/>
     </row>
-    <row r="652" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D652" s="1"/>
     </row>
-    <row r="653" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D653" s="1"/>
     </row>
-    <row r="654" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D654" s="1"/>
     </row>
-    <row r="655" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D655" s="1"/>
     </row>
-    <row r="656" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D656" s="1"/>
     </row>
-    <row r="657" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D657" s="1"/>
     </row>
-    <row r="658" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D658" s="1"/>
     </row>
-    <row r="659" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D659" s="1"/>
     </row>
-    <row r="660" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D660" s="1"/>
     </row>
-    <row r="661" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D661" s="1"/>
     </row>
-    <row r="662" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D662" s="1"/>
     </row>
-    <row r="663" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D663" s="1"/>
     </row>
-    <row r="664" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D664" s="1"/>
     </row>
-    <row r="665" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D665" s="1"/>
     </row>
-    <row r="666" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D666" s="1"/>
     </row>
-    <row r="667" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D667" s="1"/>
     </row>
-    <row r="668" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D668" s="1"/>
     </row>
-    <row r="669" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D669" s="1"/>
     </row>
-    <row r="670" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D670" s="1"/>
     </row>
-    <row r="671" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D671" s="1"/>
     </row>
-    <row r="672" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D672" s="1"/>
     </row>
-    <row r="673" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D673" s="1"/>
     </row>
-    <row r="674" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D674" s="1"/>
     </row>
-    <row r="675" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D675" s="1"/>
     </row>
-    <row r="676" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D676" s="1"/>
     </row>
-    <row r="677" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D677" s="1"/>
     </row>
-    <row r="678" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D678" s="1"/>
     </row>
-    <row r="679" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D679" s="1"/>
     </row>
-    <row r="680" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D680" s="1"/>
     </row>
-    <row r="681" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D681" s="1"/>
     </row>
-    <row r="682" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D682" s="1"/>
     </row>
-    <row r="683" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D683" s="1"/>
     </row>
-    <row r="684" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D684" s="1"/>
     </row>
-    <row r="685" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D685" s="1"/>
     </row>
-    <row r="686" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D686" s="1"/>
     </row>
-    <row r="687" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D687" s="1"/>
     </row>
-    <row r="688" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D688" s="1"/>
     </row>
-    <row r="689" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D689" s="1"/>
     </row>
-    <row r="690" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="690" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D690" s="1"/>
     </row>
-    <row r="691" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D691" s="1"/>
     </row>
-    <row r="692" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D692" s="1"/>
     </row>
-    <row r="693" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D693" s="1"/>
     </row>
-    <row r="694" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="694" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D694" s="1"/>
     </row>
-    <row r="695" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D695" s="1"/>
     </row>
-    <row r="696" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="696" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D696" s="1"/>
     </row>
-    <row r="697" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D697" s="1"/>
     </row>
-    <row r="698" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="698" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D698" s="1"/>
     </row>
-    <row r="699" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="699" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D699" s="1"/>
     </row>
-    <row r="700" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D700" s="1"/>
     </row>
-    <row r="701" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D701" s="1"/>
     </row>
-    <row r="702" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D702" s="1"/>
     </row>
-    <row r="703" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D703" s="1"/>
     </row>
-    <row r="704" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D704" s="1"/>
     </row>
-    <row r="705" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D705" s="1"/>
     </row>
-    <row r="706" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D706" s="1"/>
     </row>
-    <row r="707" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D707" s="1"/>
     </row>
-    <row r="708" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D708" s="1"/>
     </row>
-    <row r="709" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D709" s="1"/>
     </row>
-    <row r="710" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D710" s="1"/>
     </row>
-    <row r="711" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D711" s="1"/>
     </row>
-    <row r="712" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D712" s="1"/>
     </row>
-    <row r="713" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D713" s="1"/>
     </row>
-    <row r="714" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="714" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D714" s="1"/>
     </row>
-    <row r="715" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="715" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D715" s="1"/>
     </row>
-    <row r="716" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="716" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D716" s="1"/>
     </row>
-    <row r="717" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="717" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D717" s="1"/>
     </row>
-    <row r="718" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="718" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D718" s="1"/>
     </row>
-    <row r="719" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="719" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D719" s="1"/>
     </row>
-    <row r="720" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="720" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D720" s="1"/>
     </row>
-    <row r="721" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="721" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D721" s="1"/>
     </row>
-    <row r="722" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="722" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D722" s="1"/>
     </row>
-    <row r="723" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="723" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D723" s="1"/>
     </row>
-    <row r="724" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="724" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D724" s="1"/>
     </row>
-    <row r="725" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="725" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D725" s="1"/>
     </row>
-    <row r="726" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="726" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D726" s="1"/>
     </row>
-    <row r="727" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="727" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D727" s="1"/>
     </row>
-    <row r="728" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="728" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D728" s="1"/>
     </row>
-    <row r="729" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="729" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D729" s="1"/>
     </row>
-    <row r="730" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="730" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D730" s="1"/>
     </row>
-    <row r="731" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="731" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D731" s="1"/>
     </row>
-    <row r="732" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="732" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D732" s="1"/>
     </row>
-    <row r="733" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="733" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D733" s="1"/>
     </row>
-    <row r="734" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="734" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D734" s="1"/>
     </row>
-    <row r="735" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="735" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D735" s="1"/>
     </row>
-    <row r="736" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="736" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D736" s="1"/>
     </row>
-    <row r="737" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="737" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D737" s="1"/>
     </row>
-    <row r="738" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="738" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D738" s="1"/>
     </row>
-    <row r="739" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="739" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D739" s="1"/>
     </row>
-    <row r="740" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="740" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D740" s="1"/>
     </row>
-    <row r="741" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="741" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D741" s="1"/>
     </row>
-    <row r="742" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="742" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D742" s="1"/>
     </row>
-    <row r="743" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="743" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D743" s="1"/>
     </row>
-    <row r="744" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="744" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D744" s="1"/>
     </row>
-    <row r="745" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="745" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D745" s="1"/>
     </row>
-    <row r="746" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="746" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D746" s="1"/>
     </row>
-    <row r="747" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="747" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D747" s="1"/>
     </row>
-    <row r="748" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="748" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D748" s="1"/>
     </row>
-    <row r="749" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="749" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D749" s="1"/>
     </row>
-    <row r="750" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="750" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D750" s="1"/>
     </row>
-    <row r="751" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="751" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D751" s="1"/>
     </row>
-    <row r="752" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="752" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D752" s="1"/>
     </row>
-    <row r="753" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="753" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D753" s="1"/>
     </row>
-    <row r="754" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="754" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D754" s="1"/>
     </row>
-    <row r="755" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="755" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D755" s="1"/>
     </row>
-    <row r="756" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="756" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D756" s="1"/>
     </row>
-    <row r="757" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="757" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D757" s="1"/>
     </row>
-    <row r="758" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="758" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D758" s="1"/>
     </row>
-    <row r="759" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="759" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D759" s="1"/>
     </row>
-    <row r="760" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="760" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D760" s="1"/>
     </row>
-    <row r="761" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="761" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D761" s="1"/>
     </row>
-    <row r="762" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="762" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D762" s="1"/>
     </row>
-    <row r="763" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="763" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D763" s="1"/>
     </row>
-    <row r="764" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="764" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D764" s="1"/>
     </row>
-    <row r="765" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="765" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D765" s="1"/>
     </row>
-    <row r="766" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="766" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D766" s="1"/>
     </row>
-    <row r="767" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="767" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D767" s="1"/>
     </row>
-    <row r="768" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="768" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D768" s="1"/>
     </row>
-    <row r="769" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="769" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D769" s="1"/>
     </row>
-    <row r="770" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="770" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D770" s="1"/>
     </row>
-    <row r="771" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="771" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D771" s="1"/>
     </row>
-    <row r="772" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="772" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D772" s="1"/>
     </row>
-    <row r="773" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="773" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D773" s="1"/>
     </row>
-    <row r="774" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="774" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D774" s="1"/>
     </row>
-    <row r="775" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="775" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D775" s="1"/>
     </row>
-    <row r="776" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="776" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D776" s="1"/>
     </row>
-    <row r="777" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="777" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D777" s="1"/>
     </row>
-    <row r="778" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="778" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D778" s="1"/>
     </row>
-    <row r="779" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="779" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D779" s="1"/>
     </row>
-    <row r="780" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="780" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D780" s="1"/>
     </row>
-    <row r="781" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="781" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D781" s="1"/>
     </row>
-    <row r="782" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="782" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D782" s="1"/>
     </row>
-    <row r="783" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="783" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D783" s="1"/>
     </row>
-    <row r="784" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="784" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D784" s="1"/>
     </row>
-    <row r="785" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="785" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D785" s="1"/>
     </row>
-    <row r="786" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="786" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D786" s="1"/>
     </row>
-    <row r="787" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="787" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D787" s="1"/>
     </row>
-    <row r="788" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="788" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D788" s="1"/>
     </row>
-    <row r="789" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="789" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D789" s="1"/>
     </row>
-    <row r="790" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="790" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D790" s="1"/>
     </row>
-    <row r="791" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="791" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D791" s="1"/>
     </row>
-    <row r="792" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="792" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D792" s="1"/>
     </row>
-    <row r="793" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="793" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D793" s="1"/>
     </row>
-    <row r="794" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="794" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D794" s="1"/>
     </row>
-    <row r="795" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="795" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D795" s="1"/>
     </row>
-    <row r="796" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="796" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D796" s="1"/>
     </row>
-    <row r="797" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="797" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D797" s="1"/>
     </row>
-    <row r="798" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="798" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D798" s="1"/>
     </row>
-    <row r="799" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="799" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D799" s="1"/>
     </row>
-    <row r="800" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="800" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D800" s="1"/>
     </row>
-    <row r="801" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="801" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D801" s="1"/>
     </row>
-    <row r="802" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="802" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D802" s="1"/>
     </row>
-    <row r="803" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="803" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D803" s="1"/>
     </row>
-    <row r="804" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="804" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D804" s="1"/>
     </row>
-    <row r="805" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="805" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D805" s="1"/>
     </row>
-    <row r="806" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="806" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D806" s="1"/>
     </row>
-    <row r="807" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="807" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D807" s="1"/>
     </row>
-    <row r="808" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="808" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D808" s="1"/>
     </row>
-    <row r="809" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="809" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D809" s="1"/>
     </row>
-    <row r="810" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="810" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D810" s="1"/>
     </row>
-    <row r="811" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="811" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D811" s="1"/>
     </row>
-    <row r="812" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="812" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D812" s="1"/>
     </row>
-    <row r="813" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="813" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D813" s="1"/>
     </row>
-    <row r="814" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="814" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D814" s="1"/>
     </row>
-    <row r="815" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="815" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D815" s="1"/>
     </row>
-    <row r="816" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="816" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D816" s="1"/>
     </row>
-    <row r="817" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="817" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D817" s="1"/>
     </row>
-    <row r="818" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="818" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D818" s="1"/>
     </row>
-    <row r="819" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="819" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D819" s="1"/>
     </row>
-    <row r="820" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="820" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D820" s="1"/>
     </row>
-    <row r="821" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="821" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D821" s="1"/>
     </row>
-    <row r="822" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="822" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D822" s="1"/>
     </row>
-    <row r="823" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="823" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D823" s="1"/>
     </row>
-    <row r="824" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="824" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D824" s="1"/>
     </row>
-    <row r="825" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="825" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D825" s="1"/>
     </row>
-    <row r="826" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="826" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D826" s="1"/>
     </row>
-    <row r="827" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="827" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D827" s="1"/>
     </row>
-    <row r="828" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="828" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D828" s="1"/>
     </row>
-    <row r="829" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="829" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D829" s="1"/>
     </row>
-    <row r="830" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="830" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D830" s="1"/>
     </row>
-    <row r="831" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="831" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D831" s="1"/>
     </row>
-    <row r="832" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="832" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D832" s="1"/>
     </row>
-    <row r="833" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="833" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D833" s="1"/>
     </row>
-    <row r="834" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="834" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D834" s="1"/>
     </row>
-    <row r="835" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="835" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D835" s="1"/>
     </row>
-    <row r="836" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="836" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D836" s="1"/>
     </row>
-    <row r="837" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="837" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D837" s="1"/>
     </row>
-    <row r="838" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="838" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D838" s="1"/>
     </row>
-    <row r="839" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="839" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D839" s="1"/>
     </row>
-    <row r="840" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="840" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D840" s="1"/>
     </row>
-    <row r="841" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="841" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D841" s="1"/>
     </row>
-    <row r="842" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="842" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D842" s="1"/>
     </row>
-    <row r="843" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="843" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D843" s="1"/>
     </row>
-    <row r="844" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="844" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D844" s="1"/>
     </row>
-    <row r="845" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="845" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D845" s="1"/>
     </row>
-    <row r="846" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="846" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D846" s="1"/>
     </row>
-    <row r="847" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="847" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D847" s="1"/>
     </row>
-    <row r="848" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="848" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D848" s="1"/>
     </row>
-    <row r="849" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="849" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D849" s="1"/>
     </row>
-    <row r="850" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="850" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D850" s="1"/>
     </row>
-    <row r="851" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="851" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D851" s="1"/>
     </row>
-    <row r="852" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="852" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D852" s="1"/>
     </row>
-    <row r="853" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="853" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D853" s="1"/>
     </row>
-    <row r="854" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="854" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D854" s="1"/>
     </row>
-    <row r="855" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="855" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D855" s="1"/>
     </row>
-    <row r="856" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="856" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D856" s="1"/>
     </row>
-    <row r="857" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="857" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D857" s="1"/>
     </row>
-    <row r="858" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="858" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D858" s="1"/>
     </row>
-    <row r="859" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="859" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D859" s="1"/>
     </row>
-    <row r="860" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="860" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D860" s="1"/>
     </row>
-    <row r="861" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="861" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D861" s="1"/>
     </row>
-    <row r="862" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="862" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D862" s="1"/>
     </row>
-    <row r="863" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="863" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D863" s="1"/>
     </row>
-    <row r="864" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="864" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D864" s="1"/>
     </row>
-    <row r="865" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="865" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D865" s="1"/>
     </row>
-    <row r="866" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="866" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D866" s="1"/>
     </row>
-    <row r="867" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="867" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D867" s="1"/>
     </row>
-    <row r="868" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="868" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D868" s="1"/>
     </row>
-    <row r="869" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="869" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D869" s="1"/>
     </row>
-    <row r="870" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="870" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D870" s="1"/>
     </row>
-    <row r="871" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="871" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D871" s="1"/>
     </row>
-    <row r="872" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="872" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D872" s="1"/>
     </row>
-    <row r="873" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="873" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D873" s="1"/>
     </row>
-    <row r="874" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="874" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D874" s="1"/>
     </row>
-    <row r="875" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="875" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D875" s="1"/>
     </row>
-    <row r="876" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="876" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D876" s="1"/>
     </row>
-    <row r="877" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="877" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D877" s="1"/>
     </row>
-    <row r="878" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="878" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D878" s="1"/>
     </row>
-    <row r="879" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="879" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D879" s="1"/>
     </row>
-    <row r="880" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="880" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D880" s="1"/>
     </row>
-    <row r="881" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="881" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D881" s="1"/>
     </row>
-    <row r="882" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="882" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D882" s="1"/>
     </row>
-    <row r="883" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="883" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D883" s="1"/>
     </row>
-    <row r="884" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="884" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D884" s="1"/>
     </row>
-    <row r="885" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="885" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D885" s="1"/>
     </row>
-    <row r="886" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="886" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D886" s="1"/>
     </row>
-    <row r="887" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="887" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D887" s="1"/>
     </row>
-    <row r="888" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="888" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D888" s="1"/>
     </row>
-    <row r="889" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="889" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D889" s="1"/>
     </row>
-    <row r="890" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="890" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D890" s="1"/>
     </row>
-    <row r="891" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="891" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D891" s="1"/>
     </row>
-    <row r="892" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="892" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D892" s="1"/>
     </row>
-    <row r="893" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="893" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D893" s="1"/>
     </row>
-    <row r="894" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="894" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D894" s="1"/>
     </row>
-    <row r="895" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="895" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D895" s="1"/>
     </row>
-    <row r="896" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="896" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D896" s="1"/>
     </row>
-    <row r="897" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="897" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D897" s="1"/>
     </row>
-    <row r="898" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="898" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D898" s="1"/>
     </row>
-    <row r="899" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="899" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D899" s="1"/>
     </row>
-    <row r="900" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="900" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D900" s="1"/>
     </row>
-    <row r="901" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="901" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D901" s="1"/>
     </row>
-    <row r="902" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="902" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D902" s="1"/>
     </row>
-    <row r="903" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="903" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D903" s="1"/>
     </row>
-    <row r="904" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="904" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D904" s="1"/>
     </row>
-    <row r="905" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="905" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D905" s="1"/>
     </row>
-    <row r="906" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="906" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D906" s="1"/>
     </row>
-    <row r="907" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="907" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D907" s="1"/>
     </row>
-    <row r="908" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="908" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D908" s="1"/>
     </row>
-    <row r="909" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="909" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D909" s="1"/>
     </row>
-    <row r="910" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="910" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D910" s="1"/>
     </row>
-    <row r="911" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="911" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D911" s="1"/>
     </row>
-    <row r="912" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="912" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D912" s="1"/>
     </row>
-    <row r="913" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="913" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D913" s="1"/>
     </row>
-    <row r="914" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="914" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D914" s="1"/>
     </row>
-    <row r="915" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="915" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D915" s="1"/>
     </row>
-    <row r="916" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="916" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D916" s="1"/>
     </row>
-    <row r="917" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="917" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D917" s="1"/>
     </row>
-    <row r="918" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="918" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D918" s="1"/>
     </row>
-    <row r="919" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="919" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D919" s="1"/>
     </row>
-    <row r="920" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="920" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D920" s="1"/>
     </row>
-    <row r="921" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="921" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D921" s="1"/>
     </row>
-    <row r="922" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="922" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D922" s="1"/>
     </row>
-    <row r="923" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="923" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D923" s="1"/>
     </row>
-    <row r="924" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="924" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D924" s="1"/>
     </row>
-    <row r="925" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="925" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D925" s="1"/>
     </row>
-    <row r="926" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="926" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D926" s="1"/>
     </row>
-    <row r="927" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="927" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D927" s="1"/>
     </row>
-    <row r="928" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="928" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D928" s="1"/>
     </row>
-    <row r="929" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="929" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D929" s="1"/>
     </row>
-    <row r="930" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="930" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D930" s="1"/>
     </row>
-    <row r="931" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="931" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D931" s="1"/>
     </row>
-    <row r="932" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="932" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D932" s="1"/>
     </row>
-    <row r="933" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="933" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D933" s="1"/>
     </row>
-    <row r="934" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="934" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D934" s="1"/>
     </row>
-    <row r="935" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="935" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D935" s="1"/>
     </row>
-    <row r="936" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="936" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D936" s="1"/>
     </row>
-    <row r="937" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="937" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D937" s="1"/>
     </row>
-    <row r="938" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="938" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D938" s="1"/>
     </row>
-    <row r="939" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="939" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D939" s="1"/>
     </row>
-    <row r="940" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="940" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D940" s="1"/>
     </row>
-    <row r="941" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="941" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D941" s="1"/>
     </row>
-    <row r="942" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="942" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D942" s="1"/>
     </row>
-    <row r="943" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="943" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D943" s="1"/>
     </row>
-    <row r="944" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="944" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D944" s="1"/>
     </row>
-    <row r="945" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="945" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D945" s="1"/>
     </row>
-    <row r="946" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="946" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D946" s="1"/>
     </row>
-    <row r="947" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="947" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D947" s="1"/>
     </row>
-    <row r="948" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="948" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D948" s="1"/>
     </row>
-    <row r="949" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="949" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D949" s="1"/>
     </row>
-    <row r="950" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="950" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D950" s="1"/>
     </row>
-    <row r="951" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="951" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D951" s="1"/>
     </row>
-    <row r="952" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="952" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D952" s="1"/>
     </row>
-    <row r="953" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="953" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D953" s="1"/>
     </row>
-    <row r="954" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="954" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D954" s="1"/>
     </row>
-    <row r="955" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="955" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D955" s="1"/>
     </row>
-    <row r="956" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="956" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D956" s="1"/>
     </row>
-    <row r="957" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="957" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D957" s="1"/>
     </row>
-    <row r="958" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="958" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D958" s="1"/>
     </row>
-    <row r="959" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="959" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D959" s="1"/>
     </row>
-    <row r="960" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="960" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D960" s="1"/>
     </row>
-    <row r="961" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="961" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D961" s="1"/>
     </row>
-    <row r="962" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="962" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D962" s="1"/>
     </row>
-    <row r="963" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="963" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D963" s="1"/>
     </row>
-    <row r="964" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="964" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D964" s="1"/>
     </row>
-    <row r="965" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="965" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D965" s="1"/>
     </row>
-    <row r="966" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="966" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D966" s="1"/>
     </row>
-    <row r="967" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="967" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D967" s="1"/>
     </row>
-    <row r="968" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="968" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D968" s="1"/>
     </row>
-    <row r="969" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="969" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D969" s="1"/>
     </row>
-    <row r="970" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="970" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D970" s="1"/>
     </row>
-    <row r="971" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="971" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D971" s="1"/>
     </row>
-    <row r="972" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="972" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D972" s="1"/>
     </row>
-    <row r="973" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="973" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D973" s="1"/>
     </row>
-    <row r="974" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="974" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D974" s="1"/>
     </row>
-    <row r="975" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="975" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D975" s="1"/>
     </row>
-    <row r="976" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="976" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D976" s="1"/>
     </row>
-    <row r="977" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="977" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D977" s="1"/>
     </row>
-    <row r="978" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="978" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D978" s="1"/>
     </row>
-    <row r="979" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="979" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D979" s="1"/>
     </row>
-    <row r="980" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="980" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D980" s="1"/>
     </row>
-    <row r="981" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="981" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D981" s="1"/>
     </row>
-    <row r="982" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="982" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D982" s="1"/>
     </row>
-    <row r="983" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="983" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D983" s="1"/>
     </row>
-    <row r="984" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="984" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D984" s="1"/>
     </row>
-    <row r="985" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="985" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D985" s="1"/>
     </row>
-    <row r="986" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="986" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D986" s="1"/>
     </row>
-    <row r="987" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="987" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D987" s="1"/>
     </row>
-    <row r="988" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="988" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D988" s="1"/>
     </row>
-    <row r="989" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="989" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D989" s="1"/>
     </row>
-    <row r="990" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="990" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D990" s="1"/>
     </row>
-    <row r="991" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="991" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D991" s="1"/>
     </row>
-    <row r="992" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="992" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D992" s="1"/>
     </row>
-    <row r="993" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="993" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D993" s="1"/>
     </row>
-    <row r="994" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="994" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D994" s="1"/>
     </row>
-    <row r="995" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="995" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D995" s="1"/>
     </row>
-    <row r="996" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="996" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D996" s="1"/>
     </row>
-    <row r="997" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="997" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D997" s="1"/>
     </row>
   </sheetData>
@@ -9256,6 +9256,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f366023269454ced43510f73883a6d91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd01e2e1f35a8420c36650a8355a0ef6" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -9438,24 +9455,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F6FD9D-19D1-439B-8BFE-82DBC99BDEA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C79516F1-8A13-4F63-820A-89A8B84A29E0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9472,22 +9490,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F6FD9D-19D1-439B-8BFE-82DBC99BDEA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/upload files/Preferences v6.xlsx
+++ b/upload files/Preferences v6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5a8cad284f0e3288/Desktop/GitHub Repo/CrewOps360/upload files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{E846D7B7-4F52-EA4C-98E1-C56242AA7549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9C3D05C-D114-4373-8F81-F9CC74EC0F96}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AAAB9B0-7F0E-4C0E-95DC-8FC4F828A00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30120" yWindow="525" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -104,6 +104,9 @@
     <t>NP</t>
   </si>
   <si>
+    <t>N to D Flex</t>
+  </si>
+  <si>
     <t>Ahlstedt</t>
   </si>
   <si>
@@ -116,6 +119,9 @@
     <t>Saia</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Gallagher</t>
   </si>
   <si>
@@ -134,6 +140,9 @@
     <t>Pepin</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>Estanislao</t>
   </si>
   <si>
@@ -158,6 +167,9 @@
     <t>dual</t>
   </si>
   <si>
+    <t>Maybe</t>
+  </si>
+  <si>
     <t>Ender</t>
   </si>
   <si>
@@ -167,12 +179,12 @@
     <t>McKinnon</t>
   </si>
   <si>
+    <t>Boomhower</t>
+  </si>
+  <si>
     <t>Mee</t>
   </si>
   <si>
-    <t>Boomhower</t>
-  </si>
-  <si>
     <t>McNulty</t>
   </si>
   <si>
@@ -203,42 +215,45 @@
     <t>Gibbs</t>
   </si>
   <si>
+    <t>Dunn</t>
+  </si>
+  <si>
     <t>Horan</t>
   </si>
   <si>
-    <t>Dunn</t>
+    <t>Vescuso</t>
   </si>
   <si>
     <t>King</t>
   </si>
   <si>
-    <t>Vescuso</t>
-  </si>
-  <si>
     <t>Steckevicz</t>
   </si>
   <si>
+    <t>DiNardo</t>
+  </si>
+  <si>
+    <t>McGrath</t>
+  </si>
+  <si>
+    <t>Noland</t>
+  </si>
+  <si>
     <t>Murphy</t>
   </si>
   <si>
-    <t>McGrath</t>
-  </si>
-  <si>
-    <t>Noland</t>
-  </si>
-  <si>
-    <t>DiNardo</t>
+    <t>Doherty</t>
+  </si>
+  <si>
+    <t>Hanley-McCarthy</t>
+  </si>
+  <si>
+    <t>Kilduff</t>
   </si>
   <si>
     <t>Neimann</t>
   </si>
   <si>
-    <t>Hanley-McCarthy</t>
-  </si>
-  <si>
-    <t>Kilduff</t>
-  </si>
-  <si>
     <t>Grant</t>
   </si>
   <si>
@@ -251,54 +266,54 @@
     <t>Eastman</t>
   </si>
   <si>
+    <t>Charest</t>
+  </si>
+  <si>
+    <t>Rabickow</t>
+  </si>
+  <si>
     <t>Worsman</t>
   </si>
   <si>
-    <t>Charest</t>
-  </si>
-  <si>
-    <t>Rabickow</t>
+    <t>Marcosa</t>
   </si>
   <si>
     <t>Timm</t>
   </si>
   <si>
-    <t>Marcosa</t>
-  </si>
-  <si>
-    <t>Doherty</t>
-  </si>
-  <si>
     <t>Carchia</t>
   </si>
   <si>
     <t>Kraby</t>
   </si>
   <si>
+    <t>Saraceno</t>
+  </si>
+  <si>
+    <t>Machado</t>
+  </si>
+  <si>
     <t>Sammon</t>
   </si>
   <si>
-    <t>Machado</t>
-  </si>
-  <si>
     <t>Laterion</t>
   </si>
   <si>
     <t>Moore</t>
   </si>
   <si>
+    <t>Boutilier</t>
+  </si>
+  <si>
     <t>Chaber</t>
   </si>
   <si>
+    <t>Fielding</t>
+  </si>
+  <si>
     <t>Romano</t>
   </si>
   <si>
-    <t>Boutilier</t>
-  </si>
-  <si>
-    <t>Fielding</t>
-  </si>
-  <si>
     <t>Creekmuir</t>
   </si>
   <si>
@@ -308,12 +323,12 @@
     <t>Kadow</t>
   </si>
   <si>
+    <t>Bach</t>
+  </si>
+  <si>
     <t>Shelanskas</t>
   </si>
   <si>
-    <t>Bach</t>
-  </si>
-  <si>
     <t>Young</t>
   </si>
   <si>
@@ -323,47 +338,32 @@
     <t>Cowart</t>
   </si>
   <si>
+    <t>Walker</t>
+  </si>
+  <si>
     <t>Wyzansky</t>
   </si>
   <si>
-    <t>Walker</t>
-  </si>
-  <si>
     <t>Sacco</t>
   </si>
   <si>
+    <t>Clark</t>
+  </si>
+  <si>
     <t>Kelley</t>
   </si>
   <si>
-    <t>Clark</t>
+    <t>Payton</t>
   </si>
   <si>
     <t>Ravenelle</t>
-  </si>
-  <si>
-    <t>N to D Flex</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Maybe</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Saraceno</t>
-  </si>
-  <si>
-    <t>Payton</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1352,7 +1352,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U997"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -1378,7 +1378,7 @@
     <col min="22" max="26" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21">
       <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
@@ -1440,15 +1440,15 @@
         <v>19</v>
       </c>
       <c r="U1" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
       <c r="A2" s="35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="6">
         <v>1</v>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="U2" s="10"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21">
       <c r="A3" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>21</v>
       </c>
       <c r="C3" s="11">
         <v>1</v>
@@ -1569,12 +1569,12 @@
       </c>
       <c r="U3" s="15"/>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21">
       <c r="A4" s="37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="16">
         <v>1</v>
@@ -1631,15 +1631,15 @@
         <v>4</v>
       </c>
       <c r="U4" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
       <c r="A5" s="36" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C5" s="11">
         <v>1</v>
@@ -1696,15 +1696,15 @@
         <v>3</v>
       </c>
       <c r="U5" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
       <c r="A6" s="37" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C6" s="16">
         <v>1</v>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="U6" s="10"/>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21">
       <c r="A7" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="20" t="s">
         <v>27</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>25</v>
       </c>
       <c r="C7" s="20">
         <v>1</v>
@@ -1824,15 +1824,15 @@
         <v>0</v>
       </c>
       <c r="U7" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
       <c r="A8" s="36" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="23">
         <v>1</v>
@@ -1890,12 +1890,12 @@
       </c>
       <c r="U8" s="15"/>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21">
       <c r="A9" s="36" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="11">
         <v>1</v>
@@ -1952,15 +1952,15 @@
         <v>4</v>
       </c>
       <c r="U9" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
       <c r="A10" s="36" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="23">
         <v>1</v>
@@ -2018,12 +2018,12 @@
       </c>
       <c r="U10" s="15"/>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21">
       <c r="A11" s="37" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" s="20">
         <v>1</v>
@@ -2080,15 +2080,15 @@
         <v>1</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
       <c r="A12" s="36" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" s="23">
         <v>1</v>
@@ -2146,12 +2146,12 @@
       </c>
       <c r="U12" s="15"/>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21">
       <c r="A13" s="36" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" s="11">
         <v>1</v>
@@ -2208,15 +2208,15 @@
         <v>4</v>
       </c>
       <c r="U13" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
       <c r="A14" s="36" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C14" s="23">
         <v>1</v>
@@ -2273,15 +2273,15 @@
         <v>2</v>
       </c>
       <c r="U14" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
       <c r="A15" s="37" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C15" s="20">
         <v>1</v>
@@ -2338,15 +2338,15 @@
         <v>3</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
       <c r="A16" s="36" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C16" s="11">
         <v>1</v>
@@ -2403,15 +2403,15 @@
         <v>1</v>
       </c>
       <c r="U16" s="15" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
       <c r="A17" s="37" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" s="16">
         <v>1</v>
@@ -2469,12 +2469,12 @@
       </c>
       <c r="U17" s="10"/>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21">
       <c r="A18" s="37" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C18" s="20">
         <v>1</v>
@@ -2532,12 +2532,12 @@
       </c>
       <c r="U18" s="10"/>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21">
       <c r="A19" s="37" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" s="16">
         <v>1</v>
@@ -2594,15 +2594,15 @@
         <v>1</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="15.75" customHeight="1">
       <c r="A20" s="37" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C20" s="20">
         <v>1</v>
@@ -2659,15 +2659,15 @@
         <v>2</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="15.75" customHeight="1">
       <c r="A21" s="37" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C21" s="16">
         <v>1</v>
@@ -2724,15 +2724,15 @@
         <v>1</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="15.75" customHeight="1">
       <c r="A22" s="36" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C22" s="11">
         <v>1</v>
@@ -2789,15 +2789,15 @@
         <v>0</v>
       </c>
       <c r="U22" s="15" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="15.75" customHeight="1">
       <c r="A23" s="37" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C23" s="16">
         <v>1</v>
@@ -2854,15 +2854,15 @@
         <v>1</v>
       </c>
       <c r="U23" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="15.75" customHeight="1">
       <c r="A24" s="37" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C24" s="20">
         <v>1</v>
@@ -2920,12 +2920,12 @@
       </c>
       <c r="U24" s="10"/>
     </row>
-    <row r="25" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" ht="15.75" customHeight="1">
       <c r="A25" s="36" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C25" s="11">
         <v>1</v>
@@ -2982,15 +2982,15 @@
         <v>0</v>
       </c>
       <c r="U25" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="15.75" customHeight="1">
       <c r="A26" s="36" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C26" s="23">
         <v>1</v>
@@ -3047,15 +3047,15 @@
         <v>0</v>
       </c>
       <c r="U26" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="15.75" customHeight="1">
       <c r="A27" s="39" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B27" s="30" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C27" s="30">
         <v>1</v>
@@ -3112,15 +3112,15 @@
         <v>1</v>
       </c>
       <c r="U27" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="15.75" customHeight="1">
       <c r="A28" s="37" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C28" s="20">
         <v>1</v>
@@ -3177,15 +3177,15 @@
         <v>3</v>
       </c>
       <c r="U28" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="15.75" customHeight="1">
       <c r="A29" s="36" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C29" s="23">
         <v>1</v>
@@ -3242,15 +3242,15 @@
         <v>1</v>
       </c>
       <c r="U29" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="15.75" customHeight="1">
       <c r="A30" s="36" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C30" s="11">
         <v>1</v>
@@ -3307,15 +3307,15 @@
         <v>1</v>
       </c>
       <c r="U30" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="15.75" customHeight="1">
       <c r="A31" s="37" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C31" s="16">
         <v>1</v>
@@ -3372,15 +3372,15 @@
         <v>1</v>
       </c>
       <c r="U31" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="15.75" customHeight="1">
       <c r="A32" s="37" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C32" s="20">
         <v>1</v>
@@ -3437,15 +3437,15 @@
         <v>1</v>
       </c>
       <c r="U32" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="15.75" customHeight="1">
       <c r="A33" s="37" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B33" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C33" s="16">
         <v>1</v>
@@ -3502,15 +3502,15 @@
         <v>4</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="15.75" customHeight="1">
       <c r="A34" s="36" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C34" s="11">
         <v>1</v>
@@ -3567,15 +3567,15 @@
         <v>2</v>
       </c>
       <c r="U34" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="15.75" customHeight="1">
       <c r="A35" s="37" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B35" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C35" s="16">
         <v>1</v>
@@ -3632,15 +3632,15 @@
         <v>4</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" ht="15.75" customHeight="1">
       <c r="A36" s="37" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C36" s="20">
         <v>1</v>
@@ -3698,12 +3698,12 @@
       </c>
       <c r="U36" s="10"/>
     </row>
-    <row r="37" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" ht="15.75" customHeight="1">
       <c r="A37" s="37" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B37" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C37" s="16">
         <v>1</v>
@@ -3760,15 +3760,15 @@
         <v>1</v>
       </c>
       <c r="U37" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="15.75" customHeight="1">
       <c r="A38" s="38" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C38" s="26">
         <v>1</v>
@@ -3825,15 +3825,15 @@
         <v>4</v>
       </c>
       <c r="U38" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="15.75" customHeight="1">
       <c r="A39" s="37" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B39" s="20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C39" s="20">
         <v>1</v>
@@ -3890,15 +3890,15 @@
         <v>2</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="40" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" ht="15.75" customHeight="1">
       <c r="A40" s="36" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C40" s="23">
         <v>1</v>
@@ -3955,15 +3955,15 @@
         <v>1</v>
       </c>
       <c r="U40" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" ht="15.75" customHeight="1">
       <c r="A41" s="36" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C41" s="11">
         <v>1</v>
@@ -4021,12 +4021,12 @@
       </c>
       <c r="U41" s="15"/>
     </row>
-    <row r="42" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" ht="15.75" customHeight="1">
       <c r="A42" s="37" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C42" s="16">
         <v>1</v>
@@ -4083,15 +4083,15 @@
         <v>1</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" ht="15.75" customHeight="1">
       <c r="A43" s="36" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C43" s="11">
         <v>1</v>
@@ -4148,15 +4148,15 @@
         <v>4</v>
       </c>
       <c r="U43" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="44" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" ht="15.75" customHeight="1">
       <c r="A44" s="36" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C44" s="23">
         <v>1</v>
@@ -4213,15 +4213,15 @@
         <v>2</v>
       </c>
       <c r="U44" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" ht="15.75" customHeight="1">
       <c r="A45" s="36" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C45" s="11">
         <v>1</v>
@@ -4278,15 +4278,15 @@
         <v>1</v>
       </c>
       <c r="U45" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" ht="15.75" customHeight="1">
       <c r="A46" s="36" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C46" s="23">
         <v>1</v>
@@ -4343,15 +4343,15 @@
         <v>4</v>
       </c>
       <c r="U46" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="47" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" ht="15.75" customHeight="1">
       <c r="A47" s="36" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C47" s="11">
         <v>1</v>
@@ -4408,15 +4408,15 @@
         <v>2</v>
       </c>
       <c r="U47" s="15" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" ht="15.75" customHeight="1">
       <c r="A48" s="36" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C48" s="23">
         <v>1</v>
@@ -4473,15 +4473,15 @@
         <v>0</v>
       </c>
       <c r="U48" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" ht="15.75" customHeight="1">
       <c r="A49" s="36" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C49" s="11">
         <v>1</v>
@@ -4538,15 +4538,15 @@
         <v>1</v>
       </c>
       <c r="U49" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" ht="15.75" customHeight="1">
       <c r="A50" s="37" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C50" s="16">
         <v>1</v>
@@ -4603,15 +4603,15 @@
         <v>1</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" ht="15.75" customHeight="1">
       <c r="A51" s="37" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C51" s="20">
         <v>1</v>
@@ -4668,15 +4668,15 @@
         <v>4</v>
       </c>
       <c r="U51" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" ht="15.75" customHeight="1">
       <c r="A52" s="37" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C52" s="16">
         <v>1</v>
@@ -4733,15 +4733,15 @@
         <v>0</v>
       </c>
       <c r="U52" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" ht="15.75" customHeight="1">
       <c r="A53" s="37" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B53" s="20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C53" s="20">
         <v>1</v>
@@ -4798,15 +4798,15 @@
         <v>1</v>
       </c>
       <c r="U53" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" ht="15.75" customHeight="1">
       <c r="A54" s="36" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C54" s="23">
         <v>1</v>
@@ -4863,15 +4863,15 @@
         <v>4</v>
       </c>
       <c r="U54" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" ht="15.75" customHeight="1">
       <c r="A55" s="36" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C55" s="11">
         <v>1</v>
@@ -4928,15 +4928,15 @@
         <v>4</v>
       </c>
       <c r="U55" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" ht="15.75" customHeight="1">
       <c r="A56" s="37" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C56" s="16">
         <v>1</v>
@@ -4993,15 +4993,15 @@
         <v>4</v>
       </c>
       <c r="U56" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" ht="15.75" customHeight="1">
       <c r="A57" s="36" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C57" s="11">
         <v>1</v>
@@ -5058,15 +5058,15 @@
         <v>4</v>
       </c>
       <c r="U57" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" ht="15.75" customHeight="1">
       <c r="A58" s="36" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C58" s="23">
         <v>0</v>
@@ -5123,15 +5123,15 @@
         <v>4</v>
       </c>
       <c r="U58" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="59" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" ht="15.75" customHeight="1">
       <c r="A59" s="36" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C59" s="11">
         <v>1</v>
@@ -5188,15 +5188,15 @@
         <v>1</v>
       </c>
       <c r="U59" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="15.75" customHeight="1">
       <c r="A60" s="37" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C60" s="16">
         <v>0</v>
@@ -5254,12 +5254,12 @@
       </c>
       <c r="U60" s="10"/>
     </row>
-    <row r="61" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:21" ht="15.75" customHeight="1">
       <c r="A61" s="36" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C61" s="11">
         <v>0</v>
@@ -5316,15 +5316,15 @@
         <v>1</v>
       </c>
       <c r="U61" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="62" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" ht="15.75" customHeight="1">
       <c r="A62" s="37" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B62" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C62" s="16">
         <v>0</v>
@@ -5381,15 +5381,15 @@
         <v>4</v>
       </c>
       <c r="U62" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="15.75" customHeight="1">
       <c r="A63" s="37" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B63" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C63" s="20">
         <v>0</v>
@@ -5446,15 +5446,15 @@
         <v>1</v>
       </c>
       <c r="U63" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" ht="15.75" customHeight="1">
       <c r="A64" s="37" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C64" s="16">
         <v>0</v>
@@ -5511,15 +5511,15 @@
         <v>1</v>
       </c>
       <c r="U64" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" ht="15.75" customHeight="1">
       <c r="A65" s="37" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B65" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C65" s="20">
         <v>0</v>
@@ -5576,15 +5576,15 @@
         <v>4</v>
       </c>
       <c r="U65" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" ht="15.75" customHeight="1">
       <c r="A66" s="36" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C66" s="23">
         <v>0</v>
@@ -5641,18 +5641,18 @@
         <v>1</v>
       </c>
       <c r="U66" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" ht="15.75" customHeight="1">
       <c r="A67" s="36" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C67" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" s="12">
         <v>69</v>
@@ -5707,12 +5707,12 @@
       </c>
       <c r="U67" s="15"/>
     </row>
-    <row r="68" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:21" ht="15.75" customHeight="1">
       <c r="A68" s="36" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B68" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C68" s="23">
         <v>0</v>
@@ -5769,15 +5769,15 @@
         <v>1</v>
       </c>
       <c r="U68" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="69" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" ht="15.75" customHeight="1">
       <c r="A69" s="37" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B69" s="20" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C69" s="20">
         <v>0</v>
@@ -5834,15 +5834,15 @@
         <v>2</v>
       </c>
       <c r="U69" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" ht="15.75" customHeight="1">
       <c r="A70" s="37" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C70" s="16">
         <v>0</v>
@@ -5899,15 +5899,15 @@
         <v>4</v>
       </c>
       <c r="U70" s="10" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" ht="15.75" customHeight="1">
       <c r="A71" s="37" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B71" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C71" s="16">
         <v>0</v>
@@ -5964,15 +5964,15 @@
         <v>2</v>
       </c>
       <c r="U71" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" ht="15.75" customHeight="1">
       <c r="A72" s="36" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C72" s="11">
         <v>0</v>
@@ -6029,15 +6029,15 @@
         <v>0</v>
       </c>
       <c r="U72" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="73" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" ht="15.75" customHeight="1">
       <c r="A73" s="37" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C73" s="16">
         <v>0</v>
@@ -6094,15 +6094,15 @@
         <v>1</v>
       </c>
       <c r="U73" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" ht="15.75" customHeight="1">
       <c r="A74" s="36" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C74" s="11">
         <v>0</v>
@@ -6159,15 +6159,15 @@
         <v>3</v>
       </c>
       <c r="U74" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A75" s="36" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="75" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="36" t="s">
-        <v>95</v>
-      </c>
       <c r="B75" s="23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C75" s="23">
         <v>0</v>
@@ -6224,15 +6224,15 @@
         <v>2</v>
       </c>
       <c r="U75" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" ht="15.75" customHeight="1">
       <c r="A76" s="37" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B76" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C76" s="20">
         <v>0</v>
@@ -6289,15 +6289,15 @@
         <v>1</v>
       </c>
       <c r="U76" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="77" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" ht="15.75" customHeight="1">
       <c r="A77" s="37" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C77" s="16">
         <v>0</v>
@@ -6354,15 +6354,15 @@
         <v>4</v>
       </c>
       <c r="U77" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="78" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" ht="15.75" customHeight="1">
       <c r="A78" s="37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B78" s="20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C78" s="20">
         <v>0</v>
@@ -6419,15 +6419,15 @@
         <v>4</v>
       </c>
       <c r="U78" s="10" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="79" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" ht="15.75" customHeight="1" thickBot="1">
       <c r="A79" s="40" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B79" s="41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C79" s="41">
         <v>0</v>
@@ -6484,2761 +6484,2761 @@
         <v>4</v>
       </c>
       <c r="U79" s="15" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="80" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" ht="15.75" customHeight="1">
       <c r="D80" s="1"/>
     </row>
-    <row r="81" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:4" ht="15.75" customHeight="1">
       <c r="D81" s="1"/>
     </row>
-    <row r="82" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:4" ht="15.75" customHeight="1">
       <c r="D82" s="1"/>
     </row>
-    <row r="83" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:4" ht="15.75" customHeight="1">
       <c r="D83" s="1"/>
     </row>
-    <row r="84" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:4" ht="15.75" customHeight="1">
       <c r="D84" s="1"/>
     </row>
-    <row r="85" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:4" ht="15.75" customHeight="1">
       <c r="D85" s="1"/>
     </row>
-    <row r="86" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:4" ht="15.75" customHeight="1">
       <c r="D86" s="1"/>
     </row>
-    <row r="87" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:4" ht="15.75" customHeight="1">
       <c r="D87" s="1"/>
     </row>
-    <row r="88" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:4" ht="15.75" customHeight="1">
       <c r="D88" s="1"/>
     </row>
-    <row r="89" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:4" ht="15.75" customHeight="1">
       <c r="D89" s="1"/>
     </row>
-    <row r="90" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:4" ht="15.75" customHeight="1">
       <c r="D90" s="1"/>
     </row>
-    <row r="91" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:4" ht="15.75" customHeight="1">
       <c r="D91" s="1"/>
     </row>
-    <row r="92" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:4" ht="15.75" customHeight="1">
       <c r="D92" s="1"/>
     </row>
-    <row r="93" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:4" ht="15.75" customHeight="1">
       <c r="D93" s="1"/>
     </row>
-    <row r="94" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:4" ht="15.75" customHeight="1">
       <c r="D94" s="1"/>
     </row>
-    <row r="95" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:4" ht="15.75" customHeight="1">
       <c r="D95" s="1"/>
     </row>
-    <row r="96" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:4" ht="15.75" customHeight="1">
       <c r="D96" s="1"/>
     </row>
-    <row r="97" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:4" ht="15.75" customHeight="1">
       <c r="D97" s="1"/>
     </row>
-    <row r="98" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:4" ht="15.75" customHeight="1">
       <c r="D98" s="1"/>
     </row>
-    <row r="99" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:4" ht="15.75" customHeight="1">
       <c r="D99" s="1"/>
     </row>
-    <row r="100" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:4" ht="15.75" customHeight="1">
       <c r="D100" s="1"/>
     </row>
-    <row r="101" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:4" ht="15.75" customHeight="1">
       <c r="D101" s="1"/>
     </row>
-    <row r="102" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:4" ht="15.75" customHeight="1">
       <c r="D102" s="1"/>
     </row>
-    <row r="103" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:4" ht="15.75" customHeight="1">
       <c r="D103" s="1"/>
     </row>
-    <row r="104" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:4" ht="15.75" customHeight="1">
       <c r="D104" s="1"/>
     </row>
-    <row r="105" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:4" ht="15.75" customHeight="1">
       <c r="D105" s="1"/>
     </row>
-    <row r="106" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:4" ht="15.75" customHeight="1">
       <c r="D106" s="1"/>
     </row>
-    <row r="107" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:4" ht="15.75" customHeight="1">
       <c r="D107" s="1"/>
     </row>
-    <row r="108" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:4" ht="15.75" customHeight="1">
       <c r="D108" s="1"/>
     </row>
-    <row r="109" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:4" ht="15.75" customHeight="1">
       <c r="D109" s="1"/>
     </row>
-    <row r="110" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:4" ht="15.75" customHeight="1">
       <c r="D110" s="1"/>
     </row>
-    <row r="111" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:4" ht="15.75" customHeight="1">
       <c r="D111" s="1"/>
     </row>
-    <row r="112" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:4" ht="15.75" customHeight="1">
       <c r="D112" s="1"/>
     </row>
-    <row r="113" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:4" ht="15.75" customHeight="1">
       <c r="D113" s="1"/>
     </row>
-    <row r="114" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:4" ht="15.75" customHeight="1">
       <c r="D114" s="1"/>
     </row>
-    <row r="115" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:4" ht="15.75" customHeight="1">
       <c r="D115" s="1"/>
     </row>
-    <row r="116" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:4" ht="15.75" customHeight="1">
       <c r="D116" s="1"/>
     </row>
-    <row r="117" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:4" ht="15.75" customHeight="1">
       <c r="D117" s="1"/>
     </row>
-    <row r="118" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:4" ht="15.75" customHeight="1">
       <c r="D118" s="1"/>
     </row>
-    <row r="119" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:4" ht="15.75" customHeight="1">
       <c r="D119" s="1"/>
     </row>
-    <row r="120" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:4" ht="15.75" customHeight="1">
       <c r="D120" s="1"/>
     </row>
-    <row r="121" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:4" ht="15.75" customHeight="1">
       <c r="D121" s="1"/>
     </row>
-    <row r="122" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:4" ht="15.75" customHeight="1">
       <c r="D122" s="1"/>
     </row>
-    <row r="123" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:4" ht="15.75" customHeight="1">
       <c r="D123" s="1"/>
     </row>
-    <row r="124" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:4" ht="15.75" customHeight="1">
       <c r="D124" s="1"/>
     </row>
-    <row r="125" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:4" ht="15.75" customHeight="1">
       <c r="D125" s="1"/>
     </row>
-    <row r="126" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:4" ht="15.75" customHeight="1">
       <c r="D126" s="1"/>
     </row>
-    <row r="127" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:4" ht="15.75" customHeight="1">
       <c r="D127" s="1"/>
     </row>
-    <row r="128" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:4" ht="15.75" customHeight="1">
       <c r="D128" s="1"/>
     </row>
-    <row r="129" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:4" ht="15.75" customHeight="1">
       <c r="D129" s="1"/>
     </row>
-    <row r="130" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:4" ht="15.75" customHeight="1">
       <c r="D130" s="1"/>
     </row>
-    <row r="131" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:4" ht="15.75" customHeight="1">
       <c r="D131" s="1"/>
     </row>
-    <row r="132" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:4" ht="15.75" customHeight="1">
       <c r="D132" s="1"/>
     </row>
-    <row r="133" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:4" ht="15.75" customHeight="1">
       <c r="D133" s="1"/>
     </row>
-    <row r="134" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:4" ht="15.75" customHeight="1">
       <c r="D134" s="1"/>
     </row>
-    <row r="135" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:4" ht="15.75" customHeight="1">
       <c r="D135" s="1"/>
     </row>
-    <row r="136" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:4" ht="15.75" customHeight="1">
       <c r="D136" s="1"/>
     </row>
-    <row r="137" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:4" ht="15.75" customHeight="1">
       <c r="D137" s="1"/>
     </row>
-    <row r="138" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:4" ht="15.75" customHeight="1">
       <c r="D138" s="1"/>
     </row>
-    <row r="139" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:4" ht="15.75" customHeight="1">
       <c r="D139" s="1"/>
     </row>
-    <row r="140" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:4" ht="15.75" customHeight="1">
       <c r="D140" s="1"/>
     </row>
-    <row r="141" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:4" ht="15.75" customHeight="1">
       <c r="D141" s="1"/>
     </row>
-    <row r="142" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:4" ht="15.75" customHeight="1">
       <c r="D142" s="1"/>
     </row>
-    <row r="143" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:4" ht="15.75" customHeight="1">
       <c r="D143" s="1"/>
     </row>
-    <row r="144" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:4" ht="15.75" customHeight="1">
       <c r="D144" s="1"/>
     </row>
-    <row r="145" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="4:4" ht="15.75" customHeight="1">
       <c r="D145" s="1"/>
     </row>
-    <row r="146" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="4:4" ht="15.75" customHeight="1">
       <c r="D146" s="1"/>
     </row>
-    <row r="147" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="4:4" ht="15.75" customHeight="1">
       <c r="D147" s="1"/>
     </row>
-    <row r="148" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="4:4" ht="15.75" customHeight="1">
       <c r="D148" s="1"/>
     </row>
-    <row r="149" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="4:4" ht="15.75" customHeight="1">
       <c r="D149" s="1"/>
     </row>
-    <row r="150" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="4:4" ht="15.75" customHeight="1">
       <c r="D150" s="1"/>
     </row>
-    <row r="151" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="4:4" ht="15.75" customHeight="1">
       <c r="D151" s="1"/>
     </row>
-    <row r="152" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="4:4" ht="15.75" customHeight="1">
       <c r="D152" s="1"/>
     </row>
-    <row r="153" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="4:4" ht="15.75" customHeight="1">
       <c r="D153" s="1"/>
     </row>
-    <row r="154" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="4:4" ht="15.75" customHeight="1">
       <c r="D154" s="1"/>
     </row>
-    <row r="155" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="4:4" ht="15.75" customHeight="1">
       <c r="D155" s="1"/>
     </row>
-    <row r="156" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="4:4" ht="15.75" customHeight="1">
       <c r="D156" s="1"/>
     </row>
-    <row r="157" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:4" ht="15.75" customHeight="1">
       <c r="D157" s="1"/>
     </row>
-    <row r="158" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:4" ht="15.75" customHeight="1">
       <c r="D158" s="1"/>
     </row>
-    <row r="159" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:4" ht="15.75" customHeight="1">
       <c r="D159" s="1"/>
     </row>
-    <row r="160" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="4:4" ht="15.75" customHeight="1">
       <c r="D160" s="1"/>
     </row>
-    <row r="161" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:4" ht="15.75" customHeight="1">
       <c r="D161" s="1"/>
     </row>
-    <row r="162" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:4" ht="15.75" customHeight="1">
       <c r="D162" s="1"/>
     </row>
-    <row r="163" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:4" ht="15.75" customHeight="1">
       <c r="D163" s="1"/>
     </row>
-    <row r="164" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:4" ht="15.75" customHeight="1">
       <c r="D164" s="1"/>
     </row>
-    <row r="165" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:4" ht="15.75" customHeight="1">
       <c r="D165" s="1"/>
     </row>
-    <row r="166" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:4" ht="15.75" customHeight="1">
       <c r="D166" s="1"/>
     </row>
-    <row r="167" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:4" ht="15.75" customHeight="1">
       <c r="D167" s="1"/>
     </row>
-    <row r="168" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:4" ht="15.75" customHeight="1">
       <c r="D168" s="1"/>
     </row>
-    <row r="169" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:4" ht="15.75" customHeight="1">
       <c r="D169" s="1"/>
     </row>
-    <row r="170" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:4" ht="15.75" customHeight="1">
       <c r="D170" s="1"/>
     </row>
-    <row r="171" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:4" ht="15.75" customHeight="1">
       <c r="D171" s="1"/>
     </row>
-    <row r="172" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:4" ht="15.75" customHeight="1">
       <c r="D172" s="1"/>
     </row>
-    <row r="173" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:4" ht="15.75" customHeight="1">
       <c r="D173" s="1"/>
     </row>
-    <row r="174" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:4" ht="15.75" customHeight="1">
       <c r="D174" s="1"/>
     </row>
-    <row r="175" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:4" ht="15.75" customHeight="1">
       <c r="D175" s="1"/>
     </row>
-    <row r="176" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:4" ht="15.75" customHeight="1">
       <c r="D176" s="1"/>
     </row>
-    <row r="177" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:4" ht="15.75" customHeight="1">
       <c r="D177" s="1"/>
     </row>
-    <row r="178" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:4" ht="15.75" customHeight="1">
       <c r="D178" s="1"/>
     </row>
-    <row r="179" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:4" ht="15.75" customHeight="1">
       <c r="D179" s="1"/>
     </row>
-    <row r="180" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:4" ht="15.75" customHeight="1">
       <c r="D180" s="1"/>
     </row>
-    <row r="181" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:4" ht="15.75" customHeight="1">
       <c r="D181" s="1"/>
     </row>
-    <row r="182" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:4" ht="15.75" customHeight="1">
       <c r="D182" s="1"/>
     </row>
-    <row r="183" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:4" ht="15.75" customHeight="1">
       <c r="D183" s="1"/>
     </row>
-    <row r="184" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:4" ht="15.75" customHeight="1">
       <c r="D184" s="1"/>
     </row>
-    <row r="185" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:4" ht="15.75" customHeight="1">
       <c r="D185" s="1"/>
     </row>
-    <row r="186" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:4" ht="15.75" customHeight="1">
       <c r="D186" s="1"/>
     </row>
-    <row r="187" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:4" ht="15.75" customHeight="1">
       <c r="D187" s="1"/>
     </row>
-    <row r="188" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:4" ht="15.75" customHeight="1">
       <c r="D188" s="1"/>
     </row>
-    <row r="189" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:4" ht="15.75" customHeight="1">
       <c r="D189" s="1"/>
     </row>
-    <row r="190" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:4" ht="15.75" customHeight="1">
       <c r="D190" s="1"/>
     </row>
-    <row r="191" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:4" ht="15.75" customHeight="1">
       <c r="D191" s="1"/>
     </row>
-    <row r="192" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:4" ht="15.75" customHeight="1">
       <c r="D192" s="1"/>
     </row>
-    <row r="193" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:4" ht="15.75" customHeight="1">
       <c r="D193" s="1"/>
     </row>
-    <row r="194" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:4" ht="15.75" customHeight="1">
       <c r="D194" s="1"/>
     </row>
-    <row r="195" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:4" ht="15.75" customHeight="1">
       <c r="D195" s="1"/>
     </row>
-    <row r="196" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:4" ht="15.75" customHeight="1">
       <c r="D196" s="1"/>
     </row>
-    <row r="197" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:4" ht="15.75" customHeight="1">
       <c r="D197" s="1"/>
     </row>
-    <row r="198" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:4" ht="15.75" customHeight="1">
       <c r="D198" s="1"/>
     </row>
-    <row r="199" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:4" ht="15.75" customHeight="1">
       <c r="D199" s="1"/>
     </row>
-    <row r="200" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="4:4" ht="15.75" customHeight="1">
       <c r="D200" s="1"/>
     </row>
-    <row r="201" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="4:4" ht="15.75" customHeight="1">
       <c r="D201" s="1"/>
     </row>
-    <row r="202" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:4" ht="15.75" customHeight="1">
       <c r="D202" s="1"/>
     </row>
-    <row r="203" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:4" ht="15.75" customHeight="1">
       <c r="D203" s="1"/>
     </row>
-    <row r="204" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:4" ht="15.75" customHeight="1">
       <c r="D204" s="1"/>
     </row>
-    <row r="205" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:4" ht="15.75" customHeight="1">
       <c r="D205" s="1"/>
     </row>
-    <row r="206" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:4" ht="15.75" customHeight="1">
       <c r="D206" s="1"/>
     </row>
-    <row r="207" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:4" ht="15.75" customHeight="1">
       <c r="D207" s="1"/>
     </row>
-    <row r="208" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:4" ht="15.75" customHeight="1">
       <c r="D208" s="1"/>
     </row>
-    <row r="209" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="4:4" ht="15.75" customHeight="1">
       <c r="D209" s="1"/>
     </row>
-    <row r="210" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="4:4" ht="15.75" customHeight="1">
       <c r="D210" s="1"/>
     </row>
-    <row r="211" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:4" ht="15.75" customHeight="1">
       <c r="D211" s="1"/>
     </row>
-    <row r="212" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:4" ht="15.75" customHeight="1">
       <c r="D212" s="1"/>
     </row>
-    <row r="213" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:4" ht="15.75" customHeight="1">
       <c r="D213" s="1"/>
     </row>
-    <row r="214" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:4" ht="15.75" customHeight="1">
       <c r="D214" s="1"/>
     </row>
-    <row r="215" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:4" ht="15.75" customHeight="1">
       <c r="D215" s="1"/>
     </row>
-    <row r="216" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:4" ht="15.75" customHeight="1">
       <c r="D216" s="1"/>
     </row>
-    <row r="217" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:4" ht="15.75" customHeight="1">
       <c r="D217" s="1"/>
     </row>
-    <row r="218" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:4" ht="15.75" customHeight="1">
       <c r="D218" s="1"/>
     </row>
-    <row r="219" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:4" ht="15.75" customHeight="1">
       <c r="D219" s="1"/>
     </row>
-    <row r="220" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:4" ht="15.75" customHeight="1">
       <c r="D220" s="1"/>
     </row>
-    <row r="221" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:4" ht="15.75" customHeight="1">
       <c r="D221" s="1"/>
     </row>
-    <row r="222" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:4" ht="15.75" customHeight="1">
       <c r="D222" s="1"/>
     </row>
-    <row r="223" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:4" ht="15.75" customHeight="1">
       <c r="D223" s="1"/>
     </row>
-    <row r="224" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:4" ht="15.75" customHeight="1">
       <c r="D224" s="1"/>
     </row>
-    <row r="225" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="4:4" ht="15.75" customHeight="1">
       <c r="D225" s="1"/>
     </row>
-    <row r="226" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="4:4" ht="15.75" customHeight="1">
       <c r="D226" s="1"/>
     </row>
-    <row r="227" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:4" ht="15.75" customHeight="1">
       <c r="D227" s="1"/>
     </row>
-    <row r="228" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:4" ht="15.75" customHeight="1">
       <c r="D228" s="1"/>
     </row>
-    <row r="229" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:4" ht="15.75" customHeight="1">
       <c r="D229" s="1"/>
     </row>
-    <row r="230" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="4:4" ht="15.75" customHeight="1">
       <c r="D230" s="1"/>
     </row>
-    <row r="231" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:4" ht="15.75" customHeight="1">
       <c r="D231" s="1"/>
     </row>
-    <row r="232" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:4" ht="15.75" customHeight="1">
       <c r="D232" s="1"/>
     </row>
-    <row r="233" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:4" ht="15.75" customHeight="1">
       <c r="D233" s="1"/>
     </row>
-    <row r="234" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:4" ht="15.75" customHeight="1">
       <c r="D234" s="1"/>
     </row>
-    <row r="235" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:4" ht="15.75" customHeight="1">
       <c r="D235" s="1"/>
     </row>
-    <row r="236" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:4" ht="15.75" customHeight="1">
       <c r="D236" s="1"/>
     </row>
-    <row r="237" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:4" ht="15.75" customHeight="1">
       <c r="D237" s="1"/>
     </row>
-    <row r="238" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:4" ht="15.75" customHeight="1">
       <c r="D238" s="1"/>
     </row>
-    <row r="239" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:4" ht="15.75" customHeight="1">
       <c r="D239" s="1"/>
     </row>
-    <row r="240" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:4" ht="15.75" customHeight="1">
       <c r="D240" s="1"/>
     </row>
-    <row r="241" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:4" ht="15.75" customHeight="1">
       <c r="D241" s="1"/>
     </row>
-    <row r="242" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:4" ht="15.75" customHeight="1">
       <c r="D242" s="1"/>
     </row>
-    <row r="243" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:4" ht="15.75" customHeight="1">
       <c r="D243" s="1"/>
     </row>
-    <row r="244" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:4" ht="15.75" customHeight="1">
       <c r="D244" s="1"/>
     </row>
-    <row r="245" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:4" ht="15.75" customHeight="1">
       <c r="D245" s="1"/>
     </row>
-    <row r="246" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:4" ht="15.75" customHeight="1">
       <c r="D246" s="1"/>
     </row>
-    <row r="247" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:4" ht="15.75" customHeight="1">
       <c r="D247" s="1"/>
     </row>
-    <row r="248" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:4" ht="15.75" customHeight="1">
       <c r="D248" s="1"/>
     </row>
-    <row r="249" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:4" ht="15.75" customHeight="1">
       <c r="D249" s="1"/>
     </row>
-    <row r="250" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:4" ht="15.75" customHeight="1">
       <c r="D250" s="1"/>
     </row>
-    <row r="251" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="4:4" ht="15.75" customHeight="1">
       <c r="D251" s="1"/>
     </row>
-    <row r="252" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="4:4" ht="15.75" customHeight="1">
       <c r="D252" s="1"/>
     </row>
-    <row r="253" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:4" ht="15.75" customHeight="1">
       <c r="D253" s="1"/>
     </row>
-    <row r="254" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:4" ht="15.75" customHeight="1">
       <c r="D254" s="1"/>
     </row>
-    <row r="255" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:4" ht="15.75" customHeight="1">
       <c r="D255" s="1"/>
     </row>
-    <row r="256" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:4" ht="15.75" customHeight="1">
       <c r="D256" s="1"/>
     </row>
-    <row r="257" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:4" ht="15.75" customHeight="1">
       <c r="D257" s="1"/>
     </row>
-    <row r="258" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:4" ht="15.75" customHeight="1">
       <c r="D258" s="1"/>
     </row>
-    <row r="259" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:4" ht="15.75" customHeight="1">
       <c r="D259" s="1"/>
     </row>
-    <row r="260" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="4:4" ht="15.75" customHeight="1">
       <c r="D260" s="1"/>
     </row>
-    <row r="261" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="4:4" ht="15.75" customHeight="1">
       <c r="D261" s="1"/>
     </row>
-    <row r="262" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="4:4" ht="15.75" customHeight="1">
       <c r="D262" s="1"/>
     </row>
-    <row r="263" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:4" ht="15.75" customHeight="1">
       <c r="D263" s="1"/>
     </row>
-    <row r="264" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:4" ht="15.75" customHeight="1">
       <c r="D264" s="1"/>
     </row>
-    <row r="265" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:4" ht="15.75" customHeight="1">
       <c r="D265" s="1"/>
     </row>
-    <row r="266" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:4" ht="15.75" customHeight="1">
       <c r="D266" s="1"/>
     </row>
-    <row r="267" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:4" ht="15.75" customHeight="1">
       <c r="D267" s="1"/>
     </row>
-    <row r="268" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:4" ht="15.75" customHeight="1">
       <c r="D268" s="1"/>
     </row>
-    <row r="269" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:4" ht="15.75" customHeight="1">
       <c r="D269" s="1"/>
     </row>
-    <row r="270" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:4" ht="15.75" customHeight="1">
       <c r="D270" s="1"/>
     </row>
-    <row r="271" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="4:4" ht="15.75" customHeight="1">
       <c r="D271" s="1"/>
     </row>
-    <row r="272" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="4:4" ht="15.75" customHeight="1">
       <c r="D272" s="1"/>
     </row>
-    <row r="273" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:4" ht="15.75" customHeight="1">
       <c r="D273" s="1"/>
     </row>
-    <row r="274" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:4" ht="15.75" customHeight="1">
       <c r="D274" s="1"/>
     </row>
-    <row r="275" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:4" ht="15.75" customHeight="1">
       <c r="D275" s="1"/>
     </row>
-    <row r="276" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:4" ht="15.75" customHeight="1">
       <c r="D276" s="1"/>
     </row>
-    <row r="277" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:4" ht="15.75" customHeight="1">
       <c r="D277" s="1"/>
     </row>
-    <row r="278" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:4" ht="15.75" customHeight="1">
       <c r="D278" s="1"/>
     </row>
-    <row r="279" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:4" ht="15.75" customHeight="1">
       <c r="D279" s="1"/>
     </row>
-    <row r="280" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="4:4" ht="15.75" customHeight="1">
       <c r="D280" s="1"/>
     </row>
-    <row r="281" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="4:4" ht="15.75" customHeight="1">
       <c r="D281" s="1"/>
     </row>
-    <row r="282" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:4" ht="15.75" customHeight="1">
       <c r="D282" s="1"/>
     </row>
-    <row r="283" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:4" ht="15.75" customHeight="1">
       <c r="D283" s="1"/>
     </row>
-    <row r="284" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:4" ht="15.75" customHeight="1">
       <c r="D284" s="1"/>
     </row>
-    <row r="285" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:4" ht="15.75" customHeight="1">
       <c r="D285" s="1"/>
     </row>
-    <row r="286" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:4" ht="15.75" customHeight="1">
       <c r="D286" s="1"/>
     </row>
-    <row r="287" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:4" ht="15.75" customHeight="1">
       <c r="D287" s="1"/>
     </row>
-    <row r="288" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:4" ht="15.75" customHeight="1">
       <c r="D288" s="1"/>
     </row>
-    <row r="289" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="4:4" ht="15.75" customHeight="1">
       <c r="D289" s="1"/>
     </row>
-    <row r="290" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="4:4" ht="15.75" customHeight="1">
       <c r="D290" s="1"/>
     </row>
-    <row r="291" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:4" ht="15.75" customHeight="1">
       <c r="D291" s="1"/>
     </row>
-    <row r="292" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:4" ht="15.75" customHeight="1">
       <c r="D292" s="1"/>
     </row>
-    <row r="293" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:4" ht="15.75" customHeight="1">
       <c r="D293" s="1"/>
     </row>
-    <row r="294" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:4" ht="15.75" customHeight="1">
       <c r="D294" s="1"/>
     </row>
-    <row r="295" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:4" ht="15.75" customHeight="1">
       <c r="D295" s="1"/>
     </row>
-    <row r="296" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:4" ht="15.75" customHeight="1">
       <c r="D296" s="1"/>
     </row>
-    <row r="297" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:4" ht="15.75" customHeight="1">
       <c r="D297" s="1"/>
     </row>
-    <row r="298" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="4:4" ht="15.75" customHeight="1">
       <c r="D298" s="1"/>
     </row>
-    <row r="299" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="4:4" ht="15.75" customHeight="1">
       <c r="D299" s="1"/>
     </row>
-    <row r="300" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="4:4" ht="15.75" customHeight="1">
       <c r="D300" s="1"/>
     </row>
-    <row r="301" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="4:4" ht="15.75" customHeight="1">
       <c r="D301" s="1"/>
     </row>
-    <row r="302" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="4:4" ht="15.75" customHeight="1">
       <c r="D302" s="1"/>
     </row>
-    <row r="303" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="4:4" ht="15.75" customHeight="1">
       <c r="D303" s="1"/>
     </row>
-    <row r="304" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="4:4" ht="15.75" customHeight="1">
       <c r="D304" s="1"/>
     </row>
-    <row r="305" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="4:4" ht="15.75" customHeight="1">
       <c r="D305" s="1"/>
     </row>
-    <row r="306" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="4:4" ht="15.75" customHeight="1">
       <c r="D306" s="1"/>
     </row>
-    <row r="307" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="4:4" ht="15.75" customHeight="1">
       <c r="D307" s="1"/>
     </row>
-    <row r="308" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="4:4" ht="15.75" customHeight="1">
       <c r="D308" s="1"/>
     </row>
-    <row r="309" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="4:4" ht="15.75" customHeight="1">
       <c r="D309" s="1"/>
     </row>
-    <row r="310" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="4:4" ht="15.75" customHeight="1">
       <c r="D310" s="1"/>
     </row>
-    <row r="311" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="4:4" ht="15.75" customHeight="1">
       <c r="D311" s="1"/>
     </row>
-    <row r="312" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="4:4" ht="15.75" customHeight="1">
       <c r="D312" s="1"/>
     </row>
-    <row r="313" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="4:4" ht="15.75" customHeight="1">
       <c r="D313" s="1"/>
     </row>
-    <row r="314" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="4:4" ht="15.75" customHeight="1">
       <c r="D314" s="1"/>
     </row>
-    <row r="315" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="4:4" ht="15.75" customHeight="1">
       <c r="D315" s="1"/>
     </row>
-    <row r="316" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="4:4" ht="15.75" customHeight="1">
       <c r="D316" s="1"/>
     </row>
-    <row r="317" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="4:4" ht="15.75" customHeight="1">
       <c r="D317" s="1"/>
     </row>
-    <row r="318" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="4:4" ht="15.75" customHeight="1">
       <c r="D318" s="1"/>
     </row>
-    <row r="319" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="4:4" ht="15.75" customHeight="1">
       <c r="D319" s="1"/>
     </row>
-    <row r="320" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="4:4" ht="15.75" customHeight="1">
       <c r="D320" s="1"/>
     </row>
-    <row r="321" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="4:4" ht="15.75" customHeight="1">
       <c r="D321" s="1"/>
     </row>
-    <row r="322" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="4:4" ht="15.75" customHeight="1">
       <c r="D322" s="1"/>
     </row>
-    <row r="323" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="4:4" ht="15.75" customHeight="1">
       <c r="D323" s="1"/>
     </row>
-    <row r="324" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="4:4" ht="15.75" customHeight="1">
       <c r="D324" s="1"/>
     </row>
-    <row r="325" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="4:4" ht="15.75" customHeight="1">
       <c r="D325" s="1"/>
     </row>
-    <row r="326" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="4:4" ht="15.75" customHeight="1">
       <c r="D326" s="1"/>
     </row>
-    <row r="327" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="4:4" ht="15.75" customHeight="1">
       <c r="D327" s="1"/>
     </row>
-    <row r="328" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="4:4" ht="15.75" customHeight="1">
       <c r="D328" s="1"/>
     </row>
-    <row r="329" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="4:4" ht="15.75" customHeight="1">
       <c r="D329" s="1"/>
     </row>
-    <row r="330" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="4:4" ht="15.75" customHeight="1">
       <c r="D330" s="1"/>
     </row>
-    <row r="331" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="4:4" ht="15.75" customHeight="1">
       <c r="D331" s="1"/>
     </row>
-    <row r="332" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="4:4" ht="15.75" customHeight="1">
       <c r="D332" s="1"/>
     </row>
-    <row r="333" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="4:4" ht="15.75" customHeight="1">
       <c r="D333" s="1"/>
     </row>
-    <row r="334" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="4:4" ht="15.75" customHeight="1">
       <c r="D334" s="1"/>
     </row>
-    <row r="335" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="4:4" ht="15.75" customHeight="1">
       <c r="D335" s="1"/>
     </row>
-    <row r="336" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="4:4" ht="15.75" customHeight="1">
       <c r="D336" s="1"/>
     </row>
-    <row r="337" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="4:4" ht="15.75" customHeight="1">
       <c r="D337" s="1"/>
     </row>
-    <row r="338" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="4:4" ht="15.75" customHeight="1">
       <c r="D338" s="1"/>
     </row>
-    <row r="339" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="4:4" ht="15.75" customHeight="1">
       <c r="D339" s="1"/>
     </row>
-    <row r="340" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="4:4" ht="15.75" customHeight="1">
       <c r="D340" s="1"/>
     </row>
-    <row r="341" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="4:4" ht="15.75" customHeight="1">
       <c r="D341" s="1"/>
     </row>
-    <row r="342" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="4:4" ht="15.75" customHeight="1">
       <c r="D342" s="1"/>
     </row>
-    <row r="343" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="4:4" ht="15.75" customHeight="1">
       <c r="D343" s="1"/>
     </row>
-    <row r="344" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="4:4" ht="15.75" customHeight="1">
       <c r="D344" s="1"/>
     </row>
-    <row r="345" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="4:4" ht="15.75" customHeight="1">
       <c r="D345" s="1"/>
     </row>
-    <row r="346" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="4:4" ht="15.75" customHeight="1">
       <c r="D346" s="1"/>
     </row>
-    <row r="347" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="4:4" ht="15.75" customHeight="1">
       <c r="D347" s="1"/>
     </row>
-    <row r="348" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="4:4" ht="15.75" customHeight="1">
       <c r="D348" s="1"/>
     </row>
-    <row r="349" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="4:4" ht="15.75" customHeight="1">
       <c r="D349" s="1"/>
     </row>
-    <row r="350" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="4:4" ht="15.75" customHeight="1">
       <c r="D350" s="1"/>
     </row>
-    <row r="351" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="4:4" ht="15.75" customHeight="1">
       <c r="D351" s="1"/>
     </row>
-    <row r="352" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="4:4" ht="15.75" customHeight="1">
       <c r="D352" s="1"/>
     </row>
-    <row r="353" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="4:4" ht="15.75" customHeight="1">
       <c r="D353" s="1"/>
     </row>
-    <row r="354" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="4:4" ht="15.75" customHeight="1">
       <c r="D354" s="1"/>
     </row>
-    <row r="355" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="4:4" ht="15.75" customHeight="1">
       <c r="D355" s="1"/>
     </row>
-    <row r="356" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="4:4" ht="15.75" customHeight="1">
       <c r="D356" s="1"/>
     </row>
-    <row r="357" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="4:4" ht="15.75" customHeight="1">
       <c r="D357" s="1"/>
     </row>
-    <row r="358" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="4:4" ht="15.75" customHeight="1">
       <c r="D358" s="1"/>
     </row>
-    <row r="359" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="4:4" ht="15.75" customHeight="1">
       <c r="D359" s="1"/>
     </row>
-    <row r="360" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="4:4" ht="15.75" customHeight="1">
       <c r="D360" s="1"/>
     </row>
-    <row r="361" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="4:4" ht="15.75" customHeight="1">
       <c r="D361" s="1"/>
     </row>
-    <row r="362" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="4:4" ht="15.75" customHeight="1">
       <c r="D362" s="1"/>
     </row>
-    <row r="363" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="4:4" ht="15.75" customHeight="1">
       <c r="D363" s="1"/>
     </row>
-    <row r="364" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="4:4" ht="15.75" customHeight="1">
       <c r="D364" s="1"/>
     </row>
-    <row r="365" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="4:4" ht="15.75" customHeight="1">
       <c r="D365" s="1"/>
     </row>
-    <row r="366" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="4:4" ht="15.75" customHeight="1">
       <c r="D366" s="1"/>
     </row>
-    <row r="367" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="4:4" ht="15.75" customHeight="1">
       <c r="D367" s="1"/>
     </row>
-    <row r="368" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="4:4" ht="15.75" customHeight="1">
       <c r="D368" s="1"/>
     </row>
-    <row r="369" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="4:4" ht="15.75" customHeight="1">
       <c r="D369" s="1"/>
     </row>
-    <row r="370" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="4:4" ht="15.75" customHeight="1">
       <c r="D370" s="1"/>
     </row>
-    <row r="371" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="4:4" ht="15.75" customHeight="1">
       <c r="D371" s="1"/>
     </row>
-    <row r="372" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="4:4" ht="15.75" customHeight="1">
       <c r="D372" s="1"/>
     </row>
-    <row r="373" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="4:4" ht="15.75" customHeight="1">
       <c r="D373" s="1"/>
     </row>
-    <row r="374" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="4:4" ht="15.75" customHeight="1">
       <c r="D374" s="1"/>
     </row>
-    <row r="375" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="4:4" ht="15.75" customHeight="1">
       <c r="D375" s="1"/>
     </row>
-    <row r="376" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="4:4" ht="15.75" customHeight="1">
       <c r="D376" s="1"/>
     </row>
-    <row r="377" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="4:4" ht="15.75" customHeight="1">
       <c r="D377" s="1"/>
     </row>
-    <row r="378" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="4:4" ht="15.75" customHeight="1">
       <c r="D378" s="1"/>
     </row>
-    <row r="379" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="4:4" ht="15.75" customHeight="1">
       <c r="D379" s="1"/>
     </row>
-    <row r="380" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="4:4" ht="15.75" customHeight="1">
       <c r="D380" s="1"/>
     </row>
-    <row r="381" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="4:4" ht="15.75" customHeight="1">
       <c r="D381" s="1"/>
     </row>
-    <row r="382" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="4:4" ht="15.75" customHeight="1">
       <c r="D382" s="1"/>
     </row>
-    <row r="383" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="4:4" ht="15.75" customHeight="1">
       <c r="D383" s="1"/>
     </row>
-    <row r="384" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="4:4" ht="15.75" customHeight="1">
       <c r="D384" s="1"/>
     </row>
-    <row r="385" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="4:4" ht="15.75" customHeight="1">
       <c r="D385" s="1"/>
     </row>
-    <row r="386" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="4:4" ht="15.75" customHeight="1">
       <c r="D386" s="1"/>
     </row>
-    <row r="387" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="4:4" ht="15.75" customHeight="1">
       <c r="D387" s="1"/>
     </row>
-    <row r="388" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="4:4" ht="15.75" customHeight="1">
       <c r="D388" s="1"/>
     </row>
-    <row r="389" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="4:4" ht="15.75" customHeight="1">
       <c r="D389" s="1"/>
     </row>
-    <row r="390" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="4:4" ht="15.75" customHeight="1">
       <c r="D390" s="1"/>
     </row>
-    <row r="391" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="4:4" ht="15.75" customHeight="1">
       <c r="D391" s="1"/>
     </row>
-    <row r="392" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="4:4" ht="15.75" customHeight="1">
       <c r="D392" s="1"/>
     </row>
-    <row r="393" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="4:4" ht="15.75" customHeight="1">
       <c r="D393" s="1"/>
     </row>
-    <row r="394" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="4:4" ht="15.75" customHeight="1">
       <c r="D394" s="1"/>
     </row>
-    <row r="395" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="4:4" ht="15.75" customHeight="1">
       <c r="D395" s="1"/>
     </row>
-    <row r="396" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="4:4" ht="15.75" customHeight="1">
       <c r="D396" s="1"/>
     </row>
-    <row r="397" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="4:4" ht="15.75" customHeight="1">
       <c r="D397" s="1"/>
     </row>
-    <row r="398" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="4:4" ht="15.75" customHeight="1">
       <c r="D398" s="1"/>
     </row>
-    <row r="399" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="4:4" ht="15.75" customHeight="1">
       <c r="D399" s="1"/>
     </row>
-    <row r="400" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="4:4" ht="15.75" customHeight="1">
       <c r="D400" s="1"/>
     </row>
-    <row r="401" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="4:4" ht="15.75" customHeight="1">
       <c r="D401" s="1"/>
     </row>
-    <row r="402" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="4:4" ht="15.75" customHeight="1">
       <c r="D402" s="1"/>
     </row>
-    <row r="403" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="4:4" ht="15.75" customHeight="1">
       <c r="D403" s="1"/>
     </row>
-    <row r="404" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="4:4" ht="15.75" customHeight="1">
       <c r="D404" s="1"/>
     </row>
-    <row r="405" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="4:4" ht="15.75" customHeight="1">
       <c r="D405" s="1"/>
     </row>
-    <row r="406" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="4:4" ht="15.75" customHeight="1">
       <c r="D406" s="1"/>
     </row>
-    <row r="407" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="4:4" ht="15.75" customHeight="1">
       <c r="D407" s="1"/>
     </row>
-    <row r="408" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="4:4" ht="15.75" customHeight="1">
       <c r="D408" s="1"/>
     </row>
-    <row r="409" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="4:4" ht="15.75" customHeight="1">
       <c r="D409" s="1"/>
     </row>
-    <row r="410" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="4:4" ht="15.75" customHeight="1">
       <c r="D410" s="1"/>
     </row>
-    <row r="411" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="4:4" ht="15.75" customHeight="1">
       <c r="D411" s="1"/>
     </row>
-    <row r="412" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="4:4" ht="15.75" customHeight="1">
       <c r="D412" s="1"/>
     </row>
-    <row r="413" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="4:4" ht="15.75" customHeight="1">
       <c r="D413" s="1"/>
     </row>
-    <row r="414" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="4:4" ht="15.75" customHeight="1">
       <c r="D414" s="1"/>
     </row>
-    <row r="415" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="4:4" ht="15.75" customHeight="1">
       <c r="D415" s="1"/>
     </row>
-    <row r="416" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="4:4" ht="15.75" customHeight="1">
       <c r="D416" s="1"/>
     </row>
-    <row r="417" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="4:4" ht="15.75" customHeight="1">
       <c r="D417" s="1"/>
     </row>
-    <row r="418" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="4:4" ht="15.75" customHeight="1">
       <c r="D418" s="1"/>
     </row>
-    <row r="419" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="4:4" ht="15.75" customHeight="1">
       <c r="D419" s="1"/>
     </row>
-    <row r="420" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="4:4" ht="15.75" customHeight="1">
       <c r="D420" s="1"/>
     </row>
-    <row r="421" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="4:4" ht="15.75" customHeight="1">
       <c r="D421" s="1"/>
     </row>
-    <row r="422" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="4:4" ht="15.75" customHeight="1">
       <c r="D422" s="1"/>
     </row>
-    <row r="423" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="4:4" ht="15.75" customHeight="1">
       <c r="D423" s="1"/>
     </row>
-    <row r="424" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="4:4" ht="15.75" customHeight="1">
       <c r="D424" s="1"/>
     </row>
-    <row r="425" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="4:4" ht="15.75" customHeight="1">
       <c r="D425" s="1"/>
     </row>
-    <row r="426" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="4:4" ht="15.75" customHeight="1">
       <c r="D426" s="1"/>
     </row>
-    <row r="427" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="4:4" ht="15.75" customHeight="1">
       <c r="D427" s="1"/>
     </row>
-    <row r="428" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="4:4" ht="15.75" customHeight="1">
       <c r="D428" s="1"/>
     </row>
-    <row r="429" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="4:4" ht="15.75" customHeight="1">
       <c r="D429" s="1"/>
     </row>
-    <row r="430" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="4:4" ht="15.75" customHeight="1">
       <c r="D430" s="1"/>
     </row>
-    <row r="431" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="4:4" ht="15.75" customHeight="1">
       <c r="D431" s="1"/>
     </row>
-    <row r="432" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="4:4" ht="15.75" customHeight="1">
       <c r="D432" s="1"/>
     </row>
-    <row r="433" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="4:4" ht="15.75" customHeight="1">
       <c r="D433" s="1"/>
     </row>
-    <row r="434" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="4:4" ht="15.75" customHeight="1">
       <c r="D434" s="1"/>
     </row>
-    <row r="435" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="4:4" ht="15.75" customHeight="1">
       <c r="D435" s="1"/>
     </row>
-    <row r="436" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="4:4" ht="15.75" customHeight="1">
       <c r="D436" s="1"/>
     </row>
-    <row r="437" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="4:4" ht="15.75" customHeight="1">
       <c r="D437" s="1"/>
     </row>
-    <row r="438" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="4:4" ht="15.75" customHeight="1">
       <c r="D438" s="1"/>
     </row>
-    <row r="439" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="4:4" ht="15.75" customHeight="1">
       <c r="D439" s="1"/>
     </row>
-    <row r="440" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="4:4" ht="15.75" customHeight="1">
       <c r="D440" s="1"/>
     </row>
-    <row r="441" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="4:4" ht="15.75" customHeight="1">
       <c r="D441" s="1"/>
     </row>
-    <row r="442" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="4:4" ht="15.75" customHeight="1">
       <c r="D442" s="1"/>
     </row>
-    <row r="443" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="4:4" ht="15.75" customHeight="1">
       <c r="D443" s="1"/>
     </row>
-    <row r="444" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="4:4" ht="15.75" customHeight="1">
       <c r="D444" s="1"/>
     </row>
-    <row r="445" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="4:4" ht="15.75" customHeight="1">
       <c r="D445" s="1"/>
     </row>
-    <row r="446" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="4:4" ht="15.75" customHeight="1">
       <c r="D446" s="1"/>
     </row>
-    <row r="447" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="4:4" ht="15.75" customHeight="1">
       <c r="D447" s="1"/>
     </row>
-    <row r="448" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="4:4" ht="15.75" customHeight="1">
       <c r="D448" s="1"/>
     </row>
-    <row r="449" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="4:4" ht="15.75" customHeight="1">
       <c r="D449" s="1"/>
     </row>
-    <row r="450" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="4:4" ht="15.75" customHeight="1">
       <c r="D450" s="1"/>
     </row>
-    <row r="451" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="4:4" ht="15.75" customHeight="1">
       <c r="D451" s="1"/>
     </row>
-    <row r="452" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="4:4" ht="15.75" customHeight="1">
       <c r="D452" s="1"/>
     </row>
-    <row r="453" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="4:4" ht="15.75" customHeight="1">
       <c r="D453" s="1"/>
     </row>
-    <row r="454" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="4:4" ht="15.75" customHeight="1">
       <c r="D454" s="1"/>
     </row>
-    <row r="455" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="4:4" ht="15.75" customHeight="1">
       <c r="D455" s="1"/>
     </row>
-    <row r="456" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="4:4" ht="15.75" customHeight="1">
       <c r="D456" s="1"/>
     </row>
-    <row r="457" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="4:4" ht="15.75" customHeight="1">
       <c r="D457" s="1"/>
     </row>
-    <row r="458" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="4:4" ht="15.75" customHeight="1">
       <c r="D458" s="1"/>
     </row>
-    <row r="459" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="4:4" ht="15.75" customHeight="1">
       <c r="D459" s="1"/>
     </row>
-    <row r="460" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="4:4" ht="15.75" customHeight="1">
       <c r="D460" s="1"/>
     </row>
-    <row r="461" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="4:4" ht="15.75" customHeight="1">
       <c r="D461" s="1"/>
     </row>
-    <row r="462" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="4:4" ht="15.75" customHeight="1">
       <c r="D462" s="1"/>
     </row>
-    <row r="463" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="4:4" ht="15.75" customHeight="1">
       <c r="D463" s="1"/>
     </row>
-    <row r="464" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="4:4" ht="15.75" customHeight="1">
       <c r="D464" s="1"/>
     </row>
-    <row r="465" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="4:4" ht="15.75" customHeight="1">
       <c r="D465" s="1"/>
     </row>
-    <row r="466" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="4:4" ht="15.75" customHeight="1">
       <c r="D466" s="1"/>
     </row>
-    <row r="467" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="4:4" ht="15.75" customHeight="1">
       <c r="D467" s="1"/>
     </row>
-    <row r="468" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="4:4" ht="15.75" customHeight="1">
       <c r="D468" s="1"/>
     </row>
-    <row r="469" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="4:4" ht="15.75" customHeight="1">
       <c r="D469" s="1"/>
     </row>
-    <row r="470" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="4:4" ht="15.75" customHeight="1">
       <c r="D470" s="1"/>
     </row>
-    <row r="471" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="4:4" ht="15.75" customHeight="1">
       <c r="D471" s="1"/>
     </row>
-    <row r="472" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="4:4" ht="15.75" customHeight="1">
       <c r="D472" s="1"/>
     </row>
-    <row r="473" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="4:4" ht="15.75" customHeight="1">
       <c r="D473" s="1"/>
     </row>
-    <row r="474" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="4:4" ht="15.75" customHeight="1">
       <c r="D474" s="1"/>
     </row>
-    <row r="475" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="4:4" ht="15.75" customHeight="1">
       <c r="D475" s="1"/>
     </row>
-    <row r="476" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="4:4" ht="15.75" customHeight="1">
       <c r="D476" s="1"/>
     </row>
-    <row r="477" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="4:4" ht="15.75" customHeight="1">
       <c r="D477" s="1"/>
     </row>
-    <row r="478" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="4:4" ht="15.75" customHeight="1">
       <c r="D478" s="1"/>
     </row>
-    <row r="479" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="4:4" ht="15.75" customHeight="1">
       <c r="D479" s="1"/>
     </row>
-    <row r="480" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="4:4" ht="15.75" customHeight="1">
       <c r="D480" s="1"/>
     </row>
-    <row r="481" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="4:4" ht="15.75" customHeight="1">
       <c r="D481" s="1"/>
     </row>
-    <row r="482" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="4:4" ht="15.75" customHeight="1">
       <c r="D482" s="1"/>
     </row>
-    <row r="483" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="4:4" ht="15.75" customHeight="1">
       <c r="D483" s="1"/>
     </row>
-    <row r="484" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="4:4" ht="15.75" customHeight="1">
       <c r="D484" s="1"/>
     </row>
-    <row r="485" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="4:4" ht="15.75" customHeight="1">
       <c r="D485" s="1"/>
     </row>
-    <row r="486" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="4:4" ht="15.75" customHeight="1">
       <c r="D486" s="1"/>
     </row>
-    <row r="487" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="4:4" ht="15.75" customHeight="1">
       <c r="D487" s="1"/>
     </row>
-    <row r="488" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="4:4" ht="15.75" customHeight="1">
       <c r="D488" s="1"/>
     </row>
-    <row r="489" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="4:4" ht="15.75" customHeight="1">
       <c r="D489" s="1"/>
     </row>
-    <row r="490" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="4:4" ht="15.75" customHeight="1">
       <c r="D490" s="1"/>
     </row>
-    <row r="491" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="4:4" ht="15.75" customHeight="1">
       <c r="D491" s="1"/>
     </row>
-    <row r="492" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="4:4" ht="15.75" customHeight="1">
       <c r="D492" s="1"/>
     </row>
-    <row r="493" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="4:4" ht="15.75" customHeight="1">
       <c r="D493" s="1"/>
     </row>
-    <row r="494" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="4:4" ht="15.75" customHeight="1">
       <c r="D494" s="1"/>
     </row>
-    <row r="495" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="4:4" ht="15.75" customHeight="1">
       <c r="D495" s="1"/>
     </row>
-    <row r="496" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="4:4" ht="15.75" customHeight="1">
       <c r="D496" s="1"/>
     </row>
-    <row r="497" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="4:4" ht="15.75" customHeight="1">
       <c r="D497" s="1"/>
     </row>
-    <row r="498" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="4:4" ht="15.75" customHeight="1">
       <c r="D498" s="1"/>
     </row>
-    <row r="499" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="4:4" ht="15.75" customHeight="1">
       <c r="D499" s="1"/>
     </row>
-    <row r="500" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="4:4" ht="15.75" customHeight="1">
       <c r="D500" s="1"/>
     </row>
-    <row r="501" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="4:4" ht="15.75" customHeight="1">
       <c r="D501" s="1"/>
     </row>
-    <row r="502" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="4:4" ht="15.75" customHeight="1">
       <c r="D502" s="1"/>
     </row>
-    <row r="503" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="4:4" ht="15.75" customHeight="1">
       <c r="D503" s="1"/>
     </row>
-    <row r="504" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="4:4" ht="15.75" customHeight="1">
       <c r="D504" s="1"/>
     </row>
-    <row r="505" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="4:4" ht="15.75" customHeight="1">
       <c r="D505" s="1"/>
     </row>
-    <row r="506" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="4:4" ht="15.75" customHeight="1">
       <c r="D506" s="1"/>
     </row>
-    <row r="507" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="4:4" ht="15.75" customHeight="1">
       <c r="D507" s="1"/>
     </row>
-    <row r="508" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="4:4" ht="15.75" customHeight="1">
       <c r="D508" s="1"/>
     </row>
-    <row r="509" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="4:4" ht="15.75" customHeight="1">
       <c r="D509" s="1"/>
     </row>
-    <row r="510" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="4:4" ht="15.75" customHeight="1">
       <c r="D510" s="1"/>
     </row>
-    <row r="511" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="4:4" ht="15.75" customHeight="1">
       <c r="D511" s="1"/>
     </row>
-    <row r="512" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="4:4" ht="15.75" customHeight="1">
       <c r="D512" s="1"/>
     </row>
-    <row r="513" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="4:4" ht="15.75" customHeight="1">
       <c r="D513" s="1"/>
     </row>
-    <row r="514" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="4:4" ht="15.75" customHeight="1">
       <c r="D514" s="1"/>
     </row>
-    <row r="515" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="4:4" ht="15.75" customHeight="1">
       <c r="D515" s="1"/>
     </row>
-    <row r="516" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="4:4" ht="15.75" customHeight="1">
       <c r="D516" s="1"/>
     </row>
-    <row r="517" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="4:4" ht="15.75" customHeight="1">
       <c r="D517" s="1"/>
     </row>
-    <row r="518" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="4:4" ht="15.75" customHeight="1">
       <c r="D518" s="1"/>
     </row>
-    <row r="519" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="4:4" ht="15.75" customHeight="1">
       <c r="D519" s="1"/>
     </row>
-    <row r="520" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="4:4" ht="15.75" customHeight="1">
       <c r="D520" s="1"/>
     </row>
-    <row r="521" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="4:4" ht="15.75" customHeight="1">
       <c r="D521" s="1"/>
     </row>
-    <row r="522" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="4:4" ht="15.75" customHeight="1">
       <c r="D522" s="1"/>
     </row>
-    <row r="523" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="4:4" ht="15.75" customHeight="1">
       <c r="D523" s="1"/>
     </row>
-    <row r="524" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="4:4" ht="15.75" customHeight="1">
       <c r="D524" s="1"/>
     </row>
-    <row r="525" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="4:4" ht="15.75" customHeight="1">
       <c r="D525" s="1"/>
     </row>
-    <row r="526" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="4:4" ht="15.75" customHeight="1">
       <c r="D526" s="1"/>
     </row>
-    <row r="527" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="4:4" ht="15.75" customHeight="1">
       <c r="D527" s="1"/>
     </row>
-    <row r="528" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="4:4" ht="15.75" customHeight="1">
       <c r="D528" s="1"/>
     </row>
-    <row r="529" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="4:4" ht="15.75" customHeight="1">
       <c r="D529" s="1"/>
     </row>
-    <row r="530" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="4:4" ht="15.75" customHeight="1">
       <c r="D530" s="1"/>
     </row>
-    <row r="531" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="4:4" ht="15.75" customHeight="1">
       <c r="D531" s="1"/>
     </row>
-    <row r="532" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="4:4" ht="15.75" customHeight="1">
       <c r="D532" s="1"/>
     </row>
-    <row r="533" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="4:4" ht="15.75" customHeight="1">
       <c r="D533" s="1"/>
     </row>
-    <row r="534" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="4:4" ht="15.75" customHeight="1">
       <c r="D534" s="1"/>
     </row>
-    <row r="535" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="4:4" ht="15.75" customHeight="1">
       <c r="D535" s="1"/>
     </row>
-    <row r="536" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="4:4" ht="15.75" customHeight="1">
       <c r="D536" s="1"/>
     </row>
-    <row r="537" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="4:4" ht="15.75" customHeight="1">
       <c r="D537" s="1"/>
     </row>
-    <row r="538" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="4:4" ht="15.75" customHeight="1">
       <c r="D538" s="1"/>
     </row>
-    <row r="539" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="4:4" ht="15.75" customHeight="1">
       <c r="D539" s="1"/>
     </row>
-    <row r="540" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="4:4" ht="15.75" customHeight="1">
       <c r="D540" s="1"/>
     </row>
-    <row r="541" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="4:4" ht="15.75" customHeight="1">
       <c r="D541" s="1"/>
     </row>
-    <row r="542" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="4:4" ht="15.75" customHeight="1">
       <c r="D542" s="1"/>
     </row>
-    <row r="543" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="4:4" ht="15.75" customHeight="1">
       <c r="D543" s="1"/>
     </row>
-    <row r="544" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="4:4" ht="15.75" customHeight="1">
       <c r="D544" s="1"/>
     </row>
-    <row r="545" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="4:4" ht="15.75" customHeight="1">
       <c r="D545" s="1"/>
     </row>
-    <row r="546" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="4:4" ht="15.75" customHeight="1">
       <c r="D546" s="1"/>
     </row>
-    <row r="547" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="4:4" ht="15.75" customHeight="1">
       <c r="D547" s="1"/>
     </row>
-    <row r="548" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="4:4" ht="15.75" customHeight="1">
       <c r="D548" s="1"/>
     </row>
-    <row r="549" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="4:4" ht="15.75" customHeight="1">
       <c r="D549" s="1"/>
     </row>
-    <row r="550" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="4:4" ht="15.75" customHeight="1">
       <c r="D550" s="1"/>
     </row>
-    <row r="551" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="4:4" ht="15.75" customHeight="1">
       <c r="D551" s="1"/>
     </row>
-    <row r="552" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="4:4" ht="15.75" customHeight="1">
       <c r="D552" s="1"/>
     </row>
-    <row r="553" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="4:4" ht="15.75" customHeight="1">
       <c r="D553" s="1"/>
     </row>
-    <row r="554" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="4:4" ht="15.75" customHeight="1">
       <c r="D554" s="1"/>
     </row>
-    <row r="555" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="4:4" ht="15.75" customHeight="1">
       <c r="D555" s="1"/>
     </row>
-    <row r="556" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="4:4" ht="15.75" customHeight="1">
       <c r="D556" s="1"/>
     </row>
-    <row r="557" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="4:4" ht="15.75" customHeight="1">
       <c r="D557" s="1"/>
     </row>
-    <row r="558" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="4:4" ht="15.75" customHeight="1">
       <c r="D558" s="1"/>
     </row>
-    <row r="559" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="4:4" ht="15.75" customHeight="1">
       <c r="D559" s="1"/>
     </row>
-    <row r="560" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="4:4" ht="15.75" customHeight="1">
       <c r="D560" s="1"/>
     </row>
-    <row r="561" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="4:4" ht="15.75" customHeight="1">
       <c r="D561" s="1"/>
     </row>
-    <row r="562" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="4:4" ht="15.75" customHeight="1">
       <c r="D562" s="1"/>
     </row>
-    <row r="563" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="4:4" ht="15.75" customHeight="1">
       <c r="D563" s="1"/>
     </row>
-    <row r="564" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="4:4" ht="15.75" customHeight="1">
       <c r="D564" s="1"/>
     </row>
-    <row r="565" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="4:4" ht="15.75" customHeight="1">
       <c r="D565" s="1"/>
     </row>
-    <row r="566" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="4:4" ht="15.75" customHeight="1">
       <c r="D566" s="1"/>
     </row>
-    <row r="567" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="4:4" ht="15.75" customHeight="1">
       <c r="D567" s="1"/>
     </row>
-    <row r="568" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="4:4" ht="15.75" customHeight="1">
       <c r="D568" s="1"/>
     </row>
-    <row r="569" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="4:4" ht="15.75" customHeight="1">
       <c r="D569" s="1"/>
     </row>
-    <row r="570" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="4:4" ht="15.75" customHeight="1">
       <c r="D570" s="1"/>
     </row>
-    <row r="571" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="4:4" ht="15.75" customHeight="1">
       <c r="D571" s="1"/>
     </row>
-    <row r="572" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="4:4" ht="15.75" customHeight="1">
       <c r="D572" s="1"/>
     </row>
-    <row r="573" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="4:4" ht="15.75" customHeight="1">
       <c r="D573" s="1"/>
     </row>
-    <row r="574" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="4:4" ht="15.75" customHeight="1">
       <c r="D574" s="1"/>
     </row>
-    <row r="575" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="4:4" ht="15.75" customHeight="1">
       <c r="D575" s="1"/>
     </row>
-    <row r="576" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="4:4" ht="15.75" customHeight="1">
       <c r="D576" s="1"/>
     </row>
-    <row r="577" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="4:4" ht="15.75" customHeight="1">
       <c r="D577" s="1"/>
     </row>
-    <row r="578" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="4:4" ht="15.75" customHeight="1">
       <c r="D578" s="1"/>
     </row>
-    <row r="579" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="4:4" ht="15.75" customHeight="1">
       <c r="D579" s="1"/>
     </row>
-    <row r="580" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="4:4" ht="15.75" customHeight="1">
       <c r="D580" s="1"/>
     </row>
-    <row r="581" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="4:4" ht="15.75" customHeight="1">
       <c r="D581" s="1"/>
     </row>
-    <row r="582" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="4:4" ht="15.75" customHeight="1">
       <c r="D582" s="1"/>
     </row>
-    <row r="583" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="4:4" ht="15.75" customHeight="1">
       <c r="D583" s="1"/>
     </row>
-    <row r="584" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="4:4" ht="15.75" customHeight="1">
       <c r="D584" s="1"/>
     </row>
-    <row r="585" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="4:4" ht="15.75" customHeight="1">
       <c r="D585" s="1"/>
     </row>
-    <row r="586" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="4:4" ht="15.75" customHeight="1">
       <c r="D586" s="1"/>
     </row>
-    <row r="587" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="4:4" ht="15.75" customHeight="1">
       <c r="D587" s="1"/>
     </row>
-    <row r="588" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="4:4" ht="15.75" customHeight="1">
       <c r="D588" s="1"/>
     </row>
-    <row r="589" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="4:4" ht="15.75" customHeight="1">
       <c r="D589" s="1"/>
     </row>
-    <row r="590" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="4:4" ht="15.75" customHeight="1">
       <c r="D590" s="1"/>
     </row>
-    <row r="591" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="4:4" ht="15.75" customHeight="1">
       <c r="D591" s="1"/>
     </row>
-    <row r="592" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="4:4" ht="15.75" customHeight="1">
       <c r="D592" s="1"/>
     </row>
-    <row r="593" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="4:4" ht="15.75" customHeight="1">
       <c r="D593" s="1"/>
     </row>
-    <row r="594" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="4:4" ht="15.75" customHeight="1">
       <c r="D594" s="1"/>
     </row>
-    <row r="595" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="4:4" ht="15.75" customHeight="1">
       <c r="D595" s="1"/>
     </row>
-    <row r="596" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="4:4" ht="15.75" customHeight="1">
       <c r="D596" s="1"/>
     </row>
-    <row r="597" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="4:4" ht="15.75" customHeight="1">
       <c r="D597" s="1"/>
     </row>
-    <row r="598" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="4:4" ht="15.75" customHeight="1">
       <c r="D598" s="1"/>
     </row>
-    <row r="599" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="4:4" ht="15.75" customHeight="1">
       <c r="D599" s="1"/>
     </row>
-    <row r="600" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="4:4" ht="15.75" customHeight="1">
       <c r="D600" s="1"/>
     </row>
-    <row r="601" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="4:4" ht="15.75" customHeight="1">
       <c r="D601" s="1"/>
     </row>
-    <row r="602" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="4:4" ht="15.75" customHeight="1">
       <c r="D602" s="1"/>
     </row>
-    <row r="603" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="4:4" ht="15.75" customHeight="1">
       <c r="D603" s="1"/>
     </row>
-    <row r="604" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="4:4" ht="15.75" customHeight="1">
       <c r="D604" s="1"/>
     </row>
-    <row r="605" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="4:4" ht="15.75" customHeight="1">
       <c r="D605" s="1"/>
     </row>
-    <row r="606" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="4:4" ht="15.75" customHeight="1">
       <c r="D606" s="1"/>
     </row>
-    <row r="607" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="4:4" ht="15.75" customHeight="1">
       <c r="D607" s="1"/>
     </row>
-    <row r="608" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="4:4" ht="15.75" customHeight="1">
       <c r="D608" s="1"/>
     </row>
-    <row r="609" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="4:4" ht="15.75" customHeight="1">
       <c r="D609" s="1"/>
     </row>
-    <row r="610" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="4:4" ht="15.75" customHeight="1">
       <c r="D610" s="1"/>
     </row>
-    <row r="611" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="4:4" ht="15.75" customHeight="1">
       <c r="D611" s="1"/>
     </row>
-    <row r="612" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="4:4" ht="15.75" customHeight="1">
       <c r="D612" s="1"/>
     </row>
-    <row r="613" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="4:4" ht="15.75" customHeight="1">
       <c r="D613" s="1"/>
     </row>
-    <row r="614" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="4:4" ht="15.75" customHeight="1">
       <c r="D614" s="1"/>
     </row>
-    <row r="615" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="4:4" ht="15.75" customHeight="1">
       <c r="D615" s="1"/>
     </row>
-    <row r="616" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="4:4" ht="15.75" customHeight="1">
       <c r="D616" s="1"/>
     </row>
-    <row r="617" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="4:4" ht="15.75" customHeight="1">
       <c r="D617" s="1"/>
     </row>
-    <row r="618" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="4:4" ht="15.75" customHeight="1">
       <c r="D618" s="1"/>
     </row>
-    <row r="619" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="4:4" ht="15.75" customHeight="1">
       <c r="D619" s="1"/>
     </row>
-    <row r="620" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="4:4" ht="15.75" customHeight="1">
       <c r="D620" s="1"/>
     </row>
-    <row r="621" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="4:4" ht="15.75" customHeight="1">
       <c r="D621" s="1"/>
     </row>
-    <row r="622" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="4:4" ht="15.75" customHeight="1">
       <c r="D622" s="1"/>
     </row>
-    <row r="623" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="4:4" ht="15.75" customHeight="1">
       <c r="D623" s="1"/>
     </row>
-    <row r="624" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="4:4" ht="15.75" customHeight="1">
       <c r="D624" s="1"/>
     </row>
-    <row r="625" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="4:4" ht="15.75" customHeight="1">
       <c r="D625" s="1"/>
     </row>
-    <row r="626" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="4:4" ht="15.75" customHeight="1">
       <c r="D626" s="1"/>
     </row>
-    <row r="627" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="4:4" ht="15.75" customHeight="1">
       <c r="D627" s="1"/>
     </row>
-    <row r="628" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="4:4" ht="15.75" customHeight="1">
       <c r="D628" s="1"/>
     </row>
-    <row r="629" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="4:4" ht="15.75" customHeight="1">
       <c r="D629" s="1"/>
     </row>
-    <row r="630" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="4:4" ht="15.75" customHeight="1">
       <c r="D630" s="1"/>
     </row>
-    <row r="631" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="4:4" ht="15.75" customHeight="1">
       <c r="D631" s="1"/>
     </row>
-    <row r="632" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="4:4" ht="15.75" customHeight="1">
       <c r="D632" s="1"/>
     </row>
-    <row r="633" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="4:4" ht="15.75" customHeight="1">
       <c r="D633" s="1"/>
     </row>
-    <row r="634" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="4:4" ht="15.75" customHeight="1">
       <c r="D634" s="1"/>
     </row>
-    <row r="635" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="4:4" ht="15.75" customHeight="1">
       <c r="D635" s="1"/>
     </row>
-    <row r="636" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="4:4" ht="15.75" customHeight="1">
       <c r="D636" s="1"/>
     </row>
-    <row r="637" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="4:4" ht="15.75" customHeight="1">
       <c r="D637" s="1"/>
     </row>
-    <row r="638" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="4:4" ht="15.75" customHeight="1">
       <c r="D638" s="1"/>
     </row>
-    <row r="639" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="4:4" ht="15.75" customHeight="1">
       <c r="D639" s="1"/>
     </row>
-    <row r="640" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="4:4" ht="15.75" customHeight="1">
       <c r="D640" s="1"/>
     </row>
-    <row r="641" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="4:4" ht="15.75" customHeight="1">
       <c r="D641" s="1"/>
     </row>
-    <row r="642" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="4:4" ht="15.75" customHeight="1">
       <c r="D642" s="1"/>
     </row>
-    <row r="643" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="4:4" ht="15.75" customHeight="1">
       <c r="D643" s="1"/>
     </row>
-    <row r="644" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="4:4" ht="15.75" customHeight="1">
       <c r="D644" s="1"/>
     </row>
-    <row r="645" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="4:4" ht="15.75" customHeight="1">
       <c r="D645" s="1"/>
     </row>
-    <row r="646" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="4:4" ht="15.75" customHeight="1">
       <c r="D646" s="1"/>
     </row>
-    <row r="647" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="4:4" ht="15.75" customHeight="1">
       <c r="D647" s="1"/>
     </row>
-    <row r="648" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="4:4" ht="15.75" customHeight="1">
       <c r="D648" s="1"/>
     </row>
-    <row r="649" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="4:4" ht="15.75" customHeight="1">
       <c r="D649" s="1"/>
     </row>
-    <row r="650" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="4:4" ht="15.75" customHeight="1">
       <c r="D650" s="1"/>
     </row>
-    <row r="651" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="4:4" ht="15.75" customHeight="1">
       <c r="D651" s="1"/>
     </row>
-    <row r="652" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="4:4" ht="15.75" customHeight="1">
       <c r="D652" s="1"/>
     </row>
-    <row r="653" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="4:4" ht="15.75" customHeight="1">
       <c r="D653" s="1"/>
     </row>
-    <row r="654" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="4:4" ht="15.75" customHeight="1">
       <c r="D654" s="1"/>
     </row>
-    <row r="655" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="4:4" ht="15.75" customHeight="1">
       <c r="D655" s="1"/>
     </row>
-    <row r="656" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="4:4" ht="15.75" customHeight="1">
       <c r="D656" s="1"/>
     </row>
-    <row r="657" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="4:4" ht="15.75" customHeight="1">
       <c r="D657" s="1"/>
     </row>
-    <row r="658" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="4:4" ht="15.75" customHeight="1">
       <c r="D658" s="1"/>
     </row>
-    <row r="659" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="4:4" ht="15.75" customHeight="1">
       <c r="D659" s="1"/>
     </row>
-    <row r="660" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="4:4" ht="15.75" customHeight="1">
       <c r="D660" s="1"/>
     </row>
-    <row r="661" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="4:4" ht="15.75" customHeight="1">
       <c r="D661" s="1"/>
     </row>
-    <row r="662" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="4:4" ht="15.75" customHeight="1">
       <c r="D662" s="1"/>
     </row>
-    <row r="663" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="4:4" ht="15.75" customHeight="1">
       <c r="D663" s="1"/>
     </row>
-    <row r="664" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="4:4" ht="15.75" customHeight="1">
       <c r="D664" s="1"/>
     </row>
-    <row r="665" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="4:4" ht="15.75" customHeight="1">
       <c r="D665" s="1"/>
     </row>
-    <row r="666" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="4:4" ht="15.75" customHeight="1">
       <c r="D666" s="1"/>
     </row>
-    <row r="667" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="4:4" ht="15.75" customHeight="1">
       <c r="D667" s="1"/>
     </row>
-    <row r="668" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="4:4" ht="15.75" customHeight="1">
       <c r="D668" s="1"/>
     </row>
-    <row r="669" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="4:4" ht="15.75" customHeight="1">
       <c r="D669" s="1"/>
     </row>
-    <row r="670" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="4:4" ht="15.75" customHeight="1">
       <c r="D670" s="1"/>
     </row>
-    <row r="671" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="4:4" ht="15.75" customHeight="1">
       <c r="D671" s="1"/>
     </row>
-    <row r="672" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="4:4" ht="15.75" customHeight="1">
       <c r="D672" s="1"/>
     </row>
-    <row r="673" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="4:4" ht="15.75" customHeight="1">
       <c r="D673" s="1"/>
     </row>
-    <row r="674" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="4:4" ht="15.75" customHeight="1">
       <c r="D674" s="1"/>
     </row>
-    <row r="675" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="4:4" ht="15.75" customHeight="1">
       <c r="D675" s="1"/>
     </row>
-    <row r="676" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="4:4" ht="15.75" customHeight="1">
       <c r="D676" s="1"/>
     </row>
-    <row r="677" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="4:4" ht="15.75" customHeight="1">
       <c r="D677" s="1"/>
     </row>
-    <row r="678" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="4:4" ht="15.75" customHeight="1">
       <c r="D678" s="1"/>
     </row>
-    <row r="679" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="4:4" ht="15.75" customHeight="1">
       <c r="D679" s="1"/>
     </row>
-    <row r="680" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="4:4" ht="15.75" customHeight="1">
       <c r="D680" s="1"/>
     </row>
-    <row r="681" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="4:4" ht="15.75" customHeight="1">
       <c r="D681" s="1"/>
     </row>
-    <row r="682" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="4:4" ht="15.75" customHeight="1">
       <c r="D682" s="1"/>
     </row>
-    <row r="683" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="4:4" ht="15.75" customHeight="1">
       <c r="D683" s="1"/>
     </row>
-    <row r="684" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="4:4" ht="15.75" customHeight="1">
       <c r="D684" s="1"/>
     </row>
-    <row r="685" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="4:4" ht="15.75" customHeight="1">
       <c r="D685" s="1"/>
     </row>
-    <row r="686" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="4:4" ht="15.75" customHeight="1">
       <c r="D686" s="1"/>
     </row>
-    <row r="687" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="4:4" ht="15.75" customHeight="1">
       <c r="D687" s="1"/>
     </row>
-    <row r="688" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="4:4" ht="15.75" customHeight="1">
       <c r="D688" s="1"/>
     </row>
-    <row r="689" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="4:4" ht="15.75" customHeight="1">
       <c r="D689" s="1"/>
     </row>
-    <row r="690" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="4:4" ht="15.75" customHeight="1">
       <c r="D690" s="1"/>
     </row>
-    <row r="691" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="4:4" ht="15.75" customHeight="1">
       <c r="D691" s="1"/>
     </row>
-    <row r="692" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="4:4" ht="15.75" customHeight="1">
       <c r="D692" s="1"/>
     </row>
-    <row r="693" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="4:4" ht="15.75" customHeight="1">
       <c r="D693" s="1"/>
     </row>
-    <row r="694" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="4:4" ht="15.75" customHeight="1">
       <c r="D694" s="1"/>
     </row>
-    <row r="695" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="4:4" ht="15.75" customHeight="1">
       <c r="D695" s="1"/>
     </row>
-    <row r="696" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="4:4" ht="15.75" customHeight="1">
       <c r="D696" s="1"/>
     </row>
-    <row r="697" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="4:4" ht="15.75" customHeight="1">
       <c r="D697" s="1"/>
     </row>
-    <row r="698" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="4:4" ht="15.75" customHeight="1">
       <c r="D698" s="1"/>
     </row>
-    <row r="699" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="4:4" ht="15.75" customHeight="1">
       <c r="D699" s="1"/>
     </row>
-    <row r="700" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="4:4" ht="15.75" customHeight="1">
       <c r="D700" s="1"/>
     </row>
-    <row r="701" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="4:4" ht="15.75" customHeight="1">
       <c r="D701" s="1"/>
     </row>
-    <row r="702" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="4:4" ht="15.75" customHeight="1">
       <c r="D702" s="1"/>
     </row>
-    <row r="703" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="4:4" ht="15.75" customHeight="1">
       <c r="D703" s="1"/>
     </row>
-    <row r="704" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="4:4" ht="15.75" customHeight="1">
       <c r="D704" s="1"/>
     </row>
-    <row r="705" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="4:4" ht="15.75" customHeight="1">
       <c r="D705" s="1"/>
     </row>
-    <row r="706" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="4:4" ht="15.75" customHeight="1">
       <c r="D706" s="1"/>
     </row>
-    <row r="707" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="4:4" ht="15.75" customHeight="1">
       <c r="D707" s="1"/>
     </row>
-    <row r="708" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="4:4" ht="15.75" customHeight="1">
       <c r="D708" s="1"/>
     </row>
-    <row r="709" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="4:4" ht="15.75" customHeight="1">
       <c r="D709" s="1"/>
     </row>
-    <row r="710" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="4:4" ht="15.75" customHeight="1">
       <c r="D710" s="1"/>
     </row>
-    <row r="711" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="4:4" ht="15.75" customHeight="1">
       <c r="D711" s="1"/>
     </row>
-    <row r="712" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="4:4" ht="15.75" customHeight="1">
       <c r="D712" s="1"/>
     </row>
-    <row r="713" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="4:4" ht="15.75" customHeight="1">
       <c r="D713" s="1"/>
     </row>
-    <row r="714" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="4:4" ht="15.75" customHeight="1">
       <c r="D714" s="1"/>
     </row>
-    <row r="715" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="4:4" ht="15.75" customHeight="1">
       <c r="D715" s="1"/>
     </row>
-    <row r="716" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="4:4" ht="15.75" customHeight="1">
       <c r="D716" s="1"/>
     </row>
-    <row r="717" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="4:4" ht="15.75" customHeight="1">
       <c r="D717" s="1"/>
     </row>
-    <row r="718" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="4:4" ht="15.75" customHeight="1">
       <c r="D718" s="1"/>
     </row>
-    <row r="719" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="4:4" ht="15.75" customHeight="1">
       <c r="D719" s="1"/>
     </row>
-    <row r="720" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="4:4" ht="15.75" customHeight="1">
       <c r="D720" s="1"/>
     </row>
-    <row r="721" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="4:4" ht="15.75" customHeight="1">
       <c r="D721" s="1"/>
     </row>
-    <row r="722" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="4:4" ht="15.75" customHeight="1">
       <c r="D722" s="1"/>
     </row>
-    <row r="723" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="4:4" ht="15.75" customHeight="1">
       <c r="D723" s="1"/>
     </row>
-    <row r="724" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="4:4" ht="15.75" customHeight="1">
       <c r="D724" s="1"/>
     </row>
-    <row r="725" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="4:4" ht="15.75" customHeight="1">
       <c r="D725" s="1"/>
     </row>
-    <row r="726" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="4:4" ht="15.75" customHeight="1">
       <c r="D726" s="1"/>
     </row>
-    <row r="727" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="4:4" ht="15.75" customHeight="1">
       <c r="D727" s="1"/>
     </row>
-    <row r="728" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="4:4" ht="15.75" customHeight="1">
       <c r="D728" s="1"/>
     </row>
-    <row r="729" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="4:4" ht="15.75" customHeight="1">
       <c r="D729" s="1"/>
     </row>
-    <row r="730" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="4:4" ht="15.75" customHeight="1">
       <c r="D730" s="1"/>
     </row>
-    <row r="731" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="4:4" ht="15.75" customHeight="1">
       <c r="D731" s="1"/>
     </row>
-    <row r="732" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="4:4" ht="15.75" customHeight="1">
       <c r="D732" s="1"/>
     </row>
-    <row r="733" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="4:4" ht="15.75" customHeight="1">
       <c r="D733" s="1"/>
     </row>
-    <row r="734" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="4:4" ht="15.75" customHeight="1">
       <c r="D734" s="1"/>
     </row>
-    <row r="735" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="4:4" ht="15.75" customHeight="1">
       <c r="D735" s="1"/>
     </row>
-    <row r="736" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="4:4" ht="15.75" customHeight="1">
       <c r="D736" s="1"/>
     </row>
-    <row r="737" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="4:4" ht="15.75" customHeight="1">
       <c r="D737" s="1"/>
     </row>
-    <row r="738" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="4:4" ht="15.75" customHeight="1">
       <c r="D738" s="1"/>
     </row>
-    <row r="739" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="4:4" ht="15.75" customHeight="1">
       <c r="D739" s="1"/>
     </row>
-    <row r="740" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="4:4" ht="15.75" customHeight="1">
       <c r="D740" s="1"/>
     </row>
-    <row r="741" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="4:4" ht="15.75" customHeight="1">
       <c r="D741" s="1"/>
     </row>
-    <row r="742" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="4:4" ht="15.75" customHeight="1">
       <c r="D742" s="1"/>
     </row>
-    <row r="743" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="4:4" ht="15.75" customHeight="1">
       <c r="D743" s="1"/>
     </row>
-    <row r="744" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="4:4" ht="15.75" customHeight="1">
       <c r="D744" s="1"/>
     </row>
-    <row r="745" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="4:4" ht="15.75" customHeight="1">
       <c r="D745" s="1"/>
     </row>
-    <row r="746" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="4:4" ht="15.75" customHeight="1">
       <c r="D746" s="1"/>
     </row>
-    <row r="747" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="4:4" ht="15.75" customHeight="1">
       <c r="D747" s="1"/>
     </row>
-    <row r="748" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="4:4" ht="15.75" customHeight="1">
       <c r="D748" s="1"/>
     </row>
-    <row r="749" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="4:4" ht="15.75" customHeight="1">
       <c r="D749" s="1"/>
     </row>
-    <row r="750" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="4:4" ht="15.75" customHeight="1">
       <c r="D750" s="1"/>
     </row>
-    <row r="751" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="4:4" ht="15.75" customHeight="1">
       <c r="D751" s="1"/>
     </row>
-    <row r="752" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="4:4" ht="15.75" customHeight="1">
       <c r="D752" s="1"/>
     </row>
-    <row r="753" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="4:4" ht="15.75" customHeight="1">
       <c r="D753" s="1"/>
     </row>
-    <row r="754" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="4:4" ht="15.75" customHeight="1">
       <c r="D754" s="1"/>
     </row>
-    <row r="755" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="4:4" ht="15.75" customHeight="1">
       <c r="D755" s="1"/>
     </row>
-    <row r="756" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="4:4" ht="15.75" customHeight="1">
       <c r="D756" s="1"/>
     </row>
-    <row r="757" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="4:4" ht="15.75" customHeight="1">
       <c r="D757" s="1"/>
     </row>
-    <row r="758" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="4:4" ht="15.75" customHeight="1">
       <c r="D758" s="1"/>
     </row>
-    <row r="759" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="4:4" ht="15.75" customHeight="1">
       <c r="D759" s="1"/>
     </row>
-    <row r="760" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="4:4" ht="15.75" customHeight="1">
       <c r="D760" s="1"/>
     </row>
-    <row r="761" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="4:4" ht="15.75" customHeight="1">
       <c r="D761" s="1"/>
     </row>
-    <row r="762" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="4:4" ht="15.75" customHeight="1">
       <c r="D762" s="1"/>
     </row>
-    <row r="763" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="4:4" ht="15.75" customHeight="1">
       <c r="D763" s="1"/>
     </row>
-    <row r="764" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="4:4" ht="15.75" customHeight="1">
       <c r="D764" s="1"/>
     </row>
-    <row r="765" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="4:4" ht="15.75" customHeight="1">
       <c r="D765" s="1"/>
     </row>
-    <row r="766" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="4:4" ht="15.75" customHeight="1">
       <c r="D766" s="1"/>
     </row>
-    <row r="767" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="4:4" ht="15.75" customHeight="1">
       <c r="D767" s="1"/>
     </row>
-    <row r="768" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="4:4" ht="15.75" customHeight="1">
       <c r="D768" s="1"/>
     </row>
-    <row r="769" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="4:4" ht="15.75" customHeight="1">
       <c r="D769" s="1"/>
     </row>
-    <row r="770" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="4:4" ht="15.75" customHeight="1">
       <c r="D770" s="1"/>
     </row>
-    <row r="771" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="4:4" ht="15.75" customHeight="1">
       <c r="D771" s="1"/>
     </row>
-    <row r="772" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="4:4" ht="15.75" customHeight="1">
       <c r="D772" s="1"/>
     </row>
-    <row r="773" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="4:4" ht="15.75" customHeight="1">
       <c r="D773" s="1"/>
     </row>
-    <row r="774" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="4:4" ht="15.75" customHeight="1">
       <c r="D774" s="1"/>
     </row>
-    <row r="775" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="4:4" ht="15.75" customHeight="1">
       <c r="D775" s="1"/>
     </row>
-    <row r="776" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="4:4" ht="15.75" customHeight="1">
       <c r="D776" s="1"/>
     </row>
-    <row r="777" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="4:4" ht="15.75" customHeight="1">
       <c r="D777" s="1"/>
     </row>
-    <row r="778" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="4:4" ht="15.75" customHeight="1">
       <c r="D778" s="1"/>
     </row>
-    <row r="779" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="4:4" ht="15.75" customHeight="1">
       <c r="D779" s="1"/>
     </row>
-    <row r="780" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="4:4" ht="15.75" customHeight="1">
       <c r="D780" s="1"/>
     </row>
-    <row r="781" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="4:4" ht="15.75" customHeight="1">
       <c r="D781" s="1"/>
     </row>
-    <row r="782" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="4:4" ht="15.75" customHeight="1">
       <c r="D782" s="1"/>
     </row>
-    <row r="783" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="4:4" ht="15.75" customHeight="1">
       <c r="D783" s="1"/>
     </row>
-    <row r="784" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="4:4" ht="15.75" customHeight="1">
       <c r="D784" s="1"/>
     </row>
-    <row r="785" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="4:4" ht="15.75" customHeight="1">
       <c r="D785" s="1"/>
     </row>
-    <row r="786" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="4:4" ht="15.75" customHeight="1">
       <c r="D786" s="1"/>
     </row>
-    <row r="787" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="4:4" ht="15.75" customHeight="1">
       <c r="D787" s="1"/>
     </row>
-    <row r="788" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="4:4" ht="15.75" customHeight="1">
       <c r="D788" s="1"/>
     </row>
-    <row r="789" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="4:4" ht="15.75" customHeight="1">
       <c r="D789" s="1"/>
     </row>
-    <row r="790" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="4:4" ht="15.75" customHeight="1">
       <c r="D790" s="1"/>
     </row>
-    <row r="791" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="4:4" ht="15.75" customHeight="1">
       <c r="D791" s="1"/>
     </row>
-    <row r="792" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="4:4" ht="15.75" customHeight="1">
       <c r="D792" s="1"/>
     </row>
-    <row r="793" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="4:4" ht="15.75" customHeight="1">
       <c r="D793" s="1"/>
     </row>
-    <row r="794" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="4:4" ht="15.75" customHeight="1">
       <c r="D794" s="1"/>
     </row>
-    <row r="795" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="4:4" ht="15.75" customHeight="1">
       <c r="D795" s="1"/>
     </row>
-    <row r="796" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="4:4" ht="15.75" customHeight="1">
       <c r="D796" s="1"/>
     </row>
-    <row r="797" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="4:4" ht="15.75" customHeight="1">
       <c r="D797" s="1"/>
     </row>
-    <row r="798" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="4:4" ht="15.75" customHeight="1">
       <c r="D798" s="1"/>
     </row>
-    <row r="799" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="4:4" ht="15.75" customHeight="1">
       <c r="D799" s="1"/>
     </row>
-    <row r="800" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="4:4" ht="15.75" customHeight="1">
       <c r="D800" s="1"/>
     </row>
-    <row r="801" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="4:4" ht="15.75" customHeight="1">
       <c r="D801" s="1"/>
     </row>
-    <row r="802" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="4:4" ht="15.75" customHeight="1">
       <c r="D802" s="1"/>
     </row>
-    <row r="803" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="4:4" ht="15.75" customHeight="1">
       <c r="D803" s="1"/>
     </row>
-    <row r="804" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="4:4" ht="15.75" customHeight="1">
       <c r="D804" s="1"/>
     </row>
-    <row r="805" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="4:4" ht="15.75" customHeight="1">
       <c r="D805" s="1"/>
     </row>
-    <row r="806" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="4:4" ht="15.75" customHeight="1">
       <c r="D806" s="1"/>
     </row>
-    <row r="807" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="4:4" ht="15.75" customHeight="1">
       <c r="D807" s="1"/>
     </row>
-    <row r="808" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="4:4" ht="15.75" customHeight="1">
       <c r="D808" s="1"/>
     </row>
-    <row r="809" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="4:4" ht="15.75" customHeight="1">
       <c r="D809" s="1"/>
     </row>
-    <row r="810" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="4:4" ht="15.75" customHeight="1">
       <c r="D810" s="1"/>
     </row>
-    <row r="811" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="4:4" ht="15.75" customHeight="1">
       <c r="D811" s="1"/>
     </row>
-    <row r="812" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="4:4" ht="15.75" customHeight="1">
       <c r="D812" s="1"/>
     </row>
-    <row r="813" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="4:4" ht="15.75" customHeight="1">
       <c r="D813" s="1"/>
     </row>
-    <row r="814" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="4:4" ht="15.75" customHeight="1">
       <c r="D814" s="1"/>
     </row>
-    <row r="815" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="4:4" ht="15.75" customHeight="1">
       <c r="D815" s="1"/>
     </row>
-    <row r="816" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="4:4" ht="15.75" customHeight="1">
       <c r="D816" s="1"/>
     </row>
-    <row r="817" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="4:4" ht="15.75" customHeight="1">
       <c r="D817" s="1"/>
     </row>
-    <row r="818" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="4:4" ht="15.75" customHeight="1">
       <c r="D818" s="1"/>
     </row>
-    <row r="819" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="4:4" ht="15.75" customHeight="1">
       <c r="D819" s="1"/>
     </row>
-    <row r="820" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="4:4" ht="15.75" customHeight="1">
       <c r="D820" s="1"/>
     </row>
-    <row r="821" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="4:4" ht="15.75" customHeight="1">
       <c r="D821" s="1"/>
     </row>
-    <row r="822" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="4:4" ht="15.75" customHeight="1">
       <c r="D822" s="1"/>
     </row>
-    <row r="823" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="4:4" ht="15.75" customHeight="1">
       <c r="D823" s="1"/>
     </row>
-    <row r="824" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="4:4" ht="15.75" customHeight="1">
       <c r="D824" s="1"/>
     </row>
-    <row r="825" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="4:4" ht="15.75" customHeight="1">
       <c r="D825" s="1"/>
     </row>
-    <row r="826" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="4:4" ht="15.75" customHeight="1">
       <c r="D826" s="1"/>
     </row>
-    <row r="827" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="4:4" ht="15.75" customHeight="1">
       <c r="D827" s="1"/>
     </row>
-    <row r="828" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="4:4" ht="15.75" customHeight="1">
       <c r="D828" s="1"/>
     </row>
-    <row r="829" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="4:4" ht="15.75" customHeight="1">
       <c r="D829" s="1"/>
     </row>
-    <row r="830" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="4:4" ht="15.75" customHeight="1">
       <c r="D830" s="1"/>
     </row>
-    <row r="831" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="4:4" ht="15.75" customHeight="1">
       <c r="D831" s="1"/>
     </row>
-    <row r="832" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="4:4" ht="15.75" customHeight="1">
       <c r="D832" s="1"/>
     </row>
-    <row r="833" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="4:4" ht="15.75" customHeight="1">
       <c r="D833" s="1"/>
     </row>
-    <row r="834" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="4:4" ht="15.75" customHeight="1">
       <c r="D834" s="1"/>
     </row>
-    <row r="835" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="4:4" ht="15.75" customHeight="1">
       <c r="D835" s="1"/>
     </row>
-    <row r="836" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="4:4" ht="15.75" customHeight="1">
       <c r="D836" s="1"/>
     </row>
-    <row r="837" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="4:4" ht="15.75" customHeight="1">
       <c r="D837" s="1"/>
     </row>
-    <row r="838" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="4:4" ht="15.75" customHeight="1">
       <c r="D838" s="1"/>
     </row>
-    <row r="839" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="4:4" ht="15.75" customHeight="1">
       <c r="D839" s="1"/>
     </row>
-    <row r="840" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="4:4" ht="15.75" customHeight="1">
       <c r="D840" s="1"/>
     </row>
-    <row r="841" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="4:4" ht="15.75" customHeight="1">
       <c r="D841" s="1"/>
     </row>
-    <row r="842" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="4:4" ht="15.75" customHeight="1">
       <c r="D842" s="1"/>
     </row>
-    <row r="843" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="4:4" ht="15.75" customHeight="1">
       <c r="D843" s="1"/>
     </row>
-    <row r="844" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="4:4" ht="15.75" customHeight="1">
       <c r="D844" s="1"/>
     </row>
-    <row r="845" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="4:4" ht="15.75" customHeight="1">
       <c r="D845" s="1"/>
     </row>
-    <row r="846" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="4:4" ht="15.75" customHeight="1">
       <c r="D846" s="1"/>
     </row>
-    <row r="847" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="4:4" ht="15.75" customHeight="1">
       <c r="D847" s="1"/>
     </row>
-    <row r="848" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="4:4" ht="15.75" customHeight="1">
       <c r="D848" s="1"/>
     </row>
-    <row r="849" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="4:4" ht="15.75" customHeight="1">
       <c r="D849" s="1"/>
     </row>
-    <row r="850" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="4:4" ht="15.75" customHeight="1">
       <c r="D850" s="1"/>
     </row>
-    <row r="851" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="4:4" ht="15.75" customHeight="1">
       <c r="D851" s="1"/>
     </row>
-    <row r="852" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="4:4" ht="15.75" customHeight="1">
       <c r="D852" s="1"/>
     </row>
-    <row r="853" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="4:4" ht="15.75" customHeight="1">
       <c r="D853" s="1"/>
     </row>
-    <row r="854" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="4:4" ht="15.75" customHeight="1">
       <c r="D854" s="1"/>
     </row>
-    <row r="855" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="4:4" ht="15.75" customHeight="1">
       <c r="D855" s="1"/>
     </row>
-    <row r="856" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="4:4" ht="15.75" customHeight="1">
       <c r="D856" s="1"/>
     </row>
-    <row r="857" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="4:4" ht="15.75" customHeight="1">
       <c r="D857" s="1"/>
     </row>
-    <row r="858" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="4:4" ht="15.75" customHeight="1">
       <c r="D858" s="1"/>
     </row>
-    <row r="859" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="4:4" ht="15.75" customHeight="1">
       <c r="D859" s="1"/>
     </row>
-    <row r="860" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="4:4" ht="15.75" customHeight="1">
       <c r="D860" s="1"/>
     </row>
-    <row r="861" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="4:4" ht="15.75" customHeight="1">
       <c r="D861" s="1"/>
     </row>
-    <row r="862" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="4:4" ht="15.75" customHeight="1">
       <c r="D862" s="1"/>
     </row>
-    <row r="863" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="4:4" ht="15.75" customHeight="1">
       <c r="D863" s="1"/>
     </row>
-    <row r="864" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="4:4" ht="15.75" customHeight="1">
       <c r="D864" s="1"/>
     </row>
-    <row r="865" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="4:4" ht="15.75" customHeight="1">
       <c r="D865" s="1"/>
     </row>
-    <row r="866" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="4:4" ht="15.75" customHeight="1">
       <c r="D866" s="1"/>
     </row>
-    <row r="867" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="4:4" ht="15.75" customHeight="1">
       <c r="D867" s="1"/>
     </row>
-    <row r="868" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="4:4" ht="15.75" customHeight="1">
       <c r="D868" s="1"/>
     </row>
-    <row r="869" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="4:4" ht="15.75" customHeight="1">
       <c r="D869" s="1"/>
     </row>
-    <row r="870" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="4:4" ht="15.75" customHeight="1">
       <c r="D870" s="1"/>
     </row>
-    <row r="871" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="4:4" ht="15.75" customHeight="1">
       <c r="D871" s="1"/>
     </row>
-    <row r="872" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="4:4" ht="15.75" customHeight="1">
       <c r="D872" s="1"/>
     </row>
-    <row r="873" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="4:4" ht="15.75" customHeight="1">
       <c r="D873" s="1"/>
     </row>
-    <row r="874" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="4:4" ht="15.75" customHeight="1">
       <c r="D874" s="1"/>
     </row>
-    <row r="875" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="4:4" ht="15.75" customHeight="1">
       <c r="D875" s="1"/>
     </row>
-    <row r="876" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="4:4" ht="15.75" customHeight="1">
       <c r="D876" s="1"/>
     </row>
-    <row r="877" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="4:4" ht="15.75" customHeight="1">
       <c r="D877" s="1"/>
     </row>
-    <row r="878" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="4:4" ht="15.75" customHeight="1">
       <c r="D878" s="1"/>
     </row>
-    <row r="879" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="4:4" ht="15.75" customHeight="1">
       <c r="D879" s="1"/>
     </row>
-    <row r="880" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="4:4" ht="15.75" customHeight="1">
       <c r="D880" s="1"/>
     </row>
-    <row r="881" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="4:4" ht="15.75" customHeight="1">
       <c r="D881" s="1"/>
     </row>
-    <row r="882" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="4:4" ht="15.75" customHeight="1">
       <c r="D882" s="1"/>
     </row>
-    <row r="883" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="4:4" ht="15.75" customHeight="1">
       <c r="D883" s="1"/>
     </row>
-    <row r="884" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="4:4" ht="15.75" customHeight="1">
       <c r="D884" s="1"/>
     </row>
-    <row r="885" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="4:4" ht="15.75" customHeight="1">
       <c r="D885" s="1"/>
     </row>
-    <row r="886" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="4:4" ht="15.75" customHeight="1">
       <c r="D886" s="1"/>
     </row>
-    <row r="887" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="4:4" ht="15.75" customHeight="1">
       <c r="D887" s="1"/>
     </row>
-    <row r="888" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="4:4" ht="15.75" customHeight="1">
       <c r="D888" s="1"/>
     </row>
-    <row r="889" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="4:4" ht="15.75" customHeight="1">
       <c r="D889" s="1"/>
     </row>
-    <row r="890" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="4:4" ht="15.75" customHeight="1">
       <c r="D890" s="1"/>
     </row>
-    <row r="891" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="4:4" ht="15.75" customHeight="1">
       <c r="D891" s="1"/>
     </row>
-    <row r="892" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="4:4" ht="15.75" customHeight="1">
       <c r="D892" s="1"/>
     </row>
-    <row r="893" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="4:4" ht="15.75" customHeight="1">
       <c r="D893" s="1"/>
     </row>
-    <row r="894" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="4:4" ht="15.75" customHeight="1">
       <c r="D894" s="1"/>
     </row>
-    <row r="895" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="4:4" ht="15.75" customHeight="1">
       <c r="D895" s="1"/>
     </row>
-    <row r="896" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="4:4" ht="15.75" customHeight="1">
       <c r="D896" s="1"/>
     </row>
-    <row r="897" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="4:4" ht="15.75" customHeight="1">
       <c r="D897" s="1"/>
     </row>
-    <row r="898" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="4:4" ht="15.75" customHeight="1">
       <c r="D898" s="1"/>
     </row>
-    <row r="899" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="4:4" ht="15.75" customHeight="1">
       <c r="D899" s="1"/>
     </row>
-    <row r="900" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="4:4" ht="15.75" customHeight="1">
       <c r="D900" s="1"/>
     </row>
-    <row r="901" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="4:4" ht="15.75" customHeight="1">
       <c r="D901" s="1"/>
     </row>
-    <row r="902" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="4:4" ht="15.75" customHeight="1">
       <c r="D902" s="1"/>
     </row>
-    <row r="903" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="4:4" ht="15.75" customHeight="1">
       <c r="D903" s="1"/>
     </row>
-    <row r="904" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="4:4" ht="15.75" customHeight="1">
       <c r="D904" s="1"/>
     </row>
-    <row r="905" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="4:4" ht="15.75" customHeight="1">
       <c r="D905" s="1"/>
     </row>
-    <row r="906" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="4:4" ht="15.75" customHeight="1">
       <c r="D906" s="1"/>
     </row>
-    <row r="907" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="4:4" ht="15.75" customHeight="1">
       <c r="D907" s="1"/>
     </row>
-    <row r="908" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="4:4" ht="15.75" customHeight="1">
       <c r="D908" s="1"/>
     </row>
-    <row r="909" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="4:4" ht="15.75" customHeight="1">
       <c r="D909" s="1"/>
     </row>
-    <row r="910" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="4:4" ht="15.75" customHeight="1">
       <c r="D910" s="1"/>
     </row>
-    <row r="911" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="4:4" ht="15.75" customHeight="1">
       <c r="D911" s="1"/>
     </row>
-    <row r="912" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="4:4" ht="15.75" customHeight="1">
       <c r="D912" s="1"/>
     </row>
-    <row r="913" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="4:4" ht="15.75" customHeight="1">
       <c r="D913" s="1"/>
     </row>
-    <row r="914" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="4:4" ht="15.75" customHeight="1">
       <c r="D914" s="1"/>
     </row>
-    <row r="915" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="4:4" ht="15.75" customHeight="1">
       <c r="D915" s="1"/>
     </row>
-    <row r="916" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="4:4" ht="15.75" customHeight="1">
       <c r="D916" s="1"/>
     </row>
-    <row r="917" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="4:4" ht="15.75" customHeight="1">
       <c r="D917" s="1"/>
     </row>
-    <row r="918" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="4:4" ht="15.75" customHeight="1">
       <c r="D918" s="1"/>
     </row>
-    <row r="919" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="4:4" ht="15.75" customHeight="1">
       <c r="D919" s="1"/>
     </row>
-    <row r="920" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="4:4" ht="15.75" customHeight="1">
       <c r="D920" s="1"/>
     </row>
-    <row r="921" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="4:4" ht="15.75" customHeight="1">
       <c r="D921" s="1"/>
     </row>
-    <row r="922" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="4:4" ht="15.75" customHeight="1">
       <c r="D922" s="1"/>
     </row>
-    <row r="923" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="4:4" ht="15.75" customHeight="1">
       <c r="D923" s="1"/>
     </row>
-    <row r="924" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="4:4" ht="15.75" customHeight="1">
       <c r="D924" s="1"/>
     </row>
-    <row r="925" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="4:4" ht="15.75" customHeight="1">
       <c r="D925" s="1"/>
     </row>
-    <row r="926" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="4:4" ht="15.75" customHeight="1">
       <c r="D926" s="1"/>
     </row>
-    <row r="927" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="4:4" ht="15.75" customHeight="1">
       <c r="D927" s="1"/>
     </row>
-    <row r="928" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="4:4" ht="15.75" customHeight="1">
       <c r="D928" s="1"/>
     </row>
-    <row r="929" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="4:4" ht="15.75" customHeight="1">
       <c r="D929" s="1"/>
     </row>
-    <row r="930" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="4:4" ht="15.75" customHeight="1">
       <c r="D930" s="1"/>
     </row>
-    <row r="931" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="4:4" ht="15.75" customHeight="1">
       <c r="D931" s="1"/>
     </row>
-    <row r="932" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="4:4" ht="15.75" customHeight="1">
       <c r="D932" s="1"/>
     </row>
-    <row r="933" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="4:4" ht="15.75" customHeight="1">
       <c r="D933" s="1"/>
     </row>
-    <row r="934" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="4:4" ht="15.75" customHeight="1">
       <c r="D934" s="1"/>
     </row>
-    <row r="935" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="4:4" ht="15.75" customHeight="1">
       <c r="D935" s="1"/>
     </row>
-    <row r="936" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="4:4" ht="15.75" customHeight="1">
       <c r="D936" s="1"/>
     </row>
-    <row r="937" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="4:4" ht="15.75" customHeight="1">
       <c r="D937" s="1"/>
     </row>
-    <row r="938" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="4:4" ht="15.75" customHeight="1">
       <c r="D938" s="1"/>
     </row>
-    <row r="939" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="4:4" ht="15.75" customHeight="1">
       <c r="D939" s="1"/>
     </row>
-    <row r="940" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="4:4" ht="15.75" customHeight="1">
       <c r="D940" s="1"/>
     </row>
-    <row r="941" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="4:4" ht="15.75" customHeight="1">
       <c r="D941" s="1"/>
     </row>
-    <row r="942" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="4:4" ht="15.75" customHeight="1">
       <c r="D942" s="1"/>
     </row>
-    <row r="943" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="4:4" ht="15.75" customHeight="1">
       <c r="D943" s="1"/>
     </row>
-    <row r="944" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="4:4" ht="15.75" customHeight="1">
       <c r="D944" s="1"/>
     </row>
-    <row r="945" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="4:4" ht="15.75" customHeight="1">
       <c r="D945" s="1"/>
     </row>
-    <row r="946" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="4:4" ht="15.75" customHeight="1">
       <c r="D946" s="1"/>
     </row>
-    <row r="947" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="4:4" ht="15.75" customHeight="1">
       <c r="D947" s="1"/>
     </row>
-    <row r="948" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="4:4" ht="15.75" customHeight="1">
       <c r="D948" s="1"/>
     </row>
-    <row r="949" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="4:4" ht="15.75" customHeight="1">
       <c r="D949" s="1"/>
     </row>
-    <row r="950" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="950" spans="4:4" ht="15.75" customHeight="1">
       <c r="D950" s="1"/>
     </row>
-    <row r="951" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="4:4" ht="15.75" customHeight="1">
       <c r="D951" s="1"/>
     </row>
-    <row r="952" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="4:4" ht="15.75" customHeight="1">
       <c r="D952" s="1"/>
     </row>
-    <row r="953" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="4:4" ht="15.75" customHeight="1">
       <c r="D953" s="1"/>
     </row>
-    <row r="954" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="4:4" ht="15.75" customHeight="1">
       <c r="D954" s="1"/>
     </row>
-    <row r="955" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="4:4" ht="15.75" customHeight="1">
       <c r="D955" s="1"/>
     </row>
-    <row r="956" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="4:4" ht="15.75" customHeight="1">
       <c r="D956" s="1"/>
     </row>
-    <row r="957" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="4:4" ht="15.75" customHeight="1">
       <c r="D957" s="1"/>
     </row>
-    <row r="958" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="4:4" ht="15.75" customHeight="1">
       <c r="D958" s="1"/>
     </row>
-    <row r="959" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="4:4" ht="15.75" customHeight="1">
       <c r="D959" s="1"/>
     </row>
-    <row r="960" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="4:4" ht="15.75" customHeight="1">
       <c r="D960" s="1"/>
     </row>
-    <row r="961" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="4:4" ht="15.75" customHeight="1">
       <c r="D961" s="1"/>
     </row>
-    <row r="962" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="962" spans="4:4" ht="15.75" customHeight="1">
       <c r="D962" s="1"/>
     </row>
-    <row r="963" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="963" spans="4:4" ht="15.75" customHeight="1">
       <c r="D963" s="1"/>
     </row>
-    <row r="964" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="4:4" ht="15.75" customHeight="1">
       <c r="D964" s="1"/>
     </row>
-    <row r="965" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="4:4" ht="15.75" customHeight="1">
       <c r="D965" s="1"/>
     </row>
-    <row r="966" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="4:4" ht="15.75" customHeight="1">
       <c r="D966" s="1"/>
     </row>
-    <row r="967" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="4:4" ht="15.75" customHeight="1">
       <c r="D967" s="1"/>
     </row>
-    <row r="968" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="4:4" ht="15.75" customHeight="1">
       <c r="D968" s="1"/>
     </row>
-    <row r="969" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="4:4" ht="15.75" customHeight="1">
       <c r="D969" s="1"/>
     </row>
-    <row r="970" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="970" spans="4:4" ht="15.75" customHeight="1">
       <c r="D970" s="1"/>
     </row>
-    <row r="971" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="4:4" ht="15.75" customHeight="1">
       <c r="D971" s="1"/>
     </row>
-    <row r="972" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="972" spans="4:4" ht="15.75" customHeight="1">
       <c r="D972" s="1"/>
     </row>
-    <row r="973" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="4:4" ht="15.75" customHeight="1">
       <c r="D973" s="1"/>
     </row>
-    <row r="974" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="974" spans="4:4" ht="15.75" customHeight="1">
       <c r="D974" s="1"/>
     </row>
-    <row r="975" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="4:4" ht="15.75" customHeight="1">
       <c r="D975" s="1"/>
     </row>
-    <row r="976" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="4:4" ht="15.75" customHeight="1">
       <c r="D976" s="1"/>
     </row>
-    <row r="977" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="4:4" ht="15.75" customHeight="1">
       <c r="D977" s="1"/>
     </row>
-    <row r="978" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="978" spans="4:4" ht="15.75" customHeight="1">
       <c r="D978" s="1"/>
     </row>
-    <row r="979" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="979" spans="4:4" ht="15.75" customHeight="1">
       <c r="D979" s="1"/>
     </row>
-    <row r="980" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="980" spans="4:4" ht="15.75" customHeight="1">
       <c r="D980" s="1"/>
     </row>
-    <row r="981" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="4:4" ht="15.75" customHeight="1">
       <c r="D981" s="1"/>
     </row>
-    <row r="982" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="4:4" ht="15.75" customHeight="1">
       <c r="D982" s="1"/>
     </row>
-    <row r="983" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="983" spans="4:4" ht="15.75" customHeight="1">
       <c r="D983" s="1"/>
     </row>
-    <row r="984" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="984" spans="4:4" ht="15.75" customHeight="1">
       <c r="D984" s="1"/>
     </row>
-    <row r="985" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="4:4" ht="15.75" customHeight="1">
       <c r="D985" s="1"/>
     </row>
-    <row r="986" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="986" spans="4:4" ht="15.75" customHeight="1">
       <c r="D986" s="1"/>
     </row>
-    <row r="987" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="4:4" ht="15.75" customHeight="1">
       <c r="D987" s="1"/>
     </row>
-    <row r="988" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="4:4" ht="15.75" customHeight="1">
       <c r="D988" s="1"/>
     </row>
-    <row r="989" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="4:4" ht="15.75" customHeight="1">
       <c r="D989" s="1"/>
     </row>
-    <row r="990" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="4:4" ht="15.75" customHeight="1">
       <c r="D990" s="1"/>
     </row>
-    <row r="991" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="4:4" ht="15.75" customHeight="1">
       <c r="D991" s="1"/>
     </row>
-    <row r="992" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="4:4" ht="15.75" customHeight="1">
       <c r="D992" s="1"/>
     </row>
-    <row r="993" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="4:4" ht="15.75" customHeight="1">
       <c r="D993" s="1"/>
     </row>
-    <row r="994" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="4:4" ht="15.75" customHeight="1">
       <c r="D994" s="1"/>
     </row>
-    <row r="995" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="4:4" ht="15.75" customHeight="1">
       <c r="D995" s="1"/>
     </row>
-    <row r="996" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="4:4" ht="15.75" customHeight="1">
       <c r="D996" s="1"/>
     </row>
-    <row r="997" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="4:4" ht="15.75" customHeight="1">
       <c r="D997" s="1"/>
     </row>
   </sheetData>
@@ -9273,8 +9273,8 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f366023269454ced43510f73883a6d91">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dd01e2e1f35a8420c36650a8355a0ef6" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
     <xsd:import namespace="b0d30a24-05e2-4154-8fed-e579ddd987b0"/>
     <xsd:element name="properties">
@@ -9456,38 +9456,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F6FD9D-19D1-439B-8BFE-82DBC99BDEA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F6FD9D-19D1-439B-8BFE-82DBC99BDEA4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C79516F1-8A13-4F63-820A-89A8B84A29E0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-    <ds:schemaRef ds:uri="b0d30a24-05e2-4154-8fed-e579ddd987b0"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F1A155A-9D28-4350-8732-AE6833CEF998}"/>
 </file>
--- a/upload files/Preferences v6.xlsx
+++ b/upload files/Preferences v6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7AAAB9B0-7F0E-4C0E-95DC-8FC4F828A00E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C4836D4-26A3-4853-94BA-0B2EE58060BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$78</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="104">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -303,9 +303,6 @@
   </si>
   <si>
     <t>Boutilier</t>
-  </si>
-  <si>
-    <t>Chaber</t>
   </si>
   <si>
     <t>Fielding</t>
@@ -1121,10 +1118,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}" name="Table2" displayName="Table2" ref="A1:U79" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
-  <autoFilter ref="A1:U79" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U79">
-    <sortCondition ref="D1:D79"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}" name="Table2" displayName="Table2" ref="A1:U78" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
+  <autoFilter ref="A1:U78" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U78">
+    <sortCondition ref="D1:D78"/>
   </sortState>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{BB8E1DF3-CFA5-4F4C-9341-683B2C7FBF55}" name="STAFF NAME" dataDxfId="8"/>
@@ -1351,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U997"/>
+  <dimension ref="A1:U996"/>
   <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
@@ -5262,7 +5259,7 @@
         <v>22</v>
       </c>
       <c r="C61" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" s="12">
         <v>63</v>
@@ -5323,62 +5320,62 @@
       <c r="A62" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="B62" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C62" s="16">
-        <v>0</v>
-      </c>
-      <c r="D62" s="17">
-        <v>64</v>
-      </c>
-      <c r="E62" s="16">
-        <v>0</v>
+      <c r="B62" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="20">
+        <v>1</v>
+      </c>
+      <c r="D62" s="21">
+        <v>65</v>
+      </c>
+      <c r="E62" s="20">
+        <v>1</v>
       </c>
       <c r="F62" s="18">
         <v>6</v>
       </c>
-      <c r="G62" s="16">
+      <c r="G62" s="20">
         <v>7</v>
       </c>
-      <c r="H62" s="16">
-        <v>2</v>
-      </c>
-      <c r="I62" s="16">
-        <v>3</v>
-      </c>
-      <c r="J62" s="16">
-        <v>0</v>
-      </c>
-      <c r="K62" s="16">
-        <v>1</v>
-      </c>
-      <c r="L62" s="16">
+      <c r="H62" s="20">
+        <v>3</v>
+      </c>
+      <c r="I62" s="20">
+        <v>0</v>
+      </c>
+      <c r="J62" s="20">
+        <v>4</v>
+      </c>
+      <c r="K62" s="20">
+        <v>5</v>
+      </c>
+      <c r="L62" s="20">
         <v>8</v>
       </c>
-      <c r="M62" s="16">
+      <c r="M62" s="20">
         <v>9</v>
       </c>
-      <c r="N62" s="16">
-        <v>4</v>
-      </c>
-      <c r="O62" s="16">
-        <v>5</v>
+      <c r="N62" s="20">
+        <v>1</v>
+      </c>
+      <c r="O62" s="20">
+        <v>2</v>
       </c>
       <c r="P62" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q62" s="16">
-        <v>2</v>
-      </c>
-      <c r="R62" s="16">
-        <v>0</v>
-      </c>
-      <c r="S62" s="16">
-        <v>3</v>
-      </c>
-      <c r="T62" s="19">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="Q62" s="20">
+        <v>4</v>
+      </c>
+      <c r="R62" s="20">
+        <v>2</v>
+      </c>
+      <c r="S62" s="20">
+        <v>0</v>
+      </c>
+      <c r="T62" s="22">
+        <v>1</v>
       </c>
       <c r="U62" s="10" t="s">
         <v>32</v>
@@ -5388,61 +5385,61 @@
       <c r="A63" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="B63" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C63" s="20">
-        <v>0</v>
-      </c>
-      <c r="D63" s="21">
-        <v>65</v>
-      </c>
-      <c r="E63" s="20">
-        <v>1</v>
+      <c r="B63" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C63" s="16">
+        <v>1</v>
+      </c>
+      <c r="D63" s="17">
+        <v>66</v>
+      </c>
+      <c r="E63" s="16">
+        <v>0</v>
       </c>
       <c r="F63" s="18">
+        <v>3</v>
+      </c>
+      <c r="G63" s="16">
+        <v>4</v>
+      </c>
+      <c r="H63" s="16">
+        <v>7</v>
+      </c>
+      <c r="I63" s="16">
+        <v>0</v>
+      </c>
+      <c r="J63" s="16">
+        <v>5</v>
+      </c>
+      <c r="K63" s="16">
         <v>6</v>
       </c>
-      <c r="G63" s="20">
-        <v>7</v>
-      </c>
-      <c r="H63" s="20">
-        <v>3</v>
-      </c>
-      <c r="I63" s="20">
-        <v>0</v>
-      </c>
-      <c r="J63" s="20">
-        <v>4</v>
-      </c>
-      <c r="K63" s="20">
-        <v>5</v>
-      </c>
-      <c r="L63" s="20">
+      <c r="L63" s="16">
+        <v>1</v>
+      </c>
+      <c r="M63" s="16">
+        <v>2</v>
+      </c>
+      <c r="N63" s="16">
         <v>8</v>
       </c>
-      <c r="M63" s="20">
+      <c r="O63" s="16">
         <v>9</v>
       </c>
-      <c r="N63" s="20">
-        <v>1</v>
-      </c>
-      <c r="O63" s="20">
-        <v>2</v>
-      </c>
       <c r="P63" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q63" s="20">
-        <v>4</v>
-      </c>
-      <c r="R63" s="20">
-        <v>2</v>
-      </c>
-      <c r="S63" s="20">
-        <v>0</v>
-      </c>
-      <c r="T63" s="22">
+        <v>2</v>
+      </c>
+      <c r="Q63" s="16">
+        <v>3</v>
+      </c>
+      <c r="R63" s="16">
+        <v>4</v>
+      </c>
+      <c r="S63" s="16">
+        <v>0</v>
+      </c>
+      <c r="T63" s="19">
         <v>1</v>
       </c>
       <c r="U63" s="10" t="s">
@@ -5453,385 +5450,385 @@
       <c r="A64" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="B64" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C64" s="16">
-        <v>0</v>
-      </c>
-      <c r="D64" s="17">
-        <v>66</v>
-      </c>
-      <c r="E64" s="16">
+      <c r="B64" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C64" s="20">
+        <v>0</v>
+      </c>
+      <c r="D64" s="21">
+        <v>67</v>
+      </c>
+      <c r="E64" s="20">
         <v>0</v>
       </c>
       <c r="F64" s="18">
-        <v>3</v>
-      </c>
-      <c r="G64" s="16">
-        <v>4</v>
-      </c>
-      <c r="H64" s="16">
+        <v>4</v>
+      </c>
+      <c r="G64" s="20">
+        <v>5</v>
+      </c>
+      <c r="H64" s="20">
+        <v>2</v>
+      </c>
+      <c r="I64" s="20">
+        <v>3</v>
+      </c>
+      <c r="J64" s="20">
+        <v>0</v>
+      </c>
+      <c r="K64" s="20">
+        <v>1</v>
+      </c>
+      <c r="L64" s="20">
+        <v>8</v>
+      </c>
+      <c r="M64" s="20">
+        <v>9</v>
+      </c>
+      <c r="N64" s="20">
+        <v>6</v>
+      </c>
+      <c r="O64" s="20">
         <v>7</v>
       </c>
-      <c r="I64" s="16">
-        <v>0</v>
-      </c>
-      <c r="J64" s="16">
-        <v>5</v>
-      </c>
-      <c r="K64" s="16">
-        <v>6</v>
-      </c>
-      <c r="L64" s="16">
-        <v>1</v>
-      </c>
-      <c r="M64" s="16">
-        <v>2</v>
-      </c>
-      <c r="N64" s="16">
-        <v>8</v>
-      </c>
-      <c r="O64" s="16">
-        <v>9</v>
-      </c>
       <c r="P64" s="18">
-        <v>2</v>
-      </c>
-      <c r="Q64" s="16">
-        <v>3</v>
-      </c>
-      <c r="R64" s="16">
-        <v>4</v>
-      </c>
-      <c r="S64" s="16">
-        <v>0</v>
-      </c>
-      <c r="T64" s="19">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q64" s="20">
+        <v>2</v>
+      </c>
+      <c r="R64" s="20">
+        <v>0</v>
+      </c>
+      <c r="S64" s="20">
+        <v>3</v>
+      </c>
+      <c r="T64" s="22">
+        <v>4</v>
       </c>
       <c r="U64" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="65" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A65" s="37" t="s">
+      <c r="A65" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="B65" s="20" t="s">
+      <c r="B65" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C65" s="20">
-        <v>0</v>
-      </c>
-      <c r="D65" s="21">
-        <v>67</v>
-      </c>
-      <c r="E65" s="20">
-        <v>0</v>
-      </c>
-      <c r="F65" s="18">
-        <v>4</v>
-      </c>
-      <c r="G65" s="20">
+      <c r="C65" s="23">
+        <v>0</v>
+      </c>
+      <c r="D65" s="24">
+        <v>68</v>
+      </c>
+      <c r="E65" s="23">
+        <v>1</v>
+      </c>
+      <c r="F65" s="13">
+        <v>6</v>
+      </c>
+      <c r="G65" s="23">
+        <v>7</v>
+      </c>
+      <c r="H65" s="23">
         <v>5</v>
       </c>
-      <c r="H65" s="20">
-        <v>2</v>
-      </c>
-      <c r="I65" s="20">
-        <v>3</v>
-      </c>
-      <c r="J65" s="20">
-        <v>0</v>
-      </c>
-      <c r="K65" s="20">
-        <v>1</v>
-      </c>
-      <c r="L65" s="20">
+      <c r="I65" s="23">
+        <v>2</v>
+      </c>
+      <c r="J65" s="23">
         <v>8</v>
       </c>
-      <c r="M65" s="20">
+      <c r="K65" s="23">
         <v>9</v>
       </c>
-      <c r="N65" s="20">
-        <v>6</v>
-      </c>
-      <c r="O65" s="20">
-        <v>7</v>
-      </c>
-      <c r="P65" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q65" s="20">
-        <v>2</v>
-      </c>
-      <c r="R65" s="20">
-        <v>0</v>
-      </c>
-      <c r="S65" s="20">
-        <v>3</v>
-      </c>
-      <c r="T65" s="22">
-        <v>4</v>
-      </c>
-      <c r="U65" s="10" t="s">
-        <v>32</v>
+      <c r="L65" s="23">
+        <v>0</v>
+      </c>
+      <c r="M65" s="23">
+        <v>1</v>
+      </c>
+      <c r="N65" s="23">
+        <v>3</v>
+      </c>
+      <c r="O65" s="23">
+        <v>4</v>
+      </c>
+      <c r="P65" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q65" s="23">
+        <v>3</v>
+      </c>
+      <c r="R65" s="23">
+        <v>4</v>
+      </c>
+      <c r="S65" s="23">
+        <v>0</v>
+      </c>
+      <c r="T65" s="25">
+        <v>1</v>
+      </c>
+      <c r="U65" s="15" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="66" spans="1:21" ht="15.75" customHeight="1">
       <c r="A66" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="B66" s="23" t="s">
+      <c r="B66" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C66" s="23">
-        <v>0</v>
-      </c>
-      <c r="D66" s="24">
-        <v>68</v>
-      </c>
-      <c r="E66" s="23">
-        <v>1</v>
+      <c r="C66" s="11">
+        <v>1</v>
+      </c>
+      <c r="D66" s="12">
+        <v>69</v>
+      </c>
+      <c r="E66" s="11">
+        <v>0</v>
       </c>
       <c r="F66" s="13">
+        <v>4</v>
+      </c>
+      <c r="G66" s="11">
+        <v>5</v>
+      </c>
+      <c r="H66" s="11">
+        <v>2</v>
+      </c>
+      <c r="I66" s="11">
+        <v>3</v>
+      </c>
+      <c r="J66" s="11">
+        <v>0</v>
+      </c>
+      <c r="K66" s="11">
+        <v>1</v>
+      </c>
+      <c r="L66" s="11">
         <v>6</v>
       </c>
-      <c r="G66" s="23">
+      <c r="M66" s="11">
         <v>7</v>
       </c>
-      <c r="H66" s="23">
-        <v>5</v>
-      </c>
-      <c r="I66" s="23">
-        <v>2</v>
-      </c>
-      <c r="J66" s="23">
+      <c r="N66" s="11">
         <v>8</v>
       </c>
-      <c r="K66" s="23">
+      <c r="O66" s="11">
         <v>9</v>
       </c>
-      <c r="L66" s="23">
-        <v>0</v>
-      </c>
-      <c r="M66" s="23">
-        <v>1</v>
-      </c>
-      <c r="N66" s="23">
-        <v>3</v>
-      </c>
-      <c r="O66" s="23">
-        <v>4</v>
-      </c>
       <c r="P66" s="13">
-        <v>2</v>
-      </c>
-      <c r="Q66" s="23">
-        <v>3</v>
-      </c>
-      <c r="R66" s="23">
-        <v>4</v>
-      </c>
-      <c r="S66" s="23">
-        <v>0</v>
-      </c>
-      <c r="T66" s="25">
-        <v>1</v>
-      </c>
-      <c r="U66" s="15" t="s">
-        <v>25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q66" s="11">
+        <v>1</v>
+      </c>
+      <c r="R66" s="11">
+        <v>2</v>
+      </c>
+      <c r="S66" s="11">
+        <v>3</v>
+      </c>
+      <c r="T66" s="14">
+        <v>4</v>
+      </c>
+      <c r="U66" s="15"/>
     </row>
     <row r="67" spans="1:21" ht="15.75" customHeight="1">
       <c r="A67" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C67" s="11">
-        <v>1</v>
-      </c>
-      <c r="D67" s="12">
-        <v>69</v>
-      </c>
-      <c r="E67" s="11">
-        <v>0</v>
+      <c r="C67" s="23">
+        <v>0</v>
+      </c>
+      <c r="D67" s="24">
+        <v>70</v>
+      </c>
+      <c r="E67" s="23">
+        <v>1</v>
       </c>
       <c r="F67" s="13">
-        <v>4</v>
-      </c>
-      <c r="G67" s="11">
         <v>5</v>
       </c>
-      <c r="H67" s="11">
-        <v>2</v>
-      </c>
-      <c r="I67" s="11">
-        <v>3</v>
-      </c>
-      <c r="J67" s="11">
-        <v>0</v>
-      </c>
-      <c r="K67" s="11">
-        <v>1</v>
-      </c>
-      <c r="L67" s="11">
+      <c r="G67" s="23">
         <v>6</v>
       </c>
-      <c r="M67" s="11">
+      <c r="H67" s="23">
         <v>7</v>
       </c>
-      <c r="N67" s="11">
+      <c r="I67" s="23">
+        <v>2</v>
+      </c>
+      <c r="J67" s="23">
         <v>8</v>
       </c>
-      <c r="O67" s="11">
+      <c r="K67" s="23">
         <v>9</v>
       </c>
+      <c r="L67" s="23">
+        <v>0</v>
+      </c>
+      <c r="M67" s="23">
+        <v>1</v>
+      </c>
+      <c r="N67" s="23">
+        <v>3</v>
+      </c>
+      <c r="O67" s="23">
+        <v>4</v>
+      </c>
       <c r="P67" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="11">
-        <v>1</v>
-      </c>
-      <c r="R67" s="11">
-        <v>2</v>
-      </c>
-      <c r="S67" s="11">
-        <v>3</v>
-      </c>
-      <c r="T67" s="14">
-        <v>4</v>
-      </c>
-      <c r="U67" s="15"/>
+        <v>2</v>
+      </c>
+      <c r="Q67" s="23">
+        <v>3</v>
+      </c>
+      <c r="R67" s="23">
+        <v>4</v>
+      </c>
+      <c r="S67" s="23">
+        <v>0</v>
+      </c>
+      <c r="T67" s="25">
+        <v>1</v>
+      </c>
+      <c r="U67" s="15" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="68" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A68" s="36" t="s">
+      <c r="A68" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="B68" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C68" s="23">
-        <v>0</v>
-      </c>
-      <c r="D68" s="24">
-        <v>70</v>
-      </c>
-      <c r="E68" s="23">
-        <v>1</v>
-      </c>
-      <c r="F68" s="13">
+      <c r="B68" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" s="20">
+        <v>0</v>
+      </c>
+      <c r="D68" s="21">
+        <v>71</v>
+      </c>
+      <c r="E68" s="20">
+        <v>1</v>
+      </c>
+      <c r="F68" s="18">
         <v>5</v>
       </c>
-      <c r="G68" s="23">
+      <c r="G68" s="20">
+        <v>3</v>
+      </c>
+      <c r="H68" s="20">
+        <v>4</v>
+      </c>
+      <c r="I68" s="20">
+        <v>2</v>
+      </c>
+      <c r="J68" s="20">
+        <v>1</v>
+      </c>
+      <c r="K68" s="20">
+        <v>0</v>
+      </c>
+      <c r="L68" s="20">
+        <v>8</v>
+      </c>
+      <c r="M68" s="20">
         <v>6</v>
       </c>
-      <c r="H68" s="23">
+      <c r="N68" s="20">
+        <v>9</v>
+      </c>
+      <c r="O68" s="20">
         <v>7</v>
       </c>
-      <c r="I68" s="23">
-        <v>2</v>
-      </c>
-      <c r="J68" s="23">
-        <v>8</v>
-      </c>
-      <c r="K68" s="23">
-        <v>9</v>
-      </c>
-      <c r="L68" s="23">
-        <v>0</v>
-      </c>
-      <c r="M68" s="23">
-        <v>1</v>
-      </c>
-      <c r="N68" s="23">
-        <v>3</v>
-      </c>
-      <c r="O68" s="23">
-        <v>4</v>
-      </c>
-      <c r="P68" s="13">
-        <v>2</v>
-      </c>
-      <c r="Q68" s="23">
-        <v>3</v>
-      </c>
-      <c r="R68" s="23">
-        <v>4</v>
-      </c>
-      <c r="S68" s="23">
-        <v>0</v>
-      </c>
-      <c r="T68" s="25">
-        <v>1</v>
-      </c>
-      <c r="U68" s="15" t="s">
-        <v>32</v>
+      <c r="P68" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q68" s="20">
+        <v>1</v>
+      </c>
+      <c r="R68" s="20">
+        <v>0</v>
+      </c>
+      <c r="S68" s="20">
+        <v>4</v>
+      </c>
+      <c r="T68" s="22">
+        <v>2</v>
+      </c>
+      <c r="U68" s="10" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="69" spans="1:21" ht="15.75" customHeight="1">
       <c r="A69" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="B69" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C69" s="20">
-        <v>0</v>
-      </c>
-      <c r="D69" s="21">
-        <v>71</v>
-      </c>
-      <c r="E69" s="20">
-        <v>1</v>
+      <c r="B69" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C69" s="16">
+        <v>0</v>
+      </c>
+      <c r="D69" s="17">
+        <v>72</v>
+      </c>
+      <c r="E69" s="16">
+        <v>0</v>
       </c>
       <c r="F69" s="18">
+        <v>4</v>
+      </c>
+      <c r="G69" s="19">
         <v>5</v>
       </c>
-      <c r="G69" s="20">
-        <v>3</v>
-      </c>
-      <c r="H69" s="20">
-        <v>4</v>
-      </c>
-      <c r="I69" s="20">
-        <v>2</v>
-      </c>
-      <c r="J69" s="20">
-        <v>1</v>
-      </c>
-      <c r="K69" s="20">
-        <v>0</v>
-      </c>
-      <c r="L69" s="20">
+      <c r="H69" s="19">
+        <v>3</v>
+      </c>
+      <c r="I69" s="19">
+        <v>0</v>
+      </c>
+      <c r="J69" s="19">
+        <v>1</v>
+      </c>
+      <c r="K69" s="19">
+        <v>2</v>
+      </c>
+      <c r="L69" s="19">
         <v>8</v>
       </c>
-      <c r="M69" s="20">
+      <c r="M69" s="19">
+        <v>9</v>
+      </c>
+      <c r="N69" s="19">
         <v>6</v>
       </c>
-      <c r="N69" s="20">
-        <v>9</v>
-      </c>
-      <c r="O69" s="20">
+      <c r="O69" s="19">
         <v>7</v>
       </c>
       <c r="P69" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q69" s="20">
-        <v>1</v>
-      </c>
-      <c r="R69" s="20">
-        <v>0</v>
-      </c>
-      <c r="S69" s="20">
-        <v>4</v>
-      </c>
-      <c r="T69" s="22">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q69" s="19">
+        <v>2</v>
+      </c>
+      <c r="R69" s="19">
+        <v>0</v>
+      </c>
+      <c r="S69" s="19">
+        <v>3</v>
+      </c>
+      <c r="T69" s="19">
+        <v>4</v>
       </c>
       <c r="U69" s="10" t="s">
         <v>25</v>
@@ -5842,258 +5839,258 @@
         <v>95</v>
       </c>
       <c r="B70" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" s="16">
+        <v>0</v>
+      </c>
+      <c r="D70" s="17">
+        <v>73</v>
+      </c>
+      <c r="E70" s="16">
+        <v>0</v>
+      </c>
+      <c r="F70" s="18">
+        <v>7</v>
+      </c>
+      <c r="G70" s="16">
+        <v>8</v>
+      </c>
+      <c r="H70" s="16">
+        <v>9</v>
+      </c>
+      <c r="I70" s="16">
+        <v>4</v>
+      </c>
+      <c r="J70" s="16">
+        <v>5</v>
+      </c>
+      <c r="K70" s="16">
+        <v>6</v>
+      </c>
+      <c r="L70" s="16">
+        <v>0</v>
+      </c>
+      <c r="M70" s="16">
+        <v>1</v>
+      </c>
+      <c r="N70" s="16">
+        <v>2</v>
+      </c>
+      <c r="O70" s="16">
+        <v>3</v>
+      </c>
+      <c r="P70" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q70" s="16">
+        <v>4</v>
+      </c>
+      <c r="R70" s="16">
+        <v>0</v>
+      </c>
+      <c r="S70" s="16">
+        <v>1</v>
+      </c>
+      <c r="T70" s="19">
+        <v>2</v>
+      </c>
+      <c r="U70" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A71" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C71" s="11">
+        <v>0</v>
+      </c>
+      <c r="D71" s="12">
+        <v>74</v>
+      </c>
+      <c r="E71" s="11">
+        <v>1</v>
+      </c>
+      <c r="F71" s="13">
+        <v>7</v>
+      </c>
+      <c r="G71" s="11">
+        <v>6</v>
+      </c>
+      <c r="H71" s="11">
+        <v>5</v>
+      </c>
+      <c r="I71" s="11">
+        <v>4</v>
+      </c>
+      <c r="J71" s="11">
+        <v>9</v>
+      </c>
+      <c r="K71" s="11">
+        <v>8</v>
+      </c>
+      <c r="L71" s="11">
+        <v>1</v>
+      </c>
+      <c r="M71" s="11">
+        <v>0</v>
+      </c>
+      <c r="N71" s="11">
+        <v>3</v>
+      </c>
+      <c r="O71" s="11">
+        <v>2</v>
+      </c>
+      <c r="P71" s="13">
+        <v>3</v>
+      </c>
+      <c r="Q71" s="11">
+        <v>2</v>
+      </c>
+      <c r="R71" s="11">
+        <v>4</v>
+      </c>
+      <c r="S71" s="11">
+        <v>1</v>
+      </c>
+      <c r="T71" s="14">
+        <v>0</v>
+      </c>
+      <c r="U71" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A72" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B72" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C70" s="16">
-        <v>0</v>
-      </c>
-      <c r="D70" s="17">
-        <v>72</v>
-      </c>
-      <c r="E70" s="16">
-        <v>0</v>
-      </c>
-      <c r="F70" s="18">
-        <v>4</v>
-      </c>
-      <c r="G70" s="19">
+      <c r="C72" s="16">
+        <v>0</v>
+      </c>
+      <c r="D72" s="17">
+        <v>76</v>
+      </c>
+      <c r="E72" s="16">
+        <v>1</v>
+      </c>
+      <c r="F72" s="18">
+        <v>8</v>
+      </c>
+      <c r="G72" s="16">
+        <v>9</v>
+      </c>
+      <c r="H72" s="16">
         <v>5</v>
       </c>
-      <c r="H70" s="19">
-        <v>3</v>
-      </c>
-      <c r="I70" s="19">
-        <v>0</v>
-      </c>
-      <c r="J70" s="19">
-        <v>1</v>
-      </c>
-      <c r="K70" s="19">
-        <v>2</v>
-      </c>
-      <c r="L70" s="19">
+      <c r="I72" s="16">
+        <v>4</v>
+      </c>
+      <c r="J72" s="16">
+        <v>6</v>
+      </c>
+      <c r="K72" s="16">
+        <v>7</v>
+      </c>
+      <c r="L72" s="16">
+        <v>0</v>
+      </c>
+      <c r="M72" s="16">
+        <v>1</v>
+      </c>
+      <c r="N72" s="16">
+        <v>2</v>
+      </c>
+      <c r="O72" s="16">
+        <v>3</v>
+      </c>
+      <c r="P72" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="16">
+        <v>4</v>
+      </c>
+      <c r="R72" s="16">
+        <v>2</v>
+      </c>
+      <c r="S72" s="16">
+        <v>0</v>
+      </c>
+      <c r="T72" s="19">
+        <v>1</v>
+      </c>
+      <c r="U72" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A73" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C73" s="11">
+        <v>0</v>
+      </c>
+      <c r="D73" s="12">
+        <v>77</v>
+      </c>
+      <c r="E73" s="11">
+        <v>0</v>
+      </c>
+      <c r="F73" s="13">
+        <v>7</v>
+      </c>
+      <c r="G73" s="11">
+        <v>4</v>
+      </c>
+      <c r="H73" s="11">
+        <v>5</v>
+      </c>
+      <c r="I73" s="11">
+        <v>2</v>
+      </c>
+      <c r="J73" s="11">
+        <v>0</v>
+      </c>
+      <c r="K73" s="11">
+        <v>1</v>
+      </c>
+      <c r="L73" s="11">
+        <v>6</v>
+      </c>
+      <c r="M73" s="11">
+        <v>3</v>
+      </c>
+      <c r="N73" s="11">
+        <v>9</v>
+      </c>
+      <c r="O73" s="11">
         <v>8</v>
       </c>
-      <c r="M70" s="19">
-        <v>9</v>
-      </c>
-      <c r="N70" s="19">
-        <v>6</v>
-      </c>
-      <c r="O70" s="19">
-        <v>7</v>
-      </c>
-      <c r="P70" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q70" s="19">
-        <v>2</v>
-      </c>
-      <c r="R70" s="19">
-        <v>0</v>
-      </c>
-      <c r="S70" s="19">
-        <v>3</v>
-      </c>
-      <c r="T70" s="19">
-        <v>4</v>
-      </c>
-      <c r="U70" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A71" s="37" t="s">
-        <v>96</v>
-      </c>
-      <c r="B71" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C71" s="16">
-        <v>0</v>
-      </c>
-      <c r="D71" s="17">
-        <v>73</v>
-      </c>
-      <c r="E71" s="16">
-        <v>0</v>
-      </c>
-      <c r="F71" s="18">
-        <v>7</v>
-      </c>
-      <c r="G71" s="16">
-        <v>8</v>
-      </c>
-      <c r="H71" s="16">
-        <v>9</v>
-      </c>
-      <c r="I71" s="16">
-        <v>4</v>
-      </c>
-      <c r="J71" s="16">
-        <v>5</v>
-      </c>
-      <c r="K71" s="16">
-        <v>6</v>
-      </c>
-      <c r="L71" s="16">
-        <v>0</v>
-      </c>
-      <c r="M71" s="16">
-        <v>1</v>
-      </c>
-      <c r="N71" s="16">
-        <v>2</v>
-      </c>
-      <c r="O71" s="16">
-        <v>3</v>
-      </c>
-      <c r="P71" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q71" s="16">
-        <v>4</v>
-      </c>
-      <c r="R71" s="16">
-        <v>0</v>
-      </c>
-      <c r="S71" s="16">
-        <v>1</v>
-      </c>
-      <c r="T71" s="19">
-        <v>2</v>
-      </c>
-      <c r="U71" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A72" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="B72" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C72" s="11">
-        <v>0</v>
-      </c>
-      <c r="D72" s="12">
-        <v>74</v>
-      </c>
-      <c r="E72" s="11">
-        <v>1</v>
-      </c>
-      <c r="F72" s="13">
-        <v>7</v>
-      </c>
-      <c r="G72" s="11">
-        <v>6</v>
-      </c>
-      <c r="H72" s="11">
-        <v>5</v>
-      </c>
-      <c r="I72" s="11">
-        <v>4</v>
-      </c>
-      <c r="J72" s="11">
-        <v>9</v>
-      </c>
-      <c r="K72" s="11">
-        <v>8</v>
-      </c>
-      <c r="L72" s="11">
-        <v>1</v>
-      </c>
-      <c r="M72" s="11">
-        <v>0</v>
-      </c>
-      <c r="N72" s="11">
-        <v>3</v>
-      </c>
-      <c r="O72" s="11">
-        <v>2</v>
-      </c>
-      <c r="P72" s="13">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="11">
-        <v>2</v>
-      </c>
-      <c r="R72" s="11">
-        <v>4</v>
-      </c>
-      <c r="S72" s="11">
-        <v>1</v>
-      </c>
-      <c r="T72" s="14">
-        <v>0</v>
-      </c>
-      <c r="U72" s="15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="73" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A73" s="37" t="s">
-        <v>98</v>
-      </c>
-      <c r="B73" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C73" s="16">
-        <v>0</v>
-      </c>
-      <c r="D73" s="17">
-        <v>76</v>
-      </c>
-      <c r="E73" s="16">
-        <v>1</v>
-      </c>
-      <c r="F73" s="18">
-        <v>8</v>
-      </c>
-      <c r="G73" s="16">
-        <v>9</v>
-      </c>
-      <c r="H73" s="16">
-        <v>5</v>
-      </c>
-      <c r="I73" s="16">
-        <v>4</v>
-      </c>
-      <c r="J73" s="16">
-        <v>6</v>
-      </c>
-      <c r="K73" s="16">
-        <v>7</v>
-      </c>
-      <c r="L73" s="16">
-        <v>0</v>
-      </c>
-      <c r="M73" s="16">
-        <v>1</v>
-      </c>
-      <c r="N73" s="16">
-        <v>2</v>
-      </c>
-      <c r="O73" s="16">
-        <v>3</v>
-      </c>
-      <c r="P73" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q73" s="16">
-        <v>4</v>
-      </c>
-      <c r="R73" s="16">
-        <v>2</v>
-      </c>
-      <c r="S73" s="16">
-        <v>0</v>
-      </c>
-      <c r="T73" s="19">
-        <v>1</v>
-      </c>
-      <c r="U73" s="10" t="s">
+      <c r="P73" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q73" s="11">
+        <v>1</v>
+      </c>
+      <c r="R73" s="11">
+        <v>0</v>
+      </c>
+      <c r="S73" s="11">
+        <v>4</v>
+      </c>
+      <c r="T73" s="14">
+        <v>3</v>
+      </c>
+      <c r="U73" s="15" t="s">
         <v>32</v>
       </c>
     </row>
@@ -6101,192 +6098,192 @@
       <c r="A74" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="B74" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C74" s="11">
-        <v>0</v>
-      </c>
-      <c r="D74" s="12">
-        <v>77</v>
-      </c>
-      <c r="E74" s="11">
+      <c r="B74" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" s="23">
+        <v>0</v>
+      </c>
+      <c r="D74" s="24">
+        <v>78</v>
+      </c>
+      <c r="E74" s="23">
         <v>0</v>
       </c>
       <c r="F74" s="13">
+        <v>1</v>
+      </c>
+      <c r="G74" s="23">
+        <v>3</v>
+      </c>
+      <c r="H74" s="23">
+        <v>8</v>
+      </c>
+      <c r="I74" s="23">
+        <v>9</v>
+      </c>
+      <c r="J74" s="23">
+        <v>5</v>
+      </c>
+      <c r="K74" s="23">
+        <v>4</v>
+      </c>
+      <c r="L74" s="23">
+        <v>6</v>
+      </c>
+      <c r="M74" s="23">
+        <v>0</v>
+      </c>
+      <c r="N74" s="23">
         <v>7</v>
       </c>
-      <c r="G74" s="11">
-        <v>4</v>
-      </c>
-      <c r="H74" s="11">
+      <c r="O74" s="23">
+        <v>2</v>
+      </c>
+      <c r="P74" s="13">
+        <v>3</v>
+      </c>
+      <c r="Q74" s="23">
+        <v>4</v>
+      </c>
+      <c r="R74" s="23">
+        <v>0</v>
+      </c>
+      <c r="S74" s="23">
+        <v>1</v>
+      </c>
+      <c r="T74" s="25">
+        <v>2</v>
+      </c>
+      <c r="U74" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" ht="15.75" customHeight="1">
+      <c r="A75" s="37" t="s">
+        <v>100</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C75" s="20">
+        <v>0</v>
+      </c>
+      <c r="D75" s="21">
+        <v>79</v>
+      </c>
+      <c r="E75" s="20">
+        <v>0</v>
+      </c>
+      <c r="F75" s="18">
+        <v>6</v>
+      </c>
+      <c r="G75" s="20">
+        <v>7</v>
+      </c>
+      <c r="H75" s="20">
+        <v>4</v>
+      </c>
+      <c r="I75" s="20">
         <v>5</v>
       </c>
-      <c r="I74" s="11">
-        <v>2</v>
-      </c>
-      <c r="J74" s="11">
-        <v>0</v>
-      </c>
-      <c r="K74" s="11">
-        <v>1</v>
-      </c>
-      <c r="L74" s="11">
-        <v>6</v>
-      </c>
-      <c r="M74" s="11">
-        <v>3</v>
-      </c>
-      <c r="N74" s="11">
+      <c r="J75" s="20">
+        <v>8</v>
+      </c>
+      <c r="K75" s="20">
         <v>9</v>
       </c>
-      <c r="O74" s="11">
-        <v>8</v>
-      </c>
-      <c r="P74" s="13">
-        <v>2</v>
-      </c>
-      <c r="Q74" s="11">
-        <v>1</v>
-      </c>
-      <c r="R74" s="11">
-        <v>0</v>
-      </c>
-      <c r="S74" s="11">
-        <v>4</v>
-      </c>
-      <c r="T74" s="14">
-        <v>3</v>
-      </c>
-      <c r="U74" s="15" t="s">
+      <c r="L75" s="20">
+        <v>0</v>
+      </c>
+      <c r="M75" s="20">
+        <v>1</v>
+      </c>
+      <c r="N75" s="20">
+        <v>2</v>
+      </c>
+      <c r="O75" s="20">
+        <v>3</v>
+      </c>
+      <c r="P75" s="18">
+        <v>2</v>
+      </c>
+      <c r="Q75" s="20">
+        <v>3</v>
+      </c>
+      <c r="R75" s="20">
+        <v>4</v>
+      </c>
+      <c r="S75" s="20">
+        <v>0</v>
+      </c>
+      <c r="T75" s="22">
+        <v>1</v>
+      </c>
+      <c r="U75" s="10" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A75" s="36" t="s">
-        <v>100</v>
-      </c>
-      <c r="B75" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C75" s="23">
-        <v>0</v>
-      </c>
-      <c r="D75" s="24">
-        <v>78</v>
-      </c>
-      <c r="E75" s="23">
-        <v>0</v>
-      </c>
-      <c r="F75" s="13">
-        <v>1</v>
-      </c>
-      <c r="G75" s="23">
-        <v>3</v>
-      </c>
-      <c r="H75" s="23">
-        <v>8</v>
-      </c>
-      <c r="I75" s="23">
-        <v>9</v>
-      </c>
-      <c r="J75" s="23">
-        <v>5</v>
-      </c>
-      <c r="K75" s="23">
-        <v>4</v>
-      </c>
-      <c r="L75" s="23">
-        <v>6</v>
-      </c>
-      <c r="M75" s="23">
-        <v>0</v>
-      </c>
-      <c r="N75" s="23">
-        <v>7</v>
-      </c>
-      <c r="O75" s="23">
-        <v>2</v>
-      </c>
-      <c r="P75" s="13">
-        <v>3</v>
-      </c>
-      <c r="Q75" s="23">
-        <v>4</v>
-      </c>
-      <c r="R75" s="23">
-        <v>0</v>
-      </c>
-      <c r="S75" s="23">
-        <v>1</v>
-      </c>
-      <c r="T75" s="25">
-        <v>2</v>
-      </c>
-      <c r="U75" s="15" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="76" spans="1:21" ht="15.75" customHeight="1">
       <c r="A76" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="B76" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C76" s="20">
-        <v>0</v>
-      </c>
-      <c r="D76" s="21">
-        <v>79</v>
-      </c>
-      <c r="E76" s="20">
-        <v>0</v>
+      <c r="B76" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C76" s="16">
+        <v>0</v>
+      </c>
+      <c r="D76" s="17">
+        <v>80</v>
+      </c>
+      <c r="E76" s="16">
+        <v>1</v>
       </c>
       <c r="F76" s="18">
         <v>6</v>
       </c>
-      <c r="G76" s="20">
+      <c r="G76" s="16">
         <v>7</v>
       </c>
-      <c r="H76" s="20">
-        <v>4</v>
-      </c>
-      <c r="I76" s="20">
+      <c r="H76" s="16">
+        <v>2</v>
+      </c>
+      <c r="I76" s="16">
+        <v>3</v>
+      </c>
+      <c r="J76" s="16">
+        <v>0</v>
+      </c>
+      <c r="K76" s="16">
+        <v>1</v>
+      </c>
+      <c r="L76" s="16">
+        <v>8</v>
+      </c>
+      <c r="M76" s="16">
+        <v>9</v>
+      </c>
+      <c r="N76" s="16">
+        <v>4</v>
+      </c>
+      <c r="O76" s="16">
         <v>5</v>
       </c>
-      <c r="J76" s="20">
-        <v>8</v>
-      </c>
-      <c r="K76" s="20">
-        <v>9</v>
-      </c>
-      <c r="L76" s="20">
-        <v>0</v>
-      </c>
-      <c r="M76" s="20">
-        <v>1</v>
-      </c>
-      <c r="N76" s="20">
-        <v>2</v>
-      </c>
-      <c r="O76" s="20">
-        <v>3</v>
-      </c>
       <c r="P76" s="18">
-        <v>2</v>
-      </c>
-      <c r="Q76" s="20">
-        <v>3</v>
-      </c>
-      <c r="R76" s="20">
-        <v>4</v>
-      </c>
-      <c r="S76" s="20">
-        <v>0</v>
-      </c>
-      <c r="T76" s="22">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q76" s="16">
+        <v>2</v>
+      </c>
+      <c r="R76" s="16">
+        <v>0</v>
+      </c>
+      <c r="S76" s="16">
+        <v>3</v>
+      </c>
+      <c r="T76" s="19">
+        <v>4</v>
       </c>
       <c r="U76" s="10" t="s">
         <v>32</v>
@@ -6296,196 +6293,134 @@
       <c r="A77" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="B77" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C77" s="16">
-        <v>0</v>
-      </c>
-      <c r="D77" s="17">
-        <v>80</v>
-      </c>
-      <c r="E77" s="16">
+      <c r="B77" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" s="20">
+        <v>0</v>
+      </c>
+      <c r="D77" s="21">
+        <v>81</v>
+      </c>
+      <c r="E77" s="20">
         <v>1</v>
       </c>
       <c r="F77" s="18">
+        <v>5</v>
+      </c>
+      <c r="G77" s="20">
         <v>6</v>
       </c>
-      <c r="G77" s="16">
+      <c r="H77" s="20">
         <v>7</v>
       </c>
-      <c r="H77" s="16">
-        <v>2</v>
-      </c>
-      <c r="I77" s="16">
-        <v>3</v>
-      </c>
-      <c r="J77" s="16">
-        <v>0</v>
-      </c>
-      <c r="K77" s="16">
-        <v>1</v>
-      </c>
-      <c r="L77" s="16">
+      <c r="I77" s="20">
+        <v>2</v>
+      </c>
+      <c r="J77" s="20">
         <v>8</v>
       </c>
-      <c r="M77" s="16">
+      <c r="K77" s="20">
         <v>9</v>
       </c>
-      <c r="N77" s="16">
-        <v>4</v>
-      </c>
-      <c r="O77" s="16">
-        <v>5</v>
+      <c r="L77" s="20">
+        <v>0</v>
+      </c>
+      <c r="M77" s="20">
+        <v>1</v>
+      </c>
+      <c r="N77" s="20">
+        <v>3</v>
+      </c>
+      <c r="O77" s="20">
+        <v>4</v>
       </c>
       <c r="P77" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q77" s="16">
-        <v>2</v>
-      </c>
-      <c r="R77" s="16">
-        <v>0</v>
-      </c>
-      <c r="S77" s="16">
-        <v>3</v>
-      </c>
-      <c r="T77" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="20">
+        <v>1</v>
+      </c>
+      <c r="R77" s="20">
+        <v>2</v>
+      </c>
+      <c r="S77" s="20">
+        <v>3</v>
+      </c>
+      <c r="T77" s="22">
         <v>4</v>
       </c>
       <c r="U77" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A78" s="37" t="s">
+    <row r="78" spans="1:21" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A78" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B78" s="20" t="s">
+      <c r="B78" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C78" s="20">
-        <v>0</v>
-      </c>
-      <c r="D78" s="21">
-        <v>81</v>
-      </c>
-      <c r="E78" s="20">
-        <v>1</v>
-      </c>
-      <c r="F78" s="18">
+      <c r="C78" s="41">
+        <v>0</v>
+      </c>
+      <c r="D78" s="42">
+        <v>82</v>
+      </c>
+      <c r="E78" s="41">
+        <v>0</v>
+      </c>
+      <c r="F78" s="43">
         <v>5</v>
       </c>
-      <c r="G78" s="20">
+      <c r="G78" s="44">
         <v>6</v>
       </c>
-      <c r="H78" s="20">
+      <c r="H78" s="44">
         <v>7</v>
       </c>
-      <c r="I78" s="20">
-        <v>2</v>
-      </c>
-      <c r="J78" s="20">
+      <c r="I78" s="44">
+        <v>0</v>
+      </c>
+      <c r="J78" s="44">
+        <v>1</v>
+      </c>
+      <c r="K78" s="44">
+        <v>2</v>
+      </c>
+      <c r="L78" s="44">
+        <v>3</v>
+      </c>
+      <c r="M78" s="44">
+        <v>4</v>
+      </c>
+      <c r="N78" s="44">
         <v>8</v>
       </c>
-      <c r="K78" s="20">
+      <c r="O78" s="44">
         <v>9</v>
       </c>
-      <c r="L78" s="20">
-        <v>0</v>
-      </c>
-      <c r="M78" s="20">
-        <v>1</v>
-      </c>
-      <c r="N78" s="20">
-        <v>3</v>
-      </c>
-      <c r="O78" s="20">
-        <v>4</v>
-      </c>
-      <c r="P78" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="20">
-        <v>1</v>
-      </c>
-      <c r="R78" s="20">
-        <v>2</v>
-      </c>
-      <c r="S78" s="20">
-        <v>3</v>
-      </c>
-      <c r="T78" s="22">
-        <v>4</v>
-      </c>
-      <c r="U78" s="10" t="s">
+      <c r="P78" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="44">
+        <v>1</v>
+      </c>
+      <c r="R78" s="44">
+        <v>2</v>
+      </c>
+      <c r="S78" s="44">
+        <v>3</v>
+      </c>
+      <c r="T78" s="45">
+        <v>4</v>
+      </c>
+      <c r="U78" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="79" spans="1:21" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A79" s="40" t="s">
-        <v>104</v>
-      </c>
-      <c r="B79" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C79" s="41">
-        <v>0</v>
-      </c>
-      <c r="D79" s="42">
-        <v>82</v>
-      </c>
-      <c r="E79" s="41">
-        <v>0</v>
-      </c>
-      <c r="F79" s="43">
-        <v>5</v>
-      </c>
-      <c r="G79" s="44">
-        <v>6</v>
-      </c>
-      <c r="H79" s="44">
-        <v>7</v>
-      </c>
-      <c r="I79" s="44">
-        <v>0</v>
-      </c>
-      <c r="J79" s="44">
-        <v>1</v>
-      </c>
-      <c r="K79" s="44">
-        <v>2</v>
-      </c>
-      <c r="L79" s="44">
-        <v>3</v>
-      </c>
-      <c r="M79" s="44">
-        <v>4</v>
-      </c>
-      <c r="N79" s="44">
-        <v>8</v>
-      </c>
-      <c r="O79" s="44">
-        <v>9</v>
-      </c>
-      <c r="P79" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q79" s="44">
-        <v>1</v>
-      </c>
-      <c r="R79" s="44">
-        <v>2</v>
-      </c>
-      <c r="S79" s="44">
-        <v>3</v>
-      </c>
-      <c r="T79" s="45">
-        <v>4</v>
-      </c>
-      <c r="U79" s="15" t="s">
-        <v>32</v>
-      </c>
+    <row r="79" spans="1:21" ht="15.75" customHeight="1">
+      <c r="D79" s="1"/>
     </row>
     <row r="80" spans="1:21" ht="15.75" customHeight="1">
       <c r="D80" s="1"/>
@@ -9238,12 +9173,9 @@
     <row r="996" spans="4:4" ht="15.75" customHeight="1">
       <c r="D996" s="1"/>
     </row>
-    <row r="997" spans="4:4" ht="15.75" customHeight="1">
-      <c r="D997" s="1"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="D2:D79" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="D2:D78" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>AND(ISNUMBER(D2),(NOT(OR(NOT(ISERROR(DATEVALUE(D2))), AND(ISNUMBER(D2), LEFT(CELL("format", D2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
@@ -9256,23 +9188,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -9455,8 +9370,25 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F1A155A-9D28-4350-8732-AE6833CEF998}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9464,5 +9396,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F1A155A-9D28-4350-8732-AE6833CEF998}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}"/>
 </file>
--- a/upload files/Preferences v6.xlsx
+++ b/upload files/Preferences v6.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C4836D4-26A3-4853-94BA-0B2EE58060BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63F6C0B-3524-A243-90D4-EAAE790E3013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29040" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="800" yWindow="660" windowWidth="29040" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$81</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="107">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -354,13 +354,22 @@
   </si>
   <si>
     <t>Ravenelle</t>
+  </si>
+  <si>
+    <t>O'Flaherty</t>
+  </si>
+  <si>
+    <t>Phelan</t>
+  </si>
+  <si>
+    <t>VanderKooi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -594,7 +603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -721,6 +730,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1118,10 +1133,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}" name="Table2" displayName="Table2" ref="A1:U78" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
-  <autoFilter ref="A1:U78" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U78">
-    <sortCondition ref="D1:D78"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}" name="Table2" displayName="Table2" ref="A1:U81" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
+  <autoFilter ref="A1:U81" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U81">
+    <sortCondition ref="D1:D81"/>
   </sortState>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{BB8E1DF3-CFA5-4F4C-9341-683B2C7FBF55}" name="STAFF NAME" dataDxfId="8"/>
@@ -1348,34 +1363,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U996"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:U999"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" customWidth="1"/>
-    <col min="9" max="9" width="8.28515625" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" customWidth="1"/>
+    <col min="7" max="7" width="8.1640625" customWidth="1"/>
+    <col min="8" max="8" width="10.1640625" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" customWidth="1"/>
     <col min="10" max="10" width="9" customWidth="1"/>
     <col min="11" max="11" width="8" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" customWidth="1"/>
-    <col min="14" max="14" width="10.140625" customWidth="1"/>
-    <col min="15" max="15" width="8.42578125" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" customWidth="1"/>
-    <col min="17" max="17" width="8.140625" customWidth="1"/>
+    <col min="12" max="12" width="9.1640625" customWidth="1"/>
+    <col min="13" max="13" width="8.1640625" customWidth="1"/>
+    <col min="14" max="14" width="10.1640625" customWidth="1"/>
+    <col min="15" max="15" width="8.5" customWidth="1"/>
+    <col min="16" max="16" width="9.1640625" customWidth="1"/>
+    <col min="17" max="17" width="8.1640625" customWidth="1"/>
     <col min="18" max="18" width="9" customWidth="1"/>
-    <col min="19" max="19" width="9.140625" customWidth="1"/>
+    <col min="19" max="19" width="9.1640625" customWidth="1"/>
     <col min="20" max="20" width="8" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" customWidth="1"/>
-    <col min="22" max="26" width="8.85546875" customWidth="1"/>
+    <col min="21" max="21" width="12.83203125" customWidth="1"/>
+    <col min="22" max="26" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
@@ -1440,7 +1455,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="35" t="s">
         <v>21</v>
       </c>
@@ -1503,7 +1518,7 @@
       </c>
       <c r="U2" s="10"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="36" t="s">
         <v>23</v>
       </c>
@@ -1566,7 +1581,7 @@
       </c>
       <c r="U3" s="15"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="37" t="s">
         <v>24</v>
       </c>
@@ -1631,7 +1646,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
         <v>26</v>
       </c>
@@ -1696,7 +1711,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" s="37" t="s">
         <v>28</v>
       </c>
@@ -1759,7 +1774,7 @@
       </c>
       <c r="U6" s="10"/>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" s="37" t="s">
         <v>29</v>
       </c>
@@ -1824,7 +1839,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="36" t="s">
         <v>30</v>
       </c>
@@ -1887,7 +1902,7 @@
       </c>
       <c r="U8" s="15"/>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" s="36" t="s">
         <v>31</v>
       </c>
@@ -1952,7 +1967,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" s="36" t="s">
         <v>33</v>
       </c>
@@ -2015,7 +2030,7 @@
       </c>
       <c r="U10" s="15"/>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" s="37" t="s">
         <v>34</v>
       </c>
@@ -2080,7 +2095,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" s="36" t="s">
         <v>35</v>
       </c>
@@ -2143,7 +2158,7 @@
       </c>
       <c r="U12" s="15"/>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" s="36" t="s">
         <v>36</v>
       </c>
@@ -2208,7 +2223,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" s="36" t="s">
         <v>37</v>
       </c>
@@ -2273,7 +2288,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" s="37" t="s">
         <v>38</v>
       </c>
@@ -2338,7 +2353,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" s="36" t="s">
         <v>39</v>
       </c>
@@ -2403,7 +2418,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" s="37" t="s">
         <v>42</v>
       </c>
@@ -2466,7 +2481,7 @@
       </c>
       <c r="U17" s="10"/>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" s="37" t="s">
         <v>43</v>
       </c>
@@ -2529,7 +2544,7 @@
       </c>
       <c r="U18" s="10"/>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" s="37" t="s">
         <v>44</v>
       </c>
@@ -2594,7 +2609,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="15.75" customHeight="1">
+    <row r="20" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="37" t="s">
         <v>45</v>
       </c>
@@ -2659,7 +2674,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="37" t="s">
         <v>46</v>
       </c>
@@ -2724,7 +2739,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="15.75" customHeight="1">
+    <row r="22" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="36" t="s">
         <v>47</v>
       </c>
@@ -2789,7 +2804,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="15.75" customHeight="1">
+    <row r="23" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="37" t="s">
         <v>48</v>
       </c>
@@ -2854,7 +2869,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="15.75" customHeight="1">
+    <row r="24" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="37" t="s">
         <v>49</v>
       </c>
@@ -2917,7 +2932,7 @@
       </c>
       <c r="U24" s="10"/>
     </row>
-    <row r="25" spans="1:21" ht="15.75" customHeight="1">
+    <row r="25" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="36" t="s">
         <v>50</v>
       </c>
@@ -2982,7 +2997,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="15.75" customHeight="1">
+    <row r="26" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="36" t="s">
         <v>51</v>
       </c>
@@ -3047,7 +3062,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="15.75" customHeight="1">
+    <row r="27" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="39" t="s">
         <v>52</v>
       </c>
@@ -3112,7 +3127,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="15.75" customHeight="1">
+    <row r="28" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="37" t="s">
         <v>53</v>
       </c>
@@ -3177,7 +3192,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="15.75" customHeight="1">
+    <row r="29" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="36" t="s">
         <v>54</v>
       </c>
@@ -3242,7 +3257,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="15.75" customHeight="1">
+    <row r="30" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="36" t="s">
         <v>55</v>
       </c>
@@ -3307,7 +3322,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="15.75" customHeight="1">
+    <row r="31" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="37" t="s">
         <v>56</v>
       </c>
@@ -3372,7 +3387,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="15.75" customHeight="1">
+    <row r="32" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="37" t="s">
         <v>57</v>
       </c>
@@ -3437,7 +3452,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="15.75" customHeight="1">
+    <row r="33" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="37" t="s">
         <v>58</v>
       </c>
@@ -3502,7 +3517,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="15.75" customHeight="1">
+    <row r="34" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="36" t="s">
         <v>59</v>
       </c>
@@ -3567,7 +3582,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="15.75" customHeight="1">
+    <row r="35" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="37" t="s">
         <v>60</v>
       </c>
@@ -3632,7 +3647,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="15.75" customHeight="1">
+    <row r="36" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="37" t="s">
         <v>61</v>
       </c>
@@ -3695,7 +3710,7 @@
       </c>
       <c r="U36" s="10"/>
     </row>
-    <row r="37" spans="1:21" ht="15.75" customHeight="1">
+    <row r="37" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="37" t="s">
         <v>62</v>
       </c>
@@ -3760,7 +3775,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="15.75" customHeight="1">
+    <row r="38" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="38" t="s">
         <v>63</v>
       </c>
@@ -3825,7 +3840,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="39" spans="1:21" ht="15.75" customHeight="1">
+    <row r="39" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="37" t="s">
         <v>64</v>
       </c>
@@ -3890,7 +3905,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="40" spans="1:21" ht="15.75" customHeight="1">
+    <row r="40" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="36" t="s">
         <v>65</v>
       </c>
@@ -3955,7 +3970,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:21" ht="15.75" customHeight="1">
+    <row r="41" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="36" t="s">
         <v>66</v>
       </c>
@@ -4018,7 +4033,7 @@
       </c>
       <c r="U41" s="15"/>
     </row>
-    <row r="42" spans="1:21" ht="15.75" customHeight="1">
+    <row r="42" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="37" t="s">
         <v>67</v>
       </c>
@@ -4083,7 +4098,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:21" ht="15.75" customHeight="1">
+    <row r="43" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="36" t="s">
         <v>68</v>
       </c>
@@ -4148,7 +4163,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:21" ht="15.75" customHeight="1">
+    <row r="44" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="36" t="s">
         <v>69</v>
       </c>
@@ -4213,7 +4228,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="45" spans="1:21" ht="15.75" customHeight="1">
+    <row r="45" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="36" t="s">
         <v>70</v>
       </c>
@@ -4278,7 +4293,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:21" ht="15.75" customHeight="1">
+    <row r="46" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="36" t="s">
         <v>71</v>
       </c>
@@ -4343,7 +4358,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="47" spans="1:21" ht="15.75" customHeight="1">
+    <row r="47" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="36" t="s">
         <v>72</v>
       </c>
@@ -4408,7 +4423,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:21" ht="15.75" customHeight="1">
+    <row r="48" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="36" t="s">
         <v>73</v>
       </c>
@@ -4473,7 +4488,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="49" spans="1:21" ht="15.75" customHeight="1">
+    <row r="49" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="36" t="s">
         <v>74</v>
       </c>
@@ -4538,7 +4553,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="15.75" customHeight="1">
+    <row r="50" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="37" t="s">
         <v>75</v>
       </c>
@@ -4603,7 +4618,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="1:21" ht="15.75" customHeight="1">
+    <row r="51" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="37" t="s">
         <v>76</v>
       </c>
@@ -4668,7 +4683,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="52" spans="1:21" ht="15.75" customHeight="1">
+    <row r="52" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="37" t="s">
         <v>77</v>
       </c>
@@ -4733,7 +4748,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="53" spans="1:21" ht="15.75" customHeight="1">
+    <row r="53" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="37" t="s">
         <v>78</v>
       </c>
@@ -4798,7 +4813,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="54" spans="1:21" ht="15.75" customHeight="1">
+    <row r="54" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="36" t="s">
         <v>79</v>
       </c>
@@ -4863,7 +4878,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="15.75" customHeight="1">
+    <row r="55" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="36" t="s">
         <v>80</v>
       </c>
@@ -4928,7 +4943,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="15.75" customHeight="1">
+    <row r="56" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="37" t="s">
         <v>81</v>
       </c>
@@ -4993,7 +5008,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="57" spans="1:21" ht="15.75" customHeight="1">
+    <row r="57" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="36" t="s">
         <v>82</v>
       </c>
@@ -5058,7 +5073,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:21" ht="15.75" customHeight="1">
+    <row r="58" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="36" t="s">
         <v>83</v>
       </c>
@@ -5123,7 +5138,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="15.75" customHeight="1">
+    <row r="59" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="36" t="s">
         <v>84</v>
       </c>
@@ -5188,7 +5203,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="60" spans="1:21" ht="15.75" customHeight="1">
+    <row r="60" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="37" t="s">
         <v>85</v>
       </c>
@@ -5251,7 +5266,7 @@
       </c>
       <c r="U60" s="10"/>
     </row>
-    <row r="61" spans="1:21" ht="15.75" customHeight="1">
+    <row r="61" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="36" t="s">
         <v>86</v>
       </c>
@@ -5316,7 +5331,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="15.75" customHeight="1">
+    <row r="62" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="37" t="s">
         <v>87</v>
       </c>
@@ -5381,7 +5396,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="15.75" customHeight="1">
+    <row r="63" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="37" t="s">
         <v>88</v>
       </c>
@@ -5446,7 +5461,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="64" spans="1:21" ht="15.75" customHeight="1">
+    <row r="64" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="37" t="s">
         <v>89</v>
       </c>
@@ -5511,7 +5526,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:21" ht="15.75" customHeight="1">
+    <row r="65" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="36" t="s">
         <v>90</v>
       </c>
@@ -5576,7 +5591,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="66" spans="1:21" ht="15.75" customHeight="1">
+    <row r="66" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="36" t="s">
         <v>91</v>
       </c>
@@ -5639,7 +5654,7 @@
       </c>
       <c r="U66" s="15"/>
     </row>
-    <row r="67" spans="1:21" ht="15.75" customHeight="1">
+    <row r="67" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="36" t="s">
         <v>92</v>
       </c>
@@ -5704,7 +5719,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="68" spans="1:21" ht="15.75" customHeight="1">
+    <row r="68" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="37" t="s">
         <v>93</v>
       </c>
@@ -5769,7 +5784,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:21" ht="15.75" customHeight="1">
+    <row r="69" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="37" t="s">
         <v>94</v>
       </c>
@@ -5834,7 +5849,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="70" spans="1:21" ht="15.75" customHeight="1">
+    <row r="70" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="37" t="s">
         <v>95</v>
       </c>
@@ -5899,7 +5914,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:21" ht="15.75" customHeight="1">
+    <row r="71" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="36" t="s">
         <v>96</v>
       </c>
@@ -5964,7 +5979,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:21" ht="15.75" customHeight="1">
+    <row r="72" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="37" t="s">
         <v>97</v>
       </c>
@@ -6029,7 +6044,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:21" ht="15.75" customHeight="1">
+    <row r="73" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="36" t="s">
         <v>98</v>
       </c>
@@ -6094,7 +6109,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:21" ht="15.75" customHeight="1">
+    <row r="74" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="36" t="s">
         <v>99</v>
       </c>
@@ -6159,7 +6174,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" spans="1:21" ht="15.75" customHeight="1">
+    <row r="75" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="37" t="s">
         <v>100</v>
       </c>
@@ -6224,2958 +6239,3051 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A76" s="37" t="s">
+    <row r="76" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="B76" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C76" s="47">
+        <v>0</v>
+      </c>
+      <c r="D76" s="17">
+        <v>83</v>
+      </c>
+      <c r="E76" s="47"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="37"/>
+      <c r="H76" s="37"/>
+      <c r="I76" s="37"/>
+      <c r="J76" s="37"/>
+      <c r="K76" s="37"/>
+      <c r="L76" s="37"/>
+      <c r="M76" s="37"/>
+      <c r="N76" s="37"/>
+      <c r="O76" s="37"/>
+      <c r="P76" s="18"/>
+      <c r="Q76" s="37"/>
+      <c r="R76" s="37"/>
+      <c r="S76" s="37"/>
+      <c r="T76" s="19"/>
+      <c r="U76" s="10"/>
+    </row>
+    <row r="77" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="B77" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" s="47">
+        <v>0</v>
+      </c>
+      <c r="D77" s="17">
+        <v>84</v>
+      </c>
+      <c r="E77" s="47"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="37"/>
+      <c r="H77" s="37"/>
+      <c r="I77" s="37"/>
+      <c r="J77" s="37"/>
+      <c r="K77" s="37"/>
+      <c r="L77" s="37"/>
+      <c r="M77" s="37"/>
+      <c r="N77" s="37"/>
+      <c r="O77" s="37"/>
+      <c r="P77" s="18"/>
+      <c r="Q77" s="37"/>
+      <c r="R77" s="37"/>
+      <c r="S77" s="37"/>
+      <c r="T77" s="19"/>
+      <c r="U77" s="10"/>
+    </row>
+    <row r="78" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="B78" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="C78" s="47">
+        <v>0</v>
+      </c>
+      <c r="D78" s="17">
+        <v>85</v>
+      </c>
+      <c r="E78" s="47"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="37"/>
+      <c r="H78" s="37"/>
+      <c r="I78" s="37"/>
+      <c r="J78" s="37"/>
+      <c r="K78" s="37"/>
+      <c r="L78" s="37"/>
+      <c r="M78" s="37"/>
+      <c r="N78" s="37"/>
+      <c r="O78" s="37"/>
+      <c r="P78" s="18"/>
+      <c r="Q78" s="37"/>
+      <c r="R78" s="37"/>
+      <c r="S78" s="37"/>
+      <c r="T78" s="19"/>
+      <c r="U78" s="10"/>
+    </row>
+    <row r="79" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="37" t="s">
         <v>101</v>
       </c>
-      <c r="B76" s="16" t="s">
+      <c r="B79" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C76" s="16">
-        <v>0</v>
-      </c>
-      <c r="D76" s="17">
+      <c r="C79" s="16">
+        <v>0</v>
+      </c>
+      <c r="D79" s="17">
         <v>80</v>
       </c>
-      <c r="E76" s="16">
-        <v>1</v>
-      </c>
-      <c r="F76" s="18">
+      <c r="E79" s="16">
+        <v>1</v>
+      </c>
+      <c r="F79" s="18">
         <v>6</v>
       </c>
-      <c r="G76" s="16">
+      <c r="G79" s="16">
         <v>7</v>
       </c>
-      <c r="H76" s="16">
-        <v>2</v>
-      </c>
-      <c r="I76" s="16">
-        <v>3</v>
-      </c>
-      <c r="J76" s="16">
-        <v>0</v>
-      </c>
-      <c r="K76" s="16">
-        <v>1</v>
-      </c>
-      <c r="L76" s="16">
+      <c r="H79" s="16">
+        <v>2</v>
+      </c>
+      <c r="I79" s="16">
+        <v>3</v>
+      </c>
+      <c r="J79" s="16">
+        <v>0</v>
+      </c>
+      <c r="K79" s="16">
+        <v>1</v>
+      </c>
+      <c r="L79" s="16">
         <v>8</v>
       </c>
-      <c r="M76" s="16">
+      <c r="M79" s="16">
         <v>9</v>
       </c>
-      <c r="N76" s="16">
-        <v>4</v>
-      </c>
-      <c r="O76" s="16">
+      <c r="N79" s="16">
+        <v>4</v>
+      </c>
+      <c r="O79" s="16">
         <v>5</v>
       </c>
-      <c r="P76" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q76" s="16">
-        <v>2</v>
-      </c>
-      <c r="R76" s="16">
-        <v>0</v>
-      </c>
-      <c r="S76" s="16">
-        <v>3</v>
-      </c>
-      <c r="T76" s="19">
-        <v>4</v>
-      </c>
-      <c r="U76" s="10" t="s">
+      <c r="P79" s="18">
+        <v>1</v>
+      </c>
+      <c r="Q79" s="16">
+        <v>2</v>
+      </c>
+      <c r="R79" s="16">
+        <v>0</v>
+      </c>
+      <c r="S79" s="16">
+        <v>3</v>
+      </c>
+      <c r="T79" s="19">
+        <v>4</v>
+      </c>
+      <c r="U79" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="77" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A77" s="37" t="s">
+    <row r="80" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="37" t="s">
         <v>102</v>
       </c>
-      <c r="B77" s="20" t="s">
+      <c r="B80" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C77" s="20">
-        <v>0</v>
-      </c>
-      <c r="D77" s="21">
+      <c r="C80" s="20">
+        <v>0</v>
+      </c>
+      <c r="D80" s="21">
         <v>81</v>
       </c>
-      <c r="E77" s="20">
-        <v>1</v>
-      </c>
-      <c r="F77" s="18">
+      <c r="E80" s="20">
+        <v>1</v>
+      </c>
+      <c r="F80" s="18">
         <v>5</v>
       </c>
-      <c r="G77" s="20">
+      <c r="G80" s="20">
         <v>6</v>
       </c>
-      <c r="H77" s="20">
+      <c r="H80" s="20">
         <v>7</v>
       </c>
-      <c r="I77" s="20">
-        <v>2</v>
-      </c>
-      <c r="J77" s="20">
+      <c r="I80" s="20">
+        <v>2</v>
+      </c>
+      <c r="J80" s="20">
         <v>8</v>
       </c>
-      <c r="K77" s="20">
+      <c r="K80" s="20">
         <v>9</v>
       </c>
-      <c r="L77" s="20">
-        <v>0</v>
-      </c>
-      <c r="M77" s="20">
-        <v>1</v>
-      </c>
-      <c r="N77" s="20">
-        <v>3</v>
-      </c>
-      <c r="O77" s="20">
-        <v>4</v>
-      </c>
-      <c r="P77" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="20">
-        <v>1</v>
-      </c>
-      <c r="R77" s="20">
-        <v>2</v>
-      </c>
-      <c r="S77" s="20">
-        <v>3</v>
-      </c>
-      <c r="T77" s="22">
-        <v>4</v>
-      </c>
-      <c r="U77" s="10" t="s">
+      <c r="L80" s="20">
+        <v>0</v>
+      </c>
+      <c r="M80" s="20">
+        <v>1</v>
+      </c>
+      <c r="N80" s="20">
+        <v>3</v>
+      </c>
+      <c r="O80" s="20">
+        <v>4</v>
+      </c>
+      <c r="P80" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="20">
+        <v>1</v>
+      </c>
+      <c r="R80" s="20">
+        <v>2</v>
+      </c>
+      <c r="S80" s="20">
+        <v>3</v>
+      </c>
+      <c r="T80" s="22">
+        <v>4</v>
+      </c>
+      <c r="U80" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:21" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A78" s="40" t="s">
+    <row r="81" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B78" s="41" t="s">
+      <c r="B81" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C78" s="41">
-        <v>0</v>
-      </c>
-      <c r="D78" s="42">
+      <c r="C81" s="41">
+        <v>0</v>
+      </c>
+      <c r="D81" s="42">
         <v>82</v>
       </c>
-      <c r="E78" s="41">
-        <v>0</v>
-      </c>
-      <c r="F78" s="43">
+      <c r="E81" s="41">
+        <v>0</v>
+      </c>
+      <c r="F81" s="43">
         <v>5</v>
       </c>
-      <c r="G78" s="44">
+      <c r="G81" s="44">
         <v>6</v>
       </c>
-      <c r="H78" s="44">
+      <c r="H81" s="44">
         <v>7</v>
       </c>
-      <c r="I78" s="44">
-        <v>0</v>
-      </c>
-      <c r="J78" s="44">
-        <v>1</v>
-      </c>
-      <c r="K78" s="44">
-        <v>2</v>
-      </c>
-      <c r="L78" s="44">
-        <v>3</v>
-      </c>
-      <c r="M78" s="44">
-        <v>4</v>
-      </c>
-      <c r="N78" s="44">
+      <c r="I81" s="44">
+        <v>0</v>
+      </c>
+      <c r="J81" s="44">
+        <v>1</v>
+      </c>
+      <c r="K81" s="44">
+        <v>2</v>
+      </c>
+      <c r="L81" s="44">
+        <v>3</v>
+      </c>
+      <c r="M81" s="44">
+        <v>4</v>
+      </c>
+      <c r="N81" s="44">
         <v>8</v>
       </c>
-      <c r="O78" s="44">
+      <c r="O81" s="44">
         <v>9</v>
       </c>
-      <c r="P78" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="44">
-        <v>1</v>
-      </c>
-      <c r="R78" s="44">
-        <v>2</v>
-      </c>
-      <c r="S78" s="44">
-        <v>3</v>
-      </c>
-      <c r="T78" s="45">
-        <v>4</v>
-      </c>
-      <c r="U78" s="15" t="s">
+      <c r="P81" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="44">
+        <v>1</v>
+      </c>
+      <c r="R81" s="44">
+        <v>2</v>
+      </c>
+      <c r="S81" s="44">
+        <v>3</v>
+      </c>
+      <c r="T81" s="45">
+        <v>4</v>
+      </c>
+      <c r="U81" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="79" spans="1:21" ht="15.75" customHeight="1">
-      <c r="D79" s="1"/>
-    </row>
-    <row r="80" spans="1:21" ht="15.75" customHeight="1">
-      <c r="D80" s="1"/>
-    </row>
-    <row r="81" spans="4:4" ht="15.75" customHeight="1">
-      <c r="D81" s="1"/>
-    </row>
-    <row r="82" spans="4:4" ht="15.75" customHeight="1">
+    <row r="82" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D82" s="1"/>
     </row>
-    <row r="83" spans="4:4" ht="15.75" customHeight="1">
+    <row r="83" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D83" s="1"/>
     </row>
-    <row r="84" spans="4:4" ht="15.75" customHeight="1">
+    <row r="84" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D84" s="1"/>
     </row>
-    <row r="85" spans="4:4" ht="15.75" customHeight="1">
+    <row r="85" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D85" s="1"/>
     </row>
-    <row r="86" spans="4:4" ht="15.75" customHeight="1">
+    <row r="86" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D86" s="1"/>
     </row>
-    <row r="87" spans="4:4" ht="15.75" customHeight="1">
+    <row r="87" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D87" s="1"/>
     </row>
-    <row r="88" spans="4:4" ht="15.75" customHeight="1">
+    <row r="88" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D88" s="1"/>
     </row>
-    <row r="89" spans="4:4" ht="15.75" customHeight="1">
+    <row r="89" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D89" s="1"/>
     </row>
-    <row r="90" spans="4:4" ht="15.75" customHeight="1">
+    <row r="90" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D90" s="1"/>
     </row>
-    <row r="91" spans="4:4" ht="15.75" customHeight="1">
+    <row r="91" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D91" s="1"/>
     </row>
-    <row r="92" spans="4:4" ht="15.75" customHeight="1">
+    <row r="92" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D92" s="1"/>
     </row>
-    <row r="93" spans="4:4" ht="15.75" customHeight="1">
+    <row r="93" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D93" s="1"/>
     </row>
-    <row r="94" spans="4:4" ht="15.75" customHeight="1">
+    <row r="94" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D94" s="1"/>
     </row>
-    <row r="95" spans="4:4" ht="15.75" customHeight="1">
+    <row r="95" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D95" s="1"/>
     </row>
-    <row r="96" spans="4:4" ht="15.75" customHeight="1">
+    <row r="96" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D96" s="1"/>
     </row>
-    <row r="97" spans="4:4" ht="15.75" customHeight="1">
+    <row r="97" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D97" s="1"/>
     </row>
-    <row r="98" spans="4:4" ht="15.75" customHeight="1">
+    <row r="98" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D98" s="1"/>
     </row>
-    <row r="99" spans="4:4" ht="15.75" customHeight="1">
+    <row r="99" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D99" s="1"/>
     </row>
-    <row r="100" spans="4:4" ht="15.75" customHeight="1">
+    <row r="100" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D100" s="1"/>
     </row>
-    <row r="101" spans="4:4" ht="15.75" customHeight="1">
+    <row r="101" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D101" s="1"/>
     </row>
-    <row r="102" spans="4:4" ht="15.75" customHeight="1">
+    <row r="102" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D102" s="1"/>
     </row>
-    <row r="103" spans="4:4" ht="15.75" customHeight="1">
+    <row r="103" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D103" s="1"/>
     </row>
-    <row r="104" spans="4:4" ht="15.75" customHeight="1">
+    <row r="104" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D104" s="1"/>
     </row>
-    <row r="105" spans="4:4" ht="15.75" customHeight="1">
+    <row r="105" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D105" s="1"/>
     </row>
-    <row r="106" spans="4:4" ht="15.75" customHeight="1">
+    <row r="106" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D106" s="1"/>
     </row>
-    <row r="107" spans="4:4" ht="15.75" customHeight="1">
+    <row r="107" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D107" s="1"/>
     </row>
-    <row r="108" spans="4:4" ht="15.75" customHeight="1">
+    <row r="108" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D108" s="1"/>
     </row>
-    <row r="109" spans="4:4" ht="15.75" customHeight="1">
+    <row r="109" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D109" s="1"/>
     </row>
-    <row r="110" spans="4:4" ht="15.75" customHeight="1">
+    <row r="110" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D110" s="1"/>
     </row>
-    <row r="111" spans="4:4" ht="15.75" customHeight="1">
+    <row r="111" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D111" s="1"/>
     </row>
-    <row r="112" spans="4:4" ht="15.75" customHeight="1">
+    <row r="112" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D112" s="1"/>
     </row>
-    <row r="113" spans="4:4" ht="15.75" customHeight="1">
+    <row r="113" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D113" s="1"/>
     </row>
-    <row r="114" spans="4:4" ht="15.75" customHeight="1">
+    <row r="114" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D114" s="1"/>
     </row>
-    <row r="115" spans="4:4" ht="15.75" customHeight="1">
+    <row r="115" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D115" s="1"/>
     </row>
-    <row r="116" spans="4:4" ht="15.75" customHeight="1">
+    <row r="116" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D116" s="1"/>
     </row>
-    <row r="117" spans="4:4" ht="15.75" customHeight="1">
+    <row r="117" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D117" s="1"/>
     </row>
-    <row r="118" spans="4:4" ht="15.75" customHeight="1">
+    <row r="118" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D118" s="1"/>
     </row>
-    <row r="119" spans="4:4" ht="15.75" customHeight="1">
+    <row r="119" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D119" s="1"/>
     </row>
-    <row r="120" spans="4:4" ht="15.75" customHeight="1">
+    <row r="120" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D120" s="1"/>
     </row>
-    <row r="121" spans="4:4" ht="15.75" customHeight="1">
+    <row r="121" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D121" s="1"/>
     </row>
-    <row r="122" spans="4:4" ht="15.75" customHeight="1">
+    <row r="122" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D122" s="1"/>
     </row>
-    <row r="123" spans="4:4" ht="15.75" customHeight="1">
+    <row r="123" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D123" s="1"/>
     </row>
-    <row r="124" spans="4:4" ht="15.75" customHeight="1">
+    <row r="124" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D124" s="1"/>
     </row>
-    <row r="125" spans="4:4" ht="15.75" customHeight="1">
+    <row r="125" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D125" s="1"/>
     </row>
-    <row r="126" spans="4:4" ht="15.75" customHeight="1">
+    <row r="126" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D126" s="1"/>
     </row>
-    <row r="127" spans="4:4" ht="15.75" customHeight="1">
+    <row r="127" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D127" s="1"/>
     </row>
-    <row r="128" spans="4:4" ht="15.75" customHeight="1">
+    <row r="128" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D128" s="1"/>
     </row>
-    <row r="129" spans="4:4" ht="15.75" customHeight="1">
+    <row r="129" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D129" s="1"/>
     </row>
-    <row r="130" spans="4:4" ht="15.75" customHeight="1">
+    <row r="130" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D130" s="1"/>
     </row>
-    <row r="131" spans="4:4" ht="15.75" customHeight="1">
+    <row r="131" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D131" s="1"/>
     </row>
-    <row r="132" spans="4:4" ht="15.75" customHeight="1">
+    <row r="132" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D132" s="1"/>
     </row>
-    <row r="133" spans="4:4" ht="15.75" customHeight="1">
+    <row r="133" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D133" s="1"/>
     </row>
-    <row r="134" spans="4:4" ht="15.75" customHeight="1">
+    <row r="134" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D134" s="1"/>
     </row>
-    <row r="135" spans="4:4" ht="15.75" customHeight="1">
+    <row r="135" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D135" s="1"/>
     </row>
-    <row r="136" spans="4:4" ht="15.75" customHeight="1">
+    <row r="136" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D136" s="1"/>
     </row>
-    <row r="137" spans="4:4" ht="15.75" customHeight="1">
+    <row r="137" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D137" s="1"/>
     </row>
-    <row r="138" spans="4:4" ht="15.75" customHeight="1">
+    <row r="138" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D138" s="1"/>
     </row>
-    <row r="139" spans="4:4" ht="15.75" customHeight="1">
+    <row r="139" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D139" s="1"/>
     </row>
-    <row r="140" spans="4:4" ht="15.75" customHeight="1">
+    <row r="140" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D140" s="1"/>
     </row>
-    <row r="141" spans="4:4" ht="15.75" customHeight="1">
+    <row r="141" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D141" s="1"/>
     </row>
-    <row r="142" spans="4:4" ht="15.75" customHeight="1">
+    <row r="142" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D142" s="1"/>
     </row>
-    <row r="143" spans="4:4" ht="15.75" customHeight="1">
+    <row r="143" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D143" s="1"/>
     </row>
-    <row r="144" spans="4:4" ht="15.75" customHeight="1">
+    <row r="144" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D144" s="1"/>
     </row>
-    <row r="145" spans="4:4" ht="15.75" customHeight="1">
+    <row r="145" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D145" s="1"/>
     </row>
-    <row r="146" spans="4:4" ht="15.75" customHeight="1">
+    <row r="146" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D146" s="1"/>
     </row>
-    <row r="147" spans="4:4" ht="15.75" customHeight="1">
+    <row r="147" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D147" s="1"/>
     </row>
-    <row r="148" spans="4:4" ht="15.75" customHeight="1">
+    <row r="148" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D148" s="1"/>
     </row>
-    <row r="149" spans="4:4" ht="15.75" customHeight="1">
+    <row r="149" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D149" s="1"/>
     </row>
-    <row r="150" spans="4:4" ht="15.75" customHeight="1">
+    <row r="150" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D150" s="1"/>
     </row>
-    <row r="151" spans="4:4" ht="15.75" customHeight="1">
+    <row r="151" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D151" s="1"/>
     </row>
-    <row r="152" spans="4:4" ht="15.75" customHeight="1">
+    <row r="152" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D152" s="1"/>
     </row>
-    <row r="153" spans="4:4" ht="15.75" customHeight="1">
+    <row r="153" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D153" s="1"/>
     </row>
-    <row r="154" spans="4:4" ht="15.75" customHeight="1">
+    <row r="154" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D154" s="1"/>
     </row>
-    <row r="155" spans="4:4" ht="15.75" customHeight="1">
+    <row r="155" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D155" s="1"/>
     </row>
-    <row r="156" spans="4:4" ht="15.75" customHeight="1">
+    <row r="156" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D156" s="1"/>
     </row>
-    <row r="157" spans="4:4" ht="15.75" customHeight="1">
+    <row r="157" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D157" s="1"/>
     </row>
-    <row r="158" spans="4:4" ht="15.75" customHeight="1">
+    <row r="158" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D158" s="1"/>
     </row>
-    <row r="159" spans="4:4" ht="15.75" customHeight="1">
+    <row r="159" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D159" s="1"/>
     </row>
-    <row r="160" spans="4:4" ht="15.75" customHeight="1">
+    <row r="160" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D160" s="1"/>
     </row>
-    <row r="161" spans="4:4" ht="15.75" customHeight="1">
+    <row r="161" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D161" s="1"/>
     </row>
-    <row r="162" spans="4:4" ht="15.75" customHeight="1">
+    <row r="162" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D162" s="1"/>
     </row>
-    <row r="163" spans="4:4" ht="15.75" customHeight="1">
+    <row r="163" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D163" s="1"/>
     </row>
-    <row r="164" spans="4:4" ht="15.75" customHeight="1">
+    <row r="164" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D164" s="1"/>
     </row>
-    <row r="165" spans="4:4" ht="15.75" customHeight="1">
+    <row r="165" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D165" s="1"/>
     </row>
-    <row r="166" spans="4:4" ht="15.75" customHeight="1">
+    <row r="166" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D166" s="1"/>
     </row>
-    <row r="167" spans="4:4" ht="15.75" customHeight="1">
+    <row r="167" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D167" s="1"/>
     </row>
-    <row r="168" spans="4:4" ht="15.75" customHeight="1">
+    <row r="168" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D168" s="1"/>
     </row>
-    <row r="169" spans="4:4" ht="15.75" customHeight="1">
+    <row r="169" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D169" s="1"/>
     </row>
-    <row r="170" spans="4:4" ht="15.75" customHeight="1">
+    <row r="170" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D170" s="1"/>
     </row>
-    <row r="171" spans="4:4" ht="15.75" customHeight="1">
+    <row r="171" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D171" s="1"/>
     </row>
-    <row r="172" spans="4:4" ht="15.75" customHeight="1">
+    <row r="172" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D172" s="1"/>
     </row>
-    <row r="173" spans="4:4" ht="15.75" customHeight="1">
+    <row r="173" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D173" s="1"/>
     </row>
-    <row r="174" spans="4:4" ht="15.75" customHeight="1">
+    <row r="174" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D174" s="1"/>
     </row>
-    <row r="175" spans="4:4" ht="15.75" customHeight="1">
+    <row r="175" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D175" s="1"/>
     </row>
-    <row r="176" spans="4:4" ht="15.75" customHeight="1">
+    <row r="176" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D176" s="1"/>
     </row>
-    <row r="177" spans="4:4" ht="15.75" customHeight="1">
+    <row r="177" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D177" s="1"/>
     </row>
-    <row r="178" spans="4:4" ht="15.75" customHeight="1">
+    <row r="178" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D178" s="1"/>
     </row>
-    <row r="179" spans="4:4" ht="15.75" customHeight="1">
+    <row r="179" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D179" s="1"/>
     </row>
-    <row r="180" spans="4:4" ht="15.75" customHeight="1">
+    <row r="180" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D180" s="1"/>
     </row>
-    <row r="181" spans="4:4" ht="15.75" customHeight="1">
+    <row r="181" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D181" s="1"/>
     </row>
-    <row r="182" spans="4:4" ht="15.75" customHeight="1">
+    <row r="182" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D182" s="1"/>
     </row>
-    <row r="183" spans="4:4" ht="15.75" customHeight="1">
+    <row r="183" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D183" s="1"/>
     </row>
-    <row r="184" spans="4:4" ht="15.75" customHeight="1">
+    <row r="184" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D184" s="1"/>
     </row>
-    <row r="185" spans="4:4" ht="15.75" customHeight="1">
+    <row r="185" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D185" s="1"/>
     </row>
-    <row r="186" spans="4:4" ht="15.75" customHeight="1">
+    <row r="186" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D186" s="1"/>
     </row>
-    <row r="187" spans="4:4" ht="15.75" customHeight="1">
+    <row r="187" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D187" s="1"/>
     </row>
-    <row r="188" spans="4:4" ht="15.75" customHeight="1">
+    <row r="188" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D188" s="1"/>
     </row>
-    <row r="189" spans="4:4" ht="15.75" customHeight="1">
+    <row r="189" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D189" s="1"/>
     </row>
-    <row r="190" spans="4:4" ht="15.75" customHeight="1">
+    <row r="190" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D190" s="1"/>
     </row>
-    <row r="191" spans="4:4" ht="15.75" customHeight="1">
+    <row r="191" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D191" s="1"/>
     </row>
-    <row r="192" spans="4:4" ht="15.75" customHeight="1">
+    <row r="192" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D192" s="1"/>
     </row>
-    <row r="193" spans="4:4" ht="15.75" customHeight="1">
+    <row r="193" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D193" s="1"/>
     </row>
-    <row r="194" spans="4:4" ht="15.75" customHeight="1">
+    <row r="194" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D194" s="1"/>
     </row>
-    <row r="195" spans="4:4" ht="15.75" customHeight="1">
+    <row r="195" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D195" s="1"/>
     </row>
-    <row r="196" spans="4:4" ht="15.75" customHeight="1">
+    <row r="196" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D196" s="1"/>
     </row>
-    <row r="197" spans="4:4" ht="15.75" customHeight="1">
+    <row r="197" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D197" s="1"/>
     </row>
-    <row r="198" spans="4:4" ht="15.75" customHeight="1">
+    <row r="198" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D198" s="1"/>
     </row>
-    <row r="199" spans="4:4" ht="15.75" customHeight="1">
+    <row r="199" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D199" s="1"/>
     </row>
-    <row r="200" spans="4:4" ht="15.75" customHeight="1">
+    <row r="200" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D200" s="1"/>
     </row>
-    <row r="201" spans="4:4" ht="15.75" customHeight="1">
+    <row r="201" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D201" s="1"/>
     </row>
-    <row r="202" spans="4:4" ht="15.75" customHeight="1">
+    <row r="202" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D202" s="1"/>
     </row>
-    <row r="203" spans="4:4" ht="15.75" customHeight="1">
+    <row r="203" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D203" s="1"/>
     </row>
-    <row r="204" spans="4:4" ht="15.75" customHeight="1">
+    <row r="204" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D204" s="1"/>
     </row>
-    <row r="205" spans="4:4" ht="15.75" customHeight="1">
+    <row r="205" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D205" s="1"/>
     </row>
-    <row r="206" spans="4:4" ht="15.75" customHeight="1">
+    <row r="206" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D206" s="1"/>
     </row>
-    <row r="207" spans="4:4" ht="15.75" customHeight="1">
+    <row r="207" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D207" s="1"/>
     </row>
-    <row r="208" spans="4:4" ht="15.75" customHeight="1">
+    <row r="208" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D208" s="1"/>
     </row>
-    <row r="209" spans="4:4" ht="15.75" customHeight="1">
+    <row r="209" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D209" s="1"/>
     </row>
-    <row r="210" spans="4:4" ht="15.75" customHeight="1">
+    <row r="210" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D210" s="1"/>
     </row>
-    <row r="211" spans="4:4" ht="15.75" customHeight="1">
+    <row r="211" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D211" s="1"/>
     </row>
-    <row r="212" spans="4:4" ht="15.75" customHeight="1">
+    <row r="212" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D212" s="1"/>
     </row>
-    <row r="213" spans="4:4" ht="15.75" customHeight="1">
+    <row r="213" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D213" s="1"/>
     </row>
-    <row r="214" spans="4:4" ht="15.75" customHeight="1">
+    <row r="214" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D214" s="1"/>
     </row>
-    <row r="215" spans="4:4" ht="15.75" customHeight="1">
+    <row r="215" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D215" s="1"/>
     </row>
-    <row r="216" spans="4:4" ht="15.75" customHeight="1">
+    <row r="216" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D216" s="1"/>
     </row>
-    <row r="217" spans="4:4" ht="15.75" customHeight="1">
+    <row r="217" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D217" s="1"/>
     </row>
-    <row r="218" spans="4:4" ht="15.75" customHeight="1">
+    <row r="218" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D218" s="1"/>
     </row>
-    <row r="219" spans="4:4" ht="15.75" customHeight="1">
+    <row r="219" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D219" s="1"/>
     </row>
-    <row r="220" spans="4:4" ht="15.75" customHeight="1">
+    <row r="220" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D220" s="1"/>
     </row>
-    <row r="221" spans="4:4" ht="15.75" customHeight="1">
+    <row r="221" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D221" s="1"/>
     </row>
-    <row r="222" spans="4:4" ht="15.75" customHeight="1">
+    <row r="222" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D222" s="1"/>
     </row>
-    <row r="223" spans="4:4" ht="15.75" customHeight="1">
+    <row r="223" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D223" s="1"/>
     </row>
-    <row r="224" spans="4:4" ht="15.75" customHeight="1">
+    <row r="224" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D224" s="1"/>
     </row>
-    <row r="225" spans="4:4" ht="15.75" customHeight="1">
+    <row r="225" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D225" s="1"/>
     </row>
-    <row r="226" spans="4:4" ht="15.75" customHeight="1">
+    <row r="226" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D226" s="1"/>
     </row>
-    <row r="227" spans="4:4" ht="15.75" customHeight="1">
+    <row r="227" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D227" s="1"/>
     </row>
-    <row r="228" spans="4:4" ht="15.75" customHeight="1">
+    <row r="228" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D228" s="1"/>
     </row>
-    <row r="229" spans="4:4" ht="15.75" customHeight="1">
+    <row r="229" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D229" s="1"/>
     </row>
-    <row r="230" spans="4:4" ht="15.75" customHeight="1">
+    <row r="230" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D230" s="1"/>
     </row>
-    <row r="231" spans="4:4" ht="15.75" customHeight="1">
+    <row r="231" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D231" s="1"/>
     </row>
-    <row r="232" spans="4:4" ht="15.75" customHeight="1">
+    <row r="232" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D232" s="1"/>
     </row>
-    <row r="233" spans="4:4" ht="15.75" customHeight="1">
+    <row r="233" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D233" s="1"/>
     </row>
-    <row r="234" spans="4:4" ht="15.75" customHeight="1">
+    <row r="234" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D234" s="1"/>
     </row>
-    <row r="235" spans="4:4" ht="15.75" customHeight="1">
+    <row r="235" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D235" s="1"/>
     </row>
-    <row r="236" spans="4:4" ht="15.75" customHeight="1">
+    <row r="236" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D236" s="1"/>
     </row>
-    <row r="237" spans="4:4" ht="15.75" customHeight="1">
+    <row r="237" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D237" s="1"/>
     </row>
-    <row r="238" spans="4:4" ht="15.75" customHeight="1">
+    <row r="238" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D238" s="1"/>
     </row>
-    <row r="239" spans="4:4" ht="15.75" customHeight="1">
+    <row r="239" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D239" s="1"/>
     </row>
-    <row r="240" spans="4:4" ht="15.75" customHeight="1">
+    <row r="240" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D240" s="1"/>
     </row>
-    <row r="241" spans="4:4" ht="15.75" customHeight="1">
+    <row r="241" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D241" s="1"/>
     </row>
-    <row r="242" spans="4:4" ht="15.75" customHeight="1">
+    <row r="242" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D242" s="1"/>
     </row>
-    <row r="243" spans="4:4" ht="15.75" customHeight="1">
+    <row r="243" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D243" s="1"/>
     </row>
-    <row r="244" spans="4:4" ht="15.75" customHeight="1">
+    <row r="244" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D244" s="1"/>
     </row>
-    <row r="245" spans="4:4" ht="15.75" customHeight="1">
+    <row r="245" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D245" s="1"/>
     </row>
-    <row r="246" spans="4:4" ht="15.75" customHeight="1">
+    <row r="246" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D246" s="1"/>
     </row>
-    <row r="247" spans="4:4" ht="15.75" customHeight="1">
+    <row r="247" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D247" s="1"/>
     </row>
-    <row r="248" spans="4:4" ht="15.75" customHeight="1">
+    <row r="248" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D248" s="1"/>
     </row>
-    <row r="249" spans="4:4" ht="15.75" customHeight="1">
+    <row r="249" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D249" s="1"/>
     </row>
-    <row r="250" spans="4:4" ht="15.75" customHeight="1">
+    <row r="250" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D250" s="1"/>
     </row>
-    <row r="251" spans="4:4" ht="15.75" customHeight="1">
+    <row r="251" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D251" s="1"/>
     </row>
-    <row r="252" spans="4:4" ht="15.75" customHeight="1">
+    <row r="252" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D252" s="1"/>
     </row>
-    <row r="253" spans="4:4" ht="15.75" customHeight="1">
+    <row r="253" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D253" s="1"/>
     </row>
-    <row r="254" spans="4:4" ht="15.75" customHeight="1">
+    <row r="254" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D254" s="1"/>
     </row>
-    <row r="255" spans="4:4" ht="15.75" customHeight="1">
+    <row r="255" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D255" s="1"/>
     </row>
-    <row r="256" spans="4:4" ht="15.75" customHeight="1">
+    <row r="256" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D256" s="1"/>
     </row>
-    <row r="257" spans="4:4" ht="15.75" customHeight="1">
+    <row r="257" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D257" s="1"/>
     </row>
-    <row r="258" spans="4:4" ht="15.75" customHeight="1">
+    <row r="258" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D258" s="1"/>
     </row>
-    <row r="259" spans="4:4" ht="15.75" customHeight="1">
+    <row r="259" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D259" s="1"/>
     </row>
-    <row r="260" spans="4:4" ht="15.75" customHeight="1">
+    <row r="260" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D260" s="1"/>
     </row>
-    <row r="261" spans="4:4" ht="15.75" customHeight="1">
+    <row r="261" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D261" s="1"/>
     </row>
-    <row r="262" spans="4:4" ht="15.75" customHeight="1">
+    <row r="262" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D262" s="1"/>
     </row>
-    <row r="263" spans="4:4" ht="15.75" customHeight="1">
+    <row r="263" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D263" s="1"/>
     </row>
-    <row r="264" spans="4:4" ht="15.75" customHeight="1">
+    <row r="264" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D264" s="1"/>
     </row>
-    <row r="265" spans="4:4" ht="15.75" customHeight="1">
+    <row r="265" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D265" s="1"/>
     </row>
-    <row r="266" spans="4:4" ht="15.75" customHeight="1">
+    <row r="266" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D266" s="1"/>
     </row>
-    <row r="267" spans="4:4" ht="15.75" customHeight="1">
+    <row r="267" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D267" s="1"/>
     </row>
-    <row r="268" spans="4:4" ht="15.75" customHeight="1">
+    <row r="268" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D268" s="1"/>
     </row>
-    <row r="269" spans="4:4" ht="15.75" customHeight="1">
+    <row r="269" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D269" s="1"/>
     </row>
-    <row r="270" spans="4:4" ht="15.75" customHeight="1">
+    <row r="270" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D270" s="1"/>
     </row>
-    <row r="271" spans="4:4" ht="15.75" customHeight="1">
+    <row r="271" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D271" s="1"/>
     </row>
-    <row r="272" spans="4:4" ht="15.75" customHeight="1">
+    <row r="272" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D272" s="1"/>
     </row>
-    <row r="273" spans="4:4" ht="15.75" customHeight="1">
+    <row r="273" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D273" s="1"/>
     </row>
-    <row r="274" spans="4:4" ht="15.75" customHeight="1">
+    <row r="274" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D274" s="1"/>
     </row>
-    <row r="275" spans="4:4" ht="15.75" customHeight="1">
+    <row r="275" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D275" s="1"/>
     </row>
-    <row r="276" spans="4:4" ht="15.75" customHeight="1">
+    <row r="276" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D276" s="1"/>
     </row>
-    <row r="277" spans="4:4" ht="15.75" customHeight="1">
+    <row r="277" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D277" s="1"/>
     </row>
-    <row r="278" spans="4:4" ht="15.75" customHeight="1">
+    <row r="278" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D278" s="1"/>
     </row>
-    <row r="279" spans="4:4" ht="15.75" customHeight="1">
+    <row r="279" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D279" s="1"/>
     </row>
-    <row r="280" spans="4:4" ht="15.75" customHeight="1">
+    <row r="280" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D280" s="1"/>
     </row>
-    <row r="281" spans="4:4" ht="15.75" customHeight="1">
+    <row r="281" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D281" s="1"/>
     </row>
-    <row r="282" spans="4:4" ht="15.75" customHeight="1">
+    <row r="282" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D282" s="1"/>
     </row>
-    <row r="283" spans="4:4" ht="15.75" customHeight="1">
+    <row r="283" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D283" s="1"/>
     </row>
-    <row r="284" spans="4:4" ht="15.75" customHeight="1">
+    <row r="284" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D284" s="1"/>
     </row>
-    <row r="285" spans="4:4" ht="15.75" customHeight="1">
+    <row r="285" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D285" s="1"/>
     </row>
-    <row r="286" spans="4:4" ht="15.75" customHeight="1">
+    <row r="286" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D286" s="1"/>
     </row>
-    <row r="287" spans="4:4" ht="15.75" customHeight="1">
+    <row r="287" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D287" s="1"/>
     </row>
-    <row r="288" spans="4:4" ht="15.75" customHeight="1">
+    <row r="288" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D288" s="1"/>
     </row>
-    <row r="289" spans="4:4" ht="15.75" customHeight="1">
+    <row r="289" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D289" s="1"/>
     </row>
-    <row r="290" spans="4:4" ht="15.75" customHeight="1">
+    <row r="290" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D290" s="1"/>
     </row>
-    <row r="291" spans="4:4" ht="15.75" customHeight="1">
+    <row r="291" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D291" s="1"/>
     </row>
-    <row r="292" spans="4:4" ht="15.75" customHeight="1">
+    <row r="292" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D292" s="1"/>
     </row>
-    <row r="293" spans="4:4" ht="15.75" customHeight="1">
+    <row r="293" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D293" s="1"/>
     </row>
-    <row r="294" spans="4:4" ht="15.75" customHeight="1">
+    <row r="294" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D294" s="1"/>
     </row>
-    <row r="295" spans="4:4" ht="15.75" customHeight="1">
+    <row r="295" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D295" s="1"/>
     </row>
-    <row r="296" spans="4:4" ht="15.75" customHeight="1">
+    <row r="296" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D296" s="1"/>
     </row>
-    <row r="297" spans="4:4" ht="15.75" customHeight="1">
+    <row r="297" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D297" s="1"/>
     </row>
-    <row r="298" spans="4:4" ht="15.75" customHeight="1">
+    <row r="298" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D298" s="1"/>
     </row>
-    <row r="299" spans="4:4" ht="15.75" customHeight="1">
+    <row r="299" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D299" s="1"/>
     </row>
-    <row r="300" spans="4:4" ht="15.75" customHeight="1">
+    <row r="300" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D300" s="1"/>
     </row>
-    <row r="301" spans="4:4" ht="15.75" customHeight="1">
+    <row r="301" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D301" s="1"/>
     </row>
-    <row r="302" spans="4:4" ht="15.75" customHeight="1">
+    <row r="302" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D302" s="1"/>
     </row>
-    <row r="303" spans="4:4" ht="15.75" customHeight="1">
+    <row r="303" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D303" s="1"/>
     </row>
-    <row r="304" spans="4:4" ht="15.75" customHeight="1">
+    <row r="304" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D304" s="1"/>
     </row>
-    <row r="305" spans="4:4" ht="15.75" customHeight="1">
+    <row r="305" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D305" s="1"/>
     </row>
-    <row r="306" spans="4:4" ht="15.75" customHeight="1">
+    <row r="306" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D306" s="1"/>
     </row>
-    <row r="307" spans="4:4" ht="15.75" customHeight="1">
+    <row r="307" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D307" s="1"/>
     </row>
-    <row r="308" spans="4:4" ht="15.75" customHeight="1">
+    <row r="308" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D308" s="1"/>
     </row>
-    <row r="309" spans="4:4" ht="15.75" customHeight="1">
+    <row r="309" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D309" s="1"/>
     </row>
-    <row r="310" spans="4:4" ht="15.75" customHeight="1">
+    <row r="310" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D310" s="1"/>
     </row>
-    <row r="311" spans="4:4" ht="15.75" customHeight="1">
+    <row r="311" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D311" s="1"/>
     </row>
-    <row r="312" spans="4:4" ht="15.75" customHeight="1">
+    <row r="312" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D312" s="1"/>
     </row>
-    <row r="313" spans="4:4" ht="15.75" customHeight="1">
+    <row r="313" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D313" s="1"/>
     </row>
-    <row r="314" spans="4:4" ht="15.75" customHeight="1">
+    <row r="314" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D314" s="1"/>
     </row>
-    <row r="315" spans="4:4" ht="15.75" customHeight="1">
+    <row r="315" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D315" s="1"/>
     </row>
-    <row r="316" spans="4:4" ht="15.75" customHeight="1">
+    <row r="316" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D316" s="1"/>
     </row>
-    <row r="317" spans="4:4" ht="15.75" customHeight="1">
+    <row r="317" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D317" s="1"/>
     </row>
-    <row r="318" spans="4:4" ht="15.75" customHeight="1">
+    <row r="318" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D318" s="1"/>
     </row>
-    <row r="319" spans="4:4" ht="15.75" customHeight="1">
+    <row r="319" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D319" s="1"/>
     </row>
-    <row r="320" spans="4:4" ht="15.75" customHeight="1">
+    <row r="320" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D320" s="1"/>
     </row>
-    <row r="321" spans="4:4" ht="15.75" customHeight="1">
+    <row r="321" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D321" s="1"/>
     </row>
-    <row r="322" spans="4:4" ht="15.75" customHeight="1">
+    <row r="322" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D322" s="1"/>
     </row>
-    <row r="323" spans="4:4" ht="15.75" customHeight="1">
+    <row r="323" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D323" s="1"/>
     </row>
-    <row r="324" spans="4:4" ht="15.75" customHeight="1">
+    <row r="324" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D324" s="1"/>
     </row>
-    <row r="325" spans="4:4" ht="15.75" customHeight="1">
+    <row r="325" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D325" s="1"/>
     </row>
-    <row r="326" spans="4:4" ht="15.75" customHeight="1">
+    <row r="326" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D326" s="1"/>
     </row>
-    <row r="327" spans="4:4" ht="15.75" customHeight="1">
+    <row r="327" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D327" s="1"/>
     </row>
-    <row r="328" spans="4:4" ht="15.75" customHeight="1">
+    <row r="328" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D328" s="1"/>
     </row>
-    <row r="329" spans="4:4" ht="15.75" customHeight="1">
+    <row r="329" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D329" s="1"/>
     </row>
-    <row r="330" spans="4:4" ht="15.75" customHeight="1">
+    <row r="330" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D330" s="1"/>
     </row>
-    <row r="331" spans="4:4" ht="15.75" customHeight="1">
+    <row r="331" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D331" s="1"/>
     </row>
-    <row r="332" spans="4:4" ht="15.75" customHeight="1">
+    <row r="332" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D332" s="1"/>
     </row>
-    <row r="333" spans="4:4" ht="15.75" customHeight="1">
+    <row r="333" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D333" s="1"/>
     </row>
-    <row r="334" spans="4:4" ht="15.75" customHeight="1">
+    <row r="334" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D334" s="1"/>
     </row>
-    <row r="335" spans="4:4" ht="15.75" customHeight="1">
+    <row r="335" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D335" s="1"/>
     </row>
-    <row r="336" spans="4:4" ht="15.75" customHeight="1">
+    <row r="336" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D336" s="1"/>
     </row>
-    <row r="337" spans="4:4" ht="15.75" customHeight="1">
+    <row r="337" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D337" s="1"/>
     </row>
-    <row r="338" spans="4:4" ht="15.75" customHeight="1">
+    <row r="338" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D338" s="1"/>
     </row>
-    <row r="339" spans="4:4" ht="15.75" customHeight="1">
+    <row r="339" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D339" s="1"/>
     </row>
-    <row r="340" spans="4:4" ht="15.75" customHeight="1">
+    <row r="340" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D340" s="1"/>
     </row>
-    <row r="341" spans="4:4" ht="15.75" customHeight="1">
+    <row r="341" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D341" s="1"/>
     </row>
-    <row r="342" spans="4:4" ht="15.75" customHeight="1">
+    <row r="342" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D342" s="1"/>
     </row>
-    <row r="343" spans="4:4" ht="15.75" customHeight="1">
+    <row r="343" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D343" s="1"/>
     </row>
-    <row r="344" spans="4:4" ht="15.75" customHeight="1">
+    <row r="344" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D344" s="1"/>
     </row>
-    <row r="345" spans="4:4" ht="15.75" customHeight="1">
+    <row r="345" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D345" s="1"/>
     </row>
-    <row r="346" spans="4:4" ht="15.75" customHeight="1">
+    <row r="346" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D346" s="1"/>
     </row>
-    <row r="347" spans="4:4" ht="15.75" customHeight="1">
+    <row r="347" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D347" s="1"/>
     </row>
-    <row r="348" spans="4:4" ht="15.75" customHeight="1">
+    <row r="348" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D348" s="1"/>
     </row>
-    <row r="349" spans="4:4" ht="15.75" customHeight="1">
+    <row r="349" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D349" s="1"/>
     </row>
-    <row r="350" spans="4:4" ht="15.75" customHeight="1">
+    <row r="350" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D350" s="1"/>
     </row>
-    <row r="351" spans="4:4" ht="15.75" customHeight="1">
+    <row r="351" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D351" s="1"/>
     </row>
-    <row r="352" spans="4:4" ht="15.75" customHeight="1">
+    <row r="352" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D352" s="1"/>
     </row>
-    <row r="353" spans="4:4" ht="15.75" customHeight="1">
+    <row r="353" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D353" s="1"/>
     </row>
-    <row r="354" spans="4:4" ht="15.75" customHeight="1">
+    <row r="354" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D354" s="1"/>
     </row>
-    <row r="355" spans="4:4" ht="15.75" customHeight="1">
+    <row r="355" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D355" s="1"/>
     </row>
-    <row r="356" spans="4:4" ht="15.75" customHeight="1">
+    <row r="356" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D356" s="1"/>
     </row>
-    <row r="357" spans="4:4" ht="15.75" customHeight="1">
+    <row r="357" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D357" s="1"/>
     </row>
-    <row r="358" spans="4:4" ht="15.75" customHeight="1">
+    <row r="358" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D358" s="1"/>
     </row>
-    <row r="359" spans="4:4" ht="15.75" customHeight="1">
+    <row r="359" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D359" s="1"/>
     </row>
-    <row r="360" spans="4:4" ht="15.75" customHeight="1">
+    <row r="360" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D360" s="1"/>
     </row>
-    <row r="361" spans="4:4" ht="15.75" customHeight="1">
+    <row r="361" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D361" s="1"/>
     </row>
-    <row r="362" spans="4:4" ht="15.75" customHeight="1">
+    <row r="362" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D362" s="1"/>
     </row>
-    <row r="363" spans="4:4" ht="15.75" customHeight="1">
+    <row r="363" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D363" s="1"/>
     </row>
-    <row r="364" spans="4:4" ht="15.75" customHeight="1">
+    <row r="364" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D364" s="1"/>
     </row>
-    <row r="365" spans="4:4" ht="15.75" customHeight="1">
+    <row r="365" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D365" s="1"/>
     </row>
-    <row r="366" spans="4:4" ht="15.75" customHeight="1">
+    <row r="366" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D366" s="1"/>
     </row>
-    <row r="367" spans="4:4" ht="15.75" customHeight="1">
+    <row r="367" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D367" s="1"/>
     </row>
-    <row r="368" spans="4:4" ht="15.75" customHeight="1">
+    <row r="368" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D368" s="1"/>
     </row>
-    <row r="369" spans="4:4" ht="15.75" customHeight="1">
+    <row r="369" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D369" s="1"/>
     </row>
-    <row r="370" spans="4:4" ht="15.75" customHeight="1">
+    <row r="370" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D370" s="1"/>
     </row>
-    <row r="371" spans="4:4" ht="15.75" customHeight="1">
+    <row r="371" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D371" s="1"/>
     </row>
-    <row r="372" spans="4:4" ht="15.75" customHeight="1">
+    <row r="372" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D372" s="1"/>
     </row>
-    <row r="373" spans="4:4" ht="15.75" customHeight="1">
+    <row r="373" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D373" s="1"/>
     </row>
-    <row r="374" spans="4:4" ht="15.75" customHeight="1">
+    <row r="374" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D374" s="1"/>
     </row>
-    <row r="375" spans="4:4" ht="15.75" customHeight="1">
+    <row r="375" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D375" s="1"/>
     </row>
-    <row r="376" spans="4:4" ht="15.75" customHeight="1">
+    <row r="376" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D376" s="1"/>
     </row>
-    <row r="377" spans="4:4" ht="15.75" customHeight="1">
+    <row r="377" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D377" s="1"/>
     </row>
-    <row r="378" spans="4:4" ht="15.75" customHeight="1">
+    <row r="378" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D378" s="1"/>
     </row>
-    <row r="379" spans="4:4" ht="15.75" customHeight="1">
+    <row r="379" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D379" s="1"/>
     </row>
-    <row r="380" spans="4:4" ht="15.75" customHeight="1">
+    <row r="380" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D380" s="1"/>
     </row>
-    <row r="381" spans="4:4" ht="15.75" customHeight="1">
+    <row r="381" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D381" s="1"/>
     </row>
-    <row r="382" spans="4:4" ht="15.75" customHeight="1">
+    <row r="382" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D382" s="1"/>
     </row>
-    <row r="383" spans="4:4" ht="15.75" customHeight="1">
+    <row r="383" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D383" s="1"/>
     </row>
-    <row r="384" spans="4:4" ht="15.75" customHeight="1">
+    <row r="384" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D384" s="1"/>
     </row>
-    <row r="385" spans="4:4" ht="15.75" customHeight="1">
+    <row r="385" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D385" s="1"/>
     </row>
-    <row r="386" spans="4:4" ht="15.75" customHeight="1">
+    <row r="386" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D386" s="1"/>
     </row>
-    <row r="387" spans="4:4" ht="15.75" customHeight="1">
+    <row r="387" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D387" s="1"/>
     </row>
-    <row r="388" spans="4:4" ht="15.75" customHeight="1">
+    <row r="388" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D388" s="1"/>
     </row>
-    <row r="389" spans="4:4" ht="15.75" customHeight="1">
+    <row r="389" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D389" s="1"/>
     </row>
-    <row r="390" spans="4:4" ht="15.75" customHeight="1">
+    <row r="390" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D390" s="1"/>
     </row>
-    <row r="391" spans="4:4" ht="15.75" customHeight="1">
+    <row r="391" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D391" s="1"/>
     </row>
-    <row r="392" spans="4:4" ht="15.75" customHeight="1">
+    <row r="392" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D392" s="1"/>
     </row>
-    <row r="393" spans="4:4" ht="15.75" customHeight="1">
+    <row r="393" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D393" s="1"/>
     </row>
-    <row r="394" spans="4:4" ht="15.75" customHeight="1">
+    <row r="394" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D394" s="1"/>
     </row>
-    <row r="395" spans="4:4" ht="15.75" customHeight="1">
+    <row r="395" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D395" s="1"/>
     </row>
-    <row r="396" spans="4:4" ht="15.75" customHeight="1">
+    <row r="396" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D396" s="1"/>
     </row>
-    <row r="397" spans="4:4" ht="15.75" customHeight="1">
+    <row r="397" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D397" s="1"/>
     </row>
-    <row r="398" spans="4:4" ht="15.75" customHeight="1">
+    <row r="398" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D398" s="1"/>
     </row>
-    <row r="399" spans="4:4" ht="15.75" customHeight="1">
+    <row r="399" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D399" s="1"/>
     </row>
-    <row r="400" spans="4:4" ht="15.75" customHeight="1">
+    <row r="400" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D400" s="1"/>
     </row>
-    <row r="401" spans="4:4" ht="15.75" customHeight="1">
+    <row r="401" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D401" s="1"/>
     </row>
-    <row r="402" spans="4:4" ht="15.75" customHeight="1">
+    <row r="402" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D402" s="1"/>
     </row>
-    <row r="403" spans="4:4" ht="15.75" customHeight="1">
+    <row r="403" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D403" s="1"/>
     </row>
-    <row r="404" spans="4:4" ht="15.75" customHeight="1">
+    <row r="404" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D404" s="1"/>
     </row>
-    <row r="405" spans="4:4" ht="15.75" customHeight="1">
+    <row r="405" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D405" s="1"/>
     </row>
-    <row r="406" spans="4:4" ht="15.75" customHeight="1">
+    <row r="406" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D406" s="1"/>
     </row>
-    <row r="407" spans="4:4" ht="15.75" customHeight="1">
+    <row r="407" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D407" s="1"/>
     </row>
-    <row r="408" spans="4:4" ht="15.75" customHeight="1">
+    <row r="408" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D408" s="1"/>
     </row>
-    <row r="409" spans="4:4" ht="15.75" customHeight="1">
+    <row r="409" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D409" s="1"/>
     </row>
-    <row r="410" spans="4:4" ht="15.75" customHeight="1">
+    <row r="410" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D410" s="1"/>
     </row>
-    <row r="411" spans="4:4" ht="15.75" customHeight="1">
+    <row r="411" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D411" s="1"/>
     </row>
-    <row r="412" spans="4:4" ht="15.75" customHeight="1">
+    <row r="412" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D412" s="1"/>
     </row>
-    <row r="413" spans="4:4" ht="15.75" customHeight="1">
+    <row r="413" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D413" s="1"/>
     </row>
-    <row r="414" spans="4:4" ht="15.75" customHeight="1">
+    <row r="414" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D414" s="1"/>
     </row>
-    <row r="415" spans="4:4" ht="15.75" customHeight="1">
+    <row r="415" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D415" s="1"/>
     </row>
-    <row r="416" spans="4:4" ht="15.75" customHeight="1">
+    <row r="416" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D416" s="1"/>
     </row>
-    <row r="417" spans="4:4" ht="15.75" customHeight="1">
+    <row r="417" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D417" s="1"/>
     </row>
-    <row r="418" spans="4:4" ht="15.75" customHeight="1">
+    <row r="418" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D418" s="1"/>
     </row>
-    <row r="419" spans="4:4" ht="15.75" customHeight="1">
+    <row r="419" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D419" s="1"/>
     </row>
-    <row r="420" spans="4:4" ht="15.75" customHeight="1">
+    <row r="420" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D420" s="1"/>
     </row>
-    <row r="421" spans="4:4" ht="15.75" customHeight="1">
+    <row r="421" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D421" s="1"/>
     </row>
-    <row r="422" spans="4:4" ht="15.75" customHeight="1">
+    <row r="422" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D422" s="1"/>
     </row>
-    <row r="423" spans="4:4" ht="15.75" customHeight="1">
+    <row r="423" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D423" s="1"/>
     </row>
-    <row r="424" spans="4:4" ht="15.75" customHeight="1">
+    <row r="424" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D424" s="1"/>
     </row>
-    <row r="425" spans="4:4" ht="15.75" customHeight="1">
+    <row r="425" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D425" s="1"/>
     </row>
-    <row r="426" spans="4:4" ht="15.75" customHeight="1">
+    <row r="426" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D426" s="1"/>
     </row>
-    <row r="427" spans="4:4" ht="15.75" customHeight="1">
+    <row r="427" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D427" s="1"/>
     </row>
-    <row r="428" spans="4:4" ht="15.75" customHeight="1">
+    <row r="428" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D428" s="1"/>
     </row>
-    <row r="429" spans="4:4" ht="15.75" customHeight="1">
+    <row r="429" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D429" s="1"/>
     </row>
-    <row r="430" spans="4:4" ht="15.75" customHeight="1">
+    <row r="430" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D430" s="1"/>
     </row>
-    <row r="431" spans="4:4" ht="15.75" customHeight="1">
+    <row r="431" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D431" s="1"/>
     </row>
-    <row r="432" spans="4:4" ht="15.75" customHeight="1">
+    <row r="432" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D432" s="1"/>
     </row>
-    <row r="433" spans="4:4" ht="15.75" customHeight="1">
+    <row r="433" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D433" s="1"/>
     </row>
-    <row r="434" spans="4:4" ht="15.75" customHeight="1">
+    <row r="434" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D434" s="1"/>
     </row>
-    <row r="435" spans="4:4" ht="15.75" customHeight="1">
+    <row r="435" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D435" s="1"/>
     </row>
-    <row r="436" spans="4:4" ht="15.75" customHeight="1">
+    <row r="436" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D436" s="1"/>
     </row>
-    <row r="437" spans="4:4" ht="15.75" customHeight="1">
+    <row r="437" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D437" s="1"/>
     </row>
-    <row r="438" spans="4:4" ht="15.75" customHeight="1">
+    <row r="438" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D438" s="1"/>
     </row>
-    <row r="439" spans="4:4" ht="15.75" customHeight="1">
+    <row r="439" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D439" s="1"/>
     </row>
-    <row r="440" spans="4:4" ht="15.75" customHeight="1">
+    <row r="440" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D440" s="1"/>
     </row>
-    <row r="441" spans="4:4" ht="15.75" customHeight="1">
+    <row r="441" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D441" s="1"/>
     </row>
-    <row r="442" spans="4:4" ht="15.75" customHeight="1">
+    <row r="442" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D442" s="1"/>
     </row>
-    <row r="443" spans="4:4" ht="15.75" customHeight="1">
+    <row r="443" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D443" s="1"/>
     </row>
-    <row r="444" spans="4:4" ht="15.75" customHeight="1">
+    <row r="444" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D444" s="1"/>
     </row>
-    <row r="445" spans="4:4" ht="15.75" customHeight="1">
+    <row r="445" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D445" s="1"/>
     </row>
-    <row r="446" spans="4:4" ht="15.75" customHeight="1">
+    <row r="446" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D446" s="1"/>
     </row>
-    <row r="447" spans="4:4" ht="15.75" customHeight="1">
+    <row r="447" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D447" s="1"/>
     </row>
-    <row r="448" spans="4:4" ht="15.75" customHeight="1">
+    <row r="448" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D448" s="1"/>
     </row>
-    <row r="449" spans="4:4" ht="15.75" customHeight="1">
+    <row r="449" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D449" s="1"/>
     </row>
-    <row r="450" spans="4:4" ht="15.75" customHeight="1">
+    <row r="450" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D450" s="1"/>
     </row>
-    <row r="451" spans="4:4" ht="15.75" customHeight="1">
+    <row r="451" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D451" s="1"/>
     </row>
-    <row r="452" spans="4:4" ht="15.75" customHeight="1">
+    <row r="452" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D452" s="1"/>
     </row>
-    <row r="453" spans="4:4" ht="15.75" customHeight="1">
+    <row r="453" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D453" s="1"/>
     </row>
-    <row r="454" spans="4:4" ht="15.75" customHeight="1">
+    <row r="454" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D454" s="1"/>
     </row>
-    <row r="455" spans="4:4" ht="15.75" customHeight="1">
+    <row r="455" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D455" s="1"/>
     </row>
-    <row r="456" spans="4:4" ht="15.75" customHeight="1">
+    <row r="456" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D456" s="1"/>
     </row>
-    <row r="457" spans="4:4" ht="15.75" customHeight="1">
+    <row r="457" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D457" s="1"/>
     </row>
-    <row r="458" spans="4:4" ht="15.75" customHeight="1">
+    <row r="458" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D458" s="1"/>
     </row>
-    <row r="459" spans="4:4" ht="15.75" customHeight="1">
+    <row r="459" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D459" s="1"/>
     </row>
-    <row r="460" spans="4:4" ht="15.75" customHeight="1">
+    <row r="460" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D460" s="1"/>
     </row>
-    <row r="461" spans="4:4" ht="15.75" customHeight="1">
+    <row r="461" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D461" s="1"/>
     </row>
-    <row r="462" spans="4:4" ht="15.75" customHeight="1">
+    <row r="462" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D462" s="1"/>
     </row>
-    <row r="463" spans="4:4" ht="15.75" customHeight="1">
+    <row r="463" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D463" s="1"/>
     </row>
-    <row r="464" spans="4:4" ht="15.75" customHeight="1">
+    <row r="464" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D464" s="1"/>
     </row>
-    <row r="465" spans="4:4" ht="15.75" customHeight="1">
+    <row r="465" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D465" s="1"/>
     </row>
-    <row r="466" spans="4:4" ht="15.75" customHeight="1">
+    <row r="466" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D466" s="1"/>
     </row>
-    <row r="467" spans="4:4" ht="15.75" customHeight="1">
+    <row r="467" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D467" s="1"/>
     </row>
-    <row r="468" spans="4:4" ht="15.75" customHeight="1">
+    <row r="468" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D468" s="1"/>
     </row>
-    <row r="469" spans="4:4" ht="15.75" customHeight="1">
+    <row r="469" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D469" s="1"/>
     </row>
-    <row r="470" spans="4:4" ht="15.75" customHeight="1">
+    <row r="470" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D470" s="1"/>
     </row>
-    <row r="471" spans="4:4" ht="15.75" customHeight="1">
+    <row r="471" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D471" s="1"/>
     </row>
-    <row r="472" spans="4:4" ht="15.75" customHeight="1">
+    <row r="472" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D472" s="1"/>
     </row>
-    <row r="473" spans="4:4" ht="15.75" customHeight="1">
+    <row r="473" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D473" s="1"/>
     </row>
-    <row r="474" spans="4:4" ht="15.75" customHeight="1">
+    <row r="474" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D474" s="1"/>
     </row>
-    <row r="475" spans="4:4" ht="15.75" customHeight="1">
+    <row r="475" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D475" s="1"/>
     </row>
-    <row r="476" spans="4:4" ht="15.75" customHeight="1">
+    <row r="476" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D476" s="1"/>
     </row>
-    <row r="477" spans="4:4" ht="15.75" customHeight="1">
+    <row r="477" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D477" s="1"/>
     </row>
-    <row r="478" spans="4:4" ht="15.75" customHeight="1">
+    <row r="478" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D478" s="1"/>
     </row>
-    <row r="479" spans="4:4" ht="15.75" customHeight="1">
+    <row r="479" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D479" s="1"/>
     </row>
-    <row r="480" spans="4:4" ht="15.75" customHeight="1">
+    <row r="480" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D480" s="1"/>
     </row>
-    <row r="481" spans="4:4" ht="15.75" customHeight="1">
+    <row r="481" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D481" s="1"/>
     </row>
-    <row r="482" spans="4:4" ht="15.75" customHeight="1">
+    <row r="482" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D482" s="1"/>
     </row>
-    <row r="483" spans="4:4" ht="15.75" customHeight="1">
+    <row r="483" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D483" s="1"/>
     </row>
-    <row r="484" spans="4:4" ht="15.75" customHeight="1">
+    <row r="484" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D484" s="1"/>
     </row>
-    <row r="485" spans="4:4" ht="15.75" customHeight="1">
+    <row r="485" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D485" s="1"/>
     </row>
-    <row r="486" spans="4:4" ht="15.75" customHeight="1">
+    <row r="486" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D486" s="1"/>
     </row>
-    <row r="487" spans="4:4" ht="15.75" customHeight="1">
+    <row r="487" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D487" s="1"/>
     </row>
-    <row r="488" spans="4:4" ht="15.75" customHeight="1">
+    <row r="488" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D488" s="1"/>
     </row>
-    <row r="489" spans="4:4" ht="15.75" customHeight="1">
+    <row r="489" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D489" s="1"/>
     </row>
-    <row r="490" spans="4:4" ht="15.75" customHeight="1">
+    <row r="490" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D490" s="1"/>
     </row>
-    <row r="491" spans="4:4" ht="15.75" customHeight="1">
+    <row r="491" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D491" s="1"/>
     </row>
-    <row r="492" spans="4:4" ht="15.75" customHeight="1">
+    <row r="492" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D492" s="1"/>
     </row>
-    <row r="493" spans="4:4" ht="15.75" customHeight="1">
+    <row r="493" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D493" s="1"/>
     </row>
-    <row r="494" spans="4:4" ht="15.75" customHeight="1">
+    <row r="494" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D494" s="1"/>
     </row>
-    <row r="495" spans="4:4" ht="15.75" customHeight="1">
+    <row r="495" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D495" s="1"/>
     </row>
-    <row r="496" spans="4:4" ht="15.75" customHeight="1">
+    <row r="496" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D496" s="1"/>
     </row>
-    <row r="497" spans="4:4" ht="15.75" customHeight="1">
+    <row r="497" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D497" s="1"/>
     </row>
-    <row r="498" spans="4:4" ht="15.75" customHeight="1">
+    <row r="498" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D498" s="1"/>
     </row>
-    <row r="499" spans="4:4" ht="15.75" customHeight="1">
+    <row r="499" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D499" s="1"/>
     </row>
-    <row r="500" spans="4:4" ht="15.75" customHeight="1">
+    <row r="500" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D500" s="1"/>
     </row>
-    <row r="501" spans="4:4" ht="15.75" customHeight="1">
+    <row r="501" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D501" s="1"/>
     </row>
-    <row r="502" spans="4:4" ht="15.75" customHeight="1">
+    <row r="502" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D502" s="1"/>
     </row>
-    <row r="503" spans="4:4" ht="15.75" customHeight="1">
+    <row r="503" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D503" s="1"/>
     </row>
-    <row r="504" spans="4:4" ht="15.75" customHeight="1">
+    <row r="504" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D504" s="1"/>
     </row>
-    <row r="505" spans="4:4" ht="15.75" customHeight="1">
+    <row r="505" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D505" s="1"/>
     </row>
-    <row r="506" spans="4:4" ht="15.75" customHeight="1">
+    <row r="506" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D506" s="1"/>
     </row>
-    <row r="507" spans="4:4" ht="15.75" customHeight="1">
+    <row r="507" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D507" s="1"/>
     </row>
-    <row r="508" spans="4:4" ht="15.75" customHeight="1">
+    <row r="508" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D508" s="1"/>
     </row>
-    <row r="509" spans="4:4" ht="15.75" customHeight="1">
+    <row r="509" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D509" s="1"/>
     </row>
-    <row r="510" spans="4:4" ht="15.75" customHeight="1">
+    <row r="510" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D510" s="1"/>
     </row>
-    <row r="511" spans="4:4" ht="15.75" customHeight="1">
+    <row r="511" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D511" s="1"/>
     </row>
-    <row r="512" spans="4:4" ht="15.75" customHeight="1">
+    <row r="512" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D512" s="1"/>
     </row>
-    <row r="513" spans="4:4" ht="15.75" customHeight="1">
+    <row r="513" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D513" s="1"/>
     </row>
-    <row r="514" spans="4:4" ht="15.75" customHeight="1">
+    <row r="514" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D514" s="1"/>
     </row>
-    <row r="515" spans="4:4" ht="15.75" customHeight="1">
+    <row r="515" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D515" s="1"/>
     </row>
-    <row r="516" spans="4:4" ht="15.75" customHeight="1">
+    <row r="516" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D516" s="1"/>
     </row>
-    <row r="517" spans="4:4" ht="15.75" customHeight="1">
+    <row r="517" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D517" s="1"/>
     </row>
-    <row r="518" spans="4:4" ht="15.75" customHeight="1">
+    <row r="518" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D518" s="1"/>
     </row>
-    <row r="519" spans="4:4" ht="15.75" customHeight="1">
+    <row r="519" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D519" s="1"/>
     </row>
-    <row r="520" spans="4:4" ht="15.75" customHeight="1">
+    <row r="520" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D520" s="1"/>
     </row>
-    <row r="521" spans="4:4" ht="15.75" customHeight="1">
+    <row r="521" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D521" s="1"/>
     </row>
-    <row r="522" spans="4:4" ht="15.75" customHeight="1">
+    <row r="522" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D522" s="1"/>
     </row>
-    <row r="523" spans="4:4" ht="15.75" customHeight="1">
+    <row r="523" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D523" s="1"/>
     </row>
-    <row r="524" spans="4:4" ht="15.75" customHeight="1">
+    <row r="524" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D524" s="1"/>
     </row>
-    <row r="525" spans="4:4" ht="15.75" customHeight="1">
+    <row r="525" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D525" s="1"/>
     </row>
-    <row r="526" spans="4:4" ht="15.75" customHeight="1">
+    <row r="526" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D526" s="1"/>
     </row>
-    <row r="527" spans="4:4" ht="15.75" customHeight="1">
+    <row r="527" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D527" s="1"/>
     </row>
-    <row r="528" spans="4:4" ht="15.75" customHeight="1">
+    <row r="528" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D528" s="1"/>
     </row>
-    <row r="529" spans="4:4" ht="15.75" customHeight="1">
+    <row r="529" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D529" s="1"/>
     </row>
-    <row r="530" spans="4:4" ht="15.75" customHeight="1">
+    <row r="530" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D530" s="1"/>
     </row>
-    <row r="531" spans="4:4" ht="15.75" customHeight="1">
+    <row r="531" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D531" s="1"/>
     </row>
-    <row r="532" spans="4:4" ht="15.75" customHeight="1">
+    <row r="532" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D532" s="1"/>
     </row>
-    <row r="533" spans="4:4" ht="15.75" customHeight="1">
+    <row r="533" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D533" s="1"/>
     </row>
-    <row r="534" spans="4:4" ht="15.75" customHeight="1">
+    <row r="534" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D534" s="1"/>
     </row>
-    <row r="535" spans="4:4" ht="15.75" customHeight="1">
+    <row r="535" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D535" s="1"/>
     </row>
-    <row r="536" spans="4:4" ht="15.75" customHeight="1">
+    <row r="536" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D536" s="1"/>
     </row>
-    <row r="537" spans="4:4" ht="15.75" customHeight="1">
+    <row r="537" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D537" s="1"/>
     </row>
-    <row r="538" spans="4:4" ht="15.75" customHeight="1">
+    <row r="538" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D538" s="1"/>
     </row>
-    <row r="539" spans="4:4" ht="15.75" customHeight="1">
+    <row r="539" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D539" s="1"/>
     </row>
-    <row r="540" spans="4:4" ht="15.75" customHeight="1">
+    <row r="540" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D540" s="1"/>
     </row>
-    <row r="541" spans="4:4" ht="15.75" customHeight="1">
+    <row r="541" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D541" s="1"/>
     </row>
-    <row r="542" spans="4:4" ht="15.75" customHeight="1">
+    <row r="542" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D542" s="1"/>
     </row>
-    <row r="543" spans="4:4" ht="15.75" customHeight="1">
+    <row r="543" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D543" s="1"/>
     </row>
-    <row r="544" spans="4:4" ht="15.75" customHeight="1">
+    <row r="544" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D544" s="1"/>
     </row>
-    <row r="545" spans="4:4" ht="15.75" customHeight="1">
+    <row r="545" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D545" s="1"/>
     </row>
-    <row r="546" spans="4:4" ht="15.75" customHeight="1">
+    <row r="546" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D546" s="1"/>
     </row>
-    <row r="547" spans="4:4" ht="15.75" customHeight="1">
+    <row r="547" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D547" s="1"/>
     </row>
-    <row r="548" spans="4:4" ht="15.75" customHeight="1">
+    <row r="548" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D548" s="1"/>
     </row>
-    <row r="549" spans="4:4" ht="15.75" customHeight="1">
+    <row r="549" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D549" s="1"/>
     </row>
-    <row r="550" spans="4:4" ht="15.75" customHeight="1">
+    <row r="550" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D550" s="1"/>
     </row>
-    <row r="551" spans="4:4" ht="15.75" customHeight="1">
+    <row r="551" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D551" s="1"/>
     </row>
-    <row r="552" spans="4:4" ht="15.75" customHeight="1">
+    <row r="552" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D552" s="1"/>
     </row>
-    <row r="553" spans="4:4" ht="15.75" customHeight="1">
+    <row r="553" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D553" s="1"/>
     </row>
-    <row r="554" spans="4:4" ht="15.75" customHeight="1">
+    <row r="554" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D554" s="1"/>
     </row>
-    <row r="555" spans="4:4" ht="15.75" customHeight="1">
+    <row r="555" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D555" s="1"/>
     </row>
-    <row r="556" spans="4:4" ht="15.75" customHeight="1">
+    <row r="556" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D556" s="1"/>
     </row>
-    <row r="557" spans="4:4" ht="15.75" customHeight="1">
+    <row r="557" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D557" s="1"/>
     </row>
-    <row r="558" spans="4:4" ht="15.75" customHeight="1">
+    <row r="558" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D558" s="1"/>
     </row>
-    <row r="559" spans="4:4" ht="15.75" customHeight="1">
+    <row r="559" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D559" s="1"/>
     </row>
-    <row r="560" spans="4:4" ht="15.75" customHeight="1">
+    <row r="560" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D560" s="1"/>
     </row>
-    <row r="561" spans="4:4" ht="15.75" customHeight="1">
+    <row r="561" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D561" s="1"/>
     </row>
-    <row r="562" spans="4:4" ht="15.75" customHeight="1">
+    <row r="562" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D562" s="1"/>
     </row>
-    <row r="563" spans="4:4" ht="15.75" customHeight="1">
+    <row r="563" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D563" s="1"/>
     </row>
-    <row r="564" spans="4:4" ht="15.75" customHeight="1">
+    <row r="564" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D564" s="1"/>
     </row>
-    <row r="565" spans="4:4" ht="15.75" customHeight="1">
+    <row r="565" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D565" s="1"/>
     </row>
-    <row r="566" spans="4:4" ht="15.75" customHeight="1">
+    <row r="566" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D566" s="1"/>
     </row>
-    <row r="567" spans="4:4" ht="15.75" customHeight="1">
+    <row r="567" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D567" s="1"/>
     </row>
-    <row r="568" spans="4:4" ht="15.75" customHeight="1">
+    <row r="568" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D568" s="1"/>
     </row>
-    <row r="569" spans="4:4" ht="15.75" customHeight="1">
+    <row r="569" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D569" s="1"/>
     </row>
-    <row r="570" spans="4:4" ht="15.75" customHeight="1">
+    <row r="570" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D570" s="1"/>
     </row>
-    <row r="571" spans="4:4" ht="15.75" customHeight="1">
+    <row r="571" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D571" s="1"/>
     </row>
-    <row r="572" spans="4:4" ht="15.75" customHeight="1">
+    <row r="572" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D572" s="1"/>
     </row>
-    <row r="573" spans="4:4" ht="15.75" customHeight="1">
+    <row r="573" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D573" s="1"/>
     </row>
-    <row r="574" spans="4:4" ht="15.75" customHeight="1">
+    <row r="574" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D574" s="1"/>
     </row>
-    <row r="575" spans="4:4" ht="15.75" customHeight="1">
+    <row r="575" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D575" s="1"/>
     </row>
-    <row r="576" spans="4:4" ht="15.75" customHeight="1">
+    <row r="576" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D576" s="1"/>
     </row>
-    <row r="577" spans="4:4" ht="15.75" customHeight="1">
+    <row r="577" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D577" s="1"/>
     </row>
-    <row r="578" spans="4:4" ht="15.75" customHeight="1">
+    <row r="578" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D578" s="1"/>
     </row>
-    <row r="579" spans="4:4" ht="15.75" customHeight="1">
+    <row r="579" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D579" s="1"/>
     </row>
-    <row r="580" spans="4:4" ht="15.75" customHeight="1">
+    <row r="580" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D580" s="1"/>
     </row>
-    <row r="581" spans="4:4" ht="15.75" customHeight="1">
+    <row r="581" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D581" s="1"/>
     </row>
-    <row r="582" spans="4:4" ht="15.75" customHeight="1">
+    <row r="582" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D582" s="1"/>
     </row>
-    <row r="583" spans="4:4" ht="15.75" customHeight="1">
+    <row r="583" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D583" s="1"/>
     </row>
-    <row r="584" spans="4:4" ht="15.75" customHeight="1">
+    <row r="584" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D584" s="1"/>
     </row>
-    <row r="585" spans="4:4" ht="15.75" customHeight="1">
+    <row r="585" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D585" s="1"/>
     </row>
-    <row r="586" spans="4:4" ht="15.75" customHeight="1">
+    <row r="586" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D586" s="1"/>
     </row>
-    <row r="587" spans="4:4" ht="15.75" customHeight="1">
+    <row r="587" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D587" s="1"/>
     </row>
-    <row r="588" spans="4:4" ht="15.75" customHeight="1">
+    <row r="588" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D588" s="1"/>
     </row>
-    <row r="589" spans="4:4" ht="15.75" customHeight="1">
+    <row r="589" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D589" s="1"/>
     </row>
-    <row r="590" spans="4:4" ht="15.75" customHeight="1">
+    <row r="590" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D590" s="1"/>
     </row>
-    <row r="591" spans="4:4" ht="15.75" customHeight="1">
+    <row r="591" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D591" s="1"/>
     </row>
-    <row r="592" spans="4:4" ht="15.75" customHeight="1">
+    <row r="592" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D592" s="1"/>
     </row>
-    <row r="593" spans="4:4" ht="15.75" customHeight="1">
+    <row r="593" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D593" s="1"/>
     </row>
-    <row r="594" spans="4:4" ht="15.75" customHeight="1">
+    <row r="594" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D594" s="1"/>
     </row>
-    <row r="595" spans="4:4" ht="15.75" customHeight="1">
+    <row r="595" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D595" s="1"/>
     </row>
-    <row r="596" spans="4:4" ht="15.75" customHeight="1">
+    <row r="596" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D596" s="1"/>
     </row>
-    <row r="597" spans="4:4" ht="15.75" customHeight="1">
+    <row r="597" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D597" s="1"/>
     </row>
-    <row r="598" spans="4:4" ht="15.75" customHeight="1">
+    <row r="598" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D598" s="1"/>
     </row>
-    <row r="599" spans="4:4" ht="15.75" customHeight="1">
+    <row r="599" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D599" s="1"/>
     </row>
-    <row r="600" spans="4:4" ht="15.75" customHeight="1">
+    <row r="600" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D600" s="1"/>
     </row>
-    <row r="601" spans="4:4" ht="15.75" customHeight="1">
+    <row r="601" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D601" s="1"/>
     </row>
-    <row r="602" spans="4:4" ht="15.75" customHeight="1">
+    <row r="602" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D602" s="1"/>
     </row>
-    <row r="603" spans="4:4" ht="15.75" customHeight="1">
+    <row r="603" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D603" s="1"/>
     </row>
-    <row r="604" spans="4:4" ht="15.75" customHeight="1">
+    <row r="604" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D604" s="1"/>
     </row>
-    <row r="605" spans="4:4" ht="15.75" customHeight="1">
+    <row r="605" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D605" s="1"/>
     </row>
-    <row r="606" spans="4:4" ht="15.75" customHeight="1">
+    <row r="606" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D606" s="1"/>
     </row>
-    <row r="607" spans="4:4" ht="15.75" customHeight="1">
+    <row r="607" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D607" s="1"/>
     </row>
-    <row r="608" spans="4:4" ht="15.75" customHeight="1">
+    <row r="608" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D608" s="1"/>
     </row>
-    <row r="609" spans="4:4" ht="15.75" customHeight="1">
+    <row r="609" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D609" s="1"/>
     </row>
-    <row r="610" spans="4:4" ht="15.75" customHeight="1">
+    <row r="610" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D610" s="1"/>
     </row>
-    <row r="611" spans="4:4" ht="15.75" customHeight="1">
+    <row r="611" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D611" s="1"/>
     </row>
-    <row r="612" spans="4:4" ht="15.75" customHeight="1">
+    <row r="612" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D612" s="1"/>
     </row>
-    <row r="613" spans="4:4" ht="15.75" customHeight="1">
+    <row r="613" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D613" s="1"/>
     </row>
-    <row r="614" spans="4:4" ht="15.75" customHeight="1">
+    <row r="614" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D614" s="1"/>
     </row>
-    <row r="615" spans="4:4" ht="15.75" customHeight="1">
+    <row r="615" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D615" s="1"/>
     </row>
-    <row r="616" spans="4:4" ht="15.75" customHeight="1">
+    <row r="616" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D616" s="1"/>
     </row>
-    <row r="617" spans="4:4" ht="15.75" customHeight="1">
+    <row r="617" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D617" s="1"/>
     </row>
-    <row r="618" spans="4:4" ht="15.75" customHeight="1">
+    <row r="618" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D618" s="1"/>
     </row>
-    <row r="619" spans="4:4" ht="15.75" customHeight="1">
+    <row r="619" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D619" s="1"/>
     </row>
-    <row r="620" spans="4:4" ht="15.75" customHeight="1">
+    <row r="620" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D620" s="1"/>
     </row>
-    <row r="621" spans="4:4" ht="15.75" customHeight="1">
+    <row r="621" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D621" s="1"/>
     </row>
-    <row r="622" spans="4:4" ht="15.75" customHeight="1">
+    <row r="622" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D622" s="1"/>
     </row>
-    <row r="623" spans="4:4" ht="15.75" customHeight="1">
+    <row r="623" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D623" s="1"/>
     </row>
-    <row r="624" spans="4:4" ht="15.75" customHeight="1">
+    <row r="624" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D624" s="1"/>
     </row>
-    <row r="625" spans="4:4" ht="15.75" customHeight="1">
+    <row r="625" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D625" s="1"/>
     </row>
-    <row r="626" spans="4:4" ht="15.75" customHeight="1">
+    <row r="626" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D626" s="1"/>
     </row>
-    <row r="627" spans="4:4" ht="15.75" customHeight="1">
+    <row r="627" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D627" s="1"/>
     </row>
-    <row r="628" spans="4:4" ht="15.75" customHeight="1">
+    <row r="628" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D628" s="1"/>
     </row>
-    <row r="629" spans="4:4" ht="15.75" customHeight="1">
+    <row r="629" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D629" s="1"/>
     </row>
-    <row r="630" spans="4:4" ht="15.75" customHeight="1">
+    <row r="630" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D630" s="1"/>
     </row>
-    <row r="631" spans="4:4" ht="15.75" customHeight="1">
+    <row r="631" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D631" s="1"/>
     </row>
-    <row r="632" spans="4:4" ht="15.75" customHeight="1">
+    <row r="632" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D632" s="1"/>
     </row>
-    <row r="633" spans="4:4" ht="15.75" customHeight="1">
+    <row r="633" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D633" s="1"/>
     </row>
-    <row r="634" spans="4:4" ht="15.75" customHeight="1">
+    <row r="634" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D634" s="1"/>
     </row>
-    <row r="635" spans="4:4" ht="15.75" customHeight="1">
+    <row r="635" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D635" s="1"/>
     </row>
-    <row r="636" spans="4:4" ht="15.75" customHeight="1">
+    <row r="636" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D636" s="1"/>
     </row>
-    <row r="637" spans="4:4" ht="15.75" customHeight="1">
+    <row r="637" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D637" s="1"/>
     </row>
-    <row r="638" spans="4:4" ht="15.75" customHeight="1">
+    <row r="638" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D638" s="1"/>
     </row>
-    <row r="639" spans="4:4" ht="15.75" customHeight="1">
+    <row r="639" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D639" s="1"/>
     </row>
-    <row r="640" spans="4:4" ht="15.75" customHeight="1">
+    <row r="640" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D640" s="1"/>
     </row>
-    <row r="641" spans="4:4" ht="15.75" customHeight="1">
+    <row r="641" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D641" s="1"/>
     </row>
-    <row r="642" spans="4:4" ht="15.75" customHeight="1">
+    <row r="642" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D642" s="1"/>
     </row>
-    <row r="643" spans="4:4" ht="15.75" customHeight="1">
+    <row r="643" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D643" s="1"/>
     </row>
-    <row r="644" spans="4:4" ht="15.75" customHeight="1">
+    <row r="644" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D644" s="1"/>
     </row>
-    <row r="645" spans="4:4" ht="15.75" customHeight="1">
+    <row r="645" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D645" s="1"/>
     </row>
-    <row r="646" spans="4:4" ht="15.75" customHeight="1">
+    <row r="646" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D646" s="1"/>
     </row>
-    <row r="647" spans="4:4" ht="15.75" customHeight="1">
+    <row r="647" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D647" s="1"/>
     </row>
-    <row r="648" spans="4:4" ht="15.75" customHeight="1">
+    <row r="648" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D648" s="1"/>
     </row>
-    <row r="649" spans="4:4" ht="15.75" customHeight="1">
+    <row r="649" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D649" s="1"/>
     </row>
-    <row r="650" spans="4:4" ht="15.75" customHeight="1">
+    <row r="650" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D650" s="1"/>
     </row>
-    <row r="651" spans="4:4" ht="15.75" customHeight="1">
+    <row r="651" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D651" s="1"/>
     </row>
-    <row r="652" spans="4:4" ht="15.75" customHeight="1">
+    <row r="652" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D652" s="1"/>
     </row>
-    <row r="653" spans="4:4" ht="15.75" customHeight="1">
+    <row r="653" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D653" s="1"/>
     </row>
-    <row r="654" spans="4:4" ht="15.75" customHeight="1">
+    <row r="654" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D654" s="1"/>
     </row>
-    <row r="655" spans="4:4" ht="15.75" customHeight="1">
+    <row r="655" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D655" s="1"/>
     </row>
-    <row r="656" spans="4:4" ht="15.75" customHeight="1">
+    <row r="656" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D656" s="1"/>
     </row>
-    <row r="657" spans="4:4" ht="15.75" customHeight="1">
+    <row r="657" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D657" s="1"/>
     </row>
-    <row r="658" spans="4:4" ht="15.75" customHeight="1">
+    <row r="658" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D658" s="1"/>
     </row>
-    <row r="659" spans="4:4" ht="15.75" customHeight="1">
+    <row r="659" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D659" s="1"/>
     </row>
-    <row r="660" spans="4:4" ht="15.75" customHeight="1">
+    <row r="660" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D660" s="1"/>
     </row>
-    <row r="661" spans="4:4" ht="15.75" customHeight="1">
+    <row r="661" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D661" s="1"/>
     </row>
-    <row r="662" spans="4:4" ht="15.75" customHeight="1">
+    <row r="662" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D662" s="1"/>
     </row>
-    <row r="663" spans="4:4" ht="15.75" customHeight="1">
+    <row r="663" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D663" s="1"/>
     </row>
-    <row r="664" spans="4:4" ht="15.75" customHeight="1">
+    <row r="664" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D664" s="1"/>
     </row>
-    <row r="665" spans="4:4" ht="15.75" customHeight="1">
+    <row r="665" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D665" s="1"/>
     </row>
-    <row r="666" spans="4:4" ht="15.75" customHeight="1">
+    <row r="666" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D666" s="1"/>
     </row>
-    <row r="667" spans="4:4" ht="15.75" customHeight="1">
+    <row r="667" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D667" s="1"/>
     </row>
-    <row r="668" spans="4:4" ht="15.75" customHeight="1">
+    <row r="668" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D668" s="1"/>
     </row>
-    <row r="669" spans="4:4" ht="15.75" customHeight="1">
+    <row r="669" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D669" s="1"/>
     </row>
-    <row r="670" spans="4:4" ht="15.75" customHeight="1">
+    <row r="670" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D670" s="1"/>
     </row>
-    <row r="671" spans="4:4" ht="15.75" customHeight="1">
+    <row r="671" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D671" s="1"/>
     </row>
-    <row r="672" spans="4:4" ht="15.75" customHeight="1">
+    <row r="672" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D672" s="1"/>
     </row>
-    <row r="673" spans="4:4" ht="15.75" customHeight="1">
+    <row r="673" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D673" s="1"/>
     </row>
-    <row r="674" spans="4:4" ht="15.75" customHeight="1">
+    <row r="674" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D674" s="1"/>
     </row>
-    <row r="675" spans="4:4" ht="15.75" customHeight="1">
+    <row r="675" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D675" s="1"/>
     </row>
-    <row r="676" spans="4:4" ht="15.75" customHeight="1">
+    <row r="676" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D676" s="1"/>
     </row>
-    <row r="677" spans="4:4" ht="15.75" customHeight="1">
+    <row r="677" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D677" s="1"/>
     </row>
-    <row r="678" spans="4:4" ht="15.75" customHeight="1">
+    <row r="678" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D678" s="1"/>
     </row>
-    <row r="679" spans="4:4" ht="15.75" customHeight="1">
+    <row r="679" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D679" s="1"/>
     </row>
-    <row r="680" spans="4:4" ht="15.75" customHeight="1">
+    <row r="680" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D680" s="1"/>
     </row>
-    <row r="681" spans="4:4" ht="15.75" customHeight="1">
+    <row r="681" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D681" s="1"/>
     </row>
-    <row r="682" spans="4:4" ht="15.75" customHeight="1">
+    <row r="682" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D682" s="1"/>
     </row>
-    <row r="683" spans="4:4" ht="15.75" customHeight="1">
+    <row r="683" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D683" s="1"/>
     </row>
-    <row r="684" spans="4:4" ht="15.75" customHeight="1">
+    <row r="684" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D684" s="1"/>
     </row>
-    <row r="685" spans="4:4" ht="15.75" customHeight="1">
+    <row r="685" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D685" s="1"/>
     </row>
-    <row r="686" spans="4:4" ht="15.75" customHeight="1">
+    <row r="686" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D686" s="1"/>
     </row>
-    <row r="687" spans="4:4" ht="15.75" customHeight="1">
+    <row r="687" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D687" s="1"/>
     </row>
-    <row r="688" spans="4:4" ht="15.75" customHeight="1">
+    <row r="688" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D688" s="1"/>
     </row>
-    <row r="689" spans="4:4" ht="15.75" customHeight="1">
+    <row r="689" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D689" s="1"/>
     </row>
-    <row r="690" spans="4:4" ht="15.75" customHeight="1">
+    <row r="690" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D690" s="1"/>
     </row>
-    <row r="691" spans="4:4" ht="15.75" customHeight="1">
+    <row r="691" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D691" s="1"/>
     </row>
-    <row r="692" spans="4:4" ht="15.75" customHeight="1">
+    <row r="692" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D692" s="1"/>
     </row>
-    <row r="693" spans="4:4" ht="15.75" customHeight="1">
+    <row r="693" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D693" s="1"/>
     </row>
-    <row r="694" spans="4:4" ht="15.75" customHeight="1">
+    <row r="694" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D694" s="1"/>
     </row>
-    <row r="695" spans="4:4" ht="15.75" customHeight="1">
+    <row r="695" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D695" s="1"/>
     </row>
-    <row r="696" spans="4:4" ht="15.75" customHeight="1">
+    <row r="696" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D696" s="1"/>
     </row>
-    <row r="697" spans="4:4" ht="15.75" customHeight="1">
+    <row r="697" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D697" s="1"/>
     </row>
-    <row r="698" spans="4:4" ht="15.75" customHeight="1">
+    <row r="698" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D698" s="1"/>
     </row>
-    <row r="699" spans="4:4" ht="15.75" customHeight="1">
+    <row r="699" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D699" s="1"/>
     </row>
-    <row r="700" spans="4:4" ht="15.75" customHeight="1">
+    <row r="700" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D700" s="1"/>
     </row>
-    <row r="701" spans="4:4" ht="15.75" customHeight="1">
+    <row r="701" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D701" s="1"/>
     </row>
-    <row r="702" spans="4:4" ht="15.75" customHeight="1">
+    <row r="702" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D702" s="1"/>
     </row>
-    <row r="703" spans="4:4" ht="15.75" customHeight="1">
+    <row r="703" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D703" s="1"/>
     </row>
-    <row r="704" spans="4:4" ht="15.75" customHeight="1">
+    <row r="704" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D704" s="1"/>
     </row>
-    <row r="705" spans="4:4" ht="15.75" customHeight="1">
+    <row r="705" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D705" s="1"/>
     </row>
-    <row r="706" spans="4:4" ht="15.75" customHeight="1">
+    <row r="706" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D706" s="1"/>
     </row>
-    <row r="707" spans="4:4" ht="15.75" customHeight="1">
+    <row r="707" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D707" s="1"/>
     </row>
-    <row r="708" spans="4:4" ht="15.75" customHeight="1">
+    <row r="708" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D708" s="1"/>
     </row>
-    <row r="709" spans="4:4" ht="15.75" customHeight="1">
+    <row r="709" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D709" s="1"/>
     </row>
-    <row r="710" spans="4:4" ht="15.75" customHeight="1">
+    <row r="710" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D710" s="1"/>
     </row>
-    <row r="711" spans="4:4" ht="15.75" customHeight="1">
+    <row r="711" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D711" s="1"/>
     </row>
-    <row r="712" spans="4:4" ht="15.75" customHeight="1">
+    <row r="712" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D712" s="1"/>
     </row>
-    <row r="713" spans="4:4" ht="15.75" customHeight="1">
+    <row r="713" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D713" s="1"/>
     </row>
-    <row r="714" spans="4:4" ht="15.75" customHeight="1">
+    <row r="714" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D714" s="1"/>
     </row>
-    <row r="715" spans="4:4" ht="15.75" customHeight="1">
+    <row r="715" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D715" s="1"/>
     </row>
-    <row r="716" spans="4:4" ht="15.75" customHeight="1">
+    <row r="716" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D716" s="1"/>
     </row>
-    <row r="717" spans="4:4" ht="15.75" customHeight="1">
+    <row r="717" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D717" s="1"/>
     </row>
-    <row r="718" spans="4:4" ht="15.75" customHeight="1">
+    <row r="718" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D718" s="1"/>
     </row>
-    <row r="719" spans="4:4" ht="15.75" customHeight="1">
+    <row r="719" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D719" s="1"/>
     </row>
-    <row r="720" spans="4:4" ht="15.75" customHeight="1">
+    <row r="720" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D720" s="1"/>
     </row>
-    <row r="721" spans="4:4" ht="15.75" customHeight="1">
+    <row r="721" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D721" s="1"/>
     </row>
-    <row r="722" spans="4:4" ht="15.75" customHeight="1">
+    <row r="722" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D722" s="1"/>
     </row>
-    <row r="723" spans="4:4" ht="15.75" customHeight="1">
+    <row r="723" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D723" s="1"/>
     </row>
-    <row r="724" spans="4:4" ht="15.75" customHeight="1">
+    <row r="724" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D724" s="1"/>
     </row>
-    <row r="725" spans="4:4" ht="15.75" customHeight="1">
+    <row r="725" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D725" s="1"/>
     </row>
-    <row r="726" spans="4:4" ht="15.75" customHeight="1">
+    <row r="726" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D726" s="1"/>
     </row>
-    <row r="727" spans="4:4" ht="15.75" customHeight="1">
+    <row r="727" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D727" s="1"/>
     </row>
-    <row r="728" spans="4:4" ht="15.75" customHeight="1">
+    <row r="728" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D728" s="1"/>
     </row>
-    <row r="729" spans="4:4" ht="15.75" customHeight="1">
+    <row r="729" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D729" s="1"/>
     </row>
-    <row r="730" spans="4:4" ht="15.75" customHeight="1">
+    <row r="730" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D730" s="1"/>
     </row>
-    <row r="731" spans="4:4" ht="15.75" customHeight="1">
+    <row r="731" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D731" s="1"/>
     </row>
-    <row r="732" spans="4:4" ht="15.75" customHeight="1">
+    <row r="732" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D732" s="1"/>
     </row>
-    <row r="733" spans="4:4" ht="15.75" customHeight="1">
+    <row r="733" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D733" s="1"/>
     </row>
-    <row r="734" spans="4:4" ht="15.75" customHeight="1">
+    <row r="734" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D734" s="1"/>
     </row>
-    <row r="735" spans="4:4" ht="15.75" customHeight="1">
+    <row r="735" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D735" s="1"/>
     </row>
-    <row r="736" spans="4:4" ht="15.75" customHeight="1">
+    <row r="736" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D736" s="1"/>
     </row>
-    <row r="737" spans="4:4" ht="15.75" customHeight="1">
+    <row r="737" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D737" s="1"/>
     </row>
-    <row r="738" spans="4:4" ht="15.75" customHeight="1">
+    <row r="738" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D738" s="1"/>
     </row>
-    <row r="739" spans="4:4" ht="15.75" customHeight="1">
+    <row r="739" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D739" s="1"/>
     </row>
-    <row r="740" spans="4:4" ht="15.75" customHeight="1">
+    <row r="740" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D740" s="1"/>
     </row>
-    <row r="741" spans="4:4" ht="15.75" customHeight="1">
+    <row r="741" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D741" s="1"/>
     </row>
-    <row r="742" spans="4:4" ht="15.75" customHeight="1">
+    <row r="742" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D742" s="1"/>
     </row>
-    <row r="743" spans="4:4" ht="15.75" customHeight="1">
+    <row r="743" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D743" s="1"/>
     </row>
-    <row r="744" spans="4:4" ht="15.75" customHeight="1">
+    <row r="744" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D744" s="1"/>
     </row>
-    <row r="745" spans="4:4" ht="15.75" customHeight="1">
+    <row r="745" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D745" s="1"/>
     </row>
-    <row r="746" spans="4:4" ht="15.75" customHeight="1">
+    <row r="746" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D746" s="1"/>
     </row>
-    <row r="747" spans="4:4" ht="15.75" customHeight="1">
+    <row r="747" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D747" s="1"/>
     </row>
-    <row r="748" spans="4:4" ht="15.75" customHeight="1">
+    <row r="748" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D748" s="1"/>
     </row>
-    <row r="749" spans="4:4" ht="15.75" customHeight="1">
+    <row r="749" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D749" s="1"/>
     </row>
-    <row r="750" spans="4:4" ht="15.75" customHeight="1">
+    <row r="750" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D750" s="1"/>
     </row>
-    <row r="751" spans="4:4" ht="15.75" customHeight="1">
+    <row r="751" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D751" s="1"/>
     </row>
-    <row r="752" spans="4:4" ht="15.75" customHeight="1">
+    <row r="752" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D752" s="1"/>
     </row>
-    <row r="753" spans="4:4" ht="15.75" customHeight="1">
+    <row r="753" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D753" s="1"/>
     </row>
-    <row r="754" spans="4:4" ht="15.75" customHeight="1">
+    <row r="754" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D754" s="1"/>
     </row>
-    <row r="755" spans="4:4" ht="15.75" customHeight="1">
+    <row r="755" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D755" s="1"/>
     </row>
-    <row r="756" spans="4:4" ht="15.75" customHeight="1">
+    <row r="756" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D756" s="1"/>
     </row>
-    <row r="757" spans="4:4" ht="15.75" customHeight="1">
+    <row r="757" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D757" s="1"/>
     </row>
-    <row r="758" spans="4:4" ht="15.75" customHeight="1">
+    <row r="758" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D758" s="1"/>
     </row>
-    <row r="759" spans="4:4" ht="15.75" customHeight="1">
+    <row r="759" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D759" s="1"/>
     </row>
-    <row r="760" spans="4:4" ht="15.75" customHeight="1">
+    <row r="760" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D760" s="1"/>
     </row>
-    <row r="761" spans="4:4" ht="15.75" customHeight="1">
+    <row r="761" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D761" s="1"/>
     </row>
-    <row r="762" spans="4:4" ht="15.75" customHeight="1">
+    <row r="762" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D762" s="1"/>
     </row>
-    <row r="763" spans="4:4" ht="15.75" customHeight="1">
+    <row r="763" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D763" s="1"/>
     </row>
-    <row r="764" spans="4:4" ht="15.75" customHeight="1">
+    <row r="764" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D764" s="1"/>
     </row>
-    <row r="765" spans="4:4" ht="15.75" customHeight="1">
+    <row r="765" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D765" s="1"/>
     </row>
-    <row r="766" spans="4:4" ht="15.75" customHeight="1">
+    <row r="766" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D766" s="1"/>
     </row>
-    <row r="767" spans="4:4" ht="15.75" customHeight="1">
+    <row r="767" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D767" s="1"/>
     </row>
-    <row r="768" spans="4:4" ht="15.75" customHeight="1">
+    <row r="768" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D768" s="1"/>
     </row>
-    <row r="769" spans="4:4" ht="15.75" customHeight="1">
+    <row r="769" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D769" s="1"/>
     </row>
-    <row r="770" spans="4:4" ht="15.75" customHeight="1">
+    <row r="770" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D770" s="1"/>
     </row>
-    <row r="771" spans="4:4" ht="15.75" customHeight="1">
+    <row r="771" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D771" s="1"/>
     </row>
-    <row r="772" spans="4:4" ht="15.75" customHeight="1">
+    <row r="772" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D772" s="1"/>
     </row>
-    <row r="773" spans="4:4" ht="15.75" customHeight="1">
+    <row r="773" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D773" s="1"/>
     </row>
-    <row r="774" spans="4:4" ht="15.75" customHeight="1">
+    <row r="774" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D774" s="1"/>
     </row>
-    <row r="775" spans="4:4" ht="15.75" customHeight="1">
+    <row r="775" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D775" s="1"/>
     </row>
-    <row r="776" spans="4:4" ht="15.75" customHeight="1">
+    <row r="776" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D776" s="1"/>
     </row>
-    <row r="777" spans="4:4" ht="15.75" customHeight="1">
+    <row r="777" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D777" s="1"/>
     </row>
-    <row r="778" spans="4:4" ht="15.75" customHeight="1">
+    <row r="778" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D778" s="1"/>
     </row>
-    <row r="779" spans="4:4" ht="15.75" customHeight="1">
+    <row r="779" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D779" s="1"/>
     </row>
-    <row r="780" spans="4:4" ht="15.75" customHeight="1">
+    <row r="780" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D780" s="1"/>
     </row>
-    <row r="781" spans="4:4" ht="15.75" customHeight="1">
+    <row r="781" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D781" s="1"/>
     </row>
-    <row r="782" spans="4:4" ht="15.75" customHeight="1">
+    <row r="782" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D782" s="1"/>
     </row>
-    <row r="783" spans="4:4" ht="15.75" customHeight="1">
+    <row r="783" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D783" s="1"/>
     </row>
-    <row r="784" spans="4:4" ht="15.75" customHeight="1">
+    <row r="784" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D784" s="1"/>
     </row>
-    <row r="785" spans="4:4" ht="15.75" customHeight="1">
+    <row r="785" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D785" s="1"/>
     </row>
-    <row r="786" spans="4:4" ht="15.75" customHeight="1">
+    <row r="786" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D786" s="1"/>
     </row>
-    <row r="787" spans="4:4" ht="15.75" customHeight="1">
+    <row r="787" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D787" s="1"/>
     </row>
-    <row r="788" spans="4:4" ht="15.75" customHeight="1">
+    <row r="788" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D788" s="1"/>
     </row>
-    <row r="789" spans="4:4" ht="15.75" customHeight="1">
+    <row r="789" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D789" s="1"/>
     </row>
-    <row r="790" spans="4:4" ht="15.75" customHeight="1">
+    <row r="790" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D790" s="1"/>
     </row>
-    <row r="791" spans="4:4" ht="15.75" customHeight="1">
+    <row r="791" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D791" s="1"/>
     </row>
-    <row r="792" spans="4:4" ht="15.75" customHeight="1">
+    <row r="792" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D792" s="1"/>
     </row>
-    <row r="793" spans="4:4" ht="15.75" customHeight="1">
+    <row r="793" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D793" s="1"/>
     </row>
-    <row r="794" spans="4:4" ht="15.75" customHeight="1">
+    <row r="794" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D794" s="1"/>
     </row>
-    <row r="795" spans="4:4" ht="15.75" customHeight="1">
+    <row r="795" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D795" s="1"/>
     </row>
-    <row r="796" spans="4:4" ht="15.75" customHeight="1">
+    <row r="796" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D796" s="1"/>
     </row>
-    <row r="797" spans="4:4" ht="15.75" customHeight="1">
+    <row r="797" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D797" s="1"/>
     </row>
-    <row r="798" spans="4:4" ht="15.75" customHeight="1">
+    <row r="798" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D798" s="1"/>
     </row>
-    <row r="799" spans="4:4" ht="15.75" customHeight="1">
+    <row r="799" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D799" s="1"/>
     </row>
-    <row r="800" spans="4:4" ht="15.75" customHeight="1">
+    <row r="800" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D800" s="1"/>
     </row>
-    <row r="801" spans="4:4" ht="15.75" customHeight="1">
+    <row r="801" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D801" s="1"/>
     </row>
-    <row r="802" spans="4:4" ht="15.75" customHeight="1">
+    <row r="802" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D802" s="1"/>
     </row>
-    <row r="803" spans="4:4" ht="15.75" customHeight="1">
+    <row r="803" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D803" s="1"/>
     </row>
-    <row r="804" spans="4:4" ht="15.75" customHeight="1">
+    <row r="804" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D804" s="1"/>
     </row>
-    <row r="805" spans="4:4" ht="15.75" customHeight="1">
+    <row r="805" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D805" s="1"/>
     </row>
-    <row r="806" spans="4:4" ht="15.75" customHeight="1">
+    <row r="806" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D806" s="1"/>
     </row>
-    <row r="807" spans="4:4" ht="15.75" customHeight="1">
+    <row r="807" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D807" s="1"/>
     </row>
-    <row r="808" spans="4:4" ht="15.75" customHeight="1">
+    <row r="808" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D808" s="1"/>
     </row>
-    <row r="809" spans="4:4" ht="15.75" customHeight="1">
+    <row r="809" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D809" s="1"/>
     </row>
-    <row r="810" spans="4:4" ht="15.75" customHeight="1">
+    <row r="810" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D810" s="1"/>
     </row>
-    <row r="811" spans="4:4" ht="15.75" customHeight="1">
+    <row r="811" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D811" s="1"/>
     </row>
-    <row r="812" spans="4:4" ht="15.75" customHeight="1">
+    <row r="812" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D812" s="1"/>
     </row>
-    <row r="813" spans="4:4" ht="15.75" customHeight="1">
+    <row r="813" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D813" s="1"/>
     </row>
-    <row r="814" spans="4:4" ht="15.75" customHeight="1">
+    <row r="814" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D814" s="1"/>
     </row>
-    <row r="815" spans="4:4" ht="15.75" customHeight="1">
+    <row r="815" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D815" s="1"/>
     </row>
-    <row r="816" spans="4:4" ht="15.75" customHeight="1">
+    <row r="816" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D816" s="1"/>
     </row>
-    <row r="817" spans="4:4" ht="15.75" customHeight="1">
+    <row r="817" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D817" s="1"/>
     </row>
-    <row r="818" spans="4:4" ht="15.75" customHeight="1">
+    <row r="818" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D818" s="1"/>
     </row>
-    <row r="819" spans="4:4" ht="15.75" customHeight="1">
+    <row r="819" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D819" s="1"/>
     </row>
-    <row r="820" spans="4:4" ht="15.75" customHeight="1">
+    <row r="820" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D820" s="1"/>
     </row>
-    <row r="821" spans="4:4" ht="15.75" customHeight="1">
+    <row r="821" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D821" s="1"/>
     </row>
-    <row r="822" spans="4:4" ht="15.75" customHeight="1">
+    <row r="822" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D822" s="1"/>
     </row>
-    <row r="823" spans="4:4" ht="15.75" customHeight="1">
+    <row r="823" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D823" s="1"/>
     </row>
-    <row r="824" spans="4:4" ht="15.75" customHeight="1">
+    <row r="824" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D824" s="1"/>
     </row>
-    <row r="825" spans="4:4" ht="15.75" customHeight="1">
+    <row r="825" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D825" s="1"/>
     </row>
-    <row r="826" spans="4:4" ht="15.75" customHeight="1">
+    <row r="826" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D826" s="1"/>
     </row>
-    <row r="827" spans="4:4" ht="15.75" customHeight="1">
+    <row r="827" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D827" s="1"/>
     </row>
-    <row r="828" spans="4:4" ht="15.75" customHeight="1">
+    <row r="828" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D828" s="1"/>
     </row>
-    <row r="829" spans="4:4" ht="15.75" customHeight="1">
+    <row r="829" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D829" s="1"/>
     </row>
-    <row r="830" spans="4:4" ht="15.75" customHeight="1">
+    <row r="830" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D830" s="1"/>
     </row>
-    <row r="831" spans="4:4" ht="15.75" customHeight="1">
+    <row r="831" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D831" s="1"/>
     </row>
-    <row r="832" spans="4:4" ht="15.75" customHeight="1">
+    <row r="832" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D832" s="1"/>
     </row>
-    <row r="833" spans="4:4" ht="15.75" customHeight="1">
+    <row r="833" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D833" s="1"/>
     </row>
-    <row r="834" spans="4:4" ht="15.75" customHeight="1">
+    <row r="834" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D834" s="1"/>
     </row>
-    <row r="835" spans="4:4" ht="15.75" customHeight="1">
+    <row r="835" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D835" s="1"/>
     </row>
-    <row r="836" spans="4:4" ht="15.75" customHeight="1">
+    <row r="836" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D836" s="1"/>
     </row>
-    <row r="837" spans="4:4" ht="15.75" customHeight="1">
+    <row r="837" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D837" s="1"/>
     </row>
-    <row r="838" spans="4:4" ht="15.75" customHeight="1">
+    <row r="838" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D838" s="1"/>
     </row>
-    <row r="839" spans="4:4" ht="15.75" customHeight="1">
+    <row r="839" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D839" s="1"/>
     </row>
-    <row r="840" spans="4:4" ht="15.75" customHeight="1">
+    <row r="840" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D840" s="1"/>
     </row>
-    <row r="841" spans="4:4" ht="15.75" customHeight="1">
+    <row r="841" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D841" s="1"/>
     </row>
-    <row r="842" spans="4:4" ht="15.75" customHeight="1">
+    <row r="842" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D842" s="1"/>
     </row>
-    <row r="843" spans="4:4" ht="15.75" customHeight="1">
+    <row r="843" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D843" s="1"/>
     </row>
-    <row r="844" spans="4:4" ht="15.75" customHeight="1">
+    <row r="844" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D844" s="1"/>
     </row>
-    <row r="845" spans="4:4" ht="15.75" customHeight="1">
+    <row r="845" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D845" s="1"/>
     </row>
-    <row r="846" spans="4:4" ht="15.75" customHeight="1">
+    <row r="846" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D846" s="1"/>
     </row>
-    <row r="847" spans="4:4" ht="15.75" customHeight="1">
+    <row r="847" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D847" s="1"/>
     </row>
-    <row r="848" spans="4:4" ht="15.75" customHeight="1">
+    <row r="848" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D848" s="1"/>
     </row>
-    <row r="849" spans="4:4" ht="15.75" customHeight="1">
+    <row r="849" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D849" s="1"/>
     </row>
-    <row r="850" spans="4:4" ht="15.75" customHeight="1">
+    <row r="850" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D850" s="1"/>
     </row>
-    <row r="851" spans="4:4" ht="15.75" customHeight="1">
+    <row r="851" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D851" s="1"/>
     </row>
-    <row r="852" spans="4:4" ht="15.75" customHeight="1">
+    <row r="852" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D852" s="1"/>
     </row>
-    <row r="853" spans="4:4" ht="15.75" customHeight="1">
+    <row r="853" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D853" s="1"/>
     </row>
-    <row r="854" spans="4:4" ht="15.75" customHeight="1">
+    <row r="854" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D854" s="1"/>
     </row>
-    <row r="855" spans="4:4" ht="15.75" customHeight="1">
+    <row r="855" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D855" s="1"/>
     </row>
-    <row r="856" spans="4:4" ht="15.75" customHeight="1">
+    <row r="856" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D856" s="1"/>
     </row>
-    <row r="857" spans="4:4" ht="15.75" customHeight="1">
+    <row r="857" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D857" s="1"/>
     </row>
-    <row r="858" spans="4:4" ht="15.75" customHeight="1">
+    <row r="858" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D858" s="1"/>
     </row>
-    <row r="859" spans="4:4" ht="15.75" customHeight="1">
+    <row r="859" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D859" s="1"/>
     </row>
-    <row r="860" spans="4:4" ht="15.75" customHeight="1">
+    <row r="860" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D860" s="1"/>
     </row>
-    <row r="861" spans="4:4" ht="15.75" customHeight="1">
+    <row r="861" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D861" s="1"/>
     </row>
-    <row r="862" spans="4:4" ht="15.75" customHeight="1">
+    <row r="862" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D862" s="1"/>
     </row>
-    <row r="863" spans="4:4" ht="15.75" customHeight="1">
+    <row r="863" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D863" s="1"/>
     </row>
-    <row r="864" spans="4:4" ht="15.75" customHeight="1">
+    <row r="864" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D864" s="1"/>
     </row>
-    <row r="865" spans="4:4" ht="15.75" customHeight="1">
+    <row r="865" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D865" s="1"/>
     </row>
-    <row r="866" spans="4:4" ht="15.75" customHeight="1">
+    <row r="866" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D866" s="1"/>
     </row>
-    <row r="867" spans="4:4" ht="15.75" customHeight="1">
+    <row r="867" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D867" s="1"/>
     </row>
-    <row r="868" spans="4:4" ht="15.75" customHeight="1">
+    <row r="868" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D868" s="1"/>
     </row>
-    <row r="869" spans="4:4" ht="15.75" customHeight="1">
+    <row r="869" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D869" s="1"/>
     </row>
-    <row r="870" spans="4:4" ht="15.75" customHeight="1">
+    <row r="870" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D870" s="1"/>
     </row>
-    <row r="871" spans="4:4" ht="15.75" customHeight="1">
+    <row r="871" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D871" s="1"/>
     </row>
-    <row r="872" spans="4:4" ht="15.75" customHeight="1">
+    <row r="872" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D872" s="1"/>
     </row>
-    <row r="873" spans="4:4" ht="15.75" customHeight="1">
+    <row r="873" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D873" s="1"/>
     </row>
-    <row r="874" spans="4:4" ht="15.75" customHeight="1">
+    <row r="874" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D874" s="1"/>
     </row>
-    <row r="875" spans="4:4" ht="15.75" customHeight="1">
+    <row r="875" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D875" s="1"/>
     </row>
-    <row r="876" spans="4:4" ht="15.75" customHeight="1">
+    <row r="876" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D876" s="1"/>
     </row>
-    <row r="877" spans="4:4" ht="15.75" customHeight="1">
+    <row r="877" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D877" s="1"/>
     </row>
-    <row r="878" spans="4:4" ht="15.75" customHeight="1">
+    <row r="878" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D878" s="1"/>
     </row>
-    <row r="879" spans="4:4" ht="15.75" customHeight="1">
+    <row r="879" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D879" s="1"/>
     </row>
-    <row r="880" spans="4:4" ht="15.75" customHeight="1">
+    <row r="880" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D880" s="1"/>
     </row>
-    <row r="881" spans="4:4" ht="15.75" customHeight="1">
+    <row r="881" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D881" s="1"/>
     </row>
-    <row r="882" spans="4:4" ht="15.75" customHeight="1">
+    <row r="882" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D882" s="1"/>
     </row>
-    <row r="883" spans="4:4" ht="15.75" customHeight="1">
+    <row r="883" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D883" s="1"/>
     </row>
-    <row r="884" spans="4:4" ht="15.75" customHeight="1">
+    <row r="884" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D884" s="1"/>
     </row>
-    <row r="885" spans="4:4" ht="15.75" customHeight="1">
+    <row r="885" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D885" s="1"/>
     </row>
-    <row r="886" spans="4:4" ht="15.75" customHeight="1">
+    <row r="886" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D886" s="1"/>
     </row>
-    <row r="887" spans="4:4" ht="15.75" customHeight="1">
+    <row r="887" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D887" s="1"/>
     </row>
-    <row r="888" spans="4:4" ht="15.75" customHeight="1">
+    <row r="888" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D888" s="1"/>
     </row>
-    <row r="889" spans="4:4" ht="15.75" customHeight="1">
+    <row r="889" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D889" s="1"/>
     </row>
-    <row r="890" spans="4:4" ht="15.75" customHeight="1">
+    <row r="890" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D890" s="1"/>
     </row>
-    <row r="891" spans="4:4" ht="15.75" customHeight="1">
+    <row r="891" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D891" s="1"/>
     </row>
-    <row r="892" spans="4:4" ht="15.75" customHeight="1">
+    <row r="892" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D892" s="1"/>
     </row>
-    <row r="893" spans="4:4" ht="15.75" customHeight="1">
+    <row r="893" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D893" s="1"/>
     </row>
-    <row r="894" spans="4:4" ht="15.75" customHeight="1">
+    <row r="894" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D894" s="1"/>
     </row>
-    <row r="895" spans="4:4" ht="15.75" customHeight="1">
+    <row r="895" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D895" s="1"/>
     </row>
-    <row r="896" spans="4:4" ht="15.75" customHeight="1">
+    <row r="896" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D896" s="1"/>
     </row>
-    <row r="897" spans="4:4" ht="15.75" customHeight="1">
+    <row r="897" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D897" s="1"/>
     </row>
-    <row r="898" spans="4:4" ht="15.75" customHeight="1">
+    <row r="898" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D898" s="1"/>
     </row>
-    <row r="899" spans="4:4" ht="15.75" customHeight="1">
+    <row r="899" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D899" s="1"/>
     </row>
-    <row r="900" spans="4:4" ht="15.75" customHeight="1">
+    <row r="900" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D900" s="1"/>
     </row>
-    <row r="901" spans="4:4" ht="15.75" customHeight="1">
+    <row r="901" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D901" s="1"/>
     </row>
-    <row r="902" spans="4:4" ht="15.75" customHeight="1">
+    <row r="902" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D902" s="1"/>
     </row>
-    <row r="903" spans="4:4" ht="15.75" customHeight="1">
+    <row r="903" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D903" s="1"/>
     </row>
-    <row r="904" spans="4:4" ht="15.75" customHeight="1">
+    <row r="904" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D904" s="1"/>
     </row>
-    <row r="905" spans="4:4" ht="15.75" customHeight="1">
+    <row r="905" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D905" s="1"/>
     </row>
-    <row r="906" spans="4:4" ht="15.75" customHeight="1">
+    <row r="906" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D906" s="1"/>
     </row>
-    <row r="907" spans="4:4" ht="15.75" customHeight="1">
+    <row r="907" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D907" s="1"/>
     </row>
-    <row r="908" spans="4:4" ht="15.75" customHeight="1">
+    <row r="908" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D908" s="1"/>
     </row>
-    <row r="909" spans="4:4" ht="15.75" customHeight="1">
+    <row r="909" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D909" s="1"/>
     </row>
-    <row r="910" spans="4:4" ht="15.75" customHeight="1">
+    <row r="910" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D910" s="1"/>
     </row>
-    <row r="911" spans="4:4" ht="15.75" customHeight="1">
+    <row r="911" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D911" s="1"/>
     </row>
-    <row r="912" spans="4:4" ht="15.75" customHeight="1">
+    <row r="912" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D912" s="1"/>
     </row>
-    <row r="913" spans="4:4" ht="15.75" customHeight="1">
+    <row r="913" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D913" s="1"/>
     </row>
-    <row r="914" spans="4:4" ht="15.75" customHeight="1">
+    <row r="914" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D914" s="1"/>
     </row>
-    <row r="915" spans="4:4" ht="15.75" customHeight="1">
+    <row r="915" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D915" s="1"/>
     </row>
-    <row r="916" spans="4:4" ht="15.75" customHeight="1">
+    <row r="916" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D916" s="1"/>
     </row>
-    <row r="917" spans="4:4" ht="15.75" customHeight="1">
+    <row r="917" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D917" s="1"/>
     </row>
-    <row r="918" spans="4:4" ht="15.75" customHeight="1">
+    <row r="918" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D918" s="1"/>
     </row>
-    <row r="919" spans="4:4" ht="15.75" customHeight="1">
+    <row r="919" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D919" s="1"/>
     </row>
-    <row r="920" spans="4:4" ht="15.75" customHeight="1">
+    <row r="920" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D920" s="1"/>
     </row>
-    <row r="921" spans="4:4" ht="15.75" customHeight="1">
+    <row r="921" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D921" s="1"/>
     </row>
-    <row r="922" spans="4:4" ht="15.75" customHeight="1">
+    <row r="922" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D922" s="1"/>
     </row>
-    <row r="923" spans="4:4" ht="15.75" customHeight="1">
+    <row r="923" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D923" s="1"/>
     </row>
-    <row r="924" spans="4:4" ht="15.75" customHeight="1">
+    <row r="924" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D924" s="1"/>
     </row>
-    <row r="925" spans="4:4" ht="15.75" customHeight="1">
+    <row r="925" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D925" s="1"/>
     </row>
-    <row r="926" spans="4:4" ht="15.75" customHeight="1">
+    <row r="926" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D926" s="1"/>
     </row>
-    <row r="927" spans="4:4" ht="15.75" customHeight="1">
+    <row r="927" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D927" s="1"/>
     </row>
-    <row r="928" spans="4:4" ht="15.75" customHeight="1">
+    <row r="928" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D928" s="1"/>
     </row>
-    <row r="929" spans="4:4" ht="15.75" customHeight="1">
+    <row r="929" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D929" s="1"/>
     </row>
-    <row r="930" spans="4:4" ht="15.75" customHeight="1">
+    <row r="930" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D930" s="1"/>
     </row>
-    <row r="931" spans="4:4" ht="15.75" customHeight="1">
+    <row r="931" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D931" s="1"/>
     </row>
-    <row r="932" spans="4:4" ht="15.75" customHeight="1">
+    <row r="932" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D932" s="1"/>
     </row>
-    <row r="933" spans="4:4" ht="15.75" customHeight="1">
+    <row r="933" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D933" s="1"/>
     </row>
-    <row r="934" spans="4:4" ht="15.75" customHeight="1">
+    <row r="934" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D934" s="1"/>
     </row>
-    <row r="935" spans="4:4" ht="15.75" customHeight="1">
+    <row r="935" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D935" s="1"/>
     </row>
-    <row r="936" spans="4:4" ht="15.75" customHeight="1">
+    <row r="936" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D936" s="1"/>
     </row>
-    <row r="937" spans="4:4" ht="15.75" customHeight="1">
+    <row r="937" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D937" s="1"/>
     </row>
-    <row r="938" spans="4:4" ht="15.75" customHeight="1">
+    <row r="938" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D938" s="1"/>
     </row>
-    <row r="939" spans="4:4" ht="15.75" customHeight="1">
+    <row r="939" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D939" s="1"/>
     </row>
-    <row r="940" spans="4:4" ht="15.75" customHeight="1">
+    <row r="940" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D940" s="1"/>
     </row>
-    <row r="941" spans="4:4" ht="15.75" customHeight="1">
+    <row r="941" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D941" s="1"/>
     </row>
-    <row r="942" spans="4:4" ht="15.75" customHeight="1">
+    <row r="942" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D942" s="1"/>
     </row>
-    <row r="943" spans="4:4" ht="15.75" customHeight="1">
+    <row r="943" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D943" s="1"/>
     </row>
-    <row r="944" spans="4:4" ht="15.75" customHeight="1">
+    <row r="944" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D944" s="1"/>
     </row>
-    <row r="945" spans="4:4" ht="15.75" customHeight="1">
+    <row r="945" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D945" s="1"/>
     </row>
-    <row r="946" spans="4:4" ht="15.75" customHeight="1">
+    <row r="946" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D946" s="1"/>
     </row>
-    <row r="947" spans="4:4" ht="15.75" customHeight="1">
+    <row r="947" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D947" s="1"/>
     </row>
-    <row r="948" spans="4:4" ht="15.75" customHeight="1">
+    <row r="948" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D948" s="1"/>
     </row>
-    <row r="949" spans="4:4" ht="15.75" customHeight="1">
+    <row r="949" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D949" s="1"/>
     </row>
-    <row r="950" spans="4:4" ht="15.75" customHeight="1">
+    <row r="950" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D950" s="1"/>
     </row>
-    <row r="951" spans="4:4" ht="15.75" customHeight="1">
+    <row r="951" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D951" s="1"/>
     </row>
-    <row r="952" spans="4:4" ht="15.75" customHeight="1">
+    <row r="952" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D952" s="1"/>
     </row>
-    <row r="953" spans="4:4" ht="15.75" customHeight="1">
+    <row r="953" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D953" s="1"/>
     </row>
-    <row r="954" spans="4:4" ht="15.75" customHeight="1">
+    <row r="954" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D954" s="1"/>
     </row>
-    <row r="955" spans="4:4" ht="15.75" customHeight="1">
+    <row r="955" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D955" s="1"/>
     </row>
-    <row r="956" spans="4:4" ht="15.75" customHeight="1">
+    <row r="956" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D956" s="1"/>
     </row>
-    <row r="957" spans="4:4" ht="15.75" customHeight="1">
+    <row r="957" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D957" s="1"/>
     </row>
-    <row r="958" spans="4:4" ht="15.75" customHeight="1">
+    <row r="958" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D958" s="1"/>
     </row>
-    <row r="959" spans="4:4" ht="15.75" customHeight="1">
+    <row r="959" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D959" s="1"/>
     </row>
-    <row r="960" spans="4:4" ht="15.75" customHeight="1">
+    <row r="960" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D960" s="1"/>
     </row>
-    <row r="961" spans="4:4" ht="15.75" customHeight="1">
+    <row r="961" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D961" s="1"/>
     </row>
-    <row r="962" spans="4:4" ht="15.75" customHeight="1">
+    <row r="962" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D962" s="1"/>
     </row>
-    <row r="963" spans="4:4" ht="15.75" customHeight="1">
+    <row r="963" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D963" s="1"/>
     </row>
-    <row r="964" spans="4:4" ht="15.75" customHeight="1">
+    <row r="964" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D964" s="1"/>
     </row>
-    <row r="965" spans="4:4" ht="15.75" customHeight="1">
+    <row r="965" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D965" s="1"/>
     </row>
-    <row r="966" spans="4:4" ht="15.75" customHeight="1">
+    <row r="966" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D966" s="1"/>
     </row>
-    <row r="967" spans="4:4" ht="15.75" customHeight="1">
+    <row r="967" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D967" s="1"/>
     </row>
-    <row r="968" spans="4:4" ht="15.75" customHeight="1">
+    <row r="968" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D968" s="1"/>
     </row>
-    <row r="969" spans="4:4" ht="15.75" customHeight="1">
+    <row r="969" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D969" s="1"/>
     </row>
-    <row r="970" spans="4:4" ht="15.75" customHeight="1">
+    <row r="970" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D970" s="1"/>
     </row>
-    <row r="971" spans="4:4" ht="15.75" customHeight="1">
+    <row r="971" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D971" s="1"/>
     </row>
-    <row r="972" spans="4:4" ht="15.75" customHeight="1">
+    <row r="972" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D972" s="1"/>
     </row>
-    <row r="973" spans="4:4" ht="15.75" customHeight="1">
+    <row r="973" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D973" s="1"/>
     </row>
-    <row r="974" spans="4:4" ht="15.75" customHeight="1">
+    <row r="974" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D974" s="1"/>
     </row>
-    <row r="975" spans="4:4" ht="15.75" customHeight="1">
+    <row r="975" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D975" s="1"/>
     </row>
-    <row r="976" spans="4:4" ht="15.75" customHeight="1">
+    <row r="976" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D976" s="1"/>
     </row>
-    <row r="977" spans="4:4" ht="15.75" customHeight="1">
+    <row r="977" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D977" s="1"/>
     </row>
-    <row r="978" spans="4:4" ht="15.75" customHeight="1">
+    <row r="978" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D978" s="1"/>
     </row>
-    <row r="979" spans="4:4" ht="15.75" customHeight="1">
+    <row r="979" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D979" s="1"/>
     </row>
-    <row r="980" spans="4:4" ht="15.75" customHeight="1">
+    <row r="980" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D980" s="1"/>
     </row>
-    <row r="981" spans="4:4" ht="15.75" customHeight="1">
+    <row r="981" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D981" s="1"/>
     </row>
-    <row r="982" spans="4:4" ht="15.75" customHeight="1">
+    <row r="982" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D982" s="1"/>
     </row>
-    <row r="983" spans="4:4" ht="15.75" customHeight="1">
+    <row r="983" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D983" s="1"/>
     </row>
-    <row r="984" spans="4:4" ht="15.75" customHeight="1">
+    <row r="984" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D984" s="1"/>
     </row>
-    <row r="985" spans="4:4" ht="15.75" customHeight="1">
+    <row r="985" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D985" s="1"/>
     </row>
-    <row r="986" spans="4:4" ht="15.75" customHeight="1">
+    <row r="986" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D986" s="1"/>
     </row>
-    <row r="987" spans="4:4" ht="15.75" customHeight="1">
+    <row r="987" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D987" s="1"/>
     </row>
-    <row r="988" spans="4:4" ht="15.75" customHeight="1">
+    <row r="988" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D988" s="1"/>
     </row>
-    <row r="989" spans="4:4" ht="15.75" customHeight="1">
+    <row r="989" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D989" s="1"/>
     </row>
-    <row r="990" spans="4:4" ht="15.75" customHeight="1">
+    <row r="990" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D990" s="1"/>
     </row>
-    <row r="991" spans="4:4" ht="15.75" customHeight="1">
+    <row r="991" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D991" s="1"/>
     </row>
-    <row r="992" spans="4:4" ht="15.75" customHeight="1">
+    <row r="992" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D992" s="1"/>
     </row>
-    <row r="993" spans="4:4" ht="15.75" customHeight="1">
+    <row r="993" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D993" s="1"/>
     </row>
-    <row r="994" spans="4:4" ht="15.75" customHeight="1">
+    <row r="994" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D994" s="1"/>
     </row>
-    <row r="995" spans="4:4" ht="15.75" customHeight="1">
+    <row r="995" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D995" s="1"/>
     </row>
-    <row r="996" spans="4:4" ht="15.75" customHeight="1">
+    <row r="996" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D996" s="1"/>
+    </row>
+    <row r="997" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D997" s="1"/>
+    </row>
+    <row r="998" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D998" s="1"/>
+    </row>
+    <row r="999" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D999" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="D2:D78" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="D2:D81" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>AND(ISNUMBER(D2),(NOT(OR(NOT(ISERROR(DATEVALUE(D2))), AND(ISNUMBER(D2), LEFT(CELL("format", D2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
@@ -9188,6 +9296,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -9370,31 +9495,39 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F1A155A-9D28-4350-8732-AE6833CEF998}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F6FD9D-19D1-439B-8BFE-82DBC99BDEA4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F6FD9D-19D1-439B-8BFE-82DBC99BDEA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F1A155A-9D28-4350-8732-AE6833CEF998}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+    <ds:schemaRef ds:uri="b0d30a24-05e2-4154-8fed-e579ddd987b0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/upload files/Preferences v6.xlsx
+++ b/upload files/Preferences v6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63F6C0B-3524-A243-90D4-EAAE790E3013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DA28B1-DF8C-5A4F-9ED1-633008D1199B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="800" yWindow="660" windowWidth="29040" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36160" yWindow="-1520" windowWidth="29040" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="107">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -603,7 +603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -732,17 +732,48 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFFFFFFF"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFF6F8F9"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -885,43 +916,6 @@
         <name val="Aptos Narrow"/>
         <scheme val="minor"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFFFFFFF"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFF6F8F9"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
@@ -1142,9 +1136,9 @@
     <tableColumn id="1" xr3:uid="{BB8E1DF3-CFA5-4F4C-9341-683B2C7FBF55}" name="STAFF NAME" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{DC3F26C1-C7E8-BF46-A039-72B08D99BCA8}" name="ROLE" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{EF43028D-AE4E-434A-B652-8A0CDCEE720A}" name="No Matrix" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{4AEC7AC0-93A2-5043-AADB-962C27827986}" name="Seniority" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{4F928FE3-37CC-8D4A-B5A7-68E54BB080BE}" name="Reduced Rest OK" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{9B205F7E-D438-4E43-BF45-7B6996C87B80}" name="D7B" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{4AEC7AC0-93A2-5043-AADB-962C27827986}" name="Seniority" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{4F928FE3-37CC-8D4A-B5A7-68E54BB080BE}" name="Reduced Rest OK" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{9B205F7E-D438-4E43-BF45-7B6996C87B80}" name="D7B" dataDxfId="4"/>
     <tableColumn id="7" xr3:uid="{6FBAC0EB-B977-8D43-8FA4-B2A0FBD880DB}" name="GR"/>
     <tableColumn id="8" xr3:uid="{9A17850C-E6C1-B042-A5E8-EC7DE6104419}" name="D11B"/>
     <tableColumn id="9" xr3:uid="{9034B9B8-E76D-5847-BFED-8C23DB865066}" name="FW"/>
@@ -1154,12 +1148,12 @@
     <tableColumn id="13" xr3:uid="{71923762-727D-B14B-87C8-72188F6EA491}" name="PG"/>
     <tableColumn id="14" xr3:uid="{8BC734F3-1D59-AD43-8CE1-CA4E535CE633}" name="D11M"/>
     <tableColumn id="15" xr3:uid="{D9F28E89-F340-4B4B-B432-43AF835746B9}" name="MG"/>
-    <tableColumn id="16" xr3:uid="{A660998B-FE07-BF4A-B784-90FC1426BF26}" name="N7B" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{A660998B-FE07-BF4A-B784-90FC1426BF26}" name="N7B" dataDxfId="3"/>
     <tableColumn id="17" xr3:uid="{C228DA61-8989-7846-A7D5-6A77004F8103}" name="NG"/>
     <tableColumn id="18" xr3:uid="{97C3F635-2908-824A-AA6F-EE11ED8DE3FE}" name="N9L"/>
     <tableColumn id="19" xr3:uid="{E4EE6987-8112-BE4D-B329-53CB0C70AB46}" name="N7P"/>
-    <tableColumn id="20" xr3:uid="{51AFC6C1-38A4-954C-83CA-412B18BD76F0}" name="NP" dataDxfId="1"/>
-    <tableColumn id="21" xr3:uid="{27EDDB97-5263-BC41-AC06-CAA6A57A4DA2}" name="N to D Flex" dataDxfId="0"/>
+    <tableColumn id="20" xr3:uid="{51AFC6C1-38A4-954C-83CA-412B18BD76F0}" name="NP" dataDxfId="2"/>
+    <tableColumn id="21" xr3:uid="{27EDDB97-5263-BC41-AC06-CAA6A57A4DA2}" name="N to D Flex" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="Sheet1-style" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5081,7 +5075,7 @@
         <v>40</v>
       </c>
       <c r="C58" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58" s="24">
         <v>60</v>
@@ -5342,7 +5336,7 @@
         <v>1</v>
       </c>
       <c r="D62" s="21">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E62" s="20">
         <v>1</v>
@@ -5407,7 +5401,7 @@
         <v>1</v>
       </c>
       <c r="D63" s="17">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E63" s="16">
         <v>0</v>
@@ -5472,7 +5466,7 @@
         <v>0</v>
       </c>
       <c r="D64" s="21">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E64" s="20">
         <v>0</v>
@@ -5537,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="24">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E65" s="23">
         <v>1</v>
@@ -5599,10 +5593,10 @@
         <v>22</v>
       </c>
       <c r="C66" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66" s="12">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E66" s="11">
         <v>0</v>
@@ -5665,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="D67" s="24">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E67" s="23">
         <v>1</v>
@@ -5730,7 +5724,7 @@
         <v>0</v>
       </c>
       <c r="D68" s="21">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E68" s="20">
         <v>1</v>
@@ -5795,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="17">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E69" s="16">
         <v>0</v>
@@ -5860,7 +5854,7 @@
         <v>0</v>
       </c>
       <c r="D70" s="17">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E70" s="16">
         <v>0</v>
@@ -5925,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="D71" s="12">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E71" s="11">
         <v>1</v>
@@ -5990,7 +5984,7 @@
         <v>0</v>
       </c>
       <c r="D72" s="17">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E72" s="16">
         <v>1</v>
@@ -6055,7 +6049,7 @@
         <v>0</v>
       </c>
       <c r="D73" s="12">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E73" s="11">
         <v>0</v>
@@ -6120,7 +6114,7 @@
         <v>0</v>
       </c>
       <c r="D74" s="24">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E74" s="23">
         <v>0</v>
@@ -6185,7 +6179,7 @@
         <v>0</v>
       </c>
       <c r="D75" s="21">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E75" s="20">
         <v>0</v>
@@ -6240,19 +6234,21 @@
       </c>
     </row>
     <row r="76" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="46" t="s">
+      <c r="A76" s="37" t="s">
         <v>104</v>
       </c>
-      <c r="B76" s="47" t="s">
+      <c r="B76" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C76" s="47">
+      <c r="C76" s="16">
         <v>0</v>
       </c>
       <c r="D76" s="17">
-        <v>83</v>
-      </c>
-      <c r="E76" s="47"/>
+        <v>81</v>
+      </c>
+      <c r="E76" s="16">
+        <v>1</v>
+      </c>
       <c r="F76" s="18"/>
       <c r="G76" s="37"/>
       <c r="H76" s="37"/>
@@ -6268,22 +6264,26 @@
       <c r="R76" s="37"/>
       <c r="S76" s="37"/>
       <c r="T76" s="19"/>
-      <c r="U76" s="10"/>
+      <c r="U76" s="10" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="77" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="46" t="s">
+      <c r="A77" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="B77" s="47" t="s">
+      <c r="B77" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C77" s="47">
+      <c r="C77" s="16">
         <v>0</v>
       </c>
       <c r="D77" s="17">
-        <v>84</v>
-      </c>
-      <c r="E77" s="47"/>
+        <v>83</v>
+      </c>
+      <c r="E77" s="16">
+        <v>1</v>
+      </c>
       <c r="F77" s="18"/>
       <c r="G77" s="37"/>
       <c r="H77" s="37"/>
@@ -6299,22 +6299,26 @@
       <c r="R77" s="37"/>
       <c r="S77" s="37"/>
       <c r="T77" s="19"/>
-      <c r="U77" s="10"/>
+      <c r="U77" s="10" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="78" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="46" t="s">
+      <c r="A78" s="37" t="s">
         <v>106</v>
       </c>
-      <c r="B78" s="47" t="s">
+      <c r="B78" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C78" s="47">
+      <c r="C78" s="16">
         <v>0</v>
       </c>
       <c r="D78" s="17">
-        <v>85</v>
-      </c>
-      <c r="E78" s="47"/>
+        <v>82</v>
+      </c>
+      <c r="E78" s="16">
+        <v>1</v>
+      </c>
       <c r="F78" s="18"/>
       <c r="G78" s="37"/>
       <c r="H78" s="37"/>
@@ -6330,7 +6334,9 @@
       <c r="R78" s="37"/>
       <c r="S78" s="37"/>
       <c r="T78" s="19"/>
-      <c r="U78" s="10"/>
+      <c r="U78" s="10" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="79" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="37" t="s">
@@ -6343,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="17">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E79" s="16">
         <v>1</v>
@@ -6408,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="D80" s="21">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E80" s="20">
         <v>1</v>
@@ -6473,7 +6479,7 @@
         <v>0</v>
       </c>
       <c r="D81" s="42">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E81" s="41">
         <v>0</v>
@@ -9296,23 +9302,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -9495,25 +9484,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F6FD9D-19D1-439B-8BFE-82DBC99BDEA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F1A155A-9D28-4350-8732-AE6833CEF998}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9530,4 +9518,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F6FD9D-19D1-439B-8BFE-82DBC99BDEA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/upload files/Preferences v6.xlsx
+++ b/upload files/Preferences v6.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DA28B1-DF8C-5A4F-9ED1-633008D1199B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56EA8E8-5175-274C-8968-5AE72E5E0167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36160" yWindow="-1520" windowWidth="29040" windowHeight="17240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$T$80</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="106">
   <si>
     <t>STAFF NAME</t>
   </si>
@@ -230,15 +230,9 @@
     <t>Steckevicz</t>
   </si>
   <si>
-    <t>DiNardo</t>
-  </si>
-  <si>
     <t>McGrath</t>
   </si>
   <si>
-    <t>Noland</t>
-  </si>
-  <si>
     <t>Murphy</t>
   </si>
   <si>
@@ -363,6 +357,9 @@
   </si>
   <si>
     <t>VanderKooi</t>
+  </si>
+  <si>
+    <t>Seyoum</t>
   </si>
 </sst>
 </file>
@@ -738,43 +735,6 @@
   </cellStyles>
   <dxfs count="14">
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFFFFFFF"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFF6F8F9"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
@@ -916,6 +876,43 @@
         <name val="Aptos Narrow"/>
         <scheme val="minor"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFFFFFFF"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFF6F8F9"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFFFFF"/>
@@ -1127,18 +1124,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}" name="Table2" displayName="Table2" ref="A1:U81" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
-  <autoFilter ref="A1:U81" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U81">
-    <sortCondition ref="D1:D81"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}" name="Table2" displayName="Table2" ref="A1:U80" totalsRowShown="0" headerRowDxfId="10" tableBorderDxfId="9">
+  <autoFilter ref="A1:U80" xr:uid="{01B2A805-E9A0-E547-8F61-D3AC47392744}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U80">
+    <sortCondition ref="D1:D80"/>
   </sortState>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{BB8E1DF3-CFA5-4F4C-9341-683B2C7FBF55}" name="STAFF NAME" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{DC3F26C1-C7E8-BF46-A039-72B08D99BCA8}" name="ROLE" dataDxfId="7"/>
     <tableColumn id="3" xr3:uid="{EF43028D-AE4E-434A-B652-8A0CDCEE720A}" name="No Matrix" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{4AEC7AC0-93A2-5043-AADB-962C27827986}" name="Seniority" dataDxfId="0"/>
-    <tableColumn id="5" xr3:uid="{4F928FE3-37CC-8D4A-B5A7-68E54BB080BE}" name="Reduced Rest OK" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{9B205F7E-D438-4E43-BF45-7B6996C87B80}" name="D7B" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{4AEC7AC0-93A2-5043-AADB-962C27827986}" name="Seniority" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{4F928FE3-37CC-8D4A-B5A7-68E54BB080BE}" name="Reduced Rest OK" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{9B205F7E-D438-4E43-BF45-7B6996C87B80}" name="D7B" dataDxfId="3"/>
     <tableColumn id="7" xr3:uid="{6FBAC0EB-B977-8D43-8FA4-B2A0FBD880DB}" name="GR"/>
     <tableColumn id="8" xr3:uid="{9A17850C-E6C1-B042-A5E8-EC7DE6104419}" name="D11B"/>
     <tableColumn id="9" xr3:uid="{9034B9B8-E76D-5847-BFED-8C23DB865066}" name="FW"/>
@@ -1148,12 +1145,12 @@
     <tableColumn id="13" xr3:uid="{71923762-727D-B14B-87C8-72188F6EA491}" name="PG"/>
     <tableColumn id="14" xr3:uid="{8BC734F3-1D59-AD43-8CE1-CA4E535CE633}" name="D11M"/>
     <tableColumn id="15" xr3:uid="{D9F28E89-F340-4B4B-B432-43AF835746B9}" name="MG"/>
-    <tableColumn id="16" xr3:uid="{A660998B-FE07-BF4A-B784-90FC1426BF26}" name="N7B" dataDxfId="3"/>
+    <tableColumn id="16" xr3:uid="{A660998B-FE07-BF4A-B784-90FC1426BF26}" name="N7B" dataDxfId="2"/>
     <tableColumn id="17" xr3:uid="{C228DA61-8989-7846-A7D5-6A77004F8103}" name="NG"/>
     <tableColumn id="18" xr3:uid="{97C3F635-2908-824A-AA6F-EE11ED8DE3FE}" name="N9L"/>
     <tableColumn id="19" xr3:uid="{E4EE6987-8112-BE4D-B329-53CB0C70AB46}" name="N7P"/>
-    <tableColumn id="20" xr3:uid="{51AFC6C1-38A4-954C-83CA-412B18BD76F0}" name="NP" dataDxfId="2"/>
-    <tableColumn id="21" xr3:uid="{27EDDB97-5263-BC41-AC06-CAA6A57A4DA2}" name="N to D Flex" dataDxfId="1"/>
+    <tableColumn id="20" xr3:uid="{51AFC6C1-38A4-954C-83CA-412B18BD76F0}" name="NP" dataDxfId="1"/>
+    <tableColumn id="21" xr3:uid="{27EDDB97-5263-BC41-AC06-CAA6A57A4DA2}" name="N to D Flex" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Sheet1-style" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1357,7 +1354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U999"/>
+  <dimension ref="A1:U998"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -3705,518 +3702,518 @@
       <c r="U36" s="10"/>
     </row>
     <row r="37" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="37" t="s">
+      <c r="A37" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="B37" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C37" s="16">
-        <v>1</v>
-      </c>
-      <c r="D37" s="17">
-        <v>39</v>
-      </c>
-      <c r="E37" s="16">
-        <v>0</v>
-      </c>
-      <c r="F37" s="18">
+      <c r="B37" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="26">
+        <v>1</v>
+      </c>
+      <c r="D37" s="27">
+        <v>40</v>
+      </c>
+      <c r="E37" s="26">
+        <v>1</v>
+      </c>
+      <c r="F37" s="28">
+        <v>2</v>
+      </c>
+      <c r="G37" s="26">
+        <v>3</v>
+      </c>
+      <c r="H37" s="26">
         <v>5</v>
       </c>
-      <c r="G37" s="16">
+      <c r="I37" s="26">
+        <v>4</v>
+      </c>
+      <c r="J37" s="26">
+        <v>0</v>
+      </c>
+      <c r="K37" s="26">
+        <v>1</v>
+      </c>
+      <c r="L37" s="26">
+        <v>8</v>
+      </c>
+      <c r="M37" s="26">
+        <v>9</v>
+      </c>
+      <c r="N37" s="26">
         <v>6</v>
       </c>
-      <c r="H37" s="16">
+      <c r="O37" s="26">
         <v>7</v>
       </c>
-      <c r="I37" s="16">
-        <v>4</v>
-      </c>
-      <c r="J37" s="16">
+      <c r="P37" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="26">
+        <v>1</v>
+      </c>
+      <c r="R37" s="26">
+        <v>2</v>
+      </c>
+      <c r="S37" s="26">
+        <v>3</v>
+      </c>
+      <c r="T37" s="29">
+        <v>4</v>
+      </c>
+      <c r="U37" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="20">
+        <v>1</v>
+      </c>
+      <c r="D38" s="21">
+        <v>41</v>
+      </c>
+      <c r="E38" s="20">
+        <v>1</v>
+      </c>
+      <c r="F38" s="18">
+        <v>7</v>
+      </c>
+      <c r="G38" s="20">
         <v>8</v>
       </c>
-      <c r="K37" s="16">
+      <c r="H38" s="20">
         <v>9</v>
       </c>
-      <c r="L37" s="16">
-        <v>0</v>
-      </c>
-      <c r="M37" s="16">
-        <v>1</v>
-      </c>
-      <c r="N37" s="16">
-        <v>2</v>
-      </c>
-      <c r="O37" s="16">
-        <v>3</v>
-      </c>
-      <c r="P37" s="18">
-        <v>2</v>
-      </c>
-      <c r="Q37" s="16">
-        <v>3</v>
-      </c>
-      <c r="R37" s="16">
-        <v>4</v>
-      </c>
-      <c r="S37" s="16">
-        <v>0</v>
-      </c>
-      <c r="T37" s="19">
-        <v>1</v>
-      </c>
-      <c r="U37" s="10" t="s">
+      <c r="I38" s="20">
+        <v>0</v>
+      </c>
+      <c r="J38" s="20">
+        <v>5</v>
+      </c>
+      <c r="K38" s="20">
+        <v>6</v>
+      </c>
+      <c r="L38" s="20">
+        <v>3</v>
+      </c>
+      <c r="M38" s="20">
+        <v>4</v>
+      </c>
+      <c r="N38" s="20">
+        <v>1</v>
+      </c>
+      <c r="O38" s="20">
+        <v>2</v>
+      </c>
+      <c r="P38" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="20">
+        <v>4</v>
+      </c>
+      <c r="R38" s="20">
+        <v>0</v>
+      </c>
+      <c r="S38" s="20">
+        <v>1</v>
+      </c>
+      <c r="T38" s="22">
+        <v>2</v>
+      </c>
+      <c r="U38" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="38" t="s">
+    <row r="39" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="B38" s="26" t="s">
+      <c r="B39" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="26">
-        <v>1</v>
-      </c>
-      <c r="D38" s="27">
-        <v>40</v>
-      </c>
-      <c r="E38" s="26">
-        <v>1</v>
-      </c>
-      <c r="F38" s="28">
-        <v>2</v>
-      </c>
-      <c r="G38" s="26">
-        <v>3</v>
-      </c>
-      <c r="H38" s="26">
+      <c r="C39" s="23">
+        <v>1</v>
+      </c>
+      <c r="D39" s="24">
+        <v>42</v>
+      </c>
+      <c r="E39" s="23">
+        <v>0</v>
+      </c>
+      <c r="F39" s="13">
+        <v>7</v>
+      </c>
+      <c r="G39" s="23">
+        <v>6</v>
+      </c>
+      <c r="H39" s="23">
         <v>5</v>
       </c>
-      <c r="I38" s="26">
-        <v>4</v>
-      </c>
-      <c r="J38" s="26">
-        <v>0</v>
-      </c>
-      <c r="K38" s="26">
-        <v>1</v>
-      </c>
-      <c r="L38" s="26">
+      <c r="I39" s="23">
+        <v>4</v>
+      </c>
+      <c r="J39" s="23">
+        <v>9</v>
+      </c>
+      <c r="K39" s="23">
         <v>8</v>
       </c>
-      <c r="M38" s="26">
-        <v>9</v>
-      </c>
-      <c r="N38" s="26">
-        <v>6</v>
-      </c>
-      <c r="O38" s="26">
-        <v>7</v>
-      </c>
-      <c r="P38" s="28">
-        <v>0</v>
-      </c>
-      <c r="Q38" s="26">
-        <v>1</v>
-      </c>
-      <c r="R38" s="26">
-        <v>2</v>
-      </c>
-      <c r="S38" s="26">
-        <v>3</v>
-      </c>
-      <c r="T38" s="29">
-        <v>4</v>
-      </c>
-      <c r="U38" s="15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C39" s="20">
-        <v>1</v>
-      </c>
-      <c r="D39" s="21">
-        <v>41</v>
-      </c>
-      <c r="E39" s="20">
-        <v>1</v>
-      </c>
-      <c r="F39" s="18">
-        <v>7</v>
-      </c>
-      <c r="G39" s="20">
-        <v>8</v>
-      </c>
-      <c r="H39" s="20">
-        <v>9</v>
-      </c>
-      <c r="I39" s="20">
-        <v>0</v>
-      </c>
-      <c r="J39" s="20">
-        <v>5</v>
-      </c>
-      <c r="K39" s="20">
-        <v>6</v>
-      </c>
-      <c r="L39" s="20">
-        <v>3</v>
-      </c>
-      <c r="M39" s="20">
-        <v>4</v>
-      </c>
-      <c r="N39" s="20">
-        <v>1</v>
-      </c>
-      <c r="O39" s="20">
-        <v>2</v>
-      </c>
-      <c r="P39" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q39" s="20">
-        <v>4</v>
-      </c>
-      <c r="R39" s="20">
-        <v>0</v>
-      </c>
-      <c r="S39" s="20">
-        <v>1</v>
-      </c>
-      <c r="T39" s="22">
-        <v>2</v>
-      </c>
-      <c r="U39" s="10" t="s">
-        <v>32</v>
+      <c r="L39" s="23">
+        <v>0</v>
+      </c>
+      <c r="M39" s="23">
+        <v>1</v>
+      </c>
+      <c r="N39" s="23">
+        <v>3</v>
+      </c>
+      <c r="O39" s="23">
+        <v>2</v>
+      </c>
+      <c r="P39" s="13">
+        <v>3</v>
+      </c>
+      <c r="Q39" s="23">
+        <v>2</v>
+      </c>
+      <c r="R39" s="23">
+        <v>4</v>
+      </c>
+      <c r="S39" s="23">
+        <v>0</v>
+      </c>
+      <c r="T39" s="25">
+        <v>1</v>
+      </c>
+      <c r="U39" s="15" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C40" s="11">
+        <v>1</v>
+      </c>
+      <c r="D40" s="12">
+        <v>43</v>
+      </c>
+      <c r="E40" s="11">
+        <v>0</v>
+      </c>
+      <c r="F40" s="13">
+        <v>6</v>
+      </c>
+      <c r="G40" s="11">
+        <v>7</v>
+      </c>
+      <c r="H40" s="11">
+        <v>0</v>
+      </c>
+      <c r="I40" s="11">
+        <v>1</v>
+      </c>
+      <c r="J40" s="11">
+        <v>8</v>
+      </c>
+      <c r="K40" s="11">
+        <v>9</v>
+      </c>
+      <c r="L40" s="11">
+        <v>2</v>
+      </c>
+      <c r="M40" s="11">
+        <v>3</v>
+      </c>
+      <c r="N40" s="11">
+        <v>4</v>
+      </c>
+      <c r="O40" s="11">
+        <v>5</v>
+      </c>
+      <c r="P40" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="11">
+        <v>1</v>
+      </c>
+      <c r="R40" s="11">
+        <v>2</v>
+      </c>
+      <c r="S40" s="11">
+        <v>3</v>
+      </c>
+      <c r="T40" s="14">
+        <v>4</v>
+      </c>
+      <c r="U40" s="15"/>
+    </row>
+    <row r="41" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="37" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C40" s="23">
-        <v>1</v>
-      </c>
-      <c r="D40" s="24">
-        <v>42</v>
-      </c>
-      <c r="E40" s="23">
-        <v>0</v>
-      </c>
-      <c r="F40" s="13">
+      <c r="B41" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="16">
+        <v>1</v>
+      </c>
+      <c r="D41" s="17">
+        <v>44</v>
+      </c>
+      <c r="E41" s="16">
+        <v>0</v>
+      </c>
+      <c r="F41" s="18">
+        <v>6</v>
+      </c>
+      <c r="G41" s="16">
         <v>7</v>
       </c>
-      <c r="G40" s="23">
+      <c r="H41" s="16">
+        <v>8</v>
+      </c>
+      <c r="I41" s="16">
+        <v>9</v>
+      </c>
+      <c r="J41" s="16">
+        <v>4</v>
+      </c>
+      <c r="K41" s="16">
+        <v>5</v>
+      </c>
+      <c r="L41" s="16">
+        <v>0</v>
+      </c>
+      <c r="M41" s="16">
+        <v>1</v>
+      </c>
+      <c r="N41" s="16">
+        <v>2</v>
+      </c>
+      <c r="O41" s="16">
+        <v>3</v>
+      </c>
+      <c r="P41" s="18">
+        <v>2</v>
+      </c>
+      <c r="Q41" s="16">
+        <v>3</v>
+      </c>
+      <c r="R41" s="16">
+        <v>4</v>
+      </c>
+      <c r="S41" s="16">
+        <v>0</v>
+      </c>
+      <c r="T41" s="19">
+        <v>1</v>
+      </c>
+      <c r="U41" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="11">
+        <v>1</v>
+      </c>
+      <c r="D42" s="12">
+        <v>45</v>
+      </c>
+      <c r="E42" s="11">
+        <v>0</v>
+      </c>
+      <c r="F42" s="13">
+        <v>4</v>
+      </c>
+      <c r="G42" s="11">
+        <v>5</v>
+      </c>
+      <c r="H42" s="11">
+        <v>2</v>
+      </c>
+      <c r="I42" s="11">
+        <v>3</v>
+      </c>
+      <c r="J42" s="11">
+        <v>0</v>
+      </c>
+      <c r="K42" s="11">
+        <v>1</v>
+      </c>
+      <c r="L42" s="11">
+        <v>8</v>
+      </c>
+      <c r="M42" s="11">
+        <v>9</v>
+      </c>
+      <c r="N42" s="11">
         <v>6</v>
       </c>
-      <c r="H40" s="23">
-        <v>5</v>
-      </c>
-      <c r="I40" s="23">
-        <v>4</v>
-      </c>
-      <c r="J40" s="23">
-        <v>9</v>
-      </c>
-      <c r="K40" s="23">
-        <v>8</v>
-      </c>
-      <c r="L40" s="23">
-        <v>0</v>
-      </c>
-      <c r="M40" s="23">
-        <v>1</v>
-      </c>
-      <c r="N40" s="23">
-        <v>3</v>
-      </c>
-      <c r="O40" s="23">
-        <v>2</v>
-      </c>
-      <c r="P40" s="13">
-        <v>3</v>
-      </c>
-      <c r="Q40" s="23">
-        <v>2</v>
-      </c>
-      <c r="R40" s="23">
-        <v>4</v>
-      </c>
-      <c r="S40" s="23">
-        <v>0</v>
-      </c>
-      <c r="T40" s="25">
-        <v>1</v>
-      </c>
-      <c r="U40" s="15" t="s">
+      <c r="O42" s="11">
+        <v>7</v>
+      </c>
+      <c r="P42" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="11">
+        <v>1</v>
+      </c>
+      <c r="R42" s="11">
+        <v>2</v>
+      </c>
+      <c r="S42" s="11">
+        <v>3</v>
+      </c>
+      <c r="T42" s="14">
+        <v>4</v>
+      </c>
+      <c r="U42" s="15" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C41" s="11">
-        <v>1</v>
-      </c>
-      <c r="D41" s="12">
-        <v>43</v>
-      </c>
-      <c r="E41" s="11">
-        <v>0</v>
-      </c>
-      <c r="F41" s="13">
-        <v>6</v>
-      </c>
-      <c r="G41" s="11">
-        <v>7</v>
-      </c>
-      <c r="H41" s="11">
-        <v>0</v>
-      </c>
-      <c r="I41" s="11">
-        <v>1</v>
-      </c>
-      <c r="J41" s="11">
-        <v>8</v>
-      </c>
-      <c r="K41" s="11">
-        <v>9</v>
-      </c>
-      <c r="L41" s="11">
-        <v>2</v>
-      </c>
-      <c r="M41" s="11">
-        <v>3</v>
-      </c>
-      <c r="N41" s="11">
-        <v>4</v>
-      </c>
-      <c r="O41" s="11">
-        <v>5</v>
-      </c>
-      <c r="P41" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="11">
-        <v>1</v>
-      </c>
-      <c r="R41" s="11">
-        <v>2</v>
-      </c>
-      <c r="S41" s="11">
-        <v>3</v>
-      </c>
-      <c r="T41" s="14">
-        <v>4</v>
-      </c>
-      <c r="U41" s="15"/>
-    </row>
-    <row r="42" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" s="16">
-        <v>1</v>
-      </c>
-      <c r="D42" s="17">
-        <v>44</v>
-      </c>
-      <c r="E42" s="16">
-        <v>0</v>
-      </c>
-      <c r="F42" s="18">
-        <v>6</v>
-      </c>
-      <c r="G42" s="16">
-        <v>7</v>
-      </c>
-      <c r="H42" s="16">
-        <v>8</v>
-      </c>
-      <c r="I42" s="16">
-        <v>9</v>
-      </c>
-      <c r="J42" s="16">
-        <v>4</v>
-      </c>
-      <c r="K42" s="16">
-        <v>5</v>
-      </c>
-      <c r="L42" s="16">
-        <v>0</v>
-      </c>
-      <c r="M42" s="16">
-        <v>1</v>
-      </c>
-      <c r="N42" s="16">
-        <v>2</v>
-      </c>
-      <c r="O42" s="16">
-        <v>3</v>
-      </c>
-      <c r="P42" s="18">
-        <v>2</v>
-      </c>
-      <c r="Q42" s="16">
-        <v>3</v>
-      </c>
-      <c r="R42" s="16">
-        <v>4</v>
-      </c>
-      <c r="S42" s="16">
-        <v>0</v>
-      </c>
-      <c r="T42" s="19">
-        <v>1</v>
-      </c>
-      <c r="U42" s="10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" s="11">
-        <v>1</v>
-      </c>
-      <c r="D43" s="12">
-        <v>45</v>
-      </c>
-      <c r="E43" s="11">
+        <v>67</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" s="23">
+        <v>1</v>
+      </c>
+      <c r="D43" s="24">
+        <v>46</v>
+      </c>
+      <c r="E43" s="23">
         <v>0</v>
       </c>
       <c r="F43" s="13">
-        <v>4</v>
-      </c>
-      <c r="G43" s="11">
+        <v>8</v>
+      </c>
+      <c r="G43" s="23">
+        <v>9</v>
+      </c>
+      <c r="H43" s="23">
+        <v>1</v>
+      </c>
+      <c r="I43" s="23">
+        <v>0</v>
+      </c>
+      <c r="J43" s="23">
+        <v>2</v>
+      </c>
+      <c r="K43" s="23">
+        <v>3</v>
+      </c>
+      <c r="L43" s="23">
+        <v>4</v>
+      </c>
+      <c r="M43" s="23">
         <v>5</v>
       </c>
-      <c r="H43" s="11">
-        <v>2</v>
-      </c>
-      <c r="I43" s="11">
-        <v>3</v>
-      </c>
-      <c r="J43" s="11">
-        <v>0</v>
-      </c>
-      <c r="K43" s="11">
-        <v>1</v>
-      </c>
-      <c r="L43" s="11">
-        <v>8</v>
-      </c>
-      <c r="M43" s="11">
-        <v>9</v>
-      </c>
-      <c r="N43" s="11">
+      <c r="N43" s="23">
         <v>6</v>
       </c>
-      <c r="O43" s="11">
+      <c r="O43" s="23">
         <v>7</v>
       </c>
       <c r="P43" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="11">
-        <v>1</v>
-      </c>
-      <c r="R43" s="11">
-        <v>2</v>
-      </c>
-      <c r="S43" s="11">
-        <v>3</v>
-      </c>
-      <c r="T43" s="14">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="Q43" s="23">
+        <v>4</v>
+      </c>
+      <c r="R43" s="23">
+        <v>0</v>
+      </c>
+      <c r="S43" s="23">
+        <v>1</v>
+      </c>
+      <c r="T43" s="25">
+        <v>2</v>
       </c>
       <c r="U43" s="15" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="B44" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="B44" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C44" s="23">
-        <v>1</v>
-      </c>
-      <c r="D44" s="24">
-        <v>46</v>
-      </c>
-      <c r="E44" s="23">
+      <c r="C44" s="11">
+        <v>1</v>
+      </c>
+      <c r="D44" s="12">
+        <v>47</v>
+      </c>
+      <c r="E44" s="11">
         <v>0</v>
       </c>
       <c r="F44" s="13">
+        <v>6</v>
+      </c>
+      <c r="G44" s="11">
+        <v>7</v>
+      </c>
+      <c r="H44" s="11">
+        <v>1</v>
+      </c>
+      <c r="I44" s="11">
+        <v>0</v>
+      </c>
+      <c r="J44" s="11">
         <v>8</v>
       </c>
-      <c r="G44" s="23">
+      <c r="K44" s="11">
         <v>9</v>
       </c>
-      <c r="H44" s="23">
-        <v>1</v>
-      </c>
-      <c r="I44" s="23">
-        <v>0</v>
-      </c>
-      <c r="J44" s="23">
-        <v>2</v>
-      </c>
-      <c r="K44" s="23">
-        <v>3</v>
-      </c>
-      <c r="L44" s="23">
-        <v>4</v>
-      </c>
-      <c r="M44" s="23">
+      <c r="L44" s="11">
+        <v>4</v>
+      </c>
+      <c r="M44" s="11">
         <v>5</v>
       </c>
-      <c r="N44" s="23">
-        <v>6</v>
-      </c>
-      <c r="O44" s="23">
-        <v>7</v>
+      <c r="N44" s="11">
+        <v>2</v>
+      </c>
+      <c r="O44" s="11">
+        <v>3</v>
       </c>
       <c r="P44" s="13">
-        <v>3</v>
-      </c>
-      <c r="Q44" s="23">
-        <v>4</v>
-      </c>
-      <c r="R44" s="23">
-        <v>0</v>
-      </c>
-      <c r="S44" s="23">
-        <v>1</v>
-      </c>
-      <c r="T44" s="25">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="Q44" s="11">
+        <v>3</v>
+      </c>
+      <c r="R44" s="11">
+        <v>4</v>
+      </c>
+      <c r="S44" s="11">
+        <v>0</v>
+      </c>
+      <c r="T44" s="14">
+        <v>1</v>
       </c>
       <c r="U44" s="15" t="s">
         <v>32</v>
@@ -4224,64 +4221,64 @@
     </row>
     <row r="45" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C45" s="11">
-        <v>1</v>
-      </c>
-      <c r="D45" s="12">
-        <v>47</v>
-      </c>
-      <c r="E45" s="11">
+        <v>69</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="23">
+        <v>1</v>
+      </c>
+      <c r="D45" s="24">
+        <v>48</v>
+      </c>
+      <c r="E45" s="23">
         <v>0</v>
       </c>
       <c r="F45" s="13">
         <v>6</v>
       </c>
-      <c r="G45" s="11">
+      <c r="G45" s="23">
         <v>7</v>
       </c>
-      <c r="H45" s="11">
-        <v>1</v>
-      </c>
-      <c r="I45" s="11">
-        <v>0</v>
-      </c>
-      <c r="J45" s="11">
+      <c r="H45" s="23">
+        <v>2</v>
+      </c>
+      <c r="I45" s="23">
+        <v>3</v>
+      </c>
+      <c r="J45" s="23">
+        <v>0</v>
+      </c>
+      <c r="K45" s="23">
+        <v>1</v>
+      </c>
+      <c r="L45" s="23">
         <v>8</v>
       </c>
-      <c r="K45" s="11">
+      <c r="M45" s="23">
         <v>9</v>
       </c>
-      <c r="L45" s="11">
-        <v>4</v>
-      </c>
-      <c r="M45" s="11">
+      <c r="N45" s="23">
+        <v>4</v>
+      </c>
+      <c r="O45" s="23">
         <v>5</v>
       </c>
-      <c r="N45" s="11">
-        <v>2</v>
-      </c>
-      <c r="O45" s="11">
-        <v>3</v>
-      </c>
       <c r="P45" s="13">
-        <v>2</v>
-      </c>
-      <c r="Q45" s="11">
-        <v>3</v>
-      </c>
-      <c r="R45" s="11">
-        <v>4</v>
-      </c>
-      <c r="S45" s="11">
-        <v>0</v>
-      </c>
-      <c r="T45" s="14">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q45" s="23">
+        <v>2</v>
+      </c>
+      <c r="R45" s="23">
+        <v>0</v>
+      </c>
+      <c r="S45" s="23">
+        <v>3</v>
+      </c>
+      <c r="T45" s="25">
+        <v>4</v>
       </c>
       <c r="U45" s="15" t="s">
         <v>32</v>
@@ -4289,389 +4286,389 @@
     </row>
     <row r="46" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C46" s="23">
-        <v>1</v>
-      </c>
-      <c r="D46" s="24">
-        <v>48</v>
-      </c>
-      <c r="E46" s="23">
+        <v>70</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="11">
+        <v>1</v>
+      </c>
+      <c r="D46" s="12">
+        <v>49</v>
+      </c>
+      <c r="E46" s="11">
         <v>0</v>
       </c>
       <c r="F46" s="13">
+        <v>8</v>
+      </c>
+      <c r="G46" s="11">
+        <v>9</v>
+      </c>
+      <c r="H46" s="11">
+        <v>3</v>
+      </c>
+      <c r="I46" s="11">
+        <v>0</v>
+      </c>
+      <c r="J46" s="11">
+        <v>4</v>
+      </c>
+      <c r="K46" s="11">
+        <v>5</v>
+      </c>
+      <c r="L46" s="11">
         <v>6</v>
       </c>
-      <c r="G46" s="23">
+      <c r="M46" s="11">
         <v>7</v>
       </c>
-      <c r="H46" s="23">
-        <v>2</v>
-      </c>
-      <c r="I46" s="23">
-        <v>3</v>
-      </c>
-      <c r="J46" s="23">
-        <v>0</v>
-      </c>
-      <c r="K46" s="23">
-        <v>1</v>
-      </c>
-      <c r="L46" s="23">
-        <v>8</v>
-      </c>
-      <c r="M46" s="23">
-        <v>9</v>
-      </c>
-      <c r="N46" s="23">
-        <v>4</v>
-      </c>
-      <c r="O46" s="23">
-        <v>5</v>
+      <c r="N46" s="11">
+        <v>1</v>
+      </c>
+      <c r="O46" s="11">
+        <v>2</v>
       </c>
       <c r="P46" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q46" s="23">
-        <v>2</v>
-      </c>
-      <c r="R46" s="23">
-        <v>0</v>
-      </c>
-      <c r="S46" s="23">
-        <v>3</v>
-      </c>
-      <c r="T46" s="25">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="Q46" s="11">
+        <v>4</v>
+      </c>
+      <c r="R46" s="11">
+        <v>0</v>
+      </c>
+      <c r="S46" s="11">
+        <v>1</v>
+      </c>
+      <c r="T46" s="14">
+        <v>2</v>
       </c>
       <c r="U46" s="15" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C47" s="11">
-        <v>1</v>
-      </c>
-      <c r="D47" s="12">
-        <v>49</v>
-      </c>
-      <c r="E47" s="11">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="B47" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C47" s="23">
+        <v>1</v>
+      </c>
+      <c r="D47" s="24">
+        <v>50</v>
+      </c>
+      <c r="E47" s="23">
+        <v>1</v>
       </c>
       <c r="F47" s="13">
+        <v>9</v>
+      </c>
+      <c r="G47" s="23">
+        <v>5</v>
+      </c>
+      <c r="H47" s="23">
         <v>8</v>
       </c>
-      <c r="G47" s="11">
-        <v>9</v>
-      </c>
-      <c r="H47" s="11">
-        <v>3</v>
-      </c>
-      <c r="I47" s="11">
-        <v>0</v>
-      </c>
-      <c r="J47" s="11">
-        <v>4</v>
-      </c>
-      <c r="K47" s="11">
-        <v>5</v>
-      </c>
-      <c r="L47" s="11">
+      <c r="I47" s="23">
+        <v>2</v>
+      </c>
+      <c r="J47" s="23">
         <v>6</v>
       </c>
-      <c r="M47" s="11">
+      <c r="K47" s="23">
+        <v>3</v>
+      </c>
+      <c r="L47" s="23">
         <v>7</v>
       </c>
-      <c r="N47" s="11">
-        <v>1</v>
-      </c>
-      <c r="O47" s="11">
-        <v>2</v>
+      <c r="M47" s="23">
+        <v>4</v>
+      </c>
+      <c r="N47" s="23">
+        <v>0</v>
+      </c>
+      <c r="O47" s="23">
+        <v>1</v>
       </c>
       <c r="P47" s="13">
-        <v>3</v>
-      </c>
-      <c r="Q47" s="11">
-        <v>4</v>
-      </c>
-      <c r="R47" s="11">
-        <v>0</v>
-      </c>
-      <c r="S47" s="11">
-        <v>1</v>
-      </c>
-      <c r="T47" s="14">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="Q47" s="23">
+        <v>1</v>
+      </c>
+      <c r="R47" s="23">
+        <v>2</v>
+      </c>
+      <c r="S47" s="23">
+        <v>3</v>
+      </c>
+      <c r="T47" s="25">
+        <v>0</v>
       </c>
       <c r="U47" s="15" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="36" t="s">
-        <v>73</v>
-      </c>
-      <c r="B48" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C48" s="23">
-        <v>1</v>
-      </c>
-      <c r="D48" s="24">
-        <v>50</v>
-      </c>
-      <c r="E48" s="23">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" s="11">
+        <v>1</v>
+      </c>
+      <c r="D48" s="12">
+        <v>51</v>
+      </c>
+      <c r="E48" s="11">
+        <v>0</v>
       </c>
       <c r="F48" s="13">
+        <v>6</v>
+      </c>
+      <c r="G48" s="11">
+        <v>7</v>
+      </c>
+      <c r="H48" s="11">
+        <v>5</v>
+      </c>
+      <c r="I48" s="11">
+        <v>2</v>
+      </c>
+      <c r="J48" s="11">
+        <v>8</v>
+      </c>
+      <c r="K48" s="11">
         <v>9</v>
       </c>
-      <c r="G48" s="23">
-        <v>5</v>
-      </c>
-      <c r="H48" s="23">
-        <v>8</v>
-      </c>
-      <c r="I48" s="23">
-        <v>2</v>
-      </c>
-      <c r="J48" s="23">
-        <v>6</v>
-      </c>
-      <c r="K48" s="23">
-        <v>3</v>
-      </c>
-      <c r="L48" s="23">
-        <v>7</v>
-      </c>
-      <c r="M48" s="23">
-        <v>4</v>
-      </c>
-      <c r="N48" s="23">
-        <v>0</v>
-      </c>
-      <c r="O48" s="23">
-        <v>1</v>
+      <c r="L48" s="11">
+        <v>0</v>
+      </c>
+      <c r="M48" s="11">
+        <v>1</v>
+      </c>
+      <c r="N48" s="11">
+        <v>3</v>
+      </c>
+      <c r="O48" s="11">
+        <v>4</v>
       </c>
       <c r="P48" s="13">
-        <v>4</v>
-      </c>
-      <c r="Q48" s="23">
-        <v>1</v>
-      </c>
-      <c r="R48" s="23">
-        <v>2</v>
-      </c>
-      <c r="S48" s="23">
-        <v>3</v>
-      </c>
-      <c r="T48" s="25">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="Q48" s="11">
+        <v>4</v>
+      </c>
+      <c r="R48" s="11">
+        <v>2</v>
+      </c>
+      <c r="S48" s="11">
+        <v>0</v>
+      </c>
+      <c r="T48" s="14">
+        <v>1</v>
       </c>
       <c r="U48" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="49" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="B49" s="11" t="s">
+      <c r="A49" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C49" s="11">
-        <v>1</v>
-      </c>
-      <c r="D49" s="12">
-        <v>51</v>
-      </c>
-      <c r="E49" s="11">
-        <v>0</v>
-      </c>
-      <c r="F49" s="13">
+      <c r="C49" s="16">
+        <v>1</v>
+      </c>
+      <c r="D49" s="17">
+        <v>52</v>
+      </c>
+      <c r="E49" s="16">
+        <v>0</v>
+      </c>
+      <c r="F49" s="18">
         <v>6</v>
       </c>
-      <c r="G49" s="11">
+      <c r="G49" s="16">
         <v>7</v>
       </c>
-      <c r="H49" s="11">
+      <c r="H49" s="16">
         <v>5</v>
       </c>
-      <c r="I49" s="11">
-        <v>2</v>
-      </c>
-      <c r="J49" s="11">
+      <c r="I49" s="16">
+        <v>2</v>
+      </c>
+      <c r="J49" s="16">
         <v>8</v>
       </c>
-      <c r="K49" s="11">
+      <c r="K49" s="16">
         <v>9</v>
       </c>
-      <c r="L49" s="11">
-        <v>0</v>
-      </c>
-      <c r="M49" s="11">
-        <v>1</v>
-      </c>
-      <c r="N49" s="11">
-        <v>3</v>
-      </c>
-      <c r="O49" s="11">
-        <v>4</v>
-      </c>
-      <c r="P49" s="13">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="11">
-        <v>4</v>
-      </c>
-      <c r="R49" s="11">
-        <v>2</v>
-      </c>
-      <c r="S49" s="11">
-        <v>0</v>
-      </c>
-      <c r="T49" s="14">
-        <v>1</v>
-      </c>
-      <c r="U49" s="15" t="s">
-        <v>32</v>
+      <c r="L49" s="16">
+        <v>3</v>
+      </c>
+      <c r="M49" s="16">
+        <v>4</v>
+      </c>
+      <c r="N49" s="16">
+        <v>0</v>
+      </c>
+      <c r="O49" s="16">
+        <v>1</v>
+      </c>
+      <c r="P49" s="18">
+        <v>2</v>
+      </c>
+      <c r="Q49" s="16">
+        <v>3</v>
+      </c>
+      <c r="R49" s="16">
+        <v>4</v>
+      </c>
+      <c r="S49" s="16">
+        <v>0</v>
+      </c>
+      <c r="T49" s="19">
+        <v>1</v>
+      </c>
+      <c r="U49" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C50" s="16">
-        <v>1</v>
-      </c>
-      <c r="D50" s="17">
-        <v>52</v>
-      </c>
-      <c r="E50" s="16">
+        <v>74</v>
+      </c>
+      <c r="B50" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50" s="20">
+        <v>1</v>
+      </c>
+      <c r="D50" s="21">
+        <v>53</v>
+      </c>
+      <c r="E50" s="20">
         <v>0</v>
       </c>
       <c r="F50" s="18">
+        <v>3</v>
+      </c>
+      <c r="G50" s="20">
+        <v>4</v>
+      </c>
+      <c r="H50" s="20">
+        <v>5</v>
+      </c>
+      <c r="I50" s="20">
+        <v>2</v>
+      </c>
+      <c r="J50" s="20">
+        <v>0</v>
+      </c>
+      <c r="K50" s="20">
+        <v>1</v>
+      </c>
+      <c r="L50" s="20">
+        <v>8</v>
+      </c>
+      <c r="M50" s="20">
+        <v>9</v>
+      </c>
+      <c r="N50" s="20">
         <v>6</v>
       </c>
-      <c r="G50" s="16">
+      <c r="O50" s="20">
         <v>7</v>
       </c>
-      <c r="H50" s="16">
-        <v>5</v>
-      </c>
-      <c r="I50" s="16">
-        <v>2</v>
-      </c>
-      <c r="J50" s="16">
-        <v>8</v>
-      </c>
-      <c r="K50" s="16">
-        <v>9</v>
-      </c>
-      <c r="L50" s="16">
-        <v>3</v>
-      </c>
-      <c r="M50" s="16">
-        <v>4</v>
-      </c>
-      <c r="N50" s="16">
-        <v>0</v>
-      </c>
-      <c r="O50" s="16">
-        <v>1</v>
-      </c>
       <c r="P50" s="18">
-        <v>2</v>
-      </c>
-      <c r="Q50" s="16">
-        <v>3</v>
-      </c>
-      <c r="R50" s="16">
-        <v>4</v>
-      </c>
-      <c r="S50" s="16">
-        <v>0</v>
-      </c>
-      <c r="T50" s="19">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q50" s="20">
+        <v>2</v>
+      </c>
+      <c r="R50" s="20">
+        <v>0</v>
+      </c>
+      <c r="S50" s="20">
+        <v>3</v>
+      </c>
+      <c r="T50" s="22">
+        <v>4</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="37" t="s">
-        <v>76</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C51" s="20">
-        <v>1</v>
-      </c>
-      <c r="D51" s="21">
-        <v>53</v>
-      </c>
-      <c r="E51" s="20">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="16">
+        <v>1</v>
+      </c>
+      <c r="D51" s="17">
+        <v>54</v>
+      </c>
+      <c r="E51" s="16">
+        <v>1</v>
       </c>
       <c r="F51" s="18">
-        <v>3</v>
-      </c>
-      <c r="G51" s="20">
-        <v>4</v>
-      </c>
-      <c r="H51" s="20">
+        <v>8</v>
+      </c>
+      <c r="G51" s="16">
+        <v>4</v>
+      </c>
+      <c r="H51" s="16">
+        <v>7</v>
+      </c>
+      <c r="I51" s="16">
+        <v>0</v>
+      </c>
+      <c r="J51" s="16">
+        <v>9</v>
+      </c>
+      <c r="K51" s="16">
         <v>5</v>
       </c>
-      <c r="I51" s="20">
-        <v>2</v>
-      </c>
-      <c r="J51" s="20">
-        <v>0</v>
-      </c>
-      <c r="K51" s="20">
-        <v>1</v>
-      </c>
-      <c r="L51" s="20">
-        <v>8</v>
-      </c>
-      <c r="M51" s="20">
-        <v>9</v>
-      </c>
-      <c r="N51" s="20">
+      <c r="L51" s="16">
+        <v>2</v>
+      </c>
+      <c r="M51" s="16">
+        <v>1</v>
+      </c>
+      <c r="N51" s="16">
         <v>6</v>
       </c>
-      <c r="O51" s="20">
-        <v>7</v>
+      <c r="O51" s="16">
+        <v>3</v>
       </c>
       <c r="P51" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q51" s="20">
-        <v>2</v>
-      </c>
-      <c r="R51" s="20">
-        <v>0</v>
-      </c>
-      <c r="S51" s="20">
-        <v>3</v>
-      </c>
-      <c r="T51" s="22">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="Q51" s="16">
+        <v>3</v>
+      </c>
+      <c r="R51" s="16">
+        <v>2</v>
+      </c>
+      <c r="S51" s="16">
+        <v>1</v>
+      </c>
+      <c r="T51" s="19">
+        <v>0</v>
       </c>
       <c r="U51" s="10" t="s">
         <v>32</v>
@@ -4679,711 +4676,711 @@
     </row>
     <row r="52" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C52" s="16">
-        <v>1</v>
-      </c>
-      <c r="D52" s="17">
-        <v>54</v>
-      </c>
-      <c r="E52" s="16">
+        <v>76</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" s="20">
+        <v>1</v>
+      </c>
+      <c r="D52" s="21">
+        <v>55</v>
+      </c>
+      <c r="E52" s="20">
         <v>1</v>
       </c>
       <c r="F52" s="18">
+        <v>6</v>
+      </c>
+      <c r="G52" s="20">
+        <v>7</v>
+      </c>
+      <c r="H52" s="20">
+        <v>4</v>
+      </c>
+      <c r="I52" s="20">
+        <v>5</v>
+      </c>
+      <c r="J52" s="20">
         <v>8</v>
       </c>
-      <c r="G52" s="16">
-        <v>4</v>
-      </c>
-      <c r="H52" s="16">
-        <v>7</v>
-      </c>
-      <c r="I52" s="16">
-        <v>0</v>
-      </c>
-      <c r="J52" s="16">
+      <c r="K52" s="20">
         <v>9</v>
       </c>
-      <c r="K52" s="16">
-        <v>5</v>
-      </c>
-      <c r="L52" s="16">
-        <v>2</v>
-      </c>
-      <c r="M52" s="16">
-        <v>1</v>
-      </c>
-      <c r="N52" s="16">
-        <v>6</v>
-      </c>
-      <c r="O52" s="16">
+      <c r="L52" s="20">
+        <v>0</v>
+      </c>
+      <c r="M52" s="20">
+        <v>1</v>
+      </c>
+      <c r="N52" s="20">
+        <v>2</v>
+      </c>
+      <c r="O52" s="20">
         <v>3</v>
       </c>
       <c r="P52" s="18">
-        <v>4</v>
-      </c>
-      <c r="Q52" s="16">
-        <v>3</v>
-      </c>
-      <c r="R52" s="16">
-        <v>2</v>
-      </c>
-      <c r="S52" s="16">
-        <v>1</v>
-      </c>
-      <c r="T52" s="19">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q52" s="20">
+        <v>3</v>
+      </c>
+      <c r="R52" s="20">
+        <v>4</v>
+      </c>
+      <c r="S52" s="20">
+        <v>0</v>
+      </c>
+      <c r="T52" s="22">
+        <v>1</v>
       </c>
       <c r="U52" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="B53" s="20" t="s">
+      <c r="A53" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B53" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="C53" s="20">
-        <v>1</v>
-      </c>
-      <c r="D53" s="21">
-        <v>55</v>
-      </c>
-      <c r="E53" s="20">
-        <v>1</v>
-      </c>
-      <c r="F53" s="18">
+      <c r="C53" s="23">
+        <v>1</v>
+      </c>
+      <c r="D53" s="24">
+        <v>56</v>
+      </c>
+      <c r="E53" s="23">
+        <v>0</v>
+      </c>
+      <c r="F53" s="13">
+        <v>3</v>
+      </c>
+      <c r="G53" s="23">
+        <v>4</v>
+      </c>
+      <c r="H53" s="23">
+        <v>5</v>
+      </c>
+      <c r="I53" s="23">
+        <v>2</v>
+      </c>
+      <c r="J53" s="23">
+        <v>0</v>
+      </c>
+      <c r="K53" s="23">
+        <v>1</v>
+      </c>
+      <c r="L53" s="23">
         <v>6</v>
       </c>
-      <c r="G53" s="20">
+      <c r="M53" s="23">
         <v>7</v>
       </c>
-      <c r="H53" s="20">
-        <v>4</v>
-      </c>
-      <c r="I53" s="20">
-        <v>5</v>
-      </c>
-      <c r="J53" s="20">
+      <c r="N53" s="23">
         <v>8</v>
       </c>
-      <c r="K53" s="20">
+      <c r="O53" s="23">
         <v>9</v>
       </c>
-      <c r="L53" s="20">
-        <v>0</v>
-      </c>
-      <c r="M53" s="20">
-        <v>1</v>
-      </c>
-      <c r="N53" s="20">
-        <v>2</v>
-      </c>
-      <c r="O53" s="20">
-        <v>3</v>
-      </c>
-      <c r="P53" s="18">
-        <v>2</v>
-      </c>
-      <c r="Q53" s="20">
-        <v>3</v>
-      </c>
-      <c r="R53" s="20">
-        <v>4</v>
-      </c>
-      <c r="S53" s="20">
-        <v>0</v>
-      </c>
-      <c r="T53" s="22">
-        <v>1</v>
-      </c>
-      <c r="U53" s="10" t="s">
+      <c r="P53" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="23">
+        <v>2</v>
+      </c>
+      <c r="R53" s="23">
+        <v>0</v>
+      </c>
+      <c r="S53" s="23">
+        <v>3</v>
+      </c>
+      <c r="T53" s="25">
+        <v>4</v>
+      </c>
+      <c r="U53" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" s="11">
+        <v>1</v>
+      </c>
+      <c r="D54" s="12">
+        <v>57</v>
+      </c>
+      <c r="E54" s="11">
+        <v>1</v>
+      </c>
+      <c r="F54" s="13">
+        <v>2</v>
+      </c>
+      <c r="G54" s="11">
+        <v>3</v>
+      </c>
+      <c r="H54" s="11">
+        <v>6</v>
+      </c>
+      <c r="I54" s="11">
+        <v>9</v>
+      </c>
+      <c r="J54" s="11">
+        <v>0</v>
+      </c>
+      <c r="K54" s="11">
+        <v>1</v>
+      </c>
+      <c r="L54" s="11">
+        <v>4</v>
+      </c>
+      <c r="M54" s="11">
+        <v>5</v>
+      </c>
+      <c r="N54" s="11">
+        <v>7</v>
+      </c>
+      <c r="O54" s="11">
+        <v>8</v>
+      </c>
+      <c r="P54" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="11">
+        <v>1</v>
+      </c>
+      <c r="R54" s="11">
+        <v>2</v>
+      </c>
+      <c r="S54" s="11">
+        <v>3</v>
+      </c>
+      <c r="T54" s="14">
+        <v>4</v>
+      </c>
+      <c r="U54" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="37" t="s">
         <v>79</v>
       </c>
-      <c r="B54" s="23" t="s">
+      <c r="B55" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C54" s="23">
-        <v>1</v>
-      </c>
-      <c r="D54" s="24">
-        <v>56</v>
-      </c>
-      <c r="E54" s="23">
-        <v>0</v>
-      </c>
-      <c r="F54" s="13">
-        <v>3</v>
-      </c>
-      <c r="G54" s="23">
-        <v>4</v>
-      </c>
-      <c r="H54" s="23">
+      <c r="C55" s="16">
+        <v>1</v>
+      </c>
+      <c r="D55" s="17">
+        <v>58</v>
+      </c>
+      <c r="E55" s="16">
+        <v>0</v>
+      </c>
+      <c r="F55" s="18">
+        <v>4</v>
+      </c>
+      <c r="G55" s="16">
         <v>5</v>
       </c>
-      <c r="I54" s="23">
-        <v>2</v>
-      </c>
-      <c r="J54" s="23">
-        <v>0</v>
-      </c>
-      <c r="K54" s="23">
-        <v>1</v>
-      </c>
-      <c r="L54" s="23">
+      <c r="H55" s="16">
+        <v>2</v>
+      </c>
+      <c r="I55" s="16">
+        <v>3</v>
+      </c>
+      <c r="J55" s="16">
+        <v>0</v>
+      </c>
+      <c r="K55" s="16">
+        <v>1</v>
+      </c>
+      <c r="L55" s="16">
         <v>6</v>
       </c>
-      <c r="M54" s="23">
+      <c r="M55" s="16">
         <v>7</v>
       </c>
-      <c r="N54" s="23">
+      <c r="N55" s="16">
         <v>8</v>
       </c>
-      <c r="O54" s="23">
+      <c r="O55" s="16">
         <v>9</v>
       </c>
-      <c r="P54" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q54" s="23">
-        <v>2</v>
-      </c>
-      <c r="R54" s="23">
-        <v>0</v>
-      </c>
-      <c r="S54" s="23">
-        <v>3</v>
-      </c>
-      <c r="T54" s="25">
-        <v>4</v>
-      </c>
-      <c r="U54" s="15" t="s">
+      <c r="P55" s="18">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="16">
+        <v>2</v>
+      </c>
+      <c r="R55" s="16">
+        <v>0</v>
+      </c>
+      <c r="S55" s="16">
+        <v>3</v>
+      </c>
+      <c r="T55" s="19">
+        <v>4</v>
+      </c>
+      <c r="U55" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="36" t="s">
+    <row r="56" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="B55" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C55" s="11">
-        <v>1</v>
-      </c>
-      <c r="D55" s="12">
-        <v>57</v>
-      </c>
-      <c r="E55" s="11">
-        <v>1</v>
-      </c>
-      <c r="F55" s="13">
-        <v>2</v>
-      </c>
-      <c r="G55" s="11">
-        <v>3</v>
-      </c>
-      <c r="H55" s="11">
+      <c r="B56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="11">
+        <v>1</v>
+      </c>
+      <c r="D56" s="12">
+        <v>59</v>
+      </c>
+      <c r="E56" s="11">
+        <v>0</v>
+      </c>
+      <c r="F56" s="13">
+        <v>4</v>
+      </c>
+      <c r="G56" s="11">
+        <v>5</v>
+      </c>
+      <c r="H56" s="11">
+        <v>2</v>
+      </c>
+      <c r="I56" s="11">
+        <v>3</v>
+      </c>
+      <c r="J56" s="11">
+        <v>0</v>
+      </c>
+      <c r="K56" s="11">
+        <v>1</v>
+      </c>
+      <c r="L56" s="11">
         <v>6</v>
       </c>
-      <c r="I55" s="11">
+      <c r="M56" s="11">
+        <v>7</v>
+      </c>
+      <c r="N56" s="11">
+        <v>8</v>
+      </c>
+      <c r="O56" s="11">
         <v>9</v>
       </c>
-      <c r="J55" s="11">
-        <v>0</v>
-      </c>
-      <c r="K55" s="11">
-        <v>1</v>
-      </c>
-      <c r="L55" s="11">
-        <v>4</v>
-      </c>
-      <c r="M55" s="11">
-        <v>5</v>
-      </c>
-      <c r="N55" s="11">
-        <v>7</v>
-      </c>
-      <c r="O55" s="11">
-        <v>8</v>
-      </c>
-      <c r="P55" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="11">
-        <v>1</v>
-      </c>
-      <c r="R55" s="11">
-        <v>2</v>
-      </c>
-      <c r="S55" s="11">
-        <v>3</v>
-      </c>
-      <c r="T55" s="14">
-        <v>4</v>
-      </c>
-      <c r="U55" s="15" t="s">
+      <c r="P56" s="13">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="11">
+        <v>2</v>
+      </c>
+      <c r="R56" s="11">
+        <v>0</v>
+      </c>
+      <c r="S56" s="11">
+        <v>3</v>
+      </c>
+      <c r="T56" s="14">
+        <v>4</v>
+      </c>
+      <c r="U56" s="15" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C56" s="16">
-        <v>1</v>
-      </c>
-      <c r="D56" s="17">
-        <v>58</v>
-      </c>
-      <c r="E56" s="16">
-        <v>0</v>
-      </c>
-      <c r="F56" s="18">
-        <v>4</v>
-      </c>
-      <c r="G56" s="16">
-        <v>5</v>
-      </c>
-      <c r="H56" s="16">
-        <v>2</v>
-      </c>
-      <c r="I56" s="16">
-        <v>3</v>
-      </c>
-      <c r="J56" s="16">
-        <v>0</v>
-      </c>
-      <c r="K56" s="16">
-        <v>1</v>
-      </c>
-      <c r="L56" s="16">
-        <v>6</v>
-      </c>
-      <c r="M56" s="16">
-        <v>7</v>
-      </c>
-      <c r="N56" s="16">
-        <v>8</v>
-      </c>
-      <c r="O56" s="16">
-        <v>9</v>
-      </c>
-      <c r="P56" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q56" s="16">
-        <v>2</v>
-      </c>
-      <c r="R56" s="16">
-        <v>0</v>
-      </c>
-      <c r="S56" s="16">
-        <v>3</v>
-      </c>
-      <c r="T56" s="19">
-        <v>4</v>
-      </c>
-      <c r="U56" s="10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="57" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C57" s="11">
-        <v>1</v>
-      </c>
-      <c r="D57" s="12">
-        <v>59</v>
-      </c>
-      <c r="E57" s="11">
-        <v>0</v>
+        <v>81</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C57" s="23">
+        <v>1</v>
+      </c>
+      <c r="D57" s="24">
+        <v>60</v>
+      </c>
+      <c r="E57" s="23">
+        <v>1</v>
       </c>
       <c r="F57" s="13">
         <v>4</v>
       </c>
-      <c r="G57" s="11">
+      <c r="G57" s="23">
         <v>5</v>
       </c>
-      <c r="H57" s="11">
-        <v>2</v>
-      </c>
-      <c r="I57" s="11">
-        <v>3</v>
-      </c>
-      <c r="J57" s="11">
-        <v>0</v>
-      </c>
-      <c r="K57" s="11">
-        <v>1</v>
-      </c>
-      <c r="L57" s="11">
+      <c r="H57" s="23">
+        <v>3</v>
+      </c>
+      <c r="I57" s="23">
+        <v>0</v>
+      </c>
+      <c r="J57" s="23">
+        <v>1</v>
+      </c>
+      <c r="K57" s="23">
+        <v>2</v>
+      </c>
+      <c r="L57" s="23">
+        <v>8</v>
+      </c>
+      <c r="M57" s="23">
+        <v>9</v>
+      </c>
+      <c r="N57" s="23">
         <v>6</v>
       </c>
-      <c r="M57" s="11">
+      <c r="O57" s="23">
         <v>7</v>
       </c>
-      <c r="N57" s="11">
-        <v>8</v>
-      </c>
-      <c r="O57" s="11">
-        <v>9</v>
-      </c>
       <c r="P57" s="13">
         <v>1</v>
       </c>
-      <c r="Q57" s="11">
-        <v>2</v>
-      </c>
-      <c r="R57" s="11">
-        <v>0</v>
-      </c>
-      <c r="S57" s="11">
-        <v>3</v>
-      </c>
-      <c r="T57" s="14">
+      <c r="Q57" s="23">
+        <v>2</v>
+      </c>
+      <c r="R57" s="23">
+        <v>0</v>
+      </c>
+      <c r="S57" s="23">
+        <v>3</v>
+      </c>
+      <c r="T57" s="25">
         <v>4</v>
       </c>
       <c r="U57" s="15" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="36" t="s">
-        <v>83</v>
-      </c>
-      <c r="B58" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C58" s="23">
-        <v>1</v>
-      </c>
-      <c r="D58" s="24">
-        <v>60</v>
-      </c>
-      <c r="E58" s="23">
-        <v>1</v>
+        <v>82</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C58" s="11">
+        <v>1</v>
+      </c>
+      <c r="D58" s="12">
+        <v>61</v>
+      </c>
+      <c r="E58" s="11">
+        <v>0</v>
       </c>
       <c r="F58" s="13">
-        <v>4</v>
-      </c>
-      <c r="G58" s="23">
+        <v>8</v>
+      </c>
+      <c r="G58" s="11">
         <v>5</v>
       </c>
-      <c r="H58" s="23">
-        <v>3</v>
-      </c>
-      <c r="I58" s="23">
-        <v>0</v>
-      </c>
-      <c r="J58" s="23">
-        <v>1</v>
-      </c>
-      <c r="K58" s="23">
-        <v>2</v>
-      </c>
-      <c r="L58" s="23">
-        <v>8</v>
-      </c>
-      <c r="M58" s="23">
+      <c r="H58" s="11">
+        <v>7</v>
+      </c>
+      <c r="I58" s="11">
+        <v>2</v>
+      </c>
+      <c r="J58" s="11">
+        <v>6</v>
+      </c>
+      <c r="K58" s="11">
+        <v>3</v>
+      </c>
+      <c r="L58" s="11">
+        <v>1</v>
+      </c>
+      <c r="M58" s="11">
+        <v>0</v>
+      </c>
+      <c r="N58" s="11">
         <v>9</v>
       </c>
-      <c r="N58" s="23">
-        <v>6</v>
-      </c>
-      <c r="O58" s="23">
-        <v>7</v>
+      <c r="O58" s="11">
+        <v>4</v>
       </c>
       <c r="P58" s="13">
-        <v>1</v>
-      </c>
-      <c r="Q58" s="23">
-        <v>2</v>
-      </c>
-      <c r="R58" s="23">
-        <v>0</v>
-      </c>
-      <c r="S58" s="23">
-        <v>3</v>
-      </c>
-      <c r="T58" s="25">
-        <v>4</v>
+        <v>4</v>
+      </c>
+      <c r="Q58" s="11">
+        <v>3</v>
+      </c>
+      <c r="R58" s="11">
+        <v>2</v>
+      </c>
+      <c r="S58" s="11">
+        <v>0</v>
+      </c>
+      <c r="T58" s="14">
+        <v>1</v>
       </c>
       <c r="U58" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="36" t="s">
+      <c r="A59" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="B59" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C59" s="16">
+        <v>0</v>
+      </c>
+      <c r="D59" s="17">
+        <v>62</v>
+      </c>
+      <c r="E59" s="16">
+        <v>0</v>
+      </c>
+      <c r="F59" s="18">
+        <v>3</v>
+      </c>
+      <c r="G59" s="16">
+        <v>4</v>
+      </c>
+      <c r="H59" s="16">
+        <v>5</v>
+      </c>
+      <c r="I59" s="16">
+        <v>2</v>
+      </c>
+      <c r="J59" s="16">
+        <v>8</v>
+      </c>
+      <c r="K59" s="16">
+        <v>9</v>
+      </c>
+      <c r="L59" s="16">
+        <v>0</v>
+      </c>
+      <c r="M59" s="16">
+        <v>1</v>
+      </c>
+      <c r="N59" s="16">
+        <v>6</v>
+      </c>
+      <c r="O59" s="16">
+        <v>7</v>
+      </c>
+      <c r="P59" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="16">
+        <v>1</v>
+      </c>
+      <c r="R59" s="16">
+        <v>2</v>
+      </c>
+      <c r="S59" s="16">
+        <v>3</v>
+      </c>
+      <c r="T59" s="19">
+        <v>4</v>
+      </c>
+      <c r="U59" s="10"/>
+    </row>
+    <row r="60" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B60" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C59" s="11">
-        <v>1</v>
-      </c>
-      <c r="D59" s="12">
-        <v>61</v>
-      </c>
-      <c r="E59" s="11">
-        <v>0</v>
-      </c>
-      <c r="F59" s="13">
+      <c r="C60" s="11">
+        <v>1</v>
+      </c>
+      <c r="D60" s="12">
+        <v>63</v>
+      </c>
+      <c r="E60" s="11">
+        <v>0</v>
+      </c>
+      <c r="F60" s="13">
+        <v>6</v>
+      </c>
+      <c r="G60" s="11">
+        <v>7</v>
+      </c>
+      <c r="H60" s="11">
+        <v>4</v>
+      </c>
+      <c r="I60" s="11">
+        <v>5</v>
+      </c>
+      <c r="J60" s="11">
         <v>8</v>
       </c>
-      <c r="G59" s="11">
+      <c r="K60" s="11">
+        <v>9</v>
+      </c>
+      <c r="L60" s="11">
+        <v>0</v>
+      </c>
+      <c r="M60" s="11">
+        <v>1</v>
+      </c>
+      <c r="N60" s="11">
+        <v>2</v>
+      </c>
+      <c r="O60" s="11">
+        <v>3</v>
+      </c>
+      <c r="P60" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q60" s="11">
+        <v>3</v>
+      </c>
+      <c r="R60" s="11">
+        <v>4</v>
+      </c>
+      <c r="S60" s="11">
+        <v>0</v>
+      </c>
+      <c r="T60" s="14">
+        <v>1</v>
+      </c>
+      <c r="U60" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" s="20">
+        <v>1</v>
+      </c>
+      <c r="D61" s="21">
+        <v>64</v>
+      </c>
+      <c r="E61" s="20">
+        <v>1</v>
+      </c>
+      <c r="F61" s="18">
+        <v>6</v>
+      </c>
+      <c r="G61" s="20">
+        <v>7</v>
+      </c>
+      <c r="H61" s="20">
+        <v>3</v>
+      </c>
+      <c r="I61" s="20">
+        <v>0</v>
+      </c>
+      <c r="J61" s="20">
+        <v>4</v>
+      </c>
+      <c r="K61" s="20">
         <v>5</v>
       </c>
-      <c r="H59" s="11">
-        <v>7</v>
-      </c>
-      <c r="I59" s="11">
-        <v>2</v>
-      </c>
-      <c r="J59" s="11">
-        <v>6</v>
-      </c>
-      <c r="K59" s="11">
-        <v>3</v>
-      </c>
-      <c r="L59" s="11">
-        <v>1</v>
-      </c>
-      <c r="M59" s="11">
-        <v>0</v>
-      </c>
-      <c r="N59" s="11">
+      <c r="L61" s="20">
+        <v>8</v>
+      </c>
+      <c r="M61" s="20">
         <v>9</v>
       </c>
-      <c r="O59" s="11">
-        <v>4</v>
-      </c>
-      <c r="P59" s="13">
-        <v>4</v>
-      </c>
-      <c r="Q59" s="11">
-        <v>3</v>
-      </c>
-      <c r="R59" s="11">
-        <v>2</v>
-      </c>
-      <c r="S59" s="11">
-        <v>0</v>
-      </c>
-      <c r="T59" s="14">
-        <v>1</v>
-      </c>
-      <c r="U59" s="15" t="s">
+      <c r="N61" s="20">
+        <v>1</v>
+      </c>
+      <c r="O61" s="20">
+        <v>2</v>
+      </c>
+      <c r="P61" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q61" s="20">
+        <v>4</v>
+      </c>
+      <c r="R61" s="20">
+        <v>2</v>
+      </c>
+      <c r="S61" s="20">
+        <v>0</v>
+      </c>
+      <c r="T61" s="22">
+        <v>1</v>
+      </c>
+      <c r="U61" s="10" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="B60" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C60" s="16">
-        <v>0</v>
-      </c>
-      <c r="D60" s="17">
-        <v>62</v>
-      </c>
-      <c r="E60" s="16">
-        <v>0</v>
-      </c>
-      <c r="F60" s="18">
-        <v>3</v>
-      </c>
-      <c r="G60" s="16">
-        <v>4</v>
-      </c>
-      <c r="H60" s="16">
-        <v>5</v>
-      </c>
-      <c r="I60" s="16">
-        <v>2</v>
-      </c>
-      <c r="J60" s="16">
-        <v>8</v>
-      </c>
-      <c r="K60" s="16">
-        <v>9</v>
-      </c>
-      <c r="L60" s="16">
-        <v>0</v>
-      </c>
-      <c r="M60" s="16">
-        <v>1</v>
-      </c>
-      <c r="N60" s="16">
-        <v>6</v>
-      </c>
-      <c r="O60" s="16">
-        <v>7</v>
-      </c>
-      <c r="P60" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="16">
-        <v>1</v>
-      </c>
-      <c r="R60" s="16">
-        <v>2</v>
-      </c>
-      <c r="S60" s="16">
-        <v>3</v>
-      </c>
-      <c r="T60" s="19">
-        <v>4</v>
-      </c>
-      <c r="U60" s="10"/>
-    </row>
-    <row r="61" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="36" t="s">
-        <v>86</v>
-      </c>
-      <c r="B61" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C61" s="11">
-        <v>1</v>
-      </c>
-      <c r="D61" s="12">
-        <v>63</v>
-      </c>
-      <c r="E61" s="11">
-        <v>0</v>
-      </c>
-      <c r="F61" s="13">
-        <v>6</v>
-      </c>
-      <c r="G61" s="11">
-        <v>7</v>
-      </c>
-      <c r="H61" s="11">
-        <v>4</v>
-      </c>
-      <c r="I61" s="11">
-        <v>5</v>
-      </c>
-      <c r="J61" s="11">
-        <v>8</v>
-      </c>
-      <c r="K61" s="11">
-        <v>9</v>
-      </c>
-      <c r="L61" s="11">
-        <v>0</v>
-      </c>
-      <c r="M61" s="11">
-        <v>1</v>
-      </c>
-      <c r="N61" s="11">
-        <v>2</v>
-      </c>
-      <c r="O61" s="11">
-        <v>3</v>
-      </c>
-      <c r="P61" s="13">
-        <v>2</v>
-      </c>
-      <c r="Q61" s="11">
-        <v>3</v>
-      </c>
-      <c r="R61" s="11">
-        <v>4</v>
-      </c>
-      <c r="S61" s="11">
-        <v>0</v>
-      </c>
-      <c r="T61" s="14">
-        <v>1</v>
-      </c>
-      <c r="U61" s="15" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="62" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="B62" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C62" s="20">
-        <v>1</v>
-      </c>
-      <c r="D62" s="21">
-        <v>64</v>
-      </c>
-      <c r="E62" s="20">
-        <v>1</v>
+        <v>86</v>
+      </c>
+      <c r="B62" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C62" s="16">
+        <v>1</v>
+      </c>
+      <c r="D62" s="17">
+        <v>65</v>
+      </c>
+      <c r="E62" s="16">
+        <v>0</v>
       </c>
       <c r="F62" s="18">
+        <v>3</v>
+      </c>
+      <c r="G62" s="16">
+        <v>4</v>
+      </c>
+      <c r="H62" s="16">
+        <v>7</v>
+      </c>
+      <c r="I62" s="16">
+        <v>0</v>
+      </c>
+      <c r="J62" s="16">
+        <v>5</v>
+      </c>
+      <c r="K62" s="16">
         <v>6</v>
       </c>
-      <c r="G62" s="20">
-        <v>7</v>
-      </c>
-      <c r="H62" s="20">
-        <v>3</v>
-      </c>
-      <c r="I62" s="20">
-        <v>0</v>
-      </c>
-      <c r="J62" s="20">
-        <v>4</v>
-      </c>
-      <c r="K62" s="20">
-        <v>5</v>
-      </c>
-      <c r="L62" s="20">
+      <c r="L62" s="16">
+        <v>1</v>
+      </c>
+      <c r="M62" s="16">
+        <v>2</v>
+      </c>
+      <c r="N62" s="16">
         <v>8</v>
       </c>
-      <c r="M62" s="20">
+      <c r="O62" s="16">
         <v>9</v>
       </c>
-      <c r="N62" s="20">
-        <v>1</v>
-      </c>
-      <c r="O62" s="20">
-        <v>2</v>
-      </c>
       <c r="P62" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="20">
-        <v>4</v>
-      </c>
-      <c r="R62" s="20">
-        <v>2</v>
-      </c>
-      <c r="S62" s="20">
-        <v>0</v>
-      </c>
-      <c r="T62" s="22">
+        <v>2</v>
+      </c>
+      <c r="Q62" s="16">
+        <v>3</v>
+      </c>
+      <c r="R62" s="16">
+        <v>4</v>
+      </c>
+      <c r="S62" s="16">
+        <v>0</v>
+      </c>
+      <c r="T62" s="19">
         <v>1</v>
       </c>
       <c r="U62" s="10" t="s">
@@ -5392,387 +5389,387 @@
     </row>
     <row r="63" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="B63" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C63" s="16">
-        <v>1</v>
-      </c>
-      <c r="D63" s="17">
-        <v>65</v>
-      </c>
-      <c r="E63" s="16">
+        <v>87</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="20">
+        <v>0</v>
+      </c>
+      <c r="D63" s="21">
+        <v>66</v>
+      </c>
+      <c r="E63" s="20">
         <v>0</v>
       </c>
       <c r="F63" s="18">
-        <v>3</v>
-      </c>
-      <c r="G63" s="16">
-        <v>4</v>
-      </c>
-      <c r="H63" s="16">
+        <v>4</v>
+      </c>
+      <c r="G63" s="20">
+        <v>5</v>
+      </c>
+      <c r="H63" s="20">
+        <v>2</v>
+      </c>
+      <c r="I63" s="20">
+        <v>3</v>
+      </c>
+      <c r="J63" s="20">
+        <v>0</v>
+      </c>
+      <c r="K63" s="20">
+        <v>1</v>
+      </c>
+      <c r="L63" s="20">
+        <v>8</v>
+      </c>
+      <c r="M63" s="20">
+        <v>9</v>
+      </c>
+      <c r="N63" s="20">
+        <v>6</v>
+      </c>
+      <c r="O63" s="20">
         <v>7</v>
       </c>
-      <c r="I63" s="16">
-        <v>0</v>
-      </c>
-      <c r="J63" s="16">
-        <v>5</v>
-      </c>
-      <c r="K63" s="16">
-        <v>6</v>
-      </c>
-      <c r="L63" s="16">
-        <v>1</v>
-      </c>
-      <c r="M63" s="16">
-        <v>2</v>
-      </c>
-      <c r="N63" s="16">
-        <v>8</v>
-      </c>
-      <c r="O63" s="16">
-        <v>9</v>
-      </c>
       <c r="P63" s="18">
-        <v>2</v>
-      </c>
-      <c r="Q63" s="16">
-        <v>3</v>
-      </c>
-      <c r="R63" s="16">
-        <v>4</v>
-      </c>
-      <c r="S63" s="16">
-        <v>0</v>
-      </c>
-      <c r="T63" s="19">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="Q63" s="20">
+        <v>2</v>
+      </c>
+      <c r="R63" s="20">
+        <v>0</v>
+      </c>
+      <c r="S63" s="20">
+        <v>3</v>
+      </c>
+      <c r="T63" s="22">
+        <v>4</v>
       </c>
       <c r="U63" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="64" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="B64" s="20" t="s">
+      <c r="A64" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="B64" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="C64" s="20">
-        <v>0</v>
-      </c>
-      <c r="D64" s="21">
-        <v>66</v>
-      </c>
-      <c r="E64" s="20">
-        <v>0</v>
-      </c>
-      <c r="F64" s="18">
-        <v>4</v>
-      </c>
-      <c r="G64" s="20">
+      <c r="C64" s="23">
+        <v>0</v>
+      </c>
+      <c r="D64" s="24">
+        <v>67</v>
+      </c>
+      <c r="E64" s="23">
+        <v>1</v>
+      </c>
+      <c r="F64" s="13">
+        <v>6</v>
+      </c>
+      <c r="G64" s="23">
+        <v>7</v>
+      </c>
+      <c r="H64" s="23">
         <v>5</v>
       </c>
-      <c r="H64" s="20">
-        <v>2</v>
-      </c>
-      <c r="I64" s="20">
-        <v>3</v>
-      </c>
-      <c r="J64" s="20">
-        <v>0</v>
-      </c>
-      <c r="K64" s="20">
-        <v>1</v>
-      </c>
-      <c r="L64" s="20">
+      <c r="I64" s="23">
+        <v>2</v>
+      </c>
+      <c r="J64" s="23">
         <v>8</v>
       </c>
-      <c r="M64" s="20">
+      <c r="K64" s="23">
         <v>9</v>
       </c>
-      <c r="N64" s="20">
-        <v>6</v>
-      </c>
-      <c r="O64" s="20">
-        <v>7</v>
-      </c>
-      <c r="P64" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q64" s="20">
-        <v>2</v>
-      </c>
-      <c r="R64" s="20">
-        <v>0</v>
-      </c>
-      <c r="S64" s="20">
-        <v>3</v>
-      </c>
-      <c r="T64" s="22">
-        <v>4</v>
-      </c>
-      <c r="U64" s="10" t="s">
-        <v>32</v>
+      <c r="L64" s="23">
+        <v>0</v>
+      </c>
+      <c r="M64" s="23">
+        <v>1</v>
+      </c>
+      <c r="N64" s="23">
+        <v>3</v>
+      </c>
+      <c r="O64" s="23">
+        <v>4</v>
+      </c>
+      <c r="P64" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q64" s="23">
+        <v>3</v>
+      </c>
+      <c r="R64" s="23">
+        <v>4</v>
+      </c>
+      <c r="S64" s="23">
+        <v>0</v>
+      </c>
+      <c r="T64" s="25">
+        <v>1</v>
+      </c>
+      <c r="U64" s="15" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="65" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="36" t="s">
-        <v>90</v>
-      </c>
-      <c r="B65" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B65" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C65" s="23">
-        <v>0</v>
-      </c>
-      <c r="D65" s="24">
-        <v>67</v>
-      </c>
-      <c r="E65" s="23">
-        <v>1</v>
+      <c r="C65" s="11">
+        <v>0</v>
+      </c>
+      <c r="D65" s="12">
+        <v>68</v>
+      </c>
+      <c r="E65" s="11">
+        <v>0</v>
       </c>
       <c r="F65" s="13">
+        <v>4</v>
+      </c>
+      <c r="G65" s="11">
+        <v>5</v>
+      </c>
+      <c r="H65" s="11">
+        <v>2</v>
+      </c>
+      <c r="I65" s="11">
+        <v>3</v>
+      </c>
+      <c r="J65" s="11">
+        <v>0</v>
+      </c>
+      <c r="K65" s="11">
+        <v>1</v>
+      </c>
+      <c r="L65" s="11">
         <v>6</v>
       </c>
-      <c r="G65" s="23">
+      <c r="M65" s="11">
         <v>7</v>
       </c>
-      <c r="H65" s="23">
-        <v>5</v>
-      </c>
-      <c r="I65" s="23">
-        <v>2</v>
-      </c>
-      <c r="J65" s="23">
+      <c r="N65" s="11">
         <v>8</v>
       </c>
-      <c r="K65" s="23">
+      <c r="O65" s="11">
         <v>9</v>
       </c>
-      <c r="L65" s="23">
-        <v>0</v>
-      </c>
-      <c r="M65" s="23">
-        <v>1</v>
-      </c>
-      <c r="N65" s="23">
-        <v>3</v>
-      </c>
-      <c r="O65" s="23">
-        <v>4</v>
-      </c>
       <c r="P65" s="13">
-        <v>2</v>
-      </c>
-      <c r="Q65" s="23">
-        <v>3</v>
-      </c>
-      <c r="R65" s="23">
-        <v>4</v>
-      </c>
-      <c r="S65" s="23">
-        <v>0</v>
-      </c>
-      <c r="T65" s="25">
-        <v>1</v>
-      </c>
-      <c r="U65" s="15" t="s">
-        <v>25</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q65" s="11">
+        <v>1</v>
+      </c>
+      <c r="R65" s="11">
+        <v>2</v>
+      </c>
+      <c r="S65" s="11">
+        <v>3</v>
+      </c>
+      <c r="T65" s="14">
+        <v>4</v>
+      </c>
+      <c r="U65" s="15"/>
     </row>
     <row r="66" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" s="23">
+        <v>0</v>
+      </c>
+      <c r="D66" s="24">
+        <v>69</v>
+      </c>
+      <c r="E66" s="23">
+        <v>1</v>
+      </c>
+      <c r="F66" s="13">
+        <v>5</v>
+      </c>
+      <c r="G66" s="23">
+        <v>6</v>
+      </c>
+      <c r="H66" s="23">
+        <v>7</v>
+      </c>
+      <c r="I66" s="23">
+        <v>2</v>
+      </c>
+      <c r="J66" s="23">
+        <v>8</v>
+      </c>
+      <c r="K66" s="23">
+        <v>9</v>
+      </c>
+      <c r="L66" s="23">
+        <v>0</v>
+      </c>
+      <c r="M66" s="23">
+        <v>1</v>
+      </c>
+      <c r="N66" s="23">
+        <v>3</v>
+      </c>
+      <c r="O66" s="23">
+        <v>4</v>
+      </c>
+      <c r="P66" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q66" s="23">
+        <v>3</v>
+      </c>
+      <c r="R66" s="23">
+        <v>4</v>
+      </c>
+      <c r="S66" s="23">
+        <v>0</v>
+      </c>
+      <c r="T66" s="25">
+        <v>1</v>
+      </c>
+      <c r="U66" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="B66" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C66" s="11">
-        <v>0</v>
-      </c>
-      <c r="D66" s="12">
-        <v>68</v>
-      </c>
-      <c r="E66" s="11">
-        <v>0</v>
-      </c>
-      <c r="F66" s="13">
-        <v>4</v>
-      </c>
-      <c r="G66" s="11">
+      <c r="B67" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C67" s="20">
+        <v>0</v>
+      </c>
+      <c r="D67" s="21">
+        <v>70</v>
+      </c>
+      <c r="E67" s="20">
+        <v>1</v>
+      </c>
+      <c r="F67" s="18">
         <v>5</v>
       </c>
-      <c r="H66" s="11">
-        <v>2</v>
-      </c>
-      <c r="I66" s="11">
-        <v>3</v>
-      </c>
-      <c r="J66" s="11">
-        <v>0</v>
-      </c>
-      <c r="K66" s="11">
-        <v>1</v>
-      </c>
-      <c r="L66" s="11">
+      <c r="G67" s="20">
+        <v>3</v>
+      </c>
+      <c r="H67" s="20">
+        <v>4</v>
+      </c>
+      <c r="I67" s="20">
+        <v>2</v>
+      </c>
+      <c r="J67" s="20">
+        <v>1</v>
+      </c>
+      <c r="K67" s="20">
+        <v>0</v>
+      </c>
+      <c r="L67" s="20">
+        <v>8</v>
+      </c>
+      <c r="M67" s="20">
         <v>6</v>
       </c>
-      <c r="M66" s="11">
+      <c r="N67" s="20">
+        <v>9</v>
+      </c>
+      <c r="O67" s="20">
         <v>7</v>
       </c>
-      <c r="N66" s="11">
-        <v>8</v>
-      </c>
-      <c r="O66" s="11">
-        <v>9</v>
-      </c>
-      <c r="P66" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="11">
-        <v>1</v>
-      </c>
-      <c r="R66" s="11">
-        <v>2</v>
-      </c>
-      <c r="S66" s="11">
-        <v>3</v>
-      </c>
-      <c r="T66" s="14">
-        <v>4</v>
-      </c>
-      <c r="U66" s="15"/>
-    </row>
-    <row r="67" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="36" t="s">
-        <v>92</v>
-      </c>
-      <c r="B67" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C67" s="23">
-        <v>0</v>
-      </c>
-      <c r="D67" s="24">
-        <v>69</v>
-      </c>
-      <c r="E67" s="23">
-        <v>1</v>
-      </c>
-      <c r="F67" s="13">
-        <v>5</v>
-      </c>
-      <c r="G67" s="23">
-        <v>6</v>
-      </c>
-      <c r="H67" s="23">
-        <v>7</v>
-      </c>
-      <c r="I67" s="23">
-        <v>2</v>
-      </c>
-      <c r="J67" s="23">
-        <v>8</v>
-      </c>
-      <c r="K67" s="23">
-        <v>9</v>
-      </c>
-      <c r="L67" s="23">
-        <v>0</v>
-      </c>
-      <c r="M67" s="23">
-        <v>1</v>
-      </c>
-      <c r="N67" s="23">
-        <v>3</v>
-      </c>
-      <c r="O67" s="23">
-        <v>4</v>
-      </c>
-      <c r="P67" s="13">
-        <v>2</v>
-      </c>
-      <c r="Q67" s="23">
-        <v>3</v>
-      </c>
-      <c r="R67" s="23">
-        <v>4</v>
-      </c>
-      <c r="S67" s="23">
-        <v>0</v>
-      </c>
-      <c r="T67" s="25">
-        <v>1</v>
-      </c>
-      <c r="U67" s="15" t="s">
-        <v>32</v>
+      <c r="P67" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q67" s="20">
+        <v>1</v>
+      </c>
+      <c r="R67" s="20">
+        <v>0</v>
+      </c>
+      <c r="S67" s="20">
+        <v>4</v>
+      </c>
+      <c r="T67" s="22">
+        <v>2</v>
+      </c>
+      <c r="U67" s="10" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="68" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="B68" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C68" s="20">
-        <v>0</v>
-      </c>
-      <c r="D68" s="21">
-        <v>70</v>
-      </c>
-      <c r="E68" s="20">
-        <v>1</v>
+        <v>92</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C68" s="16">
+        <v>0</v>
+      </c>
+      <c r="D68" s="17">
+        <v>71</v>
+      </c>
+      <c r="E68" s="16">
+        <v>0</v>
       </c>
       <c r="F68" s="18">
+        <v>4</v>
+      </c>
+      <c r="G68" s="19">
         <v>5</v>
       </c>
-      <c r="G68" s="20">
-        <v>3</v>
-      </c>
-      <c r="H68" s="20">
-        <v>4</v>
-      </c>
-      <c r="I68" s="20">
-        <v>2</v>
-      </c>
-      <c r="J68" s="20">
-        <v>1</v>
-      </c>
-      <c r="K68" s="20">
-        <v>0</v>
-      </c>
-      <c r="L68" s="20">
+      <c r="H68" s="19">
+        <v>3</v>
+      </c>
+      <c r="I68" s="19">
+        <v>0</v>
+      </c>
+      <c r="J68" s="19">
+        <v>1</v>
+      </c>
+      <c r="K68" s="19">
+        <v>2</v>
+      </c>
+      <c r="L68" s="19">
         <v>8</v>
       </c>
-      <c r="M68" s="20">
+      <c r="M68" s="19">
+        <v>9</v>
+      </c>
+      <c r="N68" s="19">
         <v>6</v>
       </c>
-      <c r="N68" s="20">
-        <v>9</v>
-      </c>
-      <c r="O68" s="20">
+      <c r="O68" s="19">
         <v>7</v>
       </c>
       <c r="P68" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q68" s="20">
-        <v>1</v>
-      </c>
-      <c r="R68" s="20">
-        <v>0</v>
-      </c>
-      <c r="S68" s="20">
-        <v>4</v>
-      </c>
-      <c r="T68" s="22">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q68" s="19">
+        <v>2</v>
+      </c>
+      <c r="R68" s="19">
+        <v>0</v>
+      </c>
+      <c r="S68" s="19">
+        <v>3</v>
+      </c>
+      <c r="T68" s="19">
+        <v>4</v>
       </c>
       <c r="U68" s="10" t="s">
         <v>25</v>
@@ -5780,471 +5777,441 @@
     </row>
     <row r="69" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="B69" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C69" s="16">
+        <v>0</v>
+      </c>
+      <c r="D69" s="17">
+        <v>72</v>
+      </c>
+      <c r="E69" s="16">
+        <v>0</v>
+      </c>
+      <c r="F69" s="18">
+        <v>7</v>
+      </c>
+      <c r="G69" s="16">
+        <v>8</v>
+      </c>
+      <c r="H69" s="16">
+        <v>9</v>
+      </c>
+      <c r="I69" s="16">
+        <v>4</v>
+      </c>
+      <c r="J69" s="16">
+        <v>5</v>
+      </c>
+      <c r="K69" s="16">
+        <v>6</v>
+      </c>
+      <c r="L69" s="16">
+        <v>0</v>
+      </c>
+      <c r="M69" s="16">
+        <v>1</v>
+      </c>
+      <c r="N69" s="16">
+        <v>2</v>
+      </c>
+      <c r="O69" s="16">
+        <v>3</v>
+      </c>
+      <c r="P69" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q69" s="16">
+        <v>4</v>
+      </c>
+      <c r="R69" s="16">
+        <v>0</v>
+      </c>
+      <c r="S69" s="16">
+        <v>1</v>
+      </c>
+      <c r="T69" s="19">
+        <v>2</v>
+      </c>
+      <c r="U69" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="B69" s="16" t="s">
+      <c r="B70" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C70" s="11">
+        <v>0</v>
+      </c>
+      <c r="D70" s="12">
+        <v>73</v>
+      </c>
+      <c r="E70" s="11">
+        <v>1</v>
+      </c>
+      <c r="F70" s="13">
+        <v>7</v>
+      </c>
+      <c r="G70" s="11">
+        <v>6</v>
+      </c>
+      <c r="H70" s="11">
+        <v>5</v>
+      </c>
+      <c r="I70" s="11">
+        <v>4</v>
+      </c>
+      <c r="J70" s="11">
+        <v>9</v>
+      </c>
+      <c r="K70" s="11">
+        <v>8</v>
+      </c>
+      <c r="L70" s="11">
+        <v>1</v>
+      </c>
+      <c r="M70" s="11">
+        <v>0</v>
+      </c>
+      <c r="N70" s="11">
+        <v>3</v>
+      </c>
+      <c r="O70" s="11">
+        <v>2</v>
+      </c>
+      <c r="P70" s="13">
+        <v>3</v>
+      </c>
+      <c r="Q70" s="11">
+        <v>2</v>
+      </c>
+      <c r="R70" s="11">
+        <v>4</v>
+      </c>
+      <c r="S70" s="11">
+        <v>1</v>
+      </c>
+      <c r="T70" s="14">
+        <v>0</v>
+      </c>
+      <c r="U70" s="15" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B71" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C69" s="16">
-        <v>0</v>
-      </c>
-      <c r="D69" s="17">
-        <v>71</v>
-      </c>
-      <c r="E69" s="16">
-        <v>0</v>
-      </c>
-      <c r="F69" s="18">
-        <v>4</v>
-      </c>
-      <c r="G69" s="19">
+      <c r="C71" s="16">
+        <v>0</v>
+      </c>
+      <c r="D71" s="17">
+        <v>74</v>
+      </c>
+      <c r="E71" s="16">
+        <v>1</v>
+      </c>
+      <c r="F71" s="18">
+        <v>8</v>
+      </c>
+      <c r="G71" s="16">
+        <v>9</v>
+      </c>
+      <c r="H71" s="16">
         <v>5</v>
       </c>
-      <c r="H69" s="19">
-        <v>3</v>
-      </c>
-      <c r="I69" s="19">
-        <v>0</v>
-      </c>
-      <c r="J69" s="19">
-        <v>1</v>
-      </c>
-      <c r="K69" s="19">
-        <v>2</v>
-      </c>
-      <c r="L69" s="19">
+      <c r="I71" s="16">
+        <v>4</v>
+      </c>
+      <c r="J71" s="16">
+        <v>6</v>
+      </c>
+      <c r="K71" s="16">
+        <v>7</v>
+      </c>
+      <c r="L71" s="16">
+        <v>0</v>
+      </c>
+      <c r="M71" s="16">
+        <v>1</v>
+      </c>
+      <c r="N71" s="16">
+        <v>2</v>
+      </c>
+      <c r="O71" s="16">
+        <v>3</v>
+      </c>
+      <c r="P71" s="18">
+        <v>3</v>
+      </c>
+      <c r="Q71" s="16">
+        <v>4</v>
+      </c>
+      <c r="R71" s="16">
+        <v>2</v>
+      </c>
+      <c r="S71" s="16">
+        <v>0</v>
+      </c>
+      <c r="T71" s="19">
+        <v>1</v>
+      </c>
+      <c r="U71" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C72" s="11">
+        <v>0</v>
+      </c>
+      <c r="D72" s="12">
+        <v>75</v>
+      </c>
+      <c r="E72" s="11">
+        <v>0</v>
+      </c>
+      <c r="F72" s="13">
+        <v>7</v>
+      </c>
+      <c r="G72" s="11">
+        <v>4</v>
+      </c>
+      <c r="H72" s="11">
+        <v>5</v>
+      </c>
+      <c r="I72" s="11">
+        <v>2</v>
+      </c>
+      <c r="J72" s="11">
+        <v>0</v>
+      </c>
+      <c r="K72" s="11">
+        <v>1</v>
+      </c>
+      <c r="L72" s="11">
+        <v>6</v>
+      </c>
+      <c r="M72" s="11">
+        <v>3</v>
+      </c>
+      <c r="N72" s="11">
+        <v>9</v>
+      </c>
+      <c r="O72" s="11">
         <v>8</v>
       </c>
-      <c r="M69" s="19">
-        <v>9</v>
-      </c>
-      <c r="N69" s="19">
-        <v>6</v>
-      </c>
-      <c r="O69" s="19">
-        <v>7</v>
-      </c>
-      <c r="P69" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q69" s="19">
-        <v>2</v>
-      </c>
-      <c r="R69" s="19">
-        <v>0</v>
-      </c>
-      <c r="S69" s="19">
-        <v>3</v>
-      </c>
-      <c r="T69" s="19">
-        <v>4</v>
-      </c>
-      <c r="U69" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="37" t="s">
-        <v>95</v>
-      </c>
-      <c r="B70" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C70" s="16">
-        <v>0</v>
-      </c>
-      <c r="D70" s="17">
-        <v>72</v>
-      </c>
-      <c r="E70" s="16">
-        <v>0</v>
-      </c>
-      <c r="F70" s="18">
-        <v>7</v>
-      </c>
-      <c r="G70" s="16">
-        <v>8</v>
-      </c>
-      <c r="H70" s="16">
-        <v>9</v>
-      </c>
-      <c r="I70" s="16">
-        <v>4</v>
-      </c>
-      <c r="J70" s="16">
-        <v>5</v>
-      </c>
-      <c r="K70" s="16">
-        <v>6</v>
-      </c>
-      <c r="L70" s="16">
-        <v>0</v>
-      </c>
-      <c r="M70" s="16">
-        <v>1</v>
-      </c>
-      <c r="N70" s="16">
-        <v>2</v>
-      </c>
-      <c r="O70" s="16">
-        <v>3</v>
-      </c>
-      <c r="P70" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q70" s="16">
-        <v>4</v>
-      </c>
-      <c r="R70" s="16">
-        <v>0</v>
-      </c>
-      <c r="S70" s="16">
-        <v>1</v>
-      </c>
-      <c r="T70" s="19">
-        <v>2</v>
-      </c>
-      <c r="U70" s="10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="B71" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C71" s="11">
-        <v>0</v>
-      </c>
-      <c r="D71" s="12">
-        <v>73</v>
-      </c>
-      <c r="E71" s="11">
-        <v>1</v>
-      </c>
-      <c r="F71" s="13">
-        <v>7</v>
-      </c>
-      <c r="G71" s="11">
-        <v>6</v>
-      </c>
-      <c r="H71" s="11">
-        <v>5</v>
-      </c>
-      <c r="I71" s="11">
-        <v>4</v>
-      </c>
-      <c r="J71" s="11">
-        <v>9</v>
-      </c>
-      <c r="K71" s="11">
-        <v>8</v>
-      </c>
-      <c r="L71" s="11">
-        <v>1</v>
-      </c>
-      <c r="M71" s="11">
-        <v>0</v>
-      </c>
-      <c r="N71" s="11">
-        <v>3</v>
-      </c>
-      <c r="O71" s="11">
-        <v>2</v>
-      </c>
-      <c r="P71" s="13">
-        <v>3</v>
-      </c>
-      <c r="Q71" s="11">
-        <v>2</v>
-      </c>
-      <c r="R71" s="11">
-        <v>4</v>
-      </c>
-      <c r="S71" s="11">
-        <v>1</v>
-      </c>
-      <c r="T71" s="14">
-        <v>0</v>
-      </c>
-      <c r="U71" s="15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="B72" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C72" s="16">
-        <v>0</v>
-      </c>
-      <c r="D72" s="17">
-        <v>74</v>
-      </c>
-      <c r="E72" s="16">
-        <v>1</v>
-      </c>
-      <c r="F72" s="18">
-        <v>8</v>
-      </c>
-      <c r="G72" s="16">
-        <v>9</v>
-      </c>
-      <c r="H72" s="16">
-        <v>5</v>
-      </c>
-      <c r="I72" s="16">
-        <v>4</v>
-      </c>
-      <c r="J72" s="16">
-        <v>6</v>
-      </c>
-      <c r="K72" s="16">
-        <v>7</v>
-      </c>
-      <c r="L72" s="16">
-        <v>0</v>
-      </c>
-      <c r="M72" s="16">
-        <v>1</v>
-      </c>
-      <c r="N72" s="16">
-        <v>2</v>
-      </c>
-      <c r="O72" s="16">
-        <v>3</v>
-      </c>
-      <c r="P72" s="18">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="16">
-        <v>4</v>
-      </c>
-      <c r="R72" s="16">
-        <v>2</v>
-      </c>
-      <c r="S72" s="16">
-        <v>0</v>
-      </c>
-      <c r="T72" s="19">
-        <v>1</v>
-      </c>
-      <c r="U72" s="10" t="s">
+      <c r="P72" s="13">
+        <v>2</v>
+      </c>
+      <c r="Q72" s="11">
+        <v>1</v>
+      </c>
+      <c r="R72" s="11">
+        <v>0</v>
+      </c>
+      <c r="S72" s="11">
+        <v>4</v>
+      </c>
+      <c r="T72" s="14">
+        <v>3</v>
+      </c>
+      <c r="U72" s="15" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="73" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B73" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" s="23">
+        <v>0</v>
+      </c>
+      <c r="D73" s="24">
+        <v>76</v>
+      </c>
+      <c r="E73" s="23">
+        <v>0</v>
+      </c>
+      <c r="F73" s="13">
+        <v>1</v>
+      </c>
+      <c r="G73" s="23">
+        <v>3</v>
+      </c>
+      <c r="H73" s="23">
+        <v>8</v>
+      </c>
+      <c r="I73" s="23">
+        <v>9</v>
+      </c>
+      <c r="J73" s="23">
+        <v>5</v>
+      </c>
+      <c r="K73" s="23">
+        <v>4</v>
+      </c>
+      <c r="L73" s="23">
+        <v>6</v>
+      </c>
+      <c r="M73" s="23">
+        <v>0</v>
+      </c>
+      <c r="N73" s="23">
+        <v>7</v>
+      </c>
+      <c r="O73" s="23">
+        <v>2</v>
+      </c>
+      <c r="P73" s="13">
+        <v>3</v>
+      </c>
+      <c r="Q73" s="23">
+        <v>4</v>
+      </c>
+      <c r="R73" s="23">
+        <v>0</v>
+      </c>
+      <c r="S73" s="23">
+        <v>1</v>
+      </c>
+      <c r="T73" s="25">
+        <v>2</v>
+      </c>
+      <c r="U73" s="15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="37" t="s">
         <v>98</v>
       </c>
-      <c r="B73" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C73" s="11">
-        <v>0</v>
-      </c>
-      <c r="D73" s="12">
-        <v>75</v>
-      </c>
-      <c r="E73" s="11">
-        <v>0</v>
-      </c>
-      <c r="F73" s="13">
+      <c r="B74" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" s="20">
+        <v>0</v>
+      </c>
+      <c r="D74" s="21">
+        <v>77</v>
+      </c>
+      <c r="E74" s="20">
+        <v>0</v>
+      </c>
+      <c r="F74" s="18">
+        <v>6</v>
+      </c>
+      <c r="G74" s="20">
         <v>7</v>
       </c>
-      <c r="G73" s="11">
-        <v>4</v>
-      </c>
-      <c r="H73" s="11">
+      <c r="H74" s="20">
+        <v>4</v>
+      </c>
+      <c r="I74" s="20">
         <v>5</v>
       </c>
-      <c r="I73" s="11">
-        <v>2</v>
-      </c>
-      <c r="J73" s="11">
-        <v>0</v>
-      </c>
-      <c r="K73" s="11">
-        <v>1</v>
-      </c>
-      <c r="L73" s="11">
-        <v>6</v>
-      </c>
-      <c r="M73" s="11">
-        <v>3</v>
-      </c>
-      <c r="N73" s="11">
+      <c r="J74" s="20">
+        <v>8</v>
+      </c>
+      <c r="K74" s="20">
         <v>9</v>
       </c>
-      <c r="O73" s="11">
-        <v>8</v>
-      </c>
-      <c r="P73" s="13">
-        <v>2</v>
-      </c>
-      <c r="Q73" s="11">
-        <v>1</v>
-      </c>
-      <c r="R73" s="11">
-        <v>0</v>
-      </c>
-      <c r="S73" s="11">
-        <v>4</v>
-      </c>
-      <c r="T73" s="14">
-        <v>3</v>
-      </c>
-      <c r="U73" s="15" t="s">
+      <c r="L74" s="20">
+        <v>0</v>
+      </c>
+      <c r="M74" s="20">
+        <v>1</v>
+      </c>
+      <c r="N74" s="20">
+        <v>2</v>
+      </c>
+      <c r="O74" s="20">
+        <v>3</v>
+      </c>
+      <c r="P74" s="18">
+        <v>2</v>
+      </c>
+      <c r="Q74" s="20">
+        <v>3</v>
+      </c>
+      <c r="R74" s="20">
+        <v>4</v>
+      </c>
+      <c r="S74" s="20">
+        <v>0</v>
+      </c>
+      <c r="T74" s="22">
+        <v>1</v>
+      </c>
+      <c r="U74" s="10" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="74" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="B74" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C74" s="23">
-        <v>0</v>
-      </c>
-      <c r="D74" s="24">
-        <v>76</v>
-      </c>
-      <c r="E74" s="23">
-        <v>0</v>
-      </c>
-      <c r="F74" s="13">
-        <v>1</v>
-      </c>
-      <c r="G74" s="23">
-        <v>3</v>
-      </c>
-      <c r="H74" s="23">
-        <v>8</v>
-      </c>
-      <c r="I74" s="23">
-        <v>9</v>
-      </c>
-      <c r="J74" s="23">
-        <v>5</v>
-      </c>
-      <c r="K74" s="23">
-        <v>4</v>
-      </c>
-      <c r="L74" s="23">
-        <v>6</v>
-      </c>
-      <c r="M74" s="23">
-        <v>0</v>
-      </c>
-      <c r="N74" s="23">
-        <v>7</v>
-      </c>
-      <c r="O74" s="23">
-        <v>2</v>
-      </c>
-      <c r="P74" s="13">
-        <v>3</v>
-      </c>
-      <c r="Q74" s="23">
-        <v>4</v>
-      </c>
-      <c r="R74" s="23">
-        <v>0</v>
-      </c>
-      <c r="S74" s="23">
-        <v>1</v>
-      </c>
-      <c r="T74" s="25">
-        <v>2</v>
-      </c>
-      <c r="U74" s="15" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="75" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="37" t="s">
-        <v>100</v>
-      </c>
-      <c r="B75" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C75" s="20">
-        <v>0</v>
-      </c>
-      <c r="D75" s="21">
-        <v>77</v>
-      </c>
-      <c r="E75" s="20">
-        <v>0</v>
-      </c>
-      <c r="F75" s="18">
-        <v>6</v>
-      </c>
-      <c r="G75" s="20">
-        <v>7</v>
-      </c>
-      <c r="H75" s="20">
-        <v>4</v>
-      </c>
-      <c r="I75" s="20">
-        <v>5</v>
-      </c>
-      <c r="J75" s="20">
-        <v>8</v>
-      </c>
-      <c r="K75" s="20">
-        <v>9</v>
-      </c>
-      <c r="L75" s="20">
-        <v>0</v>
-      </c>
-      <c r="M75" s="20">
-        <v>1</v>
-      </c>
-      <c r="N75" s="20">
-        <v>2</v>
-      </c>
-      <c r="O75" s="20">
-        <v>3</v>
-      </c>
-      <c r="P75" s="18">
-        <v>2</v>
-      </c>
-      <c r="Q75" s="20">
-        <v>3</v>
-      </c>
-      <c r="R75" s="20">
-        <v>4</v>
-      </c>
-      <c r="S75" s="20">
-        <v>0</v>
-      </c>
-      <c r="T75" s="22">
-        <v>1</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="B75" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C75" s="16">
+        <v>0</v>
+      </c>
+      <c r="D75" s="17">
+        <v>81</v>
+      </c>
+      <c r="E75" s="16">
+        <v>1</v>
+      </c>
+      <c r="F75" s="18"/>
+      <c r="G75" s="37"/>
+      <c r="H75" s="37"/>
+      <c r="I75" s="37"/>
+      <c r="J75" s="37"/>
+      <c r="K75" s="37"/>
+      <c r="L75" s="37"/>
+      <c r="M75" s="37"/>
+      <c r="N75" s="37"/>
+      <c r="O75" s="37"/>
+      <c r="P75" s="18"/>
+      <c r="Q75" s="37"/>
+      <c r="R75" s="37"/>
+      <c r="S75" s="37"/>
+      <c r="T75" s="19"/>
       <c r="U75" s="10" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="76" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B76" s="16" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C76" s="16">
         <v>0</v>
       </c>
       <c r="D76" s="17">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E76" s="16">
         <v>1</v>
@@ -6265,12 +6232,12 @@
       <c r="S76" s="37"/>
       <c r="T76" s="19"/>
       <c r="U76" s="10" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="77" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B77" s="16" t="s">
         <v>22</v>
@@ -6279,7 +6246,7 @@
         <v>0</v>
       </c>
       <c r="D77" s="17">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E77" s="16">
         <v>1</v>
@@ -6305,277 +6272,245 @@
     </row>
     <row r="78" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="37" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C78" s="16">
         <v>0</v>
       </c>
       <c r="D78" s="17">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E78" s="16">
         <v>1</v>
       </c>
-      <c r="F78" s="18"/>
-      <c r="G78" s="37"/>
-      <c r="H78" s="37"/>
-      <c r="I78" s="37"/>
-      <c r="J78" s="37"/>
-      <c r="K78" s="37"/>
-      <c r="L78" s="37"/>
-      <c r="M78" s="37"/>
-      <c r="N78" s="37"/>
-      <c r="O78" s="37"/>
-      <c r="P78" s="18"/>
-      <c r="Q78" s="37"/>
-      <c r="R78" s="37"/>
-      <c r="S78" s="37"/>
-      <c r="T78" s="19"/>
+      <c r="F78" s="18">
+        <v>6</v>
+      </c>
+      <c r="G78" s="16">
+        <v>7</v>
+      </c>
+      <c r="H78" s="16">
+        <v>2</v>
+      </c>
+      <c r="I78" s="16">
+        <v>3</v>
+      </c>
+      <c r="J78" s="16">
+        <v>0</v>
+      </c>
+      <c r="K78" s="16">
+        <v>1</v>
+      </c>
+      <c r="L78" s="16">
+        <v>8</v>
+      </c>
+      <c r="M78" s="16">
+        <v>9</v>
+      </c>
+      <c r="N78" s="16">
+        <v>4</v>
+      </c>
+      <c r="O78" s="16">
+        <v>5</v>
+      </c>
+      <c r="P78" s="18">
+        <v>1</v>
+      </c>
+      <c r="Q78" s="16">
+        <v>2</v>
+      </c>
+      <c r="R78" s="16">
+        <v>0</v>
+      </c>
+      <c r="S78" s="16">
+        <v>3</v>
+      </c>
+      <c r="T78" s="19">
+        <v>4</v>
+      </c>
       <c r="U78" s="10" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="37" t="s">
-        <v>101</v>
-      </c>
-      <c r="B79" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C79" s="16">
-        <v>0</v>
-      </c>
-      <c r="D79" s="17">
-        <v>78</v>
-      </c>
-      <c r="E79" s="16">
+        <v>100</v>
+      </c>
+      <c r="B79" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C79" s="20">
+        <v>0</v>
+      </c>
+      <c r="D79" s="21">
+        <v>79</v>
+      </c>
+      <c r="E79" s="20">
         <v>1</v>
       </c>
       <c r="F79" s="18">
+        <v>5</v>
+      </c>
+      <c r="G79" s="20">
         <v>6</v>
       </c>
-      <c r="G79" s="16">
+      <c r="H79" s="20">
         <v>7</v>
       </c>
-      <c r="H79" s="16">
-        <v>2</v>
-      </c>
-      <c r="I79" s="16">
-        <v>3</v>
-      </c>
-      <c r="J79" s="16">
-        <v>0</v>
-      </c>
-      <c r="K79" s="16">
-        <v>1</v>
-      </c>
-      <c r="L79" s="16">
+      <c r="I79" s="20">
+        <v>2</v>
+      </c>
+      <c r="J79" s="20">
         <v>8</v>
       </c>
-      <c r="M79" s="16">
+      <c r="K79" s="20">
         <v>9</v>
       </c>
-      <c r="N79" s="16">
-        <v>4</v>
-      </c>
-      <c r="O79" s="16">
-        <v>5</v>
+      <c r="L79" s="20">
+        <v>0</v>
+      </c>
+      <c r="M79" s="20">
+        <v>1</v>
+      </c>
+      <c r="N79" s="20">
+        <v>3</v>
+      </c>
+      <c r="O79" s="20">
+        <v>4</v>
       </c>
       <c r="P79" s="18">
-        <v>1</v>
-      </c>
-      <c r="Q79" s="16">
-        <v>2</v>
-      </c>
-      <c r="R79" s="16">
-        <v>0</v>
-      </c>
-      <c r="S79" s="16">
-        <v>3</v>
-      </c>
-      <c r="T79" s="19">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="20">
+        <v>1</v>
+      </c>
+      <c r="R79" s="20">
+        <v>2</v>
+      </c>
+      <c r="S79" s="20">
+        <v>3</v>
+      </c>
+      <c r="T79" s="22">
         <v>4</v>
       </c>
       <c r="U79" s="10" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="80" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="B80" s="20" t="s">
+    <row r="80" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="40" t="s">
+        <v>101</v>
+      </c>
+      <c r="B80" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C80" s="20">
-        <v>0</v>
-      </c>
-      <c r="D80" s="21">
-        <v>79</v>
-      </c>
-      <c r="E80" s="20">
-        <v>1</v>
-      </c>
-      <c r="F80" s="18">
+      <c r="C80" s="41">
+        <v>0</v>
+      </c>
+      <c r="D80" s="42">
+        <v>80</v>
+      </c>
+      <c r="E80" s="41">
+        <v>0</v>
+      </c>
+      <c r="F80" s="43">
         <v>5</v>
       </c>
-      <c r="G80" s="20">
+      <c r="G80" s="44">
         <v>6</v>
       </c>
-      <c r="H80" s="20">
+      <c r="H80" s="44">
         <v>7</v>
       </c>
-      <c r="I80" s="20">
-        <v>2</v>
-      </c>
-      <c r="J80" s="20">
+      <c r="I80" s="44">
+        <v>0</v>
+      </c>
+      <c r="J80" s="44">
+        <v>1</v>
+      </c>
+      <c r="K80" s="44">
+        <v>2</v>
+      </c>
+      <c r="L80" s="44">
+        <v>3</v>
+      </c>
+      <c r="M80" s="44">
+        <v>4</v>
+      </c>
+      <c r="N80" s="44">
         <v>8</v>
       </c>
-      <c r="K80" s="20">
+      <c r="O80" s="44">
         <v>9</v>
       </c>
-      <c r="L80" s="20">
-        <v>0</v>
-      </c>
-      <c r="M80" s="20">
-        <v>1</v>
-      </c>
-      <c r="N80" s="20">
-        <v>3</v>
-      </c>
-      <c r="O80" s="20">
-        <v>4</v>
-      </c>
-      <c r="P80" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q80" s="20">
-        <v>1</v>
-      </c>
-      <c r="R80" s="20">
-        <v>2</v>
-      </c>
-      <c r="S80" s="20">
-        <v>3</v>
-      </c>
-      <c r="T80" s="22">
-        <v>4</v>
-      </c>
-      <c r="U80" s="10" t="s">
+      <c r="P80" s="43">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="44">
+        <v>1</v>
+      </c>
+      <c r="R80" s="44">
+        <v>2</v>
+      </c>
+      <c r="S80" s="44">
+        <v>3</v>
+      </c>
+      <c r="T80" s="45">
+        <v>4</v>
+      </c>
+      <c r="U80" s="15" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="81" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="40" t="s">
-        <v>103</v>
-      </c>
-      <c r="B81" s="41" t="s">
-        <v>22</v>
-      </c>
-      <c r="C81" s="41">
-        <v>0</v>
-      </c>
-      <c r="D81" s="42">
-        <v>80</v>
-      </c>
-      <c r="E81" s="41">
-        <v>0</v>
-      </c>
-      <c r="F81" s="43">
-        <v>5</v>
-      </c>
-      <c r="G81" s="44">
-        <v>6</v>
-      </c>
-      <c r="H81" s="44">
-        <v>7</v>
-      </c>
-      <c r="I81" s="44">
-        <v>0</v>
-      </c>
-      <c r="J81" s="44">
-        <v>1</v>
-      </c>
-      <c r="K81" s="44">
-        <v>2</v>
-      </c>
-      <c r="L81" s="44">
-        <v>3</v>
-      </c>
-      <c r="M81" s="44">
-        <v>4</v>
-      </c>
-      <c r="N81" s="44">
-        <v>8</v>
-      </c>
-      <c r="O81" s="44">
-        <v>9</v>
-      </c>
-      <c r="P81" s="43">
-        <v>0</v>
-      </c>
-      <c r="Q81" s="44">
-        <v>1</v>
-      </c>
-      <c r="R81" s="44">
-        <v>2</v>
-      </c>
-      <c r="S81" s="44">
-        <v>3</v>
-      </c>
-      <c r="T81" s="45">
-        <v>4</v>
-      </c>
-      <c r="U81" s="15" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="82" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D81" s="1"/>
+    </row>
+    <row r="82" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D82" s="1"/>
     </row>
-    <row r="83" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D83" s="1"/>
     </row>
-    <row r="84" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D84" s="1"/>
     </row>
-    <row r="85" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D85" s="1"/>
     </row>
-    <row r="86" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D86" s="1"/>
     </row>
-    <row r="87" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D87" s="1"/>
     </row>
-    <row r="88" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D88" s="1"/>
     </row>
-    <row r="89" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D89" s="1"/>
     </row>
-    <row r="90" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D90" s="1"/>
     </row>
-    <row r="91" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D91" s="1"/>
     </row>
-    <row r="92" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D92" s="1"/>
     </row>
-    <row r="93" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D93" s="1"/>
     </row>
-    <row r="94" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D94" s="1"/>
     </row>
-    <row r="95" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D95" s="1"/>
     </row>
-    <row r="96" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D96" s="1"/>
     </row>
     <row r="97" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -9284,12 +9219,9 @@
     <row r="998" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D998" s="1"/>
     </row>
-    <row r="999" spans="4:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D999" s="1"/>
-    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="D2:D81" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="D2:D80" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>AND(ISNUMBER(D2),(NOT(OR(NOT(ISERROR(DATEVALUE(D2))), AND(ISNUMBER(D2), LEFT(CELL("format", D2))="D")))))</formula1>
     </dataValidation>
   </dataValidations>
@@ -9302,6 +9234,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -9484,24 +9433,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F6FD9D-19D1-439B-8BFE-82DBC99BDEA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F1A155A-9D28-4350-8732-AE6833CEF998}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9518,22 +9468,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F6FD9D-19D1-439B-8BFE-82DBC99BDEA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/upload files/Preferences v6.xlsx
+++ b/upload files/Preferences v6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56EA8E8-5175-274C-8968-5AE72E5E0167}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B289E201-7F58-B041-99BA-EEBED3C7360D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5330,7 +5330,7 @@
         <v>40</v>
       </c>
       <c r="C62" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" s="17">
         <v>65</v>
@@ -9234,20 +9234,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9434,19 +9434,19 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F6FD9D-19D1-439B-8BFE-82DBC99BDEA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F6FD9D-19D1-439B-8BFE-82DBC99BDEA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/upload files/Preferences v6.xlsx
+++ b/upload files/Preferences v6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aaronbell/Desktop/Git Repo Clone/CrewOps360/upload files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B289E201-7F58-B041-99BA-EEBED3C7360D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C0C8B6-01D6-F14F-ACD5-9E981F78CA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1457,7 +1457,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="7">
-        <v>2</v>
+        <v>102</v>
       </c>
       <c r="E2" s="6">
         <v>1</v>
@@ -1520,7 +1520,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="12">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="E3" s="11">
         <v>0</v>
@@ -1713,7 +1713,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="17">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="E6" s="16">
         <v>0</v>
@@ -1841,7 +1841,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="24">
-        <v>9</v>
+        <v>109</v>
       </c>
       <c r="E8" s="23">
         <v>0</v>
@@ -1969,7 +1969,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="24">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="E10" s="23">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="24">
-        <v>13</v>
+        <v>113</v>
       </c>
       <c r="E12" s="23">
         <v>0</v>
@@ -2420,7 +2420,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="17">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="E17" s="16">
         <v>0</v>
@@ -2483,7 +2483,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="21">
-        <v>19</v>
+        <v>119</v>
       </c>
       <c r="E18" s="20">
         <v>0</v>
@@ -2871,7 +2871,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="21">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="E24" s="20">
         <v>0</v>
@@ -3649,7 +3649,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="21">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="E36" s="20">
         <v>1</v>
@@ -3907,7 +3907,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="12">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="E40" s="11">
         <v>0</v>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="D59" s="17">
-        <v>62</v>
+        <v>162</v>
       </c>
       <c r="E59" s="16">
         <v>0</v>
@@ -5528,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="D65" s="12">
-        <v>68</v>
+        <v>168</v>
       </c>
       <c r="E65" s="11">
         <v>0</v>
@@ -9234,23 +9234,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009F702E5FD63918449A87815BC57997B4" ma:contentTypeVersion="7" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cf92d0bbd30e3b598aabc7012889a2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xmlns:ns3="b0d30a24-05e2-4154-8fed-e579ddd987b0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ea38175e79306f27c3dbc73ee4ec0c14" ns2:_="" ns3:_="">
     <xsd:import namespace="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
@@ -9433,25 +9416,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F6FD9D-19D1-439B-8BFE-82DBC99BDEA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_Flow_SignoffStatus xmlns="3ae64878-e7bb-4c65-a932-4cdc61fbe63f" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3F1A155A-9D28-4350-8732-AE6833CEF998}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9468,4 +9450,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{76795637-1749-499A-98A7-94E1CD8F32E2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3ae64878-e7bb-4c65-a932-4cdc61fbe63f"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17F6FD9D-19D1-439B-8BFE-82DBC99BDEA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>